--- a/Documents/タスク詳細設計書.xlsx
+++ b/Documents/タスク詳細設計書.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\S-47\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\S-47\Documents\project\taskUN\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64B5D4FC-0762-4785-9F4D-8134B6DD359D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8609B89C-CA94-441B-ADB3-7C91B7328BD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1350,56 +1350,23 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1407,11 +1374,11 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1428,17 +1395,26 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
@@ -1449,28 +1425,58 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1491,17 +1497,17 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1509,23 +1515,17 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1604,22 +1604,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>200025</xdr:colOff>
+      <xdr:colOff>190500</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>47625</xdr:rowOff>
+      <xdr:rowOff>123825</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>257175</xdr:colOff>
+      <xdr:colOff>247650</xdr:colOff>
       <xdr:row>32</xdr:row>
-      <xdr:rowOff>306571</xdr:rowOff>
+      <xdr:rowOff>385236</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="図 2">
+        <xdr:cNvPr id="4" name="図 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DA0BD01A-FC03-2555-9E3D-BCC5AA66C739}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BC100C2E-E0CC-9014-175D-D5A686E9AEF2}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1641,8 +1641,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="200025" y="962025"/>
-          <a:ext cx="7772400" cy="4792846"/>
+          <a:off x="190500" y="1038225"/>
+          <a:ext cx="7772400" cy="4795311"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3274,19 +3274,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="68" t="s">
+      <c r="A1" s="57" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="69"/>
-      <c r="C1" s="70"/>
-      <c r="D1" s="46" t="s">
+      <c r="B1" s="58"/>
+      <c r="C1" s="59"/>
+      <c r="D1" s="78" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="47"/>
-      <c r="F1" s="46" t="s">
+      <c r="E1" s="66"/>
+      <c r="F1" s="78" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="47"/>
+      <c r="G1" s="66"/>
       <c r="H1" s="5" t="s">
         <v>8</v>
       </c>
@@ -3298,72 +3298,72 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="71"/>
+      <c r="A2" s="60"/>
       <c r="B2" s="42"/>
-      <c r="C2" s="51"/>
-      <c r="D2" s="48" t="s">
+      <c r="C2" s="61"/>
+      <c r="D2" s="79" t="s">
         <v>67</v>
       </c>
-      <c r="E2" s="49"/>
-      <c r="F2" s="48" t="s">
+      <c r="E2" s="80"/>
+      <c r="F2" s="79" t="s">
         <v>68</v>
       </c>
-      <c r="G2" s="49"/>
-      <c r="H2" s="54">
+      <c r="G2" s="80"/>
+      <c r="H2" s="83">
         <v>45806</v>
       </c>
-      <c r="I2" s="57" t="s">
+      <c r="I2" s="72" t="s">
         <v>69</v>
       </c>
-      <c r="J2" s="58"/>
+      <c r="J2" s="75"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="71"/>
+      <c r="A3" s="60"/>
       <c r="B3" s="42"/>
-      <c r="C3" s="51"/>
-      <c r="D3" s="50"/>
-      <c r="E3" s="51"/>
-      <c r="F3" s="50"/>
-      <c r="G3" s="51"/>
-      <c r="H3" s="55"/>
-      <c r="I3" s="55"/>
-      <c r="J3" s="59"/>
+      <c r="C3" s="61"/>
+      <c r="D3" s="81"/>
+      <c r="E3" s="61"/>
+      <c r="F3" s="81"/>
+      <c r="G3" s="61"/>
+      <c r="H3" s="73"/>
+      <c r="I3" s="73"/>
+      <c r="J3" s="76"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="72"/>
-      <c r="B4" s="73"/>
-      <c r="C4" s="53"/>
-      <c r="D4" s="52"/>
-      <c r="E4" s="53"/>
-      <c r="F4" s="52"/>
-      <c r="G4" s="53"/>
-      <c r="H4" s="56"/>
-      <c r="I4" s="56"/>
-      <c r="J4" s="60"/>
+      <c r="A4" s="62"/>
+      <c r="B4" s="63"/>
+      <c r="C4" s="64"/>
+      <c r="D4" s="82"/>
+      <c r="E4" s="64"/>
+      <c r="F4" s="82"/>
+      <c r="G4" s="64"/>
+      <c r="H4" s="74"/>
+      <c r="I4" s="74"/>
+      <c r="J4" s="77"/>
     </row>
     <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="74" t="s">
+      <c r="A5" s="65" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="75"/>
-      <c r="C5" s="47"/>
-      <c r="D5" s="81" t="s">
+      <c r="B5" s="50"/>
+      <c r="C5" s="66"/>
+      <c r="D5" s="49" t="s">
         <v>70</v>
       </c>
-      <c r="E5" s="75"/>
-      <c r="F5" s="75"/>
-      <c r="G5" s="75"/>
-      <c r="H5" s="75"/>
-      <c r="I5" s="75"/>
-      <c r="J5" s="82"/>
+      <c r="E5" s="50"/>
+      <c r="F5" s="50"/>
+      <c r="G5" s="50"/>
+      <c r="H5" s="50"/>
+      <c r="I5" s="50"/>
+      <c r="J5" s="51"/>
     </row>
     <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="62" t="s">
+      <c r="A6" s="67" t="s">
         <v>12</v>
       </c>
       <c r="B6" s="39"/>
       <c r="C6" s="40"/>
-      <c r="D6" s="63" t="s">
+      <c r="D6" s="52" t="s">
         <v>71</v>
       </c>
       <c r="E6" s="39"/>
@@ -3371,15 +3371,15 @@
       <c r="G6" s="39"/>
       <c r="H6" s="39"/>
       <c r="I6" s="39"/>
-      <c r="J6" s="64"/>
+      <c r="J6" s="53"/>
     </row>
     <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="62" t="s">
+      <c r="A7" s="67" t="s">
         <v>13</v>
       </c>
       <c r="B7" s="39"/>
       <c r="C7" s="40"/>
-      <c r="D7" s="63" t="s">
+      <c r="D7" s="52" t="s">
         <v>72</v>
       </c>
       <c r="E7" s="39"/>
@@ -3387,15 +3387,15 @@
       <c r="G7" s="39"/>
       <c r="H7" s="39"/>
       <c r="I7" s="39"/>
-      <c r="J7" s="64"/>
+      <c r="J7" s="53"/>
     </row>
     <row r="8" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A8" s="62" t="s">
+      <c r="A8" s="67" t="s">
         <v>14</v>
       </c>
       <c r="B8" s="39"/>
       <c r="C8" s="40"/>
-      <c r="D8" s="63" t="s">
+      <c r="D8" s="52" t="s">
         <v>73</v>
       </c>
       <c r="E8" s="39"/>
@@ -3403,17 +3403,17 @@
       <c r="G8" s="39"/>
       <c r="H8" s="39"/>
       <c r="I8" s="39"/>
-      <c r="J8" s="64"/>
+      <c r="J8" s="53"/>
     </row>
     <row r="9" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A9" s="76" t="s">
+      <c r="A9" s="68" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="61" t="s">
+      <c r="B9" s="71" t="s">
         <v>16</v>
       </c>
       <c r="C9" s="40"/>
-      <c r="D9" s="83" t="s">
+      <c r="D9" s="54" t="s">
         <v>75</v>
       </c>
       <c r="E9" s="39"/>
@@ -3421,43 +3421,43 @@
       <c r="G9" s="39"/>
       <c r="H9" s="39"/>
       <c r="I9" s="39"/>
-      <c r="J9" s="64"/>
+      <c r="J9" s="53"/>
     </row>
     <row r="10" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A10" s="77"/>
-      <c r="B10" s="61" t="s">
+      <c r="A10" s="69"/>
+      <c r="B10" s="71" t="s">
         <v>17</v>
       </c>
       <c r="C10" s="40"/>
-      <c r="D10" s="63"/>
+      <c r="D10" s="52"/>
       <c r="E10" s="39"/>
       <c r="F10" s="39"/>
       <c r="G10" s="39"/>
       <c r="H10" s="39"/>
       <c r="I10" s="39"/>
-      <c r="J10" s="64"/>
+      <c r="J10" s="53"/>
     </row>
     <row r="11" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A11" s="78"/>
-      <c r="B11" s="61" t="s">
+      <c r="A11" s="70"/>
+      <c r="B11" s="71" t="s">
         <v>18</v>
       </c>
       <c r="C11" s="40"/>
-      <c r="D11" s="63"/>
+      <c r="D11" s="52"/>
       <c r="E11" s="39"/>
       <c r="F11" s="39"/>
       <c r="G11" s="39"/>
       <c r="H11" s="39"/>
       <c r="I11" s="39"/>
-      <c r="J11" s="64"/>
+      <c r="J11" s="53"/>
     </row>
     <row r="12" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A12" s="62" t="s">
+      <c r="A12" s="67" t="s">
         <v>19</v>
       </c>
       <c r="B12" s="39"/>
       <c r="C12" s="40"/>
-      <c r="D12" s="63" t="s">
+      <c r="D12" s="52" t="s">
         <v>74</v>
       </c>
       <c r="E12" s="39"/>
@@ -3465,21 +3465,21 @@
       <c r="G12" s="39"/>
       <c r="H12" s="39"/>
       <c r="I12" s="39"/>
-      <c r="J12" s="64"/>
+      <c r="J12" s="53"/>
     </row>
     <row r="13" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A13" s="65" t="s">
+      <c r="A13" s="55" t="s">
         <v>20</v>
       </c>
-      <c r="B13" s="66"/>
-      <c r="C13" s="67"/>
-      <c r="D13" s="79"/>
-      <c r="E13" s="66"/>
-      <c r="F13" s="66"/>
-      <c r="G13" s="66"/>
-      <c r="H13" s="66"/>
-      <c r="I13" s="66"/>
-      <c r="J13" s="80"/>
+      <c r="B13" s="47"/>
+      <c r="C13" s="56"/>
+      <c r="D13" s="46"/>
+      <c r="E13" s="47"/>
+      <c r="F13" s="47"/>
+      <c r="G13" s="47"/>
+      <c r="H13" s="47"/>
+      <c r="I13" s="47"/>
+      <c r="J13" s="48"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -4470,6 +4470,25 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="D12:J12"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A9:A11"/>
+    <mergeCell ref="B9:C9"/>
     <mergeCell ref="D13:J13"/>
     <mergeCell ref="D5:J5"/>
     <mergeCell ref="D6:J6"/>
@@ -4478,25 +4497,6 @@
     <mergeCell ref="D9:J9"/>
     <mergeCell ref="D10:J10"/>
     <mergeCell ref="D11:J11"/>
-    <mergeCell ref="A13:C13"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="A9:A11"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="D12:J12"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
@@ -4518,16 +4518,16 @@
       <c r="A1" s="84" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="69"/>
-      <c r="C1" s="70"/>
-      <c r="D1" s="46" t="s">
+      <c r="B1" s="58"/>
+      <c r="C1" s="59"/>
+      <c r="D1" s="78" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="47"/>
-      <c r="F1" s="46" t="s">
+      <c r="E1" s="66"/>
+      <c r="F1" s="78" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="47"/>
+      <c r="G1" s="66"/>
       <c r="H1" s="4" t="s">
         <v>8</v>
       </c>
@@ -4539,48 +4539,48 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="71"/>
+      <c r="A2" s="60"/>
       <c r="B2" s="42"/>
-      <c r="C2" s="51"/>
-      <c r="D2" s="48" t="s">
+      <c r="C2" s="61"/>
+      <c r="D2" s="79" t="s">
         <v>67</v>
       </c>
-      <c r="E2" s="49"/>
-      <c r="F2" s="48" t="s">
+      <c r="E2" s="80"/>
+      <c r="F2" s="79" t="s">
         <v>68</v>
       </c>
-      <c r="G2" s="49"/>
-      <c r="H2" s="54">
+      <c r="G2" s="80"/>
+      <c r="H2" s="83">
         <v>45810</v>
       </c>
-      <c r="I2" s="57" t="s">
+      <c r="I2" s="72" t="s">
         <v>76</v>
       </c>
-      <c r="J2" s="58"/>
+      <c r="J2" s="75"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="71"/>
+      <c r="A3" s="60"/>
       <c r="B3" s="42"/>
-      <c r="C3" s="51"/>
-      <c r="D3" s="50"/>
-      <c r="E3" s="51"/>
-      <c r="F3" s="50"/>
-      <c r="G3" s="51"/>
-      <c r="H3" s="55"/>
-      <c r="I3" s="55"/>
-      <c r="J3" s="59"/>
+      <c r="C3" s="61"/>
+      <c r="D3" s="81"/>
+      <c r="E3" s="61"/>
+      <c r="F3" s="81"/>
+      <c r="G3" s="61"/>
+      <c r="H3" s="73"/>
+      <c r="I3" s="73"/>
+      <c r="J3" s="76"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="72"/>
-      <c r="B4" s="73"/>
-      <c r="C4" s="53"/>
-      <c r="D4" s="52"/>
-      <c r="E4" s="53"/>
-      <c r="F4" s="52"/>
-      <c r="G4" s="53"/>
-      <c r="H4" s="56"/>
-      <c r="I4" s="56"/>
-      <c r="J4" s="60"/>
+      <c r="A4" s="62"/>
+      <c r="B4" s="63"/>
+      <c r="C4" s="64"/>
+      <c r="D4" s="82"/>
+      <c r="E4" s="64"/>
+      <c r="F4" s="82"/>
+      <c r="G4" s="64"/>
+      <c r="H4" s="74"/>
+      <c r="I4" s="74"/>
+      <c r="J4" s="77"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -5940,16 +5940,16 @@
       <c r="A1" s="84" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="69"/>
-      <c r="C1" s="70"/>
-      <c r="D1" s="46" t="s">
+      <c r="B1" s="58"/>
+      <c r="C1" s="59"/>
+      <c r="D1" s="78" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="47"/>
-      <c r="F1" s="46" t="s">
+      <c r="E1" s="66"/>
+      <c r="F1" s="78" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="47"/>
+      <c r="G1" s="66"/>
       <c r="H1" s="4" t="s">
         <v>8</v>
       </c>
@@ -5961,48 +5961,48 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="71"/>
+      <c r="A2" s="60"/>
       <c r="B2" s="42"/>
-      <c r="C2" s="51"/>
-      <c r="D2" s="48" t="s">
+      <c r="C2" s="61"/>
+      <c r="D2" s="79" t="s">
         <v>67</v>
       </c>
-      <c r="E2" s="49"/>
-      <c r="F2" s="48" t="s">
+      <c r="E2" s="80"/>
+      <c r="F2" s="79" t="s">
         <v>68</v>
       </c>
-      <c r="G2" s="49"/>
-      <c r="H2" s="54">
+      <c r="G2" s="80"/>
+      <c r="H2" s="83">
         <v>45810</v>
       </c>
-      <c r="I2" s="57" t="s">
+      <c r="I2" s="72" t="s">
         <v>76</v>
       </c>
-      <c r="J2" s="58"/>
+      <c r="J2" s="75"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="71"/>
+      <c r="A3" s="60"/>
       <c r="B3" s="42"/>
-      <c r="C3" s="51"/>
-      <c r="D3" s="50"/>
-      <c r="E3" s="51"/>
-      <c r="F3" s="50"/>
-      <c r="G3" s="51"/>
-      <c r="H3" s="55"/>
-      <c r="I3" s="55"/>
-      <c r="J3" s="59"/>
+      <c r="C3" s="61"/>
+      <c r="D3" s="81"/>
+      <c r="E3" s="61"/>
+      <c r="F3" s="81"/>
+      <c r="G3" s="61"/>
+      <c r="H3" s="73"/>
+      <c r="I3" s="73"/>
+      <c r="J3" s="76"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="72"/>
-      <c r="B4" s="73"/>
-      <c r="C4" s="53"/>
-      <c r="D4" s="52"/>
-      <c r="E4" s="53"/>
-      <c r="F4" s="52"/>
-      <c r="G4" s="53"/>
-      <c r="H4" s="56"/>
-      <c r="I4" s="56"/>
-      <c r="J4" s="60"/>
+      <c r="A4" s="62"/>
+      <c r="B4" s="63"/>
+      <c r="C4" s="64"/>
+      <c r="D4" s="82"/>
+      <c r="E4" s="64"/>
+      <c r="F4" s="82"/>
+      <c r="G4" s="64"/>
+      <c r="H4" s="74"/>
+      <c r="I4" s="74"/>
+      <c r="J4" s="77"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -7356,16 +7356,16 @@
       <c r="A1" s="84" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="69"/>
-      <c r="C1" s="70"/>
-      <c r="D1" s="46" t="s">
+      <c r="B1" s="58"/>
+      <c r="C1" s="59"/>
+      <c r="D1" s="78" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="47"/>
-      <c r="F1" s="46" t="s">
+      <c r="E1" s="66"/>
+      <c r="F1" s="78" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="47"/>
+      <c r="G1" s="66"/>
       <c r="H1" s="4" t="s">
         <v>8</v>
       </c>
@@ -7377,67 +7377,67 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="71"/>
+      <c r="A2" s="60"/>
       <c r="B2" s="42"/>
-      <c r="C2" s="51"/>
-      <c r="D2" s="48" t="s">
+      <c r="C2" s="61"/>
+      <c r="D2" s="79" t="s">
         <v>67</v>
       </c>
-      <c r="E2" s="49"/>
-      <c r="F2" s="48" t="s">
+      <c r="E2" s="80"/>
+      <c r="F2" s="79" t="s">
         <v>68</v>
       </c>
-      <c r="G2" s="49"/>
-      <c r="H2" s="54">
+      <c r="G2" s="80"/>
+      <c r="H2" s="83">
         <v>45810</v>
       </c>
-      <c r="I2" s="57" t="s">
+      <c r="I2" s="72" t="s">
         <v>76</v>
       </c>
-      <c r="J2" s="58"/>
+      <c r="J2" s="75"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="71"/>
+      <c r="A3" s="60"/>
       <c r="B3" s="42"/>
-      <c r="C3" s="51"/>
-      <c r="D3" s="50"/>
-      <c r="E3" s="51"/>
-      <c r="F3" s="50"/>
-      <c r="G3" s="51"/>
-      <c r="H3" s="55"/>
-      <c r="I3" s="55"/>
-      <c r="J3" s="59"/>
+      <c r="C3" s="61"/>
+      <c r="D3" s="81"/>
+      <c r="E3" s="61"/>
+      <c r="F3" s="81"/>
+      <c r="G3" s="61"/>
+      <c r="H3" s="73"/>
+      <c r="I3" s="73"/>
+      <c r="J3" s="76"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="71"/>
+      <c r="A4" s="60"/>
       <c r="B4" s="42"/>
-      <c r="C4" s="51"/>
-      <c r="D4" s="50"/>
-      <c r="E4" s="51"/>
-      <c r="F4" s="50"/>
-      <c r="G4" s="51"/>
-      <c r="H4" s="55"/>
-      <c r="I4" s="55"/>
-      <c r="J4" s="59"/>
+      <c r="C4" s="61"/>
+      <c r="D4" s="81"/>
+      <c r="E4" s="61"/>
+      <c r="F4" s="81"/>
+      <c r="G4" s="61"/>
+      <c r="H4" s="73"/>
+      <c r="I4" s="73"/>
+      <c r="J4" s="76"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="93" t="s">
+      <c r="A5" s="86" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="75"/>
-      <c r="C5" s="47"/>
-      <c r="D5" s="87" t="s">
+      <c r="B5" s="50"/>
+      <c r="C5" s="66"/>
+      <c r="D5" s="89" t="s">
         <v>77</v>
       </c>
-      <c r="E5" s="75"/>
-      <c r="F5" s="75"/>
-      <c r="G5" s="75"/>
-      <c r="H5" s="75"/>
-      <c r="I5" s="75"/>
-      <c r="J5" s="82"/>
+      <c r="E5" s="50"/>
+      <c r="F5" s="50"/>
+      <c r="G5" s="50"/>
+      <c r="H5" s="50"/>
+      <c r="I5" s="50"/>
+      <c r="J5" s="51"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="85" t="s">
+      <c r="A6" s="88" t="s">
         <v>25</v>
       </c>
       <c r="B6" s="39"/>
@@ -7448,22 +7448,22 @@
       <c r="G6" s="39"/>
       <c r="H6" s="39"/>
       <c r="I6" s="39"/>
-      <c r="J6" s="64"/>
+      <c r="J6" s="53"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="88"/>
-      <c r="B7" s="89"/>
-      <c r="C7" s="89"/>
-      <c r="D7" s="89"/>
-      <c r="E7" s="89"/>
-      <c r="F7" s="89"/>
-      <c r="G7" s="89"/>
-      <c r="H7" s="89"/>
-      <c r="I7" s="89"/>
-      <c r="J7" s="90"/>
+      <c r="A7" s="90"/>
+      <c r="B7" s="91"/>
+      <c r="C7" s="91"/>
+      <c r="D7" s="91"/>
+      <c r="E7" s="91"/>
+      <c r="F7" s="91"/>
+      <c r="G7" s="91"/>
+      <c r="H7" s="91"/>
+      <c r="I7" s="91"/>
+      <c r="J7" s="92"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="71"/>
+      <c r="A8" s="60"/>
       <c r="B8" s="42"/>
       <c r="C8" s="42"/>
       <c r="D8" s="42"/>
@@ -7472,10 +7472,10 @@
       <c r="G8" s="42"/>
       <c r="H8" s="42"/>
       <c r="I8" s="42"/>
-      <c r="J8" s="91"/>
+      <c r="J8" s="93"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="71"/>
+      <c r="A9" s="60"/>
       <c r="B9" s="42"/>
       <c r="C9" s="42"/>
       <c r="D9" s="42"/>
@@ -7484,10 +7484,10 @@
       <c r="G9" s="42"/>
       <c r="H9" s="42"/>
       <c r="I9" s="42"/>
-      <c r="J9" s="91"/>
+      <c r="J9" s="93"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="71"/>
+      <c r="A10" s="60"/>
       <c r="B10" s="42"/>
       <c r="C10" s="42"/>
       <c r="D10" s="42"/>
@@ -7496,10 +7496,10 @@
       <c r="G10" s="42"/>
       <c r="H10" s="42"/>
       <c r="I10" s="42"/>
-      <c r="J10" s="91"/>
+      <c r="J10" s="93"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="71"/>
+      <c r="A11" s="60"/>
       <c r="B11" s="42"/>
       <c r="C11" s="42"/>
       <c r="D11" s="42"/>
@@ -7508,10 +7508,10 @@
       <c r="G11" s="42"/>
       <c r="H11" s="42"/>
       <c r="I11" s="42"/>
-      <c r="J11" s="91"/>
+      <c r="J11" s="93"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="71"/>
+      <c r="A12" s="60"/>
       <c r="B12" s="42"/>
       <c r="C12" s="42"/>
       <c r="D12" s="42"/>
@@ -7520,10 +7520,10 @@
       <c r="G12" s="42"/>
       <c r="H12" s="42"/>
       <c r="I12" s="42"/>
-      <c r="J12" s="91"/>
+      <c r="J12" s="93"/>
     </row>
     <row r="13" spans="1:10" ht="62.25" customHeight="1">
-      <c r="A13" s="71"/>
+      <c r="A13" s="60"/>
       <c r="B13" s="42"/>
       <c r="C13" s="42"/>
       <c r="D13" s="42"/>
@@ -7532,10 +7532,10 @@
       <c r="G13" s="42"/>
       <c r="H13" s="42"/>
       <c r="I13" s="42"/>
-      <c r="J13" s="91"/>
+      <c r="J13" s="93"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="85" t="s">
+      <c r="A14" s="88" t="s">
         <v>26</v>
       </c>
       <c r="B14" s="39"/>
@@ -7546,15 +7546,15 @@
       <c r="G14" s="39"/>
       <c r="H14" s="39"/>
       <c r="I14" s="39"/>
-      <c r="J14" s="64"/>
+      <c r="J14" s="53"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="85" t="s">
+      <c r="A15" s="88" t="s">
         <v>27</v>
       </c>
       <c r="B15" s="39"/>
       <c r="C15" s="40"/>
-      <c r="D15" s="63" t="s">
+      <c r="D15" s="52" t="s">
         <v>86</v>
       </c>
       <c r="E15" s="39"/>
@@ -7569,7 +7569,7 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="85" t="s">
+      <c r="A16" s="88" t="s">
         <v>29</v>
       </c>
       <c r="B16" s="39"/>
@@ -7586,14 +7586,14 @@
       <c r="G16" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="H16" s="92" t="s">
+      <c r="H16" s="94" t="s">
         <v>20</v>
       </c>
       <c r="I16" s="39"/>
-      <c r="J16" s="64"/>
+      <c r="J16" s="53"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="86">
+      <c r="A17" s="85">
         <v>1</v>
       </c>
       <c r="B17" s="39"/>
@@ -7608,14 +7608,14 @@
       <c r="G17" s="18" t="s">
         <v>83</v>
       </c>
-      <c r="H17" s="63" t="s">
+      <c r="H17" s="52" t="s">
         <v>87</v>
       </c>
       <c r="I17" s="39"/>
-      <c r="J17" s="64"/>
+      <c r="J17" s="53"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="86">
+      <c r="A18" s="85">
         <v>2</v>
       </c>
       <c r="B18" s="39"/>
@@ -7630,14 +7630,14 @@
       <c r="G18" s="18" t="s">
         <v>84</v>
       </c>
-      <c r="H18" s="63" t="s">
+      <c r="H18" s="52" t="s">
         <v>87</v>
       </c>
       <c r="I18" s="39"/>
-      <c r="J18" s="64"/>
+      <c r="J18" s="53"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="86">
+      <c r="A19" s="85">
         <v>3</v>
       </c>
       <c r="B19" s="39"/>
@@ -7652,59 +7652,59 @@
       <c r="G19" s="18" t="s">
         <v>85</v>
       </c>
-      <c r="H19" s="63" t="s">
+      <c r="H19" s="52" t="s">
         <v>87</v>
       </c>
       <c r="I19" s="39"/>
-      <c r="J19" s="64"/>
+      <c r="J19" s="53"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="86"/>
+      <c r="A20" s="85"/>
       <c r="B20" s="39"/>
       <c r="C20" s="40"/>
       <c r="D20" s="17"/>
       <c r="E20" s="17"/>
       <c r="F20" s="18"/>
       <c r="G20" s="18"/>
-      <c r="H20" s="63"/>
+      <c r="H20" s="52"/>
       <c r="I20" s="39"/>
-      <c r="J20" s="64"/>
+      <c r="J20" s="53"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="86"/>
+      <c r="A21" s="85"/>
       <c r="B21" s="39"/>
       <c r="C21" s="40"/>
       <c r="D21" s="17"/>
       <c r="E21" s="17"/>
       <c r="F21" s="18"/>
       <c r="G21" s="18"/>
-      <c r="H21" s="63"/>
+      <c r="H21" s="52"/>
       <c r="I21" s="39"/>
-      <c r="J21" s="64"/>
+      <c r="J21" s="53"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="86"/>
+      <c r="A22" s="85"/>
       <c r="B22" s="39"/>
       <c r="C22" s="40"/>
       <c r="D22" s="17"/>
       <c r="E22" s="17"/>
       <c r="F22" s="18"/>
       <c r="G22" s="18"/>
-      <c r="H22" s="63"/>
+      <c r="H22" s="52"/>
       <c r="I22" s="39"/>
-      <c r="J22" s="64"/>
+      <c r="J22" s="53"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A23" s="94"/>
-      <c r="B23" s="66"/>
-      <c r="C23" s="67"/>
+      <c r="A23" s="87"/>
+      <c r="B23" s="47"/>
+      <c r="C23" s="56"/>
       <c r="D23" s="19"/>
       <c r="E23" s="19"/>
       <c r="F23" s="20"/>
       <c r="G23" s="20"/>
-      <c r="H23" s="79"/>
-      <c r="I23" s="66"/>
-      <c r="J23" s="80"/>
+      <c r="H23" s="46"/>
+      <c r="I23" s="47"/>
+      <c r="J23" s="48"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
@@ -8685,17 +8685,10 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="H23:J23"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
     <mergeCell ref="A1:C4"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="D1:E1"/>
@@ -8712,10 +8705,17 @@
     <mergeCell ref="H16:J16"/>
     <mergeCell ref="H17:J17"/>
     <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="H23:J23"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="H22:J22"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -8735,137 +8735,137 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="68" t="s">
+      <c r="A1" s="57" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="69"/>
-      <c r="C1" s="69"/>
-      <c r="D1" s="69"/>
-      <c r="E1" s="69"/>
-      <c r="F1" s="70"/>
-      <c r="G1" s="46" t="s">
+      <c r="B1" s="58"/>
+      <c r="C1" s="58"/>
+      <c r="D1" s="58"/>
+      <c r="E1" s="58"/>
+      <c r="F1" s="59"/>
+      <c r="G1" s="78" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="75"/>
-      <c r="I1" s="75"/>
-      <c r="J1" s="47"/>
-      <c r="K1" s="46" t="s">
+      <c r="H1" s="50"/>
+      <c r="I1" s="50"/>
+      <c r="J1" s="66"/>
+      <c r="K1" s="78" t="s">
         <v>7</v>
       </c>
-      <c r="L1" s="75"/>
-      <c r="M1" s="75"/>
-      <c r="N1" s="47"/>
-      <c r="O1" s="46" t="s">
+      <c r="L1" s="50"/>
+      <c r="M1" s="50"/>
+      <c r="N1" s="66"/>
+      <c r="O1" s="78" t="s">
         <v>8</v>
       </c>
-      <c r="P1" s="47"/>
-      <c r="Q1" s="46" t="s">
+      <c r="P1" s="66"/>
+      <c r="Q1" s="78" t="s">
         <v>9</v>
       </c>
-      <c r="R1" s="47"/>
-      <c r="S1" s="46" t="s">
+      <c r="R1" s="66"/>
+      <c r="S1" s="78" t="s">
         <v>10</v>
       </c>
-      <c r="T1" s="82"/>
+      <c r="T1" s="51"/>
     </row>
     <row r="2" spans="1:26" ht="18" customHeight="1">
-      <c r="A2" s="71"/>
+      <c r="A2" s="60"/>
       <c r="B2" s="42"/>
       <c r="C2" s="42"/>
       <c r="D2" s="42"/>
       <c r="E2" s="42"/>
-      <c r="F2" s="51"/>
-      <c r="G2" s="48" t="s">
+      <c r="F2" s="61"/>
+      <c r="G2" s="79" t="s">
         <v>67</v>
       </c>
-      <c r="H2" s="89"/>
-      <c r="I2" s="89"/>
-      <c r="J2" s="49"/>
-      <c r="K2" s="48" t="s">
+      <c r="H2" s="91"/>
+      <c r="I2" s="91"/>
+      <c r="J2" s="80"/>
+      <c r="K2" s="79" t="s">
         <v>68</v>
       </c>
-      <c r="L2" s="89"/>
-      <c r="M2" s="89"/>
-      <c r="N2" s="49"/>
-      <c r="O2" s="48"/>
-      <c r="P2" s="49"/>
-      <c r="Q2" s="48"/>
-      <c r="R2" s="49"/>
-      <c r="S2" s="48"/>
-      <c r="T2" s="90"/>
+      <c r="L2" s="91"/>
+      <c r="M2" s="91"/>
+      <c r="N2" s="80"/>
+      <c r="O2" s="79"/>
+      <c r="P2" s="80"/>
+      <c r="Q2" s="79"/>
+      <c r="R2" s="80"/>
+      <c r="S2" s="79"/>
+      <c r="T2" s="92"/>
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
-      <c r="A3" s="71"/>
+      <c r="A3" s="60"/>
       <c r="B3" s="42"/>
       <c r="C3" s="42"/>
       <c r="D3" s="42"/>
       <c r="E3" s="42"/>
-      <c r="F3" s="51"/>
-      <c r="G3" s="50"/>
+      <c r="F3" s="61"/>
+      <c r="G3" s="81"/>
       <c r="H3" s="42"/>
       <c r="I3" s="42"/>
-      <c r="J3" s="51"/>
-      <c r="K3" s="50"/>
+      <c r="J3" s="61"/>
+      <c r="K3" s="81"/>
       <c r="L3" s="42"/>
       <c r="M3" s="42"/>
-      <c r="N3" s="51"/>
-      <c r="O3" s="50"/>
-      <c r="P3" s="51"/>
-      <c r="Q3" s="50"/>
-      <c r="R3" s="51"/>
-      <c r="S3" s="50"/>
-      <c r="T3" s="91"/>
+      <c r="N3" s="61"/>
+      <c r="O3" s="81"/>
+      <c r="P3" s="61"/>
+      <c r="Q3" s="81"/>
+      <c r="R3" s="61"/>
+      <c r="S3" s="81"/>
+      <c r="T3" s="93"/>
     </row>
     <row r="4" spans="1:26" ht="18" customHeight="1">
-      <c r="A4" s="72"/>
-      <c r="B4" s="73"/>
-      <c r="C4" s="73"/>
-      <c r="D4" s="73"/>
-      <c r="E4" s="73"/>
-      <c r="F4" s="53"/>
-      <c r="G4" s="52"/>
-      <c r="H4" s="73"/>
-      <c r="I4" s="73"/>
-      <c r="J4" s="53"/>
-      <c r="K4" s="52"/>
-      <c r="L4" s="73"/>
-      <c r="M4" s="73"/>
-      <c r="N4" s="53"/>
-      <c r="O4" s="52"/>
-      <c r="P4" s="53"/>
-      <c r="Q4" s="52"/>
-      <c r="R4" s="53"/>
-      <c r="S4" s="52"/>
-      <c r="T4" s="99"/>
+      <c r="A4" s="62"/>
+      <c r="B4" s="63"/>
+      <c r="C4" s="63"/>
+      <c r="D4" s="63"/>
+      <c r="E4" s="63"/>
+      <c r="F4" s="64"/>
+      <c r="G4" s="82"/>
+      <c r="H4" s="63"/>
+      <c r="I4" s="63"/>
+      <c r="J4" s="64"/>
+      <c r="K4" s="82"/>
+      <c r="L4" s="63"/>
+      <c r="M4" s="63"/>
+      <c r="N4" s="64"/>
+      <c r="O4" s="82"/>
+      <c r="P4" s="64"/>
+      <c r="Q4" s="82"/>
+      <c r="R4" s="64"/>
+      <c r="S4" s="82"/>
+      <c r="T4" s="103"/>
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="93" t="s">
+      <c r="A5" s="86" t="s">
         <v>35</v>
       </c>
-      <c r="B5" s="75"/>
-      <c r="C5" s="75"/>
-      <c r="D5" s="75"/>
-      <c r="E5" s="75"/>
-      <c r="F5" s="47"/>
-      <c r="G5" s="81" t="s">
+      <c r="B5" s="50"/>
+      <c r="C5" s="50"/>
+      <c r="D5" s="50"/>
+      <c r="E5" s="50"/>
+      <c r="F5" s="66"/>
+      <c r="G5" s="49" t="s">
         <v>36</v>
       </c>
-      <c r="H5" s="75"/>
-      <c r="I5" s="75"/>
-      <c r="J5" s="75"/>
-      <c r="K5" s="75"/>
-      <c r="L5" s="75"/>
-      <c r="M5" s="75"/>
-      <c r="N5" s="75"/>
-      <c r="O5" s="75"/>
-      <c r="P5" s="75"/>
-      <c r="Q5" s="75"/>
-      <c r="R5" s="75"/>
-      <c r="S5" s="75"/>
-      <c r="T5" s="82"/>
+      <c r="H5" s="50"/>
+      <c r="I5" s="50"/>
+      <c r="J5" s="50"/>
+      <c r="K5" s="50"/>
+      <c r="L5" s="50"/>
+      <c r="M5" s="50"/>
+      <c r="N5" s="50"/>
+      <c r="O5" s="50"/>
+      <c r="P5" s="50"/>
+      <c r="Q5" s="50"/>
+      <c r="R5" s="50"/>
+      <c r="S5" s="50"/>
+      <c r="T5" s="51"/>
     </row>
     <row r="6" spans="1:26" ht="18" customHeight="1">
-      <c r="A6" s="85" t="s">
+      <c r="A6" s="88" t="s">
         <v>37</v>
       </c>
       <c r="B6" s="39"/>
@@ -8873,7 +8873,7 @@
       <c r="D6" s="39"/>
       <c r="E6" s="39"/>
       <c r="F6" s="40"/>
-      <c r="G6" s="63" t="s">
+      <c r="G6" s="52" t="s">
         <v>21</v>
       </c>
       <c r="H6" s="39"/>
@@ -8888,10 +8888,10 @@
       <c r="Q6" s="39"/>
       <c r="R6" s="39"/>
       <c r="S6" s="39"/>
-      <c r="T6" s="64"/>
+      <c r="T6" s="53"/>
     </row>
     <row r="7" spans="1:26" ht="18" customHeight="1">
-      <c r="A7" s="85" t="s">
+      <c r="A7" s="88" t="s">
         <v>38</v>
       </c>
       <c r="B7" s="39"/>
@@ -8899,7 +8899,7 @@
       <c r="D7" s="39"/>
       <c r="E7" s="39"/>
       <c r="F7" s="40"/>
-      <c r="G7" s="63" t="s">
+      <c r="G7" s="52" t="s">
         <v>39</v>
       </c>
       <c r="H7" s="39"/>
@@ -8914,7 +8914,7 @@
       <c r="Q7" s="39"/>
       <c r="R7" s="39"/>
       <c r="S7" s="39"/>
-      <c r="T7" s="64"/>
+      <c r="T7" s="53"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
       <c r="A8" s="8"/>
@@ -9113,7 +9113,7 @@
       <c r="T14" s="10"/>
     </row>
     <row r="15" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A15" s="85" t="s">
+      <c r="A15" s="88" t="s">
         <v>46</v>
       </c>
       <c r="B15" s="40"/>
@@ -9121,25 +9121,25 @@
         <v>40</v>
       </c>
       <c r="D15" s="40"/>
-      <c r="E15" s="92" t="s">
+      <c r="E15" s="94" t="s">
         <v>47</v>
       </c>
       <c r="F15" s="40"/>
-      <c r="G15" s="92" t="s">
+      <c r="G15" s="94" t="s">
         <v>48</v>
       </c>
       <c r="H15" s="39"/>
       <c r="I15" s="40"/>
-      <c r="J15" s="92" t="s">
+      <c r="J15" s="94" t="s">
         <v>49</v>
       </c>
       <c r="K15" s="40"/>
-      <c r="L15" s="92" t="s">
+      <c r="L15" s="94" t="s">
         <v>50</v>
       </c>
       <c r="M15" s="39"/>
       <c r="N15" s="40"/>
-      <c r="O15" s="92" t="s">
+      <c r="O15" s="94" t="s">
         <v>51</v>
       </c>
       <c r="P15" s="39"/>
@@ -9155,33 +9155,33 @@
       </c>
     </row>
     <row r="16" spans="1:26" ht="48" customHeight="1">
-      <c r="A16" s="100">
+      <c r="A16" s="95">
         <v>1</v>
       </c>
       <c r="B16" s="40"/>
-      <c r="C16" s="101" t="s">
+      <c r="C16" s="96" t="s">
         <v>55</v>
       </c>
       <c r="D16" s="40"/>
-      <c r="E16" s="101" t="s">
+      <c r="E16" s="96" t="s">
         <v>56</v>
       </c>
       <c r="F16" s="40"/>
-      <c r="G16" s="95" t="s">
+      <c r="G16" s="101" t="s">
         <v>57</v>
       </c>
       <c r="H16" s="39"/>
       <c r="I16" s="40"/>
-      <c r="J16" s="95" t="s">
+      <c r="J16" s="101" t="s">
         <v>58</v>
       </c>
       <c r="K16" s="40"/>
-      <c r="L16" s="97" t="s">
+      <c r="L16" s="99" t="s">
         <v>59</v>
       </c>
       <c r="M16" s="39"/>
       <c r="N16" s="40"/>
-      <c r="O16" s="97" t="s">
+      <c r="O16" s="99" t="s">
         <v>60</v>
       </c>
       <c r="P16" s="39"/>
@@ -9197,33 +9197,33 @@
       <c r="Z16" s="35"/>
     </row>
     <row r="17" spans="1:26" ht="41.25" customHeight="1">
-      <c r="A17" s="100">
+      <c r="A17" s="95">
         <v>2</v>
       </c>
       <c r="B17" s="40"/>
-      <c r="C17" s="101" t="s">
+      <c r="C17" s="96" t="s">
         <v>61</v>
       </c>
       <c r="D17" s="40"/>
-      <c r="E17" s="101" t="s">
+      <c r="E17" s="96" t="s">
         <v>62</v>
       </c>
       <c r="F17" s="40"/>
-      <c r="G17" s="95" t="s">
+      <c r="G17" s="101" t="s">
         <v>63</v>
       </c>
       <c r="H17" s="39"/>
       <c r="I17" s="40"/>
-      <c r="J17" s="95" t="s">
+      <c r="J17" s="101" t="s">
         <v>64</v>
       </c>
       <c r="K17" s="40"/>
-      <c r="L17" s="97" t="s">
+      <c r="L17" s="99" t="s">
         <v>65</v>
       </c>
       <c r="M17" s="39"/>
       <c r="N17" s="40"/>
-      <c r="O17" s="97" t="s">
+      <c r="O17" s="99" t="s">
         <v>66</v>
       </c>
       <c r="P17" s="39"/>
@@ -9239,21 +9239,21 @@
       <c r="Z17" s="35"/>
     </row>
     <row r="18" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A18" s="100"/>
+      <c r="A18" s="95"/>
       <c r="B18" s="40"/>
-      <c r="C18" s="101"/>
+      <c r="C18" s="96"/>
       <c r="D18" s="40"/>
-      <c r="E18" s="101"/>
+      <c r="E18" s="96"/>
       <c r="F18" s="40"/>
-      <c r="G18" s="95"/>
+      <c r="G18" s="101"/>
       <c r="H18" s="39"/>
       <c r="I18" s="40"/>
-      <c r="J18" s="95"/>
+      <c r="J18" s="101"/>
       <c r="K18" s="40"/>
-      <c r="L18" s="97"/>
+      <c r="L18" s="99"/>
       <c r="M18" s="39"/>
       <c r="N18" s="40"/>
-      <c r="O18" s="97"/>
+      <c r="O18" s="99"/>
       <c r="P18" s="39"/>
       <c r="Q18" s="40"/>
       <c r="R18" s="33"/>
@@ -9267,21 +9267,21 @@
       <c r="Z18" s="35"/>
     </row>
     <row r="19" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A19" s="100"/>
+      <c r="A19" s="95"/>
       <c r="B19" s="40"/>
-      <c r="C19" s="101"/>
+      <c r="C19" s="96"/>
       <c r="D19" s="40"/>
-      <c r="E19" s="101"/>
+      <c r="E19" s="96"/>
       <c r="F19" s="40"/>
-      <c r="G19" s="95"/>
+      <c r="G19" s="101"/>
       <c r="H19" s="39"/>
       <c r="I19" s="40"/>
-      <c r="J19" s="95"/>
+      <c r="J19" s="101"/>
       <c r="K19" s="40"/>
-      <c r="L19" s="97"/>
+      <c r="L19" s="99"/>
       <c r="M19" s="39"/>
       <c r="N19" s="40"/>
-      <c r="O19" s="97"/>
+      <c r="O19" s="99"/>
       <c r="P19" s="39"/>
       <c r="Q19" s="40"/>
       <c r="R19" s="33"/>
@@ -9295,21 +9295,21 @@
       <c r="Z19" s="35"/>
     </row>
     <row r="20" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A20" s="100"/>
+      <c r="A20" s="95"/>
       <c r="B20" s="40"/>
-      <c r="C20" s="101"/>
+      <c r="C20" s="96"/>
       <c r="D20" s="40"/>
-      <c r="E20" s="101"/>
+      <c r="E20" s="96"/>
       <c r="F20" s="40"/>
-      <c r="G20" s="95"/>
+      <c r="G20" s="101"/>
       <c r="H20" s="39"/>
       <c r="I20" s="40"/>
-      <c r="J20" s="95"/>
+      <c r="J20" s="101"/>
       <c r="K20" s="40"/>
-      <c r="L20" s="97"/>
+      <c r="L20" s="99"/>
       <c r="M20" s="39"/>
       <c r="N20" s="40"/>
-      <c r="O20" s="97"/>
+      <c r="O20" s="99"/>
       <c r="P20" s="39"/>
       <c r="Q20" s="40"/>
       <c r="R20" s="33"/>
@@ -9323,21 +9323,21 @@
       <c r="Z20" s="35"/>
     </row>
     <row r="21" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A21" s="100"/>
+      <c r="A21" s="95"/>
       <c r="B21" s="40"/>
-      <c r="C21" s="101"/>
+      <c r="C21" s="96"/>
       <c r="D21" s="40"/>
-      <c r="E21" s="101"/>
+      <c r="E21" s="96"/>
       <c r="F21" s="40"/>
-      <c r="G21" s="95"/>
+      <c r="G21" s="101"/>
       <c r="H21" s="39"/>
       <c r="I21" s="40"/>
-      <c r="J21" s="95"/>
+      <c r="J21" s="101"/>
       <c r="K21" s="40"/>
-      <c r="L21" s="97"/>
+      <c r="L21" s="99"/>
       <c r="M21" s="39"/>
       <c r="N21" s="40"/>
-      <c r="O21" s="97"/>
+      <c r="O21" s="99"/>
       <c r="P21" s="39"/>
       <c r="Q21" s="40"/>
       <c r="R21" s="33"/>
@@ -9351,21 +9351,21 @@
       <c r="Z21" s="35"/>
     </row>
     <row r="22" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A22" s="100"/>
+      <c r="A22" s="95"/>
       <c r="B22" s="40"/>
-      <c r="C22" s="101"/>
+      <c r="C22" s="96"/>
       <c r="D22" s="40"/>
-      <c r="E22" s="101"/>
+      <c r="E22" s="96"/>
       <c r="F22" s="40"/>
-      <c r="G22" s="95"/>
+      <c r="G22" s="101"/>
       <c r="H22" s="39"/>
       <c r="I22" s="40"/>
-      <c r="J22" s="95"/>
+      <c r="J22" s="101"/>
       <c r="K22" s="40"/>
-      <c r="L22" s="97"/>
+      <c r="L22" s="99"/>
       <c r="M22" s="39"/>
       <c r="N22" s="40"/>
-      <c r="O22" s="97"/>
+      <c r="O22" s="99"/>
       <c r="P22" s="39"/>
       <c r="Q22" s="40"/>
       <c r="R22" s="33"/>
@@ -9379,21 +9379,21 @@
       <c r="Z22" s="35"/>
     </row>
     <row r="23" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A23" s="100"/>
+      <c r="A23" s="95"/>
       <c r="B23" s="40"/>
-      <c r="C23" s="101"/>
+      <c r="C23" s="96"/>
       <c r="D23" s="40"/>
-      <c r="E23" s="101"/>
+      <c r="E23" s="96"/>
       <c r="F23" s="40"/>
-      <c r="G23" s="95"/>
+      <c r="G23" s="101"/>
       <c r="H23" s="39"/>
       <c r="I23" s="40"/>
-      <c r="J23" s="95"/>
+      <c r="J23" s="101"/>
       <c r="K23" s="40"/>
-      <c r="L23" s="97"/>
+      <c r="L23" s="99"/>
       <c r="M23" s="39"/>
       <c r="N23" s="40"/>
-      <c r="O23" s="97"/>
+      <c r="O23" s="99"/>
       <c r="P23" s="39"/>
       <c r="Q23" s="40"/>
       <c r="R23" s="33"/>
@@ -9407,21 +9407,21 @@
       <c r="Z23" s="35"/>
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A24" s="100"/>
+      <c r="A24" s="95"/>
       <c r="B24" s="40"/>
-      <c r="C24" s="101"/>
+      <c r="C24" s="96"/>
       <c r="D24" s="40"/>
-      <c r="E24" s="101"/>
+      <c r="E24" s="96"/>
       <c r="F24" s="40"/>
-      <c r="G24" s="95"/>
+      <c r="G24" s="101"/>
       <c r="H24" s="39"/>
       <c r="I24" s="40"/>
-      <c r="J24" s="95"/>
+      <c r="J24" s="101"/>
       <c r="K24" s="40"/>
-      <c r="L24" s="97"/>
+      <c r="L24" s="99"/>
       <c r="M24" s="39"/>
       <c r="N24" s="40"/>
-      <c r="O24" s="97"/>
+      <c r="O24" s="99"/>
       <c r="P24" s="39"/>
       <c r="Q24" s="40"/>
       <c r="R24" s="33"/>
@@ -9435,21 +9435,21 @@
       <c r="Z24" s="35"/>
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A25" s="100"/>
+      <c r="A25" s="95"/>
       <c r="B25" s="40"/>
-      <c r="C25" s="101"/>
+      <c r="C25" s="96"/>
       <c r="D25" s="40"/>
-      <c r="E25" s="101"/>
+      <c r="E25" s="96"/>
       <c r="F25" s="40"/>
-      <c r="G25" s="95"/>
+      <c r="G25" s="101"/>
       <c r="H25" s="39"/>
       <c r="I25" s="40"/>
-      <c r="J25" s="95"/>
+      <c r="J25" s="101"/>
       <c r="K25" s="40"/>
-      <c r="L25" s="97"/>
+      <c r="L25" s="99"/>
       <c r="M25" s="39"/>
       <c r="N25" s="40"/>
-      <c r="O25" s="97"/>
+      <c r="O25" s="99"/>
       <c r="P25" s="39"/>
       <c r="Q25" s="40"/>
       <c r="R25" s="33"/>
@@ -9463,21 +9463,21 @@
       <c r="Z25" s="35"/>
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A26" s="100"/>
+      <c r="A26" s="95"/>
       <c r="B26" s="40"/>
-      <c r="C26" s="101"/>
+      <c r="C26" s="96"/>
       <c r="D26" s="40"/>
-      <c r="E26" s="101"/>
+      <c r="E26" s="96"/>
       <c r="F26" s="40"/>
-      <c r="G26" s="95"/>
+      <c r="G26" s="101"/>
       <c r="H26" s="39"/>
       <c r="I26" s="40"/>
-      <c r="J26" s="95"/>
+      <c r="J26" s="101"/>
       <c r="K26" s="40"/>
-      <c r="L26" s="97"/>
+      <c r="L26" s="99"/>
       <c r="M26" s="39"/>
       <c r="N26" s="40"/>
-      <c r="O26" s="97"/>
+      <c r="O26" s="99"/>
       <c r="P26" s="39"/>
       <c r="Q26" s="40"/>
       <c r="R26" s="33"/>
@@ -9491,21 +9491,21 @@
       <c r="Z26" s="35"/>
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A27" s="100"/>
+      <c r="A27" s="95"/>
       <c r="B27" s="40"/>
-      <c r="C27" s="101"/>
+      <c r="C27" s="96"/>
       <c r="D27" s="40"/>
-      <c r="E27" s="101"/>
+      <c r="E27" s="96"/>
       <c r="F27" s="40"/>
-      <c r="G27" s="95"/>
+      <c r="G27" s="101"/>
       <c r="H27" s="39"/>
       <c r="I27" s="40"/>
-      <c r="J27" s="95"/>
+      <c r="J27" s="101"/>
       <c r="K27" s="40"/>
-      <c r="L27" s="97"/>
+      <c r="L27" s="99"/>
       <c r="M27" s="39"/>
       <c r="N27" s="40"/>
-      <c r="O27" s="97"/>
+      <c r="O27" s="99"/>
       <c r="P27" s="39"/>
       <c r="Q27" s="40"/>
       <c r="R27" s="33"/>
@@ -9519,21 +9519,21 @@
       <c r="Z27" s="35"/>
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A28" s="100"/>
+      <c r="A28" s="95"/>
       <c r="B28" s="40"/>
-      <c r="C28" s="101"/>
+      <c r="C28" s="96"/>
       <c r="D28" s="40"/>
-      <c r="E28" s="101"/>
+      <c r="E28" s="96"/>
       <c r="F28" s="40"/>
-      <c r="G28" s="95"/>
+      <c r="G28" s="101"/>
       <c r="H28" s="39"/>
       <c r="I28" s="40"/>
-      <c r="J28" s="95"/>
+      <c r="J28" s="101"/>
       <c r="K28" s="40"/>
-      <c r="L28" s="97"/>
+      <c r="L28" s="99"/>
       <c r="M28" s="39"/>
       <c r="N28" s="40"/>
-      <c r="O28" s="97"/>
+      <c r="O28" s="99"/>
       <c r="P28" s="39"/>
       <c r="Q28" s="40"/>
       <c r="R28" s="33"/>
@@ -9547,21 +9547,21 @@
       <c r="Z28" s="35"/>
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A29" s="100"/>
+      <c r="A29" s="95"/>
       <c r="B29" s="40"/>
-      <c r="C29" s="101"/>
+      <c r="C29" s="96"/>
       <c r="D29" s="40"/>
-      <c r="E29" s="101"/>
+      <c r="E29" s="96"/>
       <c r="F29" s="40"/>
-      <c r="G29" s="95"/>
+      <c r="G29" s="101"/>
       <c r="H29" s="39"/>
       <c r="I29" s="40"/>
-      <c r="J29" s="95"/>
+      <c r="J29" s="101"/>
       <c r="K29" s="40"/>
-      <c r="L29" s="97"/>
+      <c r="L29" s="99"/>
       <c r="M29" s="39"/>
       <c r="N29" s="40"/>
-      <c r="O29" s="97"/>
+      <c r="O29" s="99"/>
       <c r="P29" s="39"/>
       <c r="Q29" s="40"/>
       <c r="R29" s="33"/>
@@ -9575,21 +9575,21 @@
       <c r="Z29" s="35"/>
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A30" s="100"/>
+      <c r="A30" s="95"/>
       <c r="B30" s="40"/>
-      <c r="C30" s="101"/>
+      <c r="C30" s="96"/>
       <c r="D30" s="40"/>
-      <c r="E30" s="101"/>
+      <c r="E30" s="96"/>
       <c r="F30" s="40"/>
-      <c r="G30" s="95"/>
+      <c r="G30" s="101"/>
       <c r="H30" s="39"/>
       <c r="I30" s="40"/>
-      <c r="J30" s="95"/>
+      <c r="J30" s="101"/>
       <c r="K30" s="40"/>
-      <c r="L30" s="97"/>
+      <c r="L30" s="99"/>
       <c r="M30" s="39"/>
       <c r="N30" s="40"/>
-      <c r="O30" s="97"/>
+      <c r="O30" s="99"/>
       <c r="P30" s="39"/>
       <c r="Q30" s="40"/>
       <c r="R30" s="33"/>
@@ -9603,23 +9603,23 @@
       <c r="Z30" s="35"/>
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A31" s="103"/>
-      <c r="B31" s="67"/>
-      <c r="C31" s="104"/>
-      <c r="D31" s="67"/>
-      <c r="E31" s="104"/>
-      <c r="F31" s="67"/>
-      <c r="G31" s="96"/>
-      <c r="H31" s="66"/>
-      <c r="I31" s="67"/>
-      <c r="J31" s="96"/>
-      <c r="K31" s="67"/>
-      <c r="L31" s="98"/>
-      <c r="M31" s="66"/>
-      <c r="N31" s="67"/>
-      <c r="O31" s="98"/>
-      <c r="P31" s="66"/>
-      <c r="Q31" s="67"/>
+      <c r="A31" s="97"/>
+      <c r="B31" s="56"/>
+      <c r="C31" s="98"/>
+      <c r="D31" s="56"/>
+      <c r="E31" s="98"/>
+      <c r="F31" s="56"/>
+      <c r="G31" s="104"/>
+      <c r="H31" s="47"/>
+      <c r="I31" s="56"/>
+      <c r="J31" s="104"/>
+      <c r="K31" s="56"/>
+      <c r="L31" s="100"/>
+      <c r="M31" s="47"/>
+      <c r="N31" s="56"/>
+      <c r="O31" s="100"/>
+      <c r="P31" s="47"/>
+      <c r="Q31" s="56"/>
       <c r="R31" s="36"/>
       <c r="S31" s="36"/>
       <c r="T31" s="37"/>
@@ -10617,6 +10617,118 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="136">
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:K19"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="K2:N4"/>
+    <mergeCell ref="O2:P4"/>
+    <mergeCell ref="Q2:R4"/>
+    <mergeCell ref="S2:T4"/>
+    <mergeCell ref="A1:F4"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="G5:T5"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="G6:T6"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="G7:T7"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="G20:I20"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="L20:N20"/>
+    <mergeCell ref="O20:Q20"/>
+    <mergeCell ref="L15:N15"/>
+    <mergeCell ref="O15:Q15"/>
+    <mergeCell ref="L16:N16"/>
+    <mergeCell ref="O16:Q16"/>
+    <mergeCell ref="L17:N17"/>
+    <mergeCell ref="O17:Q17"/>
+    <mergeCell ref="O18:Q18"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="O27:Q27"/>
+    <mergeCell ref="O28:Q28"/>
+    <mergeCell ref="O29:Q29"/>
+    <mergeCell ref="O30:Q30"/>
+    <mergeCell ref="O31:Q31"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="O26:Q26"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="A23:B23"/>
     <mergeCell ref="A30:B30"/>
     <mergeCell ref="C30:D30"/>
     <mergeCell ref="E30:F30"/>
@@ -10641,118 +10753,6 @@
     <mergeCell ref="C28:D28"/>
     <mergeCell ref="E28:F28"/>
     <mergeCell ref="A29:B29"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="O27:Q27"/>
-    <mergeCell ref="O28:Q28"/>
-    <mergeCell ref="O29:Q29"/>
-    <mergeCell ref="O30:Q30"/>
-    <mergeCell ref="O31:Q31"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="O26:Q26"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="G5:T5"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="G6:T6"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="G7:T7"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="L20:N20"/>
-    <mergeCell ref="O20:Q20"/>
-    <mergeCell ref="L15:N15"/>
-    <mergeCell ref="O15:Q15"/>
-    <mergeCell ref="L16:N16"/>
-    <mergeCell ref="O16:Q16"/>
-    <mergeCell ref="L17:N17"/>
-    <mergeCell ref="O17:Q17"/>
-    <mergeCell ref="O18:Q18"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="K2:N4"/>
-    <mergeCell ref="O2:P4"/>
-    <mergeCell ref="Q2:R4"/>
-    <mergeCell ref="S2:T4"/>
-    <mergeCell ref="A1:F4"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="G2:J4"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:K19"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>

--- a/Documents/タスク詳細設計書.xlsx
+++ b/Documents/タスク詳細設計書.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\S-47\Documents\project\taskUN\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8609B89C-CA94-441B-ADB3-7C91B7328BD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{288B7703-FBAF-41DD-B028-C894FB43C7F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1603,23 +1603,23 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>190500</xdr:colOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>57150</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
+      <xdr:rowOff>114300</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>247650</xdr:colOff>
+      <xdr:colOff>457200</xdr:colOff>
       <xdr:row>32</xdr:row>
-      <xdr:rowOff>385236</xdr:rowOff>
+      <xdr:rowOff>375711</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="図 3">
+        <xdr:cNvPr id="8" name="図 7">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BC100C2E-E0CC-9014-175D-D5A686E9AEF2}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{56378EB8-CE5F-99F7-9AD8-ADD23446FEDB}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1641,7 +1641,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="190500" y="1038225"/>
+          <a:off x="400050" y="1028700"/>
           <a:ext cx="7772400" cy="4795311"/>
         </a:xfrm>
         <a:prstGeom prst="rect">

--- a/Documents/タスク詳細設計書.xlsx
+++ b/Documents/タスク詳細設計書.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\S-47\Documents\project\taskUN\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{288B7703-FBAF-41DD-B028-C894FB43C7F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B308C57-F0F0-4BE4-89B2-8714AE68C16F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1350,23 +1350,56 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1374,11 +1407,11 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1395,26 +1428,17 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
@@ -1425,49 +1449,22 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1477,6 +1474,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1497,17 +1497,11 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1515,17 +1509,23 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1603,23 +1603,23 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>57150</xdr:colOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>295275</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
+      <xdr:rowOff>95250</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>457200</xdr:colOff>
+      <xdr:colOff>352425</xdr:colOff>
       <xdr:row>32</xdr:row>
-      <xdr:rowOff>375711</xdr:rowOff>
+      <xdr:rowOff>356661</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="8" name="図 7">
+        <xdr:cNvPr id="3" name="図 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{56378EB8-CE5F-99F7-9AD8-ADD23446FEDB}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9B59259F-1147-D29A-76FB-9AF8DA23E9CF}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1641,7 +1641,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="400050" y="1028700"/>
+          <a:off x="295275" y="1009650"/>
           <a:ext cx="7772400" cy="4795311"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3274,19 +3274,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="57" t="s">
+      <c r="A1" s="68" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="58"/>
-      <c r="C1" s="59"/>
-      <c r="D1" s="78" t="s">
+      <c r="B1" s="69"/>
+      <c r="C1" s="70"/>
+      <c r="D1" s="46" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="66"/>
-      <c r="F1" s="78" t="s">
+      <c r="E1" s="47"/>
+      <c r="F1" s="46" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="66"/>
+      <c r="G1" s="47"/>
       <c r="H1" s="5" t="s">
         <v>8</v>
       </c>
@@ -3298,72 +3298,72 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="60"/>
+      <c r="A2" s="71"/>
       <c r="B2" s="42"/>
-      <c r="C2" s="61"/>
-      <c r="D2" s="79" t="s">
+      <c r="C2" s="51"/>
+      <c r="D2" s="48" t="s">
         <v>67</v>
       </c>
-      <c r="E2" s="80"/>
-      <c r="F2" s="79" t="s">
+      <c r="E2" s="49"/>
+      <c r="F2" s="48" t="s">
         <v>68</v>
       </c>
-      <c r="G2" s="80"/>
-      <c r="H2" s="83">
+      <c r="G2" s="49"/>
+      <c r="H2" s="54">
         <v>45806</v>
       </c>
-      <c r="I2" s="72" t="s">
+      <c r="I2" s="57" t="s">
         <v>69</v>
       </c>
-      <c r="J2" s="75"/>
+      <c r="J2" s="58"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="60"/>
+      <c r="A3" s="71"/>
       <c r="B3" s="42"/>
-      <c r="C3" s="61"/>
-      <c r="D3" s="81"/>
-      <c r="E3" s="61"/>
-      <c r="F3" s="81"/>
-      <c r="G3" s="61"/>
-      <c r="H3" s="73"/>
-      <c r="I3" s="73"/>
-      <c r="J3" s="76"/>
+      <c r="C3" s="51"/>
+      <c r="D3" s="50"/>
+      <c r="E3" s="51"/>
+      <c r="F3" s="50"/>
+      <c r="G3" s="51"/>
+      <c r="H3" s="55"/>
+      <c r="I3" s="55"/>
+      <c r="J3" s="59"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="62"/>
-      <c r="B4" s="63"/>
-      <c r="C4" s="64"/>
-      <c r="D4" s="82"/>
-      <c r="E4" s="64"/>
-      <c r="F4" s="82"/>
-      <c r="G4" s="64"/>
-      <c r="H4" s="74"/>
-      <c r="I4" s="74"/>
-      <c r="J4" s="77"/>
+      <c r="A4" s="72"/>
+      <c r="B4" s="73"/>
+      <c r="C4" s="53"/>
+      <c r="D4" s="52"/>
+      <c r="E4" s="53"/>
+      <c r="F4" s="52"/>
+      <c r="G4" s="53"/>
+      <c r="H4" s="56"/>
+      <c r="I4" s="56"/>
+      <c r="J4" s="60"/>
     </row>
     <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="65" t="s">
+      <c r="A5" s="74" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="50"/>
-      <c r="C5" s="66"/>
-      <c r="D5" s="49" t="s">
+      <c r="B5" s="75"/>
+      <c r="C5" s="47"/>
+      <c r="D5" s="81" t="s">
         <v>70</v>
       </c>
-      <c r="E5" s="50"/>
-      <c r="F5" s="50"/>
-      <c r="G5" s="50"/>
-      <c r="H5" s="50"/>
-      <c r="I5" s="50"/>
-      <c r="J5" s="51"/>
+      <c r="E5" s="75"/>
+      <c r="F5" s="75"/>
+      <c r="G5" s="75"/>
+      <c r="H5" s="75"/>
+      <c r="I5" s="75"/>
+      <c r="J5" s="82"/>
     </row>
     <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="67" t="s">
+      <c r="A6" s="62" t="s">
         <v>12</v>
       </c>
       <c r="B6" s="39"/>
       <c r="C6" s="40"/>
-      <c r="D6" s="52" t="s">
+      <c r="D6" s="63" t="s">
         <v>71</v>
       </c>
       <c r="E6" s="39"/>
@@ -3371,15 +3371,15 @@
       <c r="G6" s="39"/>
       <c r="H6" s="39"/>
       <c r="I6" s="39"/>
-      <c r="J6" s="53"/>
+      <c r="J6" s="64"/>
     </row>
     <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="67" t="s">
+      <c r="A7" s="62" t="s">
         <v>13</v>
       </c>
       <c r="B7" s="39"/>
       <c r="C7" s="40"/>
-      <c r="D7" s="52" t="s">
+      <c r="D7" s="63" t="s">
         <v>72</v>
       </c>
       <c r="E7" s="39"/>
@@ -3387,15 +3387,15 @@
       <c r="G7" s="39"/>
       <c r="H7" s="39"/>
       <c r="I7" s="39"/>
-      <c r="J7" s="53"/>
+      <c r="J7" s="64"/>
     </row>
     <row r="8" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A8" s="67" t="s">
+      <c r="A8" s="62" t="s">
         <v>14</v>
       </c>
       <c r="B8" s="39"/>
       <c r="C8" s="40"/>
-      <c r="D8" s="52" t="s">
+      <c r="D8" s="63" t="s">
         <v>73</v>
       </c>
       <c r="E8" s="39"/>
@@ -3403,17 +3403,17 @@
       <c r="G8" s="39"/>
       <c r="H8" s="39"/>
       <c r="I8" s="39"/>
-      <c r="J8" s="53"/>
+      <c r="J8" s="64"/>
     </row>
     <row r="9" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A9" s="68" t="s">
+      <c r="A9" s="76" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="71" t="s">
+      <c r="B9" s="61" t="s">
         <v>16</v>
       </c>
       <c r="C9" s="40"/>
-      <c r="D9" s="54" t="s">
+      <c r="D9" s="83" t="s">
         <v>75</v>
       </c>
       <c r="E9" s="39"/>
@@ -3421,43 +3421,43 @@
       <c r="G9" s="39"/>
       <c r="H9" s="39"/>
       <c r="I9" s="39"/>
-      <c r="J9" s="53"/>
+      <c r="J9" s="64"/>
     </row>
     <row r="10" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A10" s="69"/>
-      <c r="B10" s="71" t="s">
+      <c r="A10" s="77"/>
+      <c r="B10" s="61" t="s">
         <v>17</v>
       </c>
       <c r="C10" s="40"/>
-      <c r="D10" s="52"/>
+      <c r="D10" s="63"/>
       <c r="E10" s="39"/>
       <c r="F10" s="39"/>
       <c r="G10" s="39"/>
       <c r="H10" s="39"/>
       <c r="I10" s="39"/>
-      <c r="J10" s="53"/>
+      <c r="J10" s="64"/>
     </row>
     <row r="11" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A11" s="70"/>
-      <c r="B11" s="71" t="s">
+      <c r="A11" s="78"/>
+      <c r="B11" s="61" t="s">
         <v>18</v>
       </c>
       <c r="C11" s="40"/>
-      <c r="D11" s="52"/>
+      <c r="D11" s="63"/>
       <c r="E11" s="39"/>
       <c r="F11" s="39"/>
       <c r="G11" s="39"/>
       <c r="H11" s="39"/>
       <c r="I11" s="39"/>
-      <c r="J11" s="53"/>
+      <c r="J11" s="64"/>
     </row>
     <row r="12" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A12" s="67" t="s">
+      <c r="A12" s="62" t="s">
         <v>19</v>
       </c>
       <c r="B12" s="39"/>
       <c r="C12" s="40"/>
-      <c r="D12" s="52" t="s">
+      <c r="D12" s="63" t="s">
         <v>74</v>
       </c>
       <c r="E12" s="39"/>
@@ -3465,21 +3465,21 @@
       <c r="G12" s="39"/>
       <c r="H12" s="39"/>
       <c r="I12" s="39"/>
-      <c r="J12" s="53"/>
+      <c r="J12" s="64"/>
     </row>
     <row r="13" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A13" s="55" t="s">
+      <c r="A13" s="65" t="s">
         <v>20</v>
       </c>
-      <c r="B13" s="47"/>
-      <c r="C13" s="56"/>
-      <c r="D13" s="46"/>
-      <c r="E13" s="47"/>
-      <c r="F13" s="47"/>
-      <c r="G13" s="47"/>
-      <c r="H13" s="47"/>
-      <c r="I13" s="47"/>
-      <c r="J13" s="48"/>
+      <c r="B13" s="66"/>
+      <c r="C13" s="67"/>
+      <c r="D13" s="79"/>
+      <c r="E13" s="66"/>
+      <c r="F13" s="66"/>
+      <c r="G13" s="66"/>
+      <c r="H13" s="66"/>
+      <c r="I13" s="66"/>
+      <c r="J13" s="80"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -4470,17 +4470,14 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="D12:J12"/>
+    <mergeCell ref="D13:J13"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="D6:J6"/>
+    <mergeCell ref="D7:J7"/>
+    <mergeCell ref="D8:J8"/>
+    <mergeCell ref="D9:J9"/>
+    <mergeCell ref="D10:J10"/>
+    <mergeCell ref="D11:J11"/>
     <mergeCell ref="A13:C13"/>
     <mergeCell ref="A1:C4"/>
     <mergeCell ref="A5:C5"/>
@@ -4489,14 +4486,17 @@
     <mergeCell ref="A8:C8"/>
     <mergeCell ref="A9:A11"/>
     <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D13:J13"/>
-    <mergeCell ref="D5:J5"/>
-    <mergeCell ref="D6:J6"/>
-    <mergeCell ref="D7:J7"/>
-    <mergeCell ref="D8:J8"/>
-    <mergeCell ref="D9:J9"/>
-    <mergeCell ref="D10:J10"/>
-    <mergeCell ref="D11:J11"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="D12:J12"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
@@ -4518,16 +4518,16 @@
       <c r="A1" s="84" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="58"/>
-      <c r="C1" s="59"/>
-      <c r="D1" s="78" t="s">
+      <c r="B1" s="69"/>
+      <c r="C1" s="70"/>
+      <c r="D1" s="46" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="66"/>
-      <c r="F1" s="78" t="s">
+      <c r="E1" s="47"/>
+      <c r="F1" s="46" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="66"/>
+      <c r="G1" s="47"/>
       <c r="H1" s="4" t="s">
         <v>8</v>
       </c>
@@ -4539,48 +4539,48 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="60"/>
+      <c r="A2" s="71"/>
       <c r="B2" s="42"/>
-      <c r="C2" s="61"/>
-      <c r="D2" s="79" t="s">
+      <c r="C2" s="51"/>
+      <c r="D2" s="48" t="s">
         <v>67</v>
       </c>
-      <c r="E2" s="80"/>
-      <c r="F2" s="79" t="s">
+      <c r="E2" s="49"/>
+      <c r="F2" s="48" t="s">
         <v>68</v>
       </c>
-      <c r="G2" s="80"/>
-      <c r="H2" s="83">
+      <c r="G2" s="49"/>
+      <c r="H2" s="54">
         <v>45810</v>
       </c>
-      <c r="I2" s="72" t="s">
+      <c r="I2" s="57" t="s">
         <v>76</v>
       </c>
-      <c r="J2" s="75"/>
+      <c r="J2" s="58"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="60"/>
+      <c r="A3" s="71"/>
       <c r="B3" s="42"/>
-      <c r="C3" s="61"/>
-      <c r="D3" s="81"/>
-      <c r="E3" s="61"/>
-      <c r="F3" s="81"/>
-      <c r="G3" s="61"/>
-      <c r="H3" s="73"/>
-      <c r="I3" s="73"/>
-      <c r="J3" s="76"/>
+      <c r="C3" s="51"/>
+      <c r="D3" s="50"/>
+      <c r="E3" s="51"/>
+      <c r="F3" s="50"/>
+      <c r="G3" s="51"/>
+      <c r="H3" s="55"/>
+      <c r="I3" s="55"/>
+      <c r="J3" s="59"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="62"/>
-      <c r="B4" s="63"/>
-      <c r="C4" s="64"/>
-      <c r="D4" s="82"/>
-      <c r="E4" s="64"/>
-      <c r="F4" s="82"/>
-      <c r="G4" s="64"/>
-      <c r="H4" s="74"/>
-      <c r="I4" s="74"/>
-      <c r="J4" s="77"/>
+      <c r="A4" s="72"/>
+      <c r="B4" s="73"/>
+      <c r="C4" s="53"/>
+      <c r="D4" s="52"/>
+      <c r="E4" s="53"/>
+      <c r="F4" s="52"/>
+      <c r="G4" s="53"/>
+      <c r="H4" s="56"/>
+      <c r="I4" s="56"/>
+      <c r="J4" s="60"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -5940,16 +5940,16 @@
       <c r="A1" s="84" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="58"/>
-      <c r="C1" s="59"/>
-      <c r="D1" s="78" t="s">
+      <c r="B1" s="69"/>
+      <c r="C1" s="70"/>
+      <c r="D1" s="46" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="66"/>
-      <c r="F1" s="78" t="s">
+      <c r="E1" s="47"/>
+      <c r="F1" s="46" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="66"/>
+      <c r="G1" s="47"/>
       <c r="H1" s="4" t="s">
         <v>8</v>
       </c>
@@ -5961,48 +5961,48 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="60"/>
+      <c r="A2" s="71"/>
       <c r="B2" s="42"/>
-      <c r="C2" s="61"/>
-      <c r="D2" s="79" t="s">
+      <c r="C2" s="51"/>
+      <c r="D2" s="48" t="s">
         <v>67</v>
       </c>
-      <c r="E2" s="80"/>
-      <c r="F2" s="79" t="s">
+      <c r="E2" s="49"/>
+      <c r="F2" s="48" t="s">
         <v>68</v>
       </c>
-      <c r="G2" s="80"/>
-      <c r="H2" s="83">
+      <c r="G2" s="49"/>
+      <c r="H2" s="54">
         <v>45810</v>
       </c>
-      <c r="I2" s="72" t="s">
+      <c r="I2" s="57" t="s">
         <v>76</v>
       </c>
-      <c r="J2" s="75"/>
+      <c r="J2" s="58"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="60"/>
+      <c r="A3" s="71"/>
       <c r="B3" s="42"/>
-      <c r="C3" s="61"/>
-      <c r="D3" s="81"/>
-      <c r="E3" s="61"/>
-      <c r="F3" s="81"/>
-      <c r="G3" s="61"/>
-      <c r="H3" s="73"/>
-      <c r="I3" s="73"/>
-      <c r="J3" s="76"/>
+      <c r="C3" s="51"/>
+      <c r="D3" s="50"/>
+      <c r="E3" s="51"/>
+      <c r="F3" s="50"/>
+      <c r="G3" s="51"/>
+      <c r="H3" s="55"/>
+      <c r="I3" s="55"/>
+      <c r="J3" s="59"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="62"/>
-      <c r="B4" s="63"/>
-      <c r="C4" s="64"/>
-      <c r="D4" s="82"/>
-      <c r="E4" s="64"/>
-      <c r="F4" s="82"/>
-      <c r="G4" s="64"/>
-      <c r="H4" s="74"/>
-      <c r="I4" s="74"/>
-      <c r="J4" s="77"/>
+      <c r="A4" s="72"/>
+      <c r="B4" s="73"/>
+      <c r="C4" s="53"/>
+      <c r="D4" s="52"/>
+      <c r="E4" s="53"/>
+      <c r="F4" s="52"/>
+      <c r="G4" s="53"/>
+      <c r="H4" s="56"/>
+      <c r="I4" s="56"/>
+      <c r="J4" s="60"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -7356,16 +7356,16 @@
       <c r="A1" s="84" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="58"/>
-      <c r="C1" s="59"/>
-      <c r="D1" s="78" t="s">
+      <c r="B1" s="69"/>
+      <c r="C1" s="70"/>
+      <c r="D1" s="46" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="66"/>
-      <c r="F1" s="78" t="s">
+      <c r="E1" s="47"/>
+      <c r="F1" s="46" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="66"/>
+      <c r="G1" s="47"/>
       <c r="H1" s="4" t="s">
         <v>8</v>
       </c>
@@ -7377,67 +7377,67 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="60"/>
+      <c r="A2" s="71"/>
       <c r="B2" s="42"/>
-      <c r="C2" s="61"/>
-      <c r="D2" s="79" t="s">
+      <c r="C2" s="51"/>
+      <c r="D2" s="48" t="s">
         <v>67</v>
       </c>
-      <c r="E2" s="80"/>
-      <c r="F2" s="79" t="s">
+      <c r="E2" s="49"/>
+      <c r="F2" s="48" t="s">
         <v>68</v>
       </c>
-      <c r="G2" s="80"/>
-      <c r="H2" s="83">
+      <c r="G2" s="49"/>
+      <c r="H2" s="54">
         <v>45810</v>
       </c>
-      <c r="I2" s="72" t="s">
+      <c r="I2" s="57" t="s">
         <v>76</v>
       </c>
-      <c r="J2" s="75"/>
+      <c r="J2" s="58"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="60"/>
+      <c r="A3" s="71"/>
       <c r="B3" s="42"/>
-      <c r="C3" s="61"/>
-      <c r="D3" s="81"/>
-      <c r="E3" s="61"/>
-      <c r="F3" s="81"/>
-      <c r="G3" s="61"/>
-      <c r="H3" s="73"/>
-      <c r="I3" s="73"/>
-      <c r="J3" s="76"/>
+      <c r="C3" s="51"/>
+      <c r="D3" s="50"/>
+      <c r="E3" s="51"/>
+      <c r="F3" s="50"/>
+      <c r="G3" s="51"/>
+      <c r="H3" s="55"/>
+      <c r="I3" s="55"/>
+      <c r="J3" s="59"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="60"/>
+      <c r="A4" s="71"/>
       <c r="B4" s="42"/>
-      <c r="C4" s="61"/>
-      <c r="D4" s="81"/>
-      <c r="E4" s="61"/>
-      <c r="F4" s="81"/>
-      <c r="G4" s="61"/>
-      <c r="H4" s="73"/>
-      <c r="I4" s="73"/>
-      <c r="J4" s="76"/>
+      <c r="C4" s="51"/>
+      <c r="D4" s="50"/>
+      <c r="E4" s="51"/>
+      <c r="F4" s="50"/>
+      <c r="G4" s="51"/>
+      <c r="H4" s="55"/>
+      <c r="I4" s="55"/>
+      <c r="J4" s="59"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="86" t="s">
+      <c r="A5" s="85" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="50"/>
-      <c r="C5" s="66"/>
+      <c r="B5" s="75"/>
+      <c r="C5" s="47"/>
       <c r="D5" s="89" t="s">
         <v>77</v>
       </c>
-      <c r="E5" s="50"/>
-      <c r="F5" s="50"/>
-      <c r="G5" s="50"/>
-      <c r="H5" s="50"/>
-      <c r="I5" s="50"/>
-      <c r="J5" s="51"/>
+      <c r="E5" s="75"/>
+      <c r="F5" s="75"/>
+      <c r="G5" s="75"/>
+      <c r="H5" s="75"/>
+      <c r="I5" s="75"/>
+      <c r="J5" s="82"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="88" t="s">
+      <c r="A6" s="87" t="s">
         <v>25</v>
       </c>
       <c r="B6" s="39"/>
@@ -7448,7 +7448,7 @@
       <c r="G6" s="39"/>
       <c r="H6" s="39"/>
       <c r="I6" s="39"/>
-      <c r="J6" s="53"/>
+      <c r="J6" s="64"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
       <c r="A7" s="90"/>
@@ -7463,7 +7463,7 @@
       <c r="J7" s="92"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="60"/>
+      <c r="A8" s="71"/>
       <c r="B8" s="42"/>
       <c r="C8" s="42"/>
       <c r="D8" s="42"/>
@@ -7475,7 +7475,7 @@
       <c r="J8" s="93"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="60"/>
+      <c r="A9" s="71"/>
       <c r="B9" s="42"/>
       <c r="C9" s="42"/>
       <c r="D9" s="42"/>
@@ -7487,7 +7487,7 @@
       <c r="J9" s="93"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="60"/>
+      <c r="A10" s="71"/>
       <c r="B10" s="42"/>
       <c r="C10" s="42"/>
       <c r="D10" s="42"/>
@@ -7499,7 +7499,7 @@
       <c r="J10" s="93"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="60"/>
+      <c r="A11" s="71"/>
       <c r="B11" s="42"/>
       <c r="C11" s="42"/>
       <c r="D11" s="42"/>
@@ -7511,7 +7511,7 @@
       <c r="J11" s="93"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="60"/>
+      <c r="A12" s="71"/>
       <c r="B12" s="42"/>
       <c r="C12" s="42"/>
       <c r="D12" s="42"/>
@@ -7523,7 +7523,7 @@
       <c r="J12" s="93"/>
     </row>
     <row r="13" spans="1:10" ht="62.25" customHeight="1">
-      <c r="A13" s="60"/>
+      <c r="A13" s="71"/>
       <c r="B13" s="42"/>
       <c r="C13" s="42"/>
       <c r="D13" s="42"/>
@@ -7535,7 +7535,7 @@
       <c r="J13" s="93"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="88" t="s">
+      <c r="A14" s="87" t="s">
         <v>26</v>
       </c>
       <c r="B14" s="39"/>
@@ -7546,15 +7546,15 @@
       <c r="G14" s="39"/>
       <c r="H14" s="39"/>
       <c r="I14" s="39"/>
-      <c r="J14" s="53"/>
+      <c r="J14" s="64"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="88" t="s">
+      <c r="A15" s="87" t="s">
         <v>27</v>
       </c>
       <c r="B15" s="39"/>
       <c r="C15" s="40"/>
-      <c r="D15" s="52" t="s">
+      <c r="D15" s="63" t="s">
         <v>86</v>
       </c>
       <c r="E15" s="39"/>
@@ -7569,7 +7569,7 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="88" t="s">
+      <c r="A16" s="87" t="s">
         <v>29</v>
       </c>
       <c r="B16" s="39"/>
@@ -7590,10 +7590,10 @@
         <v>20</v>
       </c>
       <c r="I16" s="39"/>
-      <c r="J16" s="53"/>
+      <c r="J16" s="64"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="85">
+      <c r="A17" s="88">
         <v>1</v>
       </c>
       <c r="B17" s="39"/>
@@ -7608,14 +7608,14 @@
       <c r="G17" s="18" t="s">
         <v>83</v>
       </c>
-      <c r="H17" s="52" t="s">
+      <c r="H17" s="63" t="s">
         <v>87</v>
       </c>
       <c r="I17" s="39"/>
-      <c r="J17" s="53"/>
+      <c r="J17" s="64"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="85">
+      <c r="A18" s="88">
         <v>2</v>
       </c>
       <c r="B18" s="39"/>
@@ -7630,14 +7630,14 @@
       <c r="G18" s="18" t="s">
         <v>84</v>
       </c>
-      <c r="H18" s="52" t="s">
+      <c r="H18" s="63" t="s">
         <v>87</v>
       </c>
       <c r="I18" s="39"/>
-      <c r="J18" s="53"/>
+      <c r="J18" s="64"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="85">
+      <c r="A19" s="88">
         <v>3</v>
       </c>
       <c r="B19" s="39"/>
@@ -7652,59 +7652,59 @@
       <c r="G19" s="18" t="s">
         <v>85</v>
       </c>
-      <c r="H19" s="52" t="s">
+      <c r="H19" s="63" t="s">
         <v>87</v>
       </c>
       <c r="I19" s="39"/>
-      <c r="J19" s="53"/>
+      <c r="J19" s="64"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="85"/>
+      <c r="A20" s="88"/>
       <c r="B20" s="39"/>
       <c r="C20" s="40"/>
       <c r="D20" s="17"/>
       <c r="E20" s="17"/>
       <c r="F20" s="18"/>
       <c r="G20" s="18"/>
-      <c r="H20" s="52"/>
+      <c r="H20" s="63"/>
       <c r="I20" s="39"/>
-      <c r="J20" s="53"/>
+      <c r="J20" s="64"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="85"/>
+      <c r="A21" s="88"/>
       <c r="B21" s="39"/>
       <c r="C21" s="40"/>
       <c r="D21" s="17"/>
       <c r="E21" s="17"/>
       <c r="F21" s="18"/>
       <c r="G21" s="18"/>
-      <c r="H21" s="52"/>
+      <c r="H21" s="63"/>
       <c r="I21" s="39"/>
-      <c r="J21" s="53"/>
+      <c r="J21" s="64"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="85"/>
+      <c r="A22" s="88"/>
       <c r="B22" s="39"/>
       <c r="C22" s="40"/>
       <c r="D22" s="17"/>
       <c r="E22" s="17"/>
       <c r="F22" s="18"/>
       <c r="G22" s="18"/>
-      <c r="H22" s="52"/>
+      <c r="H22" s="63"/>
       <c r="I22" s="39"/>
-      <c r="J22" s="53"/>
+      <c r="J22" s="64"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A23" s="87"/>
-      <c r="B23" s="47"/>
-      <c r="C23" s="56"/>
+      <c r="A23" s="86"/>
+      <c r="B23" s="66"/>
+      <c r="C23" s="67"/>
       <c r="D23" s="19"/>
       <c r="E23" s="19"/>
       <c r="F23" s="20"/>
       <c r="G23" s="20"/>
-      <c r="H23" s="46"/>
-      <c r="I23" s="47"/>
-      <c r="J23" s="48"/>
+      <c r="H23" s="79"/>
+      <c r="I23" s="66"/>
+      <c r="J23" s="80"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
@@ -8685,11 +8685,16 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A22:C22"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="F1:G1"/>
@@ -8706,16 +8711,11 @@
     <mergeCell ref="H17:J17"/>
     <mergeCell ref="D2:E4"/>
     <mergeCell ref="H23:J23"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A1:C4"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -8735,137 +8735,137 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="57" t="s">
+      <c r="A1" s="68" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="58"/>
-      <c r="C1" s="58"/>
-      <c r="D1" s="58"/>
-      <c r="E1" s="58"/>
-      <c r="F1" s="59"/>
-      <c r="G1" s="78" t="s">
+      <c r="B1" s="69"/>
+      <c r="C1" s="69"/>
+      <c r="D1" s="69"/>
+      <c r="E1" s="69"/>
+      <c r="F1" s="70"/>
+      <c r="G1" s="46" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="50"/>
-      <c r="I1" s="50"/>
-      <c r="J1" s="66"/>
-      <c r="K1" s="78" t="s">
+      <c r="H1" s="75"/>
+      <c r="I1" s="75"/>
+      <c r="J1" s="47"/>
+      <c r="K1" s="46" t="s">
         <v>7</v>
       </c>
-      <c r="L1" s="50"/>
-      <c r="M1" s="50"/>
-      <c r="N1" s="66"/>
-      <c r="O1" s="78" t="s">
+      <c r="L1" s="75"/>
+      <c r="M1" s="75"/>
+      <c r="N1" s="47"/>
+      <c r="O1" s="46" t="s">
         <v>8</v>
       </c>
-      <c r="P1" s="66"/>
-      <c r="Q1" s="78" t="s">
+      <c r="P1" s="47"/>
+      <c r="Q1" s="46" t="s">
         <v>9</v>
       </c>
-      <c r="R1" s="66"/>
-      <c r="S1" s="78" t="s">
+      <c r="R1" s="47"/>
+      <c r="S1" s="46" t="s">
         <v>10</v>
       </c>
-      <c r="T1" s="51"/>
+      <c r="T1" s="82"/>
     </row>
     <row r="2" spans="1:26" ht="18" customHeight="1">
-      <c r="A2" s="60"/>
+      <c r="A2" s="71"/>
       <c r="B2" s="42"/>
       <c r="C2" s="42"/>
       <c r="D2" s="42"/>
       <c r="E2" s="42"/>
-      <c r="F2" s="61"/>
-      <c r="G2" s="79" t="s">
+      <c r="F2" s="51"/>
+      <c r="G2" s="48" t="s">
         <v>67</v>
       </c>
       <c r="H2" s="91"/>
       <c r="I2" s="91"/>
-      <c r="J2" s="80"/>
-      <c r="K2" s="79" t="s">
+      <c r="J2" s="49"/>
+      <c r="K2" s="48" t="s">
         <v>68</v>
       </c>
       <c r="L2" s="91"/>
       <c r="M2" s="91"/>
-      <c r="N2" s="80"/>
-      <c r="O2" s="79"/>
-      <c r="P2" s="80"/>
-      <c r="Q2" s="79"/>
-      <c r="R2" s="80"/>
-      <c r="S2" s="79"/>
+      <c r="N2" s="49"/>
+      <c r="O2" s="48"/>
+      <c r="P2" s="49"/>
+      <c r="Q2" s="48"/>
+      <c r="R2" s="49"/>
+      <c r="S2" s="48"/>
       <c r="T2" s="92"/>
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
-      <c r="A3" s="60"/>
+      <c r="A3" s="71"/>
       <c r="B3" s="42"/>
       <c r="C3" s="42"/>
       <c r="D3" s="42"/>
       <c r="E3" s="42"/>
-      <c r="F3" s="61"/>
-      <c r="G3" s="81"/>
+      <c r="F3" s="51"/>
+      <c r="G3" s="50"/>
       <c r="H3" s="42"/>
       <c r="I3" s="42"/>
-      <c r="J3" s="61"/>
-      <c r="K3" s="81"/>
+      <c r="J3" s="51"/>
+      <c r="K3" s="50"/>
       <c r="L3" s="42"/>
       <c r="M3" s="42"/>
-      <c r="N3" s="61"/>
-      <c r="O3" s="81"/>
-      <c r="P3" s="61"/>
-      <c r="Q3" s="81"/>
-      <c r="R3" s="61"/>
-      <c r="S3" s="81"/>
+      <c r="N3" s="51"/>
+      <c r="O3" s="50"/>
+      <c r="P3" s="51"/>
+      <c r="Q3" s="50"/>
+      <c r="R3" s="51"/>
+      <c r="S3" s="50"/>
       <c r="T3" s="93"/>
     </row>
     <row r="4" spans="1:26" ht="18" customHeight="1">
-      <c r="A4" s="62"/>
-      <c r="B4" s="63"/>
-      <c r="C4" s="63"/>
-      <c r="D4" s="63"/>
-      <c r="E4" s="63"/>
-      <c r="F4" s="64"/>
-      <c r="G4" s="82"/>
-      <c r="H4" s="63"/>
-      <c r="I4" s="63"/>
-      <c r="J4" s="64"/>
-      <c r="K4" s="82"/>
-      <c r="L4" s="63"/>
-      <c r="M4" s="63"/>
-      <c r="N4" s="64"/>
-      <c r="O4" s="82"/>
-      <c r="P4" s="64"/>
-      <c r="Q4" s="82"/>
-      <c r="R4" s="64"/>
-      <c r="S4" s="82"/>
-      <c r="T4" s="103"/>
+      <c r="A4" s="72"/>
+      <c r="B4" s="73"/>
+      <c r="C4" s="73"/>
+      <c r="D4" s="73"/>
+      <c r="E4" s="73"/>
+      <c r="F4" s="53"/>
+      <c r="G4" s="52"/>
+      <c r="H4" s="73"/>
+      <c r="I4" s="73"/>
+      <c r="J4" s="53"/>
+      <c r="K4" s="52"/>
+      <c r="L4" s="73"/>
+      <c r="M4" s="73"/>
+      <c r="N4" s="53"/>
+      <c r="O4" s="52"/>
+      <c r="P4" s="53"/>
+      <c r="Q4" s="52"/>
+      <c r="R4" s="53"/>
+      <c r="S4" s="52"/>
+      <c r="T4" s="99"/>
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="86" t="s">
+      <c r="A5" s="85" t="s">
         <v>35</v>
       </c>
-      <c r="B5" s="50"/>
-      <c r="C5" s="50"/>
-      <c r="D5" s="50"/>
-      <c r="E5" s="50"/>
-      <c r="F5" s="66"/>
-      <c r="G5" s="49" t="s">
+      <c r="B5" s="75"/>
+      <c r="C5" s="75"/>
+      <c r="D5" s="75"/>
+      <c r="E5" s="75"/>
+      <c r="F5" s="47"/>
+      <c r="G5" s="81" t="s">
         <v>36</v>
       </c>
-      <c r="H5" s="50"/>
-      <c r="I5" s="50"/>
-      <c r="J5" s="50"/>
-      <c r="K5" s="50"/>
-      <c r="L5" s="50"/>
-      <c r="M5" s="50"/>
-      <c r="N5" s="50"/>
-      <c r="O5" s="50"/>
-      <c r="P5" s="50"/>
-      <c r="Q5" s="50"/>
-      <c r="R5" s="50"/>
-      <c r="S5" s="50"/>
-      <c r="T5" s="51"/>
+      <c r="H5" s="75"/>
+      <c r="I5" s="75"/>
+      <c r="J5" s="75"/>
+      <c r="K5" s="75"/>
+      <c r="L5" s="75"/>
+      <c r="M5" s="75"/>
+      <c r="N5" s="75"/>
+      <c r="O5" s="75"/>
+      <c r="P5" s="75"/>
+      <c r="Q5" s="75"/>
+      <c r="R5" s="75"/>
+      <c r="S5" s="75"/>
+      <c r="T5" s="82"/>
     </row>
     <row r="6" spans="1:26" ht="18" customHeight="1">
-      <c r="A6" s="88" t="s">
+      <c r="A6" s="87" t="s">
         <v>37</v>
       </c>
       <c r="B6" s="39"/>
@@ -8873,7 +8873,7 @@
       <c r="D6" s="39"/>
       <c r="E6" s="39"/>
       <c r="F6" s="40"/>
-      <c r="G6" s="52" t="s">
+      <c r="G6" s="63" t="s">
         <v>21</v>
       </c>
       <c r="H6" s="39"/>
@@ -8888,10 +8888,10 @@
       <c r="Q6" s="39"/>
       <c r="R6" s="39"/>
       <c r="S6" s="39"/>
-      <c r="T6" s="53"/>
+      <c r="T6" s="64"/>
     </row>
     <row r="7" spans="1:26" ht="18" customHeight="1">
-      <c r="A7" s="88" t="s">
+      <c r="A7" s="87" t="s">
         <v>38</v>
       </c>
       <c r="B7" s="39"/>
@@ -8899,7 +8899,7 @@
       <c r="D7" s="39"/>
       <c r="E7" s="39"/>
       <c r="F7" s="40"/>
-      <c r="G7" s="52" t="s">
+      <c r="G7" s="63" t="s">
         <v>39</v>
       </c>
       <c r="H7" s="39"/>
@@ -8914,7 +8914,7 @@
       <c r="Q7" s="39"/>
       <c r="R7" s="39"/>
       <c r="S7" s="39"/>
-      <c r="T7" s="53"/>
+      <c r="T7" s="64"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
       <c r="A8" s="8"/>
@@ -9113,7 +9113,7 @@
       <c r="T14" s="10"/>
     </row>
     <row r="15" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A15" s="88" t="s">
+      <c r="A15" s="87" t="s">
         <v>46</v>
       </c>
       <c r="B15" s="40"/>
@@ -9155,33 +9155,33 @@
       </c>
     </row>
     <row r="16" spans="1:26" ht="48" customHeight="1">
-      <c r="A16" s="95">
+      <c r="A16" s="100">
         <v>1</v>
       </c>
       <c r="B16" s="40"/>
-      <c r="C16" s="96" t="s">
+      <c r="C16" s="101" t="s">
         <v>55</v>
       </c>
       <c r="D16" s="40"/>
-      <c r="E16" s="96" t="s">
+      <c r="E16" s="101" t="s">
         <v>56</v>
       </c>
       <c r="F16" s="40"/>
-      <c r="G16" s="101" t="s">
+      <c r="G16" s="95" t="s">
         <v>57</v>
       </c>
       <c r="H16" s="39"/>
       <c r="I16" s="40"/>
-      <c r="J16" s="101" t="s">
+      <c r="J16" s="95" t="s">
         <v>58</v>
       </c>
       <c r="K16" s="40"/>
-      <c r="L16" s="99" t="s">
+      <c r="L16" s="97" t="s">
         <v>59</v>
       </c>
       <c r="M16" s="39"/>
       <c r="N16" s="40"/>
-      <c r="O16" s="99" t="s">
+      <c r="O16" s="97" t="s">
         <v>60</v>
       </c>
       <c r="P16" s="39"/>
@@ -9197,33 +9197,33 @@
       <c r="Z16" s="35"/>
     </row>
     <row r="17" spans="1:26" ht="41.25" customHeight="1">
-      <c r="A17" s="95">
+      <c r="A17" s="100">
         <v>2</v>
       </c>
       <c r="B17" s="40"/>
-      <c r="C17" s="96" t="s">
+      <c r="C17" s="101" t="s">
         <v>61</v>
       </c>
       <c r="D17" s="40"/>
-      <c r="E17" s="96" t="s">
+      <c r="E17" s="101" t="s">
         <v>62</v>
       </c>
       <c r="F17" s="40"/>
-      <c r="G17" s="101" t="s">
+      <c r="G17" s="95" t="s">
         <v>63</v>
       </c>
       <c r="H17" s="39"/>
       <c r="I17" s="40"/>
-      <c r="J17" s="101" t="s">
+      <c r="J17" s="95" t="s">
         <v>64</v>
       </c>
       <c r="K17" s="40"/>
-      <c r="L17" s="99" t="s">
+      <c r="L17" s="97" t="s">
         <v>65</v>
       </c>
       <c r="M17" s="39"/>
       <c r="N17" s="40"/>
-      <c r="O17" s="99" t="s">
+      <c r="O17" s="97" t="s">
         <v>66</v>
       </c>
       <c r="P17" s="39"/>
@@ -9239,21 +9239,21 @@
       <c r="Z17" s="35"/>
     </row>
     <row r="18" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A18" s="95"/>
+      <c r="A18" s="100"/>
       <c r="B18" s="40"/>
-      <c r="C18" s="96"/>
+      <c r="C18" s="101"/>
       <c r="D18" s="40"/>
-      <c r="E18" s="96"/>
+      <c r="E18" s="101"/>
       <c r="F18" s="40"/>
-      <c r="G18" s="101"/>
+      <c r="G18" s="95"/>
       <c r="H18" s="39"/>
       <c r="I18" s="40"/>
-      <c r="J18" s="101"/>
+      <c r="J18" s="95"/>
       <c r="K18" s="40"/>
-      <c r="L18" s="99"/>
+      <c r="L18" s="97"/>
       <c r="M18" s="39"/>
       <c r="N18" s="40"/>
-      <c r="O18" s="99"/>
+      <c r="O18" s="97"/>
       <c r="P18" s="39"/>
       <c r="Q18" s="40"/>
       <c r="R18" s="33"/>
@@ -9267,21 +9267,21 @@
       <c r="Z18" s="35"/>
     </row>
     <row r="19" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A19" s="95"/>
+      <c r="A19" s="100"/>
       <c r="B19" s="40"/>
-      <c r="C19" s="96"/>
+      <c r="C19" s="101"/>
       <c r="D19" s="40"/>
-      <c r="E19" s="96"/>
+      <c r="E19" s="101"/>
       <c r="F19" s="40"/>
-      <c r="G19" s="101"/>
+      <c r="G19" s="95"/>
       <c r="H19" s="39"/>
       <c r="I19" s="40"/>
-      <c r="J19" s="101"/>
+      <c r="J19" s="95"/>
       <c r="K19" s="40"/>
-      <c r="L19" s="99"/>
+      <c r="L19" s="97"/>
       <c r="M19" s="39"/>
       <c r="N19" s="40"/>
-      <c r="O19" s="99"/>
+      <c r="O19" s="97"/>
       <c r="P19" s="39"/>
       <c r="Q19" s="40"/>
       <c r="R19" s="33"/>
@@ -9295,21 +9295,21 @@
       <c r="Z19" s="35"/>
     </row>
     <row r="20" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A20" s="95"/>
+      <c r="A20" s="100"/>
       <c r="B20" s="40"/>
-      <c r="C20" s="96"/>
+      <c r="C20" s="101"/>
       <c r="D20" s="40"/>
-      <c r="E20" s="96"/>
+      <c r="E20" s="101"/>
       <c r="F20" s="40"/>
-      <c r="G20" s="101"/>
+      <c r="G20" s="95"/>
       <c r="H20" s="39"/>
       <c r="I20" s="40"/>
-      <c r="J20" s="101"/>
+      <c r="J20" s="95"/>
       <c r="K20" s="40"/>
-      <c r="L20" s="99"/>
+      <c r="L20" s="97"/>
       <c r="M20" s="39"/>
       <c r="N20" s="40"/>
-      <c r="O20" s="99"/>
+      <c r="O20" s="97"/>
       <c r="P20" s="39"/>
       <c r="Q20" s="40"/>
       <c r="R20" s="33"/>
@@ -9323,21 +9323,21 @@
       <c r="Z20" s="35"/>
     </row>
     <row r="21" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A21" s="95"/>
+      <c r="A21" s="100"/>
       <c r="B21" s="40"/>
-      <c r="C21" s="96"/>
+      <c r="C21" s="101"/>
       <c r="D21" s="40"/>
-      <c r="E21" s="96"/>
+      <c r="E21" s="101"/>
       <c r="F21" s="40"/>
-      <c r="G21" s="101"/>
+      <c r="G21" s="95"/>
       <c r="H21" s="39"/>
       <c r="I21" s="40"/>
-      <c r="J21" s="101"/>
+      <c r="J21" s="95"/>
       <c r="K21" s="40"/>
-      <c r="L21" s="99"/>
+      <c r="L21" s="97"/>
       <c r="M21" s="39"/>
       <c r="N21" s="40"/>
-      <c r="O21" s="99"/>
+      <c r="O21" s="97"/>
       <c r="P21" s="39"/>
       <c r="Q21" s="40"/>
       <c r="R21" s="33"/>
@@ -9351,21 +9351,21 @@
       <c r="Z21" s="35"/>
     </row>
     <row r="22" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A22" s="95"/>
+      <c r="A22" s="100"/>
       <c r="B22" s="40"/>
-      <c r="C22" s="96"/>
+      <c r="C22" s="101"/>
       <c r="D22" s="40"/>
-      <c r="E22" s="96"/>
+      <c r="E22" s="101"/>
       <c r="F22" s="40"/>
-      <c r="G22" s="101"/>
+      <c r="G22" s="95"/>
       <c r="H22" s="39"/>
       <c r="I22" s="40"/>
-      <c r="J22" s="101"/>
+      <c r="J22" s="95"/>
       <c r="K22" s="40"/>
-      <c r="L22" s="99"/>
+      <c r="L22" s="97"/>
       <c r="M22" s="39"/>
       <c r="N22" s="40"/>
-      <c r="O22" s="99"/>
+      <c r="O22" s="97"/>
       <c r="P22" s="39"/>
       <c r="Q22" s="40"/>
       <c r="R22" s="33"/>
@@ -9379,21 +9379,21 @@
       <c r="Z22" s="35"/>
     </row>
     <row r="23" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A23" s="95"/>
+      <c r="A23" s="100"/>
       <c r="B23" s="40"/>
-      <c r="C23" s="96"/>
+      <c r="C23" s="101"/>
       <c r="D23" s="40"/>
-      <c r="E23" s="96"/>
+      <c r="E23" s="101"/>
       <c r="F23" s="40"/>
-      <c r="G23" s="101"/>
+      <c r="G23" s="95"/>
       <c r="H23" s="39"/>
       <c r="I23" s="40"/>
-      <c r="J23" s="101"/>
+      <c r="J23" s="95"/>
       <c r="K23" s="40"/>
-      <c r="L23" s="99"/>
+      <c r="L23" s="97"/>
       <c r="M23" s="39"/>
       <c r="N23" s="40"/>
-      <c r="O23" s="99"/>
+      <c r="O23" s="97"/>
       <c r="P23" s="39"/>
       <c r="Q23" s="40"/>
       <c r="R23" s="33"/>
@@ -9407,21 +9407,21 @@
       <c r="Z23" s="35"/>
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A24" s="95"/>
+      <c r="A24" s="100"/>
       <c r="B24" s="40"/>
-      <c r="C24" s="96"/>
+      <c r="C24" s="101"/>
       <c r="D24" s="40"/>
-      <c r="E24" s="96"/>
+      <c r="E24" s="101"/>
       <c r="F24" s="40"/>
-      <c r="G24" s="101"/>
+      <c r="G24" s="95"/>
       <c r="H24" s="39"/>
       <c r="I24" s="40"/>
-      <c r="J24" s="101"/>
+      <c r="J24" s="95"/>
       <c r="K24" s="40"/>
-      <c r="L24" s="99"/>
+      <c r="L24" s="97"/>
       <c r="M24" s="39"/>
       <c r="N24" s="40"/>
-      <c r="O24" s="99"/>
+      <c r="O24" s="97"/>
       <c r="P24" s="39"/>
       <c r="Q24" s="40"/>
       <c r="R24" s="33"/>
@@ -9435,21 +9435,21 @@
       <c r="Z24" s="35"/>
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A25" s="95"/>
+      <c r="A25" s="100"/>
       <c r="B25" s="40"/>
-      <c r="C25" s="96"/>
+      <c r="C25" s="101"/>
       <c r="D25" s="40"/>
-      <c r="E25" s="96"/>
+      <c r="E25" s="101"/>
       <c r="F25" s="40"/>
-      <c r="G25" s="101"/>
+      <c r="G25" s="95"/>
       <c r="H25" s="39"/>
       <c r="I25" s="40"/>
-      <c r="J25" s="101"/>
+      <c r="J25" s="95"/>
       <c r="K25" s="40"/>
-      <c r="L25" s="99"/>
+      <c r="L25" s="97"/>
       <c r="M25" s="39"/>
       <c r="N25" s="40"/>
-      <c r="O25" s="99"/>
+      <c r="O25" s="97"/>
       <c r="P25" s="39"/>
       <c r="Q25" s="40"/>
       <c r="R25" s="33"/>
@@ -9463,21 +9463,21 @@
       <c r="Z25" s="35"/>
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A26" s="95"/>
+      <c r="A26" s="100"/>
       <c r="B26" s="40"/>
-      <c r="C26" s="96"/>
+      <c r="C26" s="101"/>
       <c r="D26" s="40"/>
-      <c r="E26" s="96"/>
+      <c r="E26" s="101"/>
       <c r="F26" s="40"/>
-      <c r="G26" s="101"/>
+      <c r="G26" s="95"/>
       <c r="H26" s="39"/>
       <c r="I26" s="40"/>
-      <c r="J26" s="101"/>
+      <c r="J26" s="95"/>
       <c r="K26" s="40"/>
-      <c r="L26" s="99"/>
+      <c r="L26" s="97"/>
       <c r="M26" s="39"/>
       <c r="N26" s="40"/>
-      <c r="O26" s="99"/>
+      <c r="O26" s="97"/>
       <c r="P26" s="39"/>
       <c r="Q26" s="40"/>
       <c r="R26" s="33"/>
@@ -9491,21 +9491,21 @@
       <c r="Z26" s="35"/>
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A27" s="95"/>
+      <c r="A27" s="100"/>
       <c r="B27" s="40"/>
-      <c r="C27" s="96"/>
+      <c r="C27" s="101"/>
       <c r="D27" s="40"/>
-      <c r="E27" s="96"/>
+      <c r="E27" s="101"/>
       <c r="F27" s="40"/>
-      <c r="G27" s="101"/>
+      <c r="G27" s="95"/>
       <c r="H27" s="39"/>
       <c r="I27" s="40"/>
-      <c r="J27" s="101"/>
+      <c r="J27" s="95"/>
       <c r="K27" s="40"/>
-      <c r="L27" s="99"/>
+      <c r="L27" s="97"/>
       <c r="M27" s="39"/>
       <c r="N27" s="40"/>
-      <c r="O27" s="99"/>
+      <c r="O27" s="97"/>
       <c r="P27" s="39"/>
       <c r="Q27" s="40"/>
       <c r="R27" s="33"/>
@@ -9519,21 +9519,21 @@
       <c r="Z27" s="35"/>
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A28" s="95"/>
+      <c r="A28" s="100"/>
       <c r="B28" s="40"/>
-      <c r="C28" s="96"/>
+      <c r="C28" s="101"/>
       <c r="D28" s="40"/>
-      <c r="E28" s="96"/>
+      <c r="E28" s="101"/>
       <c r="F28" s="40"/>
-      <c r="G28" s="101"/>
+      <c r="G28" s="95"/>
       <c r="H28" s="39"/>
       <c r="I28" s="40"/>
-      <c r="J28" s="101"/>
+      <c r="J28" s="95"/>
       <c r="K28" s="40"/>
-      <c r="L28" s="99"/>
+      <c r="L28" s="97"/>
       <c r="M28" s="39"/>
       <c r="N28" s="40"/>
-      <c r="O28" s="99"/>
+      <c r="O28" s="97"/>
       <c r="P28" s="39"/>
       <c r="Q28" s="40"/>
       <c r="R28" s="33"/>
@@ -9547,21 +9547,21 @@
       <c r="Z28" s="35"/>
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A29" s="95"/>
+      <c r="A29" s="100"/>
       <c r="B29" s="40"/>
-      <c r="C29" s="96"/>
+      <c r="C29" s="101"/>
       <c r="D29" s="40"/>
-      <c r="E29" s="96"/>
+      <c r="E29" s="101"/>
       <c r="F29" s="40"/>
-      <c r="G29" s="101"/>
+      <c r="G29" s="95"/>
       <c r="H29" s="39"/>
       <c r="I29" s="40"/>
-      <c r="J29" s="101"/>
+      <c r="J29" s="95"/>
       <c r="K29" s="40"/>
-      <c r="L29" s="99"/>
+      <c r="L29" s="97"/>
       <c r="M29" s="39"/>
       <c r="N29" s="40"/>
-      <c r="O29" s="99"/>
+      <c r="O29" s="97"/>
       <c r="P29" s="39"/>
       <c r="Q29" s="40"/>
       <c r="R29" s="33"/>
@@ -9575,21 +9575,21 @@
       <c r="Z29" s="35"/>
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A30" s="95"/>
+      <c r="A30" s="100"/>
       <c r="B30" s="40"/>
-      <c r="C30" s="96"/>
+      <c r="C30" s="101"/>
       <c r="D30" s="40"/>
-      <c r="E30" s="96"/>
+      <c r="E30" s="101"/>
       <c r="F30" s="40"/>
-      <c r="G30" s="101"/>
+      <c r="G30" s="95"/>
       <c r="H30" s="39"/>
       <c r="I30" s="40"/>
-      <c r="J30" s="101"/>
+      <c r="J30" s="95"/>
       <c r="K30" s="40"/>
-      <c r="L30" s="99"/>
+      <c r="L30" s="97"/>
       <c r="M30" s="39"/>
       <c r="N30" s="40"/>
-      <c r="O30" s="99"/>
+      <c r="O30" s="97"/>
       <c r="P30" s="39"/>
       <c r="Q30" s="40"/>
       <c r="R30" s="33"/>
@@ -9603,23 +9603,23 @@
       <c r="Z30" s="35"/>
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A31" s="97"/>
-      <c r="B31" s="56"/>
-      <c r="C31" s="98"/>
-      <c r="D31" s="56"/>
-      <c r="E31" s="98"/>
-      <c r="F31" s="56"/>
-      <c r="G31" s="104"/>
-      <c r="H31" s="47"/>
-      <c r="I31" s="56"/>
-      <c r="J31" s="104"/>
-      <c r="K31" s="56"/>
-      <c r="L31" s="100"/>
-      <c r="M31" s="47"/>
-      <c r="N31" s="56"/>
-      <c r="O31" s="100"/>
-      <c r="P31" s="47"/>
-      <c r="Q31" s="56"/>
+      <c r="A31" s="103"/>
+      <c r="B31" s="67"/>
+      <c r="C31" s="104"/>
+      <c r="D31" s="67"/>
+      <c r="E31" s="104"/>
+      <c r="F31" s="67"/>
+      <c r="G31" s="96"/>
+      <c r="H31" s="66"/>
+      <c r="I31" s="67"/>
+      <c r="J31" s="96"/>
+      <c r="K31" s="67"/>
+      <c r="L31" s="98"/>
+      <c r="M31" s="66"/>
+      <c r="N31" s="67"/>
+      <c r="O31" s="98"/>
+      <c r="P31" s="66"/>
+      <c r="Q31" s="67"/>
       <c r="R31" s="36"/>
       <c r="S31" s="36"/>
       <c r="T31" s="37"/>
@@ -10617,62 +10617,62 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="136">
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:K19"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="K2:N4"/>
-    <mergeCell ref="O2:P4"/>
-    <mergeCell ref="Q2:R4"/>
-    <mergeCell ref="S2:T4"/>
-    <mergeCell ref="A1:F4"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="O27:Q27"/>
+    <mergeCell ref="O28:Q28"/>
+    <mergeCell ref="O29:Q29"/>
+    <mergeCell ref="O30:Q30"/>
+    <mergeCell ref="O31:Q31"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="O26:Q26"/>
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="G5:T5"/>
     <mergeCell ref="A6:F6"/>
@@ -10697,62 +10697,62 @@
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="E15:F15"/>
     <mergeCell ref="A16:B16"/>
-    <mergeCell ref="O27:Q27"/>
-    <mergeCell ref="O28:Q28"/>
-    <mergeCell ref="O29:Q29"/>
-    <mergeCell ref="O30:Q30"/>
-    <mergeCell ref="O31:Q31"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="O26:Q26"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="K2:N4"/>
+    <mergeCell ref="O2:P4"/>
+    <mergeCell ref="Q2:R4"/>
+    <mergeCell ref="S2:T4"/>
+    <mergeCell ref="A1:F4"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:K19"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>

--- a/Documents/タスク詳細設計書.xlsx
+++ b/Documents/タスク詳細設計書.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\S-47\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\S-47\Documents\project\taskUN\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A3606C8-031A-4C21-B140-18ACA1DF21D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DE22809-A13D-4A26-B65C-069C1591D3BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8535" yWindow="555" windowWidth="11415" windowHeight="8955" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="91">
   <si>
     <t>プロジェクト型演習　成果ドキュメント</t>
   </si>
@@ -558,6 +558,50 @@
     </rPh>
     <phoneticPr fontId="8"/>
   </si>
+  <si>
+    <t>異常系</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>ログアウト状態でのページ表示</t>
+    <rPh sb="5" eb="7">
+      <t>ジョウタイ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>ログアウト状態であること</t>
+    <rPh sb="5" eb="7">
+      <t>ジョウタイ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>ログインされていませんというメッセージが表示され、その下にログイン画面へ誘導するリンクが表示される</t>
+    <rPh sb="20" eb="22">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>シタ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>ユウドウ</t>
+    </rPh>
+    <rPh sb="44" eb="46">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>http://localhost:8080/taskUN/task-detail.jsp</t>
+    <phoneticPr fontId="8"/>
+  </si>
 </sst>
 </file>
 
@@ -566,7 +610,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="[$-411]h:mm"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -636,6 +680,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -1312,11 +1364,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="109">
+  <cellXfs count="115">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1455,135 +1508,135 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1602,50 +1655,65 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="2" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="45" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="46" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
+    <cellStyle name="ハイパーリンク" xfId="2" builtinId="8"/>
     <cellStyle name="標準" xfId="0" builtinId="0"/>
     <cellStyle name="標準 2" xfId="1" xr:uid="{22DBA653-F2E1-482B-8564-0AB808DB1A6C}"/>
   </cellStyles>
@@ -3392,19 +3460,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="57" t="s">
+      <c r="A1" s="68" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="58"/>
-      <c r="C1" s="59"/>
-      <c r="D1" s="78" t="s">
+      <c r="B1" s="69"/>
+      <c r="C1" s="70"/>
+      <c r="D1" s="46" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="66"/>
-      <c r="F1" s="78" t="s">
+      <c r="E1" s="47"/>
+      <c r="F1" s="46" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="66"/>
+      <c r="G1" s="47"/>
       <c r="H1" s="5" t="s">
         <v>8</v>
       </c>
@@ -3416,72 +3484,72 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="60"/>
+      <c r="A2" s="71"/>
       <c r="B2" s="42"/>
-      <c r="C2" s="61"/>
-      <c r="D2" s="79" t="s">
+      <c r="C2" s="51"/>
+      <c r="D2" s="48" t="s">
         <v>56</v>
       </c>
-      <c r="E2" s="80"/>
-      <c r="F2" s="79" t="s">
+      <c r="E2" s="49"/>
+      <c r="F2" s="48" t="s">
         <v>57</v>
       </c>
-      <c r="G2" s="80"/>
-      <c r="H2" s="83">
+      <c r="G2" s="49"/>
+      <c r="H2" s="54">
         <v>45812</v>
       </c>
-      <c r="I2" s="72" t="s">
+      <c r="I2" s="57" t="s">
         <v>58</v>
       </c>
-      <c r="J2" s="75"/>
+      <c r="J2" s="58"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="60"/>
+      <c r="A3" s="71"/>
       <c r="B3" s="42"/>
-      <c r="C3" s="61"/>
-      <c r="D3" s="81"/>
-      <c r="E3" s="61"/>
-      <c r="F3" s="81"/>
-      <c r="G3" s="61"/>
-      <c r="H3" s="73"/>
-      <c r="I3" s="73"/>
-      <c r="J3" s="76"/>
+      <c r="C3" s="51"/>
+      <c r="D3" s="50"/>
+      <c r="E3" s="51"/>
+      <c r="F3" s="50"/>
+      <c r="G3" s="51"/>
+      <c r="H3" s="55"/>
+      <c r="I3" s="55"/>
+      <c r="J3" s="59"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="62"/>
-      <c r="B4" s="63"/>
-      <c r="C4" s="64"/>
-      <c r="D4" s="82"/>
-      <c r="E4" s="64"/>
-      <c r="F4" s="82"/>
-      <c r="G4" s="64"/>
-      <c r="H4" s="74"/>
-      <c r="I4" s="74"/>
-      <c r="J4" s="77"/>
+      <c r="A4" s="72"/>
+      <c r="B4" s="73"/>
+      <c r="C4" s="53"/>
+      <c r="D4" s="52"/>
+      <c r="E4" s="53"/>
+      <c r="F4" s="52"/>
+      <c r="G4" s="53"/>
+      <c r="H4" s="56"/>
+      <c r="I4" s="56"/>
+      <c r="J4" s="60"/>
     </row>
     <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="65" t="s">
+      <c r="A5" s="74" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="50"/>
-      <c r="C5" s="66"/>
-      <c r="D5" s="49" t="s">
+      <c r="B5" s="75"/>
+      <c r="C5" s="47"/>
+      <c r="D5" s="81" t="s">
         <v>59</v>
       </c>
-      <c r="E5" s="50"/>
-      <c r="F5" s="50"/>
-      <c r="G5" s="50"/>
-      <c r="H5" s="50"/>
-      <c r="I5" s="50"/>
-      <c r="J5" s="51"/>
+      <c r="E5" s="75"/>
+      <c r="F5" s="75"/>
+      <c r="G5" s="75"/>
+      <c r="H5" s="75"/>
+      <c r="I5" s="75"/>
+      <c r="J5" s="82"/>
     </row>
     <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="67" t="s">
+      <c r="A6" s="62" t="s">
         <v>12</v>
       </c>
       <c r="B6" s="39"/>
       <c r="C6" s="40"/>
-      <c r="D6" s="52" t="s">
+      <c r="D6" s="63" t="s">
         <v>60</v>
       </c>
       <c r="E6" s="39"/>
@@ -3489,15 +3557,15 @@
       <c r="G6" s="39"/>
       <c r="H6" s="39"/>
       <c r="I6" s="39"/>
-      <c r="J6" s="53"/>
+      <c r="J6" s="64"/>
     </row>
     <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="67" t="s">
+      <c r="A7" s="62" t="s">
         <v>13</v>
       </c>
       <c r="B7" s="39"/>
       <c r="C7" s="40"/>
-      <c r="D7" s="52" t="s">
+      <c r="D7" s="63" t="s">
         <v>61</v>
       </c>
       <c r="E7" s="39"/>
@@ -3505,15 +3573,15 @@
       <c r="G7" s="39"/>
       <c r="H7" s="39"/>
       <c r="I7" s="39"/>
-      <c r="J7" s="53"/>
+      <c r="J7" s="64"/>
     </row>
     <row r="8" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A8" s="67" t="s">
+      <c r="A8" s="62" t="s">
         <v>14</v>
       </c>
       <c r="B8" s="39"/>
       <c r="C8" s="40"/>
-      <c r="D8" s="52" t="s">
+      <c r="D8" s="63" t="s">
         <v>62</v>
       </c>
       <c r="E8" s="39"/>
@@ -3521,17 +3589,17 @@
       <c r="G8" s="39"/>
       <c r="H8" s="39"/>
       <c r="I8" s="39"/>
-      <c r="J8" s="53"/>
+      <c r="J8" s="64"/>
     </row>
     <row r="9" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A9" s="68" t="s">
+      <c r="A9" s="76" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="71" t="s">
+      <c r="B9" s="61" t="s">
         <v>16</v>
       </c>
       <c r="C9" s="40"/>
-      <c r="D9" s="54" t="s">
+      <c r="D9" s="83" t="s">
         <v>76</v>
       </c>
       <c r="E9" s="39"/>
@@ -3539,43 +3607,43 @@
       <c r="G9" s="39"/>
       <c r="H9" s="39"/>
       <c r="I9" s="39"/>
-      <c r="J9" s="53"/>
+      <c r="J9" s="64"/>
     </row>
     <row r="10" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A10" s="69"/>
-      <c r="B10" s="71" t="s">
+      <c r="A10" s="77"/>
+      <c r="B10" s="61" t="s">
         <v>17</v>
       </c>
       <c r="C10" s="40"/>
-      <c r="D10" s="52"/>
+      <c r="D10" s="63"/>
       <c r="E10" s="39"/>
       <c r="F10" s="39"/>
       <c r="G10" s="39"/>
       <c r="H10" s="39"/>
       <c r="I10" s="39"/>
-      <c r="J10" s="53"/>
+      <c r="J10" s="64"/>
     </row>
     <row r="11" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A11" s="70"/>
-      <c r="B11" s="71" t="s">
+      <c r="A11" s="78"/>
+      <c r="B11" s="61" t="s">
         <v>18</v>
       </c>
       <c r="C11" s="40"/>
-      <c r="D11" s="52"/>
+      <c r="D11" s="63"/>
       <c r="E11" s="39"/>
       <c r="F11" s="39"/>
       <c r="G11" s="39"/>
       <c r="H11" s="39"/>
       <c r="I11" s="39"/>
-      <c r="J11" s="53"/>
+      <c r="J11" s="64"/>
     </row>
     <row r="12" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A12" s="67" t="s">
+      <c r="A12" s="62" t="s">
         <v>19</v>
       </c>
       <c r="B12" s="39"/>
       <c r="C12" s="40"/>
-      <c r="D12" s="52" t="s">
+      <c r="D12" s="63" t="s">
         <v>63</v>
       </c>
       <c r="E12" s="39"/>
@@ -3583,21 +3651,21 @@
       <c r="G12" s="39"/>
       <c r="H12" s="39"/>
       <c r="I12" s="39"/>
-      <c r="J12" s="53"/>
+      <c r="J12" s="64"/>
     </row>
     <row r="13" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A13" s="55" t="s">
+      <c r="A13" s="65" t="s">
         <v>20</v>
       </c>
-      <c r="B13" s="47"/>
-      <c r="C13" s="56"/>
-      <c r="D13" s="46"/>
-      <c r="E13" s="47"/>
-      <c r="F13" s="47"/>
-      <c r="G13" s="47"/>
-      <c r="H13" s="47"/>
-      <c r="I13" s="47"/>
-      <c r="J13" s="48"/>
+      <c r="B13" s="66"/>
+      <c r="C13" s="67"/>
+      <c r="D13" s="79"/>
+      <c r="E13" s="66"/>
+      <c r="F13" s="66"/>
+      <c r="G13" s="66"/>
+      <c r="H13" s="66"/>
+      <c r="I13" s="66"/>
+      <c r="J13" s="80"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -4588,17 +4656,14 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="D12:J12"/>
+    <mergeCell ref="D13:J13"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="D6:J6"/>
+    <mergeCell ref="D7:J7"/>
+    <mergeCell ref="D8:J8"/>
+    <mergeCell ref="D9:J9"/>
+    <mergeCell ref="D10:J10"/>
+    <mergeCell ref="D11:J11"/>
     <mergeCell ref="A13:C13"/>
     <mergeCell ref="A1:C4"/>
     <mergeCell ref="A5:C5"/>
@@ -4607,14 +4672,17 @@
     <mergeCell ref="A8:C8"/>
     <mergeCell ref="A9:A11"/>
     <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D13:J13"/>
-    <mergeCell ref="D5:J5"/>
-    <mergeCell ref="D6:J6"/>
-    <mergeCell ref="D7:J7"/>
-    <mergeCell ref="D8:J8"/>
-    <mergeCell ref="D9:J9"/>
-    <mergeCell ref="D10:J10"/>
-    <mergeCell ref="D11:J11"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="D12:J12"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
@@ -4636,16 +4704,16 @@
       <c r="A1" s="84" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="58"/>
-      <c r="C1" s="59"/>
-      <c r="D1" s="78" t="s">
+      <c r="B1" s="69"/>
+      <c r="C1" s="70"/>
+      <c r="D1" s="46" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="66"/>
-      <c r="F1" s="78" t="s">
+      <c r="E1" s="47"/>
+      <c r="F1" s="46" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="66"/>
+      <c r="G1" s="47"/>
       <c r="H1" s="4" t="s">
         <v>8</v>
       </c>
@@ -4657,48 +4725,48 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="60"/>
+      <c r="A2" s="71"/>
       <c r="B2" s="42"/>
-      <c r="C2" s="61"/>
-      <c r="D2" s="79" t="s">
+      <c r="C2" s="51"/>
+      <c r="D2" s="48" t="s">
         <v>56</v>
       </c>
-      <c r="E2" s="80"/>
-      <c r="F2" s="79" t="s">
+      <c r="E2" s="49"/>
+      <c r="F2" s="48" t="s">
         <v>57</v>
       </c>
-      <c r="G2" s="80"/>
-      <c r="H2" s="83">
+      <c r="G2" s="49"/>
+      <c r="H2" s="54">
         <v>45810</v>
       </c>
-      <c r="I2" s="72" t="s">
+      <c r="I2" s="57" t="s">
         <v>64</v>
       </c>
-      <c r="J2" s="75"/>
+      <c r="J2" s="58"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="60"/>
+      <c r="A3" s="71"/>
       <c r="B3" s="42"/>
-      <c r="C3" s="61"/>
-      <c r="D3" s="81"/>
-      <c r="E3" s="61"/>
-      <c r="F3" s="81"/>
-      <c r="G3" s="61"/>
-      <c r="H3" s="73"/>
-      <c r="I3" s="73"/>
-      <c r="J3" s="76"/>
+      <c r="C3" s="51"/>
+      <c r="D3" s="50"/>
+      <c r="E3" s="51"/>
+      <c r="F3" s="50"/>
+      <c r="G3" s="51"/>
+      <c r="H3" s="55"/>
+      <c r="I3" s="55"/>
+      <c r="J3" s="59"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="62"/>
-      <c r="B4" s="63"/>
-      <c r="C4" s="64"/>
-      <c r="D4" s="82"/>
-      <c r="E4" s="64"/>
-      <c r="F4" s="82"/>
-      <c r="G4" s="64"/>
-      <c r="H4" s="74"/>
-      <c r="I4" s="74"/>
-      <c r="J4" s="77"/>
+      <c r="A4" s="72"/>
+      <c r="B4" s="73"/>
+      <c r="C4" s="53"/>
+      <c r="D4" s="52"/>
+      <c r="E4" s="53"/>
+      <c r="F4" s="52"/>
+      <c r="G4" s="53"/>
+      <c r="H4" s="56"/>
+      <c r="I4" s="56"/>
+      <c r="J4" s="60"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -6058,16 +6126,16 @@
       <c r="A1" s="84" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="58"/>
-      <c r="C1" s="59"/>
-      <c r="D1" s="78" t="s">
+      <c r="B1" s="69"/>
+      <c r="C1" s="70"/>
+      <c r="D1" s="46" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="66"/>
-      <c r="F1" s="78" t="s">
+      <c r="E1" s="47"/>
+      <c r="F1" s="46" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="66"/>
+      <c r="G1" s="47"/>
       <c r="H1" s="4" t="s">
         <v>8</v>
       </c>
@@ -6079,48 +6147,48 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="60"/>
+      <c r="A2" s="71"/>
       <c r="B2" s="42"/>
-      <c r="C2" s="61"/>
-      <c r="D2" s="79" t="s">
+      <c r="C2" s="51"/>
+      <c r="D2" s="48" t="s">
         <v>56</v>
       </c>
-      <c r="E2" s="80"/>
-      <c r="F2" s="79" t="s">
+      <c r="E2" s="49"/>
+      <c r="F2" s="48" t="s">
         <v>57</v>
       </c>
-      <c r="G2" s="80"/>
-      <c r="H2" s="83">
+      <c r="G2" s="49"/>
+      <c r="H2" s="54">
         <v>45810</v>
       </c>
-      <c r="I2" s="72" t="s">
+      <c r="I2" s="57" t="s">
         <v>64</v>
       </c>
-      <c r="J2" s="75"/>
+      <c r="J2" s="58"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="60"/>
+      <c r="A3" s="71"/>
       <c r="B3" s="42"/>
-      <c r="C3" s="61"/>
-      <c r="D3" s="81"/>
-      <c r="E3" s="61"/>
-      <c r="F3" s="81"/>
-      <c r="G3" s="61"/>
-      <c r="H3" s="73"/>
-      <c r="I3" s="73"/>
-      <c r="J3" s="76"/>
+      <c r="C3" s="51"/>
+      <c r="D3" s="50"/>
+      <c r="E3" s="51"/>
+      <c r="F3" s="50"/>
+      <c r="G3" s="51"/>
+      <c r="H3" s="55"/>
+      <c r="I3" s="55"/>
+      <c r="J3" s="59"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="62"/>
-      <c r="B4" s="63"/>
-      <c r="C4" s="64"/>
-      <c r="D4" s="82"/>
-      <c r="E4" s="64"/>
-      <c r="F4" s="82"/>
-      <c r="G4" s="64"/>
-      <c r="H4" s="74"/>
-      <c r="I4" s="74"/>
-      <c r="J4" s="77"/>
+      <c r="A4" s="72"/>
+      <c r="B4" s="73"/>
+      <c r="C4" s="53"/>
+      <c r="D4" s="52"/>
+      <c r="E4" s="53"/>
+      <c r="F4" s="52"/>
+      <c r="G4" s="53"/>
+      <c r="H4" s="56"/>
+      <c r="I4" s="56"/>
+      <c r="J4" s="60"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -7474,16 +7542,16 @@
       <c r="A1" s="84" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="58"/>
-      <c r="C1" s="59"/>
-      <c r="D1" s="78" t="s">
+      <c r="B1" s="69"/>
+      <c r="C1" s="70"/>
+      <c r="D1" s="46" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="66"/>
-      <c r="F1" s="78" t="s">
+      <c r="E1" s="47"/>
+      <c r="F1" s="46" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="66"/>
+      <c r="G1" s="47"/>
       <c r="H1" s="4" t="s">
         <v>8</v>
       </c>
@@ -7495,67 +7563,67 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="60"/>
+      <c r="A2" s="71"/>
       <c r="B2" s="42"/>
-      <c r="C2" s="61"/>
-      <c r="D2" s="79" t="s">
+      <c r="C2" s="51"/>
+      <c r="D2" s="48" t="s">
         <v>56</v>
       </c>
-      <c r="E2" s="80"/>
-      <c r="F2" s="79" t="s">
+      <c r="E2" s="49"/>
+      <c r="F2" s="48" t="s">
         <v>57</v>
       </c>
-      <c r="G2" s="80"/>
-      <c r="H2" s="83">
+      <c r="G2" s="49"/>
+      <c r="H2" s="54">
         <v>45810</v>
       </c>
-      <c r="I2" s="72" t="s">
+      <c r="I2" s="57" t="s">
         <v>64</v>
       </c>
-      <c r="J2" s="75"/>
+      <c r="J2" s="58"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="60"/>
+      <c r="A3" s="71"/>
       <c r="B3" s="42"/>
-      <c r="C3" s="61"/>
-      <c r="D3" s="81"/>
-      <c r="E3" s="61"/>
-      <c r="F3" s="81"/>
-      <c r="G3" s="61"/>
-      <c r="H3" s="73"/>
-      <c r="I3" s="73"/>
-      <c r="J3" s="76"/>
+      <c r="C3" s="51"/>
+      <c r="D3" s="50"/>
+      <c r="E3" s="51"/>
+      <c r="F3" s="50"/>
+      <c r="G3" s="51"/>
+      <c r="H3" s="55"/>
+      <c r="I3" s="55"/>
+      <c r="J3" s="59"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="60"/>
+      <c r="A4" s="71"/>
       <c r="B4" s="42"/>
-      <c r="C4" s="61"/>
-      <c r="D4" s="81"/>
-      <c r="E4" s="61"/>
-      <c r="F4" s="81"/>
-      <c r="G4" s="61"/>
-      <c r="H4" s="73"/>
-      <c r="I4" s="73"/>
-      <c r="J4" s="76"/>
+      <c r="C4" s="51"/>
+      <c r="D4" s="50"/>
+      <c r="E4" s="51"/>
+      <c r="F4" s="50"/>
+      <c r="G4" s="51"/>
+      <c r="H4" s="55"/>
+      <c r="I4" s="55"/>
+      <c r="J4" s="59"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="86" t="s">
+      <c r="A5" s="85" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="50"/>
-      <c r="C5" s="66"/>
+      <c r="B5" s="75"/>
+      <c r="C5" s="47"/>
       <c r="D5" s="89" t="s">
         <v>65</v>
       </c>
-      <c r="E5" s="50"/>
-      <c r="F5" s="50"/>
-      <c r="G5" s="50"/>
-      <c r="H5" s="50"/>
-      <c r="I5" s="50"/>
-      <c r="J5" s="51"/>
+      <c r="E5" s="75"/>
+      <c r="F5" s="75"/>
+      <c r="G5" s="75"/>
+      <c r="H5" s="75"/>
+      <c r="I5" s="75"/>
+      <c r="J5" s="82"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="88" t="s">
+      <c r="A6" s="87" t="s">
         <v>25</v>
       </c>
       <c r="B6" s="39"/>
@@ -7566,7 +7634,7 @@
       <c r="G6" s="39"/>
       <c r="H6" s="39"/>
       <c r="I6" s="39"/>
-      <c r="J6" s="53"/>
+      <c r="J6" s="64"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
       <c r="A7" s="90"/>
@@ -7581,7 +7649,7 @@
       <c r="J7" s="92"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="60"/>
+      <c r="A8" s="71"/>
       <c r="B8" s="42"/>
       <c r="C8" s="42"/>
       <c r="D8" s="42"/>
@@ -7593,7 +7661,7 @@
       <c r="J8" s="93"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="60"/>
+      <c r="A9" s="71"/>
       <c r="B9" s="42"/>
       <c r="C9" s="42"/>
       <c r="D9" s="42"/>
@@ -7605,7 +7673,7 @@
       <c r="J9" s="93"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="60"/>
+      <c r="A10" s="71"/>
       <c r="B10" s="42"/>
       <c r="C10" s="42"/>
       <c r="D10" s="42"/>
@@ -7617,7 +7685,7 @@
       <c r="J10" s="93"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="60"/>
+      <c r="A11" s="71"/>
       <c r="B11" s="42"/>
       <c r="C11" s="42"/>
       <c r="D11" s="42"/>
@@ -7629,7 +7697,7 @@
       <c r="J11" s="93"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="60"/>
+      <c r="A12" s="71"/>
       <c r="B12" s="42"/>
       <c r="C12" s="42"/>
       <c r="D12" s="42"/>
@@ -7641,7 +7709,7 @@
       <c r="J12" s="93"/>
     </row>
     <row r="13" spans="1:10" ht="62.25" customHeight="1">
-      <c r="A13" s="60"/>
+      <c r="A13" s="71"/>
       <c r="B13" s="42"/>
       <c r="C13" s="42"/>
       <c r="D13" s="42"/>
@@ -7653,7 +7721,7 @@
       <c r="J13" s="93"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="88" t="s">
+      <c r="A14" s="87" t="s">
         <v>26</v>
       </c>
       <c r="B14" s="39"/>
@@ -7664,15 +7732,15 @@
       <c r="G14" s="39"/>
       <c r="H14" s="39"/>
       <c r="I14" s="39"/>
-      <c r="J14" s="53"/>
+      <c r="J14" s="64"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="88" t="s">
+      <c r="A15" s="87" t="s">
         <v>27</v>
       </c>
       <c r="B15" s="39"/>
       <c r="C15" s="40"/>
-      <c r="D15" s="52" t="s">
+      <c r="D15" s="63" t="s">
         <v>74</v>
       </c>
       <c r="E15" s="39"/>
@@ -7687,7 +7755,7 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="88" t="s">
+      <c r="A16" s="87" t="s">
         <v>29</v>
       </c>
       <c r="B16" s="39"/>
@@ -7708,10 +7776,10 @@
         <v>20</v>
       </c>
       <c r="I16" s="39"/>
-      <c r="J16" s="53"/>
+      <c r="J16" s="64"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="85">
+      <c r="A17" s="88">
         <v>1</v>
       </c>
       <c r="B17" s="39"/>
@@ -7726,14 +7794,14 @@
       <c r="G17" s="18" t="s">
         <v>71</v>
       </c>
-      <c r="H17" s="52" t="s">
+      <c r="H17" s="63" t="s">
         <v>75</v>
       </c>
       <c r="I17" s="39"/>
-      <c r="J17" s="53"/>
+      <c r="J17" s="64"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="85">
+      <c r="A18" s="88">
         <v>2</v>
       </c>
       <c r="B18" s="39"/>
@@ -7748,14 +7816,14 @@
       <c r="G18" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="H18" s="52" t="s">
+      <c r="H18" s="63" t="s">
         <v>75</v>
       </c>
       <c r="I18" s="39"/>
-      <c r="J18" s="53"/>
+      <c r="J18" s="64"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="85">
+      <c r="A19" s="88">
         <v>3</v>
       </c>
       <c r="B19" s="39"/>
@@ -7770,59 +7838,59 @@
       <c r="G19" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="H19" s="52" t="s">
+      <c r="H19" s="63" t="s">
         <v>75</v>
       </c>
       <c r="I19" s="39"/>
-      <c r="J19" s="53"/>
+      <c r="J19" s="64"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="85"/>
+      <c r="A20" s="88"/>
       <c r="B20" s="39"/>
       <c r="C20" s="40"/>
       <c r="D20" s="17"/>
       <c r="E20" s="17"/>
       <c r="F20" s="18"/>
       <c r="G20" s="18"/>
-      <c r="H20" s="52"/>
+      <c r="H20" s="63"/>
       <c r="I20" s="39"/>
-      <c r="J20" s="53"/>
+      <c r="J20" s="64"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="85"/>
+      <c r="A21" s="88"/>
       <c r="B21" s="39"/>
       <c r="C21" s="40"/>
       <c r="D21" s="17"/>
       <c r="E21" s="17"/>
       <c r="F21" s="18"/>
       <c r="G21" s="18"/>
-      <c r="H21" s="52"/>
+      <c r="H21" s="63"/>
       <c r="I21" s="39"/>
-      <c r="J21" s="53"/>
+      <c r="J21" s="64"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="85"/>
+      <c r="A22" s="88"/>
       <c r="B22" s="39"/>
       <c r="C22" s="40"/>
       <c r="D22" s="17"/>
       <c r="E22" s="17"/>
       <c r="F22" s="18"/>
       <c r="G22" s="18"/>
-      <c r="H22" s="52"/>
+      <c r="H22" s="63"/>
       <c r="I22" s="39"/>
-      <c r="J22" s="53"/>
+      <c r="J22" s="64"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A23" s="87"/>
-      <c r="B23" s="47"/>
-      <c r="C23" s="56"/>
+      <c r="A23" s="86"/>
+      <c r="B23" s="66"/>
+      <c r="C23" s="67"/>
       <c r="D23" s="19"/>
       <c r="E23" s="19"/>
       <c r="F23" s="20"/>
       <c r="G23" s="20"/>
-      <c r="H23" s="46"/>
-      <c r="I23" s="47"/>
-      <c r="J23" s="48"/>
+      <c r="H23" s="79"/>
+      <c r="I23" s="66"/>
+      <c r="J23" s="80"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
@@ -8803,11 +8871,16 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A22:C22"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="F1:G1"/>
@@ -8824,16 +8897,11 @@
     <mergeCell ref="H17:J17"/>
     <mergeCell ref="D2:E4"/>
     <mergeCell ref="H23:J23"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A1:C4"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -8853,141 +8921,141 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="57" t="s">
+      <c r="A1" s="68" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="58"/>
-      <c r="C1" s="58"/>
-      <c r="D1" s="58"/>
-      <c r="E1" s="58"/>
-      <c r="F1" s="59"/>
-      <c r="G1" s="78" t="s">
+      <c r="B1" s="69"/>
+      <c r="C1" s="69"/>
+      <c r="D1" s="69"/>
+      <c r="E1" s="69"/>
+      <c r="F1" s="70"/>
+      <c r="G1" s="46" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="50"/>
-      <c r="I1" s="50"/>
-      <c r="J1" s="66"/>
-      <c r="K1" s="78" t="s">
+      <c r="H1" s="75"/>
+      <c r="I1" s="75"/>
+      <c r="J1" s="47"/>
+      <c r="K1" s="46" t="s">
         <v>7</v>
       </c>
-      <c r="L1" s="50"/>
-      <c r="M1" s="50"/>
-      <c r="N1" s="66"/>
-      <c r="O1" s="78" t="s">
+      <c r="L1" s="75"/>
+      <c r="M1" s="75"/>
+      <c r="N1" s="47"/>
+      <c r="O1" s="46" t="s">
         <v>8</v>
       </c>
-      <c r="P1" s="66"/>
-      <c r="Q1" s="78" t="s">
+      <c r="P1" s="47"/>
+      <c r="Q1" s="46" t="s">
         <v>9</v>
       </c>
-      <c r="R1" s="66"/>
-      <c r="S1" s="78" t="s">
+      <c r="R1" s="47"/>
+      <c r="S1" s="46" t="s">
         <v>10</v>
       </c>
-      <c r="T1" s="51"/>
+      <c r="T1" s="82"/>
     </row>
     <row r="2" spans="1:26" ht="18" customHeight="1">
-      <c r="A2" s="60"/>
+      <c r="A2" s="71"/>
       <c r="B2" s="42"/>
       <c r="C2" s="42"/>
       <c r="D2" s="42"/>
       <c r="E2" s="42"/>
-      <c r="F2" s="61"/>
-      <c r="G2" s="79" t="s">
+      <c r="F2" s="51"/>
+      <c r="G2" s="48" t="s">
         <v>56</v>
       </c>
       <c r="H2" s="91"/>
       <c r="I2" s="91"/>
-      <c r="J2" s="80"/>
-      <c r="K2" s="79" t="s">
+      <c r="J2" s="49"/>
+      <c r="K2" s="48" t="s">
         <v>57</v>
       </c>
       <c r="L2" s="91"/>
       <c r="M2" s="91"/>
-      <c r="N2" s="80"/>
-      <c r="O2" s="105">
+      <c r="N2" s="49"/>
+      <c r="O2" s="102">
         <v>45818</v>
       </c>
-      <c r="P2" s="80"/>
-      <c r="Q2" s="79" t="s">
+      <c r="P2" s="49"/>
+      <c r="Q2" s="48" t="s">
         <v>64</v>
       </c>
-      <c r="R2" s="80"/>
-      <c r="S2" s="79"/>
+      <c r="R2" s="49"/>
+      <c r="S2" s="48"/>
       <c r="T2" s="92"/>
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
-      <c r="A3" s="60"/>
+      <c r="A3" s="71"/>
       <c r="B3" s="42"/>
       <c r="C3" s="42"/>
       <c r="D3" s="42"/>
       <c r="E3" s="42"/>
-      <c r="F3" s="61"/>
-      <c r="G3" s="81"/>
+      <c r="F3" s="51"/>
+      <c r="G3" s="50"/>
       <c r="H3" s="42"/>
       <c r="I3" s="42"/>
-      <c r="J3" s="61"/>
-      <c r="K3" s="81"/>
+      <c r="J3" s="51"/>
+      <c r="K3" s="50"/>
       <c r="L3" s="42"/>
       <c r="M3" s="42"/>
-      <c r="N3" s="61"/>
-      <c r="O3" s="81"/>
-      <c r="P3" s="61"/>
-      <c r="Q3" s="81"/>
-      <c r="R3" s="61"/>
-      <c r="S3" s="81"/>
+      <c r="N3" s="51"/>
+      <c r="O3" s="50"/>
+      <c r="P3" s="51"/>
+      <c r="Q3" s="50"/>
+      <c r="R3" s="51"/>
+      <c r="S3" s="50"/>
       <c r="T3" s="93"/>
     </row>
     <row r="4" spans="1:26" ht="18" customHeight="1">
-      <c r="A4" s="62"/>
-      <c r="B4" s="63"/>
-      <c r="C4" s="63"/>
-      <c r="D4" s="63"/>
-      <c r="E4" s="63"/>
-      <c r="F4" s="64"/>
-      <c r="G4" s="82"/>
-      <c r="H4" s="63"/>
-      <c r="I4" s="63"/>
-      <c r="J4" s="64"/>
-      <c r="K4" s="82"/>
-      <c r="L4" s="63"/>
-      <c r="M4" s="63"/>
-      <c r="N4" s="64"/>
-      <c r="O4" s="82"/>
-      <c r="P4" s="64"/>
-      <c r="Q4" s="82"/>
-      <c r="R4" s="64"/>
-      <c r="S4" s="82"/>
+      <c r="A4" s="72"/>
+      <c r="B4" s="73"/>
+      <c r="C4" s="73"/>
+      <c r="D4" s="73"/>
+      <c r="E4" s="73"/>
+      <c r="F4" s="53"/>
+      <c r="G4" s="52"/>
+      <c r="H4" s="73"/>
+      <c r="I4" s="73"/>
+      <c r="J4" s="53"/>
+      <c r="K4" s="52"/>
+      <c r="L4" s="73"/>
+      <c r="M4" s="73"/>
+      <c r="N4" s="53"/>
+      <c r="O4" s="52"/>
+      <c r="P4" s="53"/>
+      <c r="Q4" s="52"/>
+      <c r="R4" s="53"/>
+      <c r="S4" s="52"/>
       <c r="T4" s="103"/>
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="86" t="s">
+      <c r="A5" s="85" t="s">
         <v>35</v>
       </c>
-      <c r="B5" s="50"/>
-      <c r="C5" s="50"/>
-      <c r="D5" s="50"/>
-      <c r="E5" s="50"/>
-      <c r="F5" s="66"/>
-      <c r="G5" s="49" t="s">
+      <c r="B5" s="75"/>
+      <c r="C5" s="75"/>
+      <c r="D5" s="75"/>
+      <c r="E5" s="75"/>
+      <c r="F5" s="47"/>
+      <c r="G5" s="81" t="s">
         <v>36</v>
       </c>
-      <c r="H5" s="50"/>
-      <c r="I5" s="50"/>
-      <c r="J5" s="50"/>
-      <c r="K5" s="50"/>
-      <c r="L5" s="50"/>
-      <c r="M5" s="50"/>
-      <c r="N5" s="50"/>
-      <c r="O5" s="50"/>
-      <c r="P5" s="50"/>
-      <c r="Q5" s="50"/>
-      <c r="R5" s="50"/>
-      <c r="S5" s="50"/>
-      <c r="T5" s="51"/>
+      <c r="H5" s="75"/>
+      <c r="I5" s="75"/>
+      <c r="J5" s="75"/>
+      <c r="K5" s="75"/>
+      <c r="L5" s="75"/>
+      <c r="M5" s="75"/>
+      <c r="N5" s="75"/>
+      <c r="O5" s="75"/>
+      <c r="P5" s="75"/>
+      <c r="Q5" s="75"/>
+      <c r="R5" s="75"/>
+      <c r="S5" s="75"/>
+      <c r="T5" s="82"/>
     </row>
     <row r="6" spans="1:26" ht="18" customHeight="1">
-      <c r="A6" s="88" t="s">
+      <c r="A6" s="87" t="s">
         <v>37</v>
       </c>
       <c r="B6" s="39"/>
@@ -8995,7 +9063,7 @@
       <c r="D6" s="39"/>
       <c r="E6" s="39"/>
       <c r="F6" s="40"/>
-      <c r="G6" s="52" t="s">
+      <c r="G6" s="63" t="s">
         <v>21</v>
       </c>
       <c r="H6" s="39"/>
@@ -9010,10 +9078,10 @@
       <c r="Q6" s="39"/>
       <c r="R6" s="39"/>
       <c r="S6" s="39"/>
-      <c r="T6" s="53"/>
+      <c r="T6" s="64"/>
     </row>
     <row r="7" spans="1:26" ht="18" customHeight="1">
-      <c r="A7" s="88" t="s">
+      <c r="A7" s="87" t="s">
         <v>38</v>
       </c>
       <c r="B7" s="39"/>
@@ -9021,7 +9089,7 @@
       <c r="D7" s="39"/>
       <c r="E7" s="39"/>
       <c r="F7" s="40"/>
-      <c r="G7" s="52" t="s">
+      <c r="G7" s="63" t="s">
         <v>59</v>
       </c>
       <c r="H7" s="39"/>
@@ -9036,7 +9104,7 @@
       <c r="Q7" s="39"/>
       <c r="R7" s="39"/>
       <c r="S7" s="39"/>
-      <c r="T7" s="53"/>
+      <c r="T7" s="64"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
       <c r="A8" s="8"/>
@@ -9235,11 +9303,11 @@
       <c r="T14" s="10"/>
     </row>
     <row r="15" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A15" s="88" t="s">
+      <c r="A15" s="87" t="s">
         <v>45</v>
       </c>
       <c r="B15" s="40"/>
-      <c r="C15" s="102" t="s">
+      <c r="C15" s="106" t="s">
         <v>39</v>
       </c>
       <c r="D15" s="40"/>
@@ -9277,33 +9345,33 @@
       </c>
     </row>
     <row r="16" spans="1:26" ht="48" customHeight="1">
-      <c r="A16" s="95">
+      <c r="A16" s="104">
         <v>1</v>
       </c>
       <c r="B16" s="40"/>
-      <c r="C16" s="96" t="s">
+      <c r="C16" s="105" t="s">
         <v>54</v>
       </c>
       <c r="D16" s="40"/>
-      <c r="E16" s="96" t="s">
+      <c r="E16" s="105" t="s">
         <v>55</v>
       </c>
       <c r="F16" s="40"/>
-      <c r="G16" s="101" t="s">
+      <c r="G16" s="95" t="s">
         <v>77</v>
       </c>
       <c r="H16" s="39"/>
       <c r="I16" s="40"/>
-      <c r="J16" s="106" t="s">
+      <c r="J16" s="96" t="s">
         <v>78</v>
       </c>
-      <c r="K16" s="107"/>
-      <c r="L16" s="99" t="s">
+      <c r="K16" s="97"/>
+      <c r="L16" s="100" t="s">
         <v>79</v>
       </c>
       <c r="M16" s="39"/>
       <c r="N16" s="40"/>
-      <c r="O16" s="99" t="s">
+      <c r="O16" s="100" t="s">
         <v>80</v>
       </c>
       <c r="P16" s="39"/>
@@ -9319,33 +9387,33 @@
       <c r="Z16" s="35"/>
     </row>
     <row r="17" spans="1:26" ht="51" customHeight="1">
-      <c r="A17" s="95">
+      <c r="A17" s="104">
         <v>2</v>
       </c>
       <c r="B17" s="40"/>
-      <c r="C17" s="96" t="s">
+      <c r="C17" s="105" t="s">
         <v>54</v>
       </c>
       <c r="D17" s="40"/>
-      <c r="E17" s="96" t="s">
+      <c r="E17" s="105" t="s">
         <v>55</v>
       </c>
       <c r="F17" s="40"/>
-      <c r="G17" s="106" t="s">
+      <c r="G17" s="96" t="s">
         <v>81</v>
       </c>
-      <c r="H17" s="108"/>
-      <c r="I17" s="107"/>
-      <c r="J17" s="106" t="s">
+      <c r="H17" s="98"/>
+      <c r="I17" s="97"/>
+      <c r="J17" s="96" t="s">
         <v>78</v>
       </c>
-      <c r="K17" s="107"/>
-      <c r="L17" s="99" t="s">
+      <c r="K17" s="97"/>
+      <c r="L17" s="100" t="s">
         <v>79</v>
       </c>
       <c r="M17" s="39"/>
       <c r="N17" s="40"/>
-      <c r="O17" s="99" t="s">
+      <c r="O17" s="100" t="s">
         <v>82</v>
       </c>
       <c r="P17" s="39"/>
@@ -9361,29 +9429,29 @@
       <c r="Z17" s="35"/>
     </row>
     <row r="18" spans="1:26" ht="59.25" customHeight="1">
-      <c r="A18" s="95">
+      <c r="A18" s="104">
         <v>3</v>
       </c>
       <c r="B18" s="40"/>
-      <c r="C18" s="96" t="s">
+      <c r="C18" s="105" t="s">
         <v>54</v>
       </c>
       <c r="D18" s="40"/>
-      <c r="E18" s="96" t="s">
+      <c r="E18" s="105" t="s">
         <v>55</v>
       </c>
       <c r="F18" s="40"/>
-      <c r="G18" s="101" t="s">
+      <c r="G18" s="95" t="s">
         <v>83</v>
       </c>
       <c r="H18" s="39"/>
       <c r="I18" s="40"/>
-      <c r="J18" s="101"/>
+      <c r="J18" s="95"/>
       <c r="K18" s="40"/>
-      <c r="L18" s="99"/>
+      <c r="L18" s="100"/>
       <c r="M18" s="39"/>
       <c r="N18" s="40"/>
-      <c r="O18" s="99"/>
+      <c r="O18" s="100"/>
       <c r="P18" s="39"/>
       <c r="Q18" s="40"/>
       <c r="R18" s="33"/>
@@ -9397,29 +9465,29 @@
       <c r="Z18" s="35"/>
     </row>
     <row r="19" spans="1:26" ht="51.75" customHeight="1">
-      <c r="A19" s="95">
+      <c r="A19" s="104">
         <v>4</v>
       </c>
       <c r="B19" s="40"/>
-      <c r="C19" s="96" t="s">
+      <c r="C19" s="105" t="s">
         <v>54</v>
       </c>
       <c r="D19" s="40"/>
-      <c r="E19" s="96" t="s">
+      <c r="E19" s="105" t="s">
         <v>55</v>
       </c>
       <c r="F19" s="40"/>
-      <c r="G19" s="101" t="s">
+      <c r="G19" s="95" t="s">
         <v>84</v>
       </c>
       <c r="H19" s="39"/>
       <c r="I19" s="40"/>
-      <c r="J19" s="101"/>
+      <c r="J19" s="95"/>
       <c r="K19" s="40"/>
-      <c r="L19" s="99"/>
+      <c r="L19" s="100"/>
       <c r="M19" s="39"/>
       <c r="N19" s="40"/>
-      <c r="O19" s="99"/>
+      <c r="O19" s="100"/>
       <c r="P19" s="39"/>
       <c r="Q19" s="40"/>
       <c r="R19" s="33"/>
@@ -9433,29 +9501,29 @@
       <c r="Z19" s="35"/>
     </row>
     <row r="20" spans="1:26" ht="54" customHeight="1">
-      <c r="A20" s="95">
+      <c r="A20" s="104">
         <v>5</v>
       </c>
       <c r="B20" s="40"/>
-      <c r="C20" s="96" t="s">
+      <c r="C20" s="105" t="s">
         <v>54</v>
       </c>
       <c r="D20" s="40"/>
-      <c r="E20" s="96" t="s">
+      <c r="E20" s="105" t="s">
         <v>55</v>
       </c>
       <c r="F20" s="40"/>
-      <c r="G20" s="101" t="s">
+      <c r="G20" s="95" t="s">
         <v>85</v>
       </c>
       <c r="H20" s="39"/>
       <c r="I20" s="40"/>
-      <c r="J20" s="101"/>
+      <c r="J20" s="95"/>
       <c r="K20" s="40"/>
-      <c r="L20" s="99"/>
+      <c r="L20" s="100"/>
       <c r="M20" s="39"/>
       <c r="N20" s="40"/>
-      <c r="O20" s="99"/>
+      <c r="O20" s="100"/>
       <c r="P20" s="39"/>
       <c r="Q20" s="40"/>
       <c r="R20" s="33"/>
@@ -9468,27 +9536,41 @@
       <c r="Y20" s="35"/>
       <c r="Z20" s="35"/>
     </row>
-    <row r="21" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A21" s="95"/>
-      <c r="B21" s="40"/>
-      <c r="C21" s="96"/>
-      <c r="D21" s="40"/>
-      <c r="E21" s="96"/>
-      <c r="F21" s="40"/>
-      <c r="G21" s="101"/>
-      <c r="H21" s="39"/>
-      <c r="I21" s="40"/>
-      <c r="J21" s="101"/>
-      <c r="K21" s="40"/>
-      <c r="L21" s="99"/>
-      <c r="M21" s="39"/>
-      <c r="N21" s="40"/>
-      <c r="O21" s="99"/>
+    <row r="21" spans="1:26" ht="53.25" customHeight="1">
+      <c r="A21" s="109">
+        <v>7</v>
+      </c>
+      <c r="B21" s="97"/>
+      <c r="C21" s="110" t="s">
+        <v>54</v>
+      </c>
+      <c r="D21" s="97"/>
+      <c r="E21" s="110" t="s">
+        <v>86</v>
+      </c>
+      <c r="F21" s="97"/>
+      <c r="G21" s="96" t="s">
+        <v>87</v>
+      </c>
+      <c r="H21" s="98"/>
+      <c r="I21" s="97"/>
+      <c r="J21" s="96" t="s">
+        <v>88</v>
+      </c>
+      <c r="K21" s="97"/>
+      <c r="L21" s="111" t="s">
+        <v>90</v>
+      </c>
+      <c r="M21" s="112"/>
+      <c r="N21" s="112"/>
+      <c r="O21" s="100" t="s">
+        <v>89</v>
+      </c>
       <c r="P21" s="39"/>
       <c r="Q21" s="40"/>
-      <c r="R21" s="33"/>
-      <c r="S21" s="33"/>
-      <c r="T21" s="34"/>
+      <c r="R21" s="113"/>
+      <c r="S21" s="113"/>
+      <c r="T21" s="114"/>
       <c r="U21" s="35"/>
       <c r="V21" s="35"/>
       <c r="W21" s="35"/>
@@ -9497,21 +9579,21 @@
       <c r="Z21" s="35"/>
     </row>
     <row r="22" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A22" s="95"/>
+      <c r="A22" s="104"/>
       <c r="B22" s="40"/>
-      <c r="C22" s="96"/>
+      <c r="C22" s="105"/>
       <c r="D22" s="40"/>
-      <c r="E22" s="96"/>
+      <c r="E22" s="105"/>
       <c r="F22" s="40"/>
-      <c r="G22" s="101"/>
+      <c r="G22" s="95"/>
       <c r="H22" s="39"/>
       <c r="I22" s="40"/>
-      <c r="J22" s="101"/>
+      <c r="J22" s="95"/>
       <c r="K22" s="40"/>
-      <c r="L22" s="99"/>
+      <c r="L22" s="100"/>
       <c r="M22" s="39"/>
       <c r="N22" s="40"/>
-      <c r="O22" s="99"/>
+      <c r="O22" s="100"/>
       <c r="P22" s="39"/>
       <c r="Q22" s="40"/>
       <c r="R22" s="33"/>
@@ -9525,21 +9607,21 @@
       <c r="Z22" s="35"/>
     </row>
     <row r="23" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A23" s="95"/>
+      <c r="A23" s="104"/>
       <c r="B23" s="40"/>
-      <c r="C23" s="96"/>
+      <c r="C23" s="105"/>
       <c r="D23" s="40"/>
-      <c r="E23" s="96"/>
+      <c r="E23" s="105"/>
       <c r="F23" s="40"/>
-      <c r="G23" s="101"/>
+      <c r="G23" s="95"/>
       <c r="H23" s="39"/>
       <c r="I23" s="40"/>
-      <c r="J23" s="101"/>
+      <c r="J23" s="95"/>
       <c r="K23" s="40"/>
-      <c r="L23" s="99"/>
+      <c r="L23" s="100"/>
       <c r="M23" s="39"/>
       <c r="N23" s="40"/>
-      <c r="O23" s="99"/>
+      <c r="O23" s="100"/>
       <c r="P23" s="39"/>
       <c r="Q23" s="40"/>
       <c r="R23" s="33"/>
@@ -9553,21 +9635,21 @@
       <c r="Z23" s="35"/>
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A24" s="95"/>
+      <c r="A24" s="104"/>
       <c r="B24" s="40"/>
-      <c r="C24" s="96"/>
+      <c r="C24" s="105"/>
       <c r="D24" s="40"/>
-      <c r="E24" s="96"/>
+      <c r="E24" s="105"/>
       <c r="F24" s="40"/>
-      <c r="G24" s="101"/>
+      <c r="G24" s="95"/>
       <c r="H24" s="39"/>
       <c r="I24" s="40"/>
-      <c r="J24" s="101"/>
+      <c r="J24" s="95"/>
       <c r="K24" s="40"/>
-      <c r="L24" s="99"/>
+      <c r="L24" s="100"/>
       <c r="M24" s="39"/>
       <c r="N24" s="40"/>
-      <c r="O24" s="99"/>
+      <c r="O24" s="100"/>
       <c r="P24" s="39"/>
       <c r="Q24" s="40"/>
       <c r="R24" s="33"/>
@@ -9581,21 +9663,21 @@
       <c r="Z24" s="35"/>
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A25" s="95"/>
+      <c r="A25" s="104"/>
       <c r="B25" s="40"/>
-      <c r="C25" s="96"/>
+      <c r="C25" s="105"/>
       <c r="D25" s="40"/>
-      <c r="E25" s="96"/>
+      <c r="E25" s="105"/>
       <c r="F25" s="40"/>
-      <c r="G25" s="101"/>
+      <c r="G25" s="95"/>
       <c r="H25" s="39"/>
       <c r="I25" s="40"/>
-      <c r="J25" s="101"/>
+      <c r="J25" s="95"/>
       <c r="K25" s="40"/>
-      <c r="L25" s="99"/>
+      <c r="L25" s="100"/>
       <c r="M25" s="39"/>
       <c r="N25" s="40"/>
-      <c r="O25" s="99"/>
+      <c r="O25" s="100"/>
       <c r="P25" s="39"/>
       <c r="Q25" s="40"/>
       <c r="R25" s="33"/>
@@ -9609,21 +9691,21 @@
       <c r="Z25" s="35"/>
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A26" s="95"/>
+      <c r="A26" s="104"/>
       <c r="B26" s="40"/>
-      <c r="C26" s="96"/>
+      <c r="C26" s="105"/>
       <c r="D26" s="40"/>
-      <c r="E26" s="96"/>
+      <c r="E26" s="105"/>
       <c r="F26" s="40"/>
-      <c r="G26" s="101"/>
+      <c r="G26" s="95"/>
       <c r="H26" s="39"/>
       <c r="I26" s="40"/>
-      <c r="J26" s="101"/>
+      <c r="J26" s="95"/>
       <c r="K26" s="40"/>
-      <c r="L26" s="99"/>
+      <c r="L26" s="100"/>
       <c r="M26" s="39"/>
       <c r="N26" s="40"/>
-      <c r="O26" s="99"/>
+      <c r="O26" s="100"/>
       <c r="P26" s="39"/>
       <c r="Q26" s="40"/>
       <c r="R26" s="33"/>
@@ -9637,21 +9719,21 @@
       <c r="Z26" s="35"/>
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A27" s="95"/>
+      <c r="A27" s="104"/>
       <c r="B27" s="40"/>
-      <c r="C27" s="96"/>
+      <c r="C27" s="105"/>
       <c r="D27" s="40"/>
-      <c r="E27" s="96"/>
+      <c r="E27" s="105"/>
       <c r="F27" s="40"/>
-      <c r="G27" s="101"/>
+      <c r="G27" s="95"/>
       <c r="H27" s="39"/>
       <c r="I27" s="40"/>
-      <c r="J27" s="101"/>
+      <c r="J27" s="95"/>
       <c r="K27" s="40"/>
-      <c r="L27" s="99"/>
+      <c r="L27" s="100"/>
       <c r="M27" s="39"/>
       <c r="N27" s="40"/>
-      <c r="O27" s="99"/>
+      <c r="O27" s="100"/>
       <c r="P27" s="39"/>
       <c r="Q27" s="40"/>
       <c r="R27" s="33"/>
@@ -9665,21 +9747,21 @@
       <c r="Z27" s="35"/>
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A28" s="95"/>
+      <c r="A28" s="104"/>
       <c r="B28" s="40"/>
-      <c r="C28" s="96"/>
+      <c r="C28" s="105"/>
       <c r="D28" s="40"/>
-      <c r="E28" s="96"/>
+      <c r="E28" s="105"/>
       <c r="F28" s="40"/>
-      <c r="G28" s="101"/>
+      <c r="G28" s="95"/>
       <c r="H28" s="39"/>
       <c r="I28" s="40"/>
-      <c r="J28" s="101"/>
+      <c r="J28" s="95"/>
       <c r="K28" s="40"/>
-      <c r="L28" s="99"/>
+      <c r="L28" s="100"/>
       <c r="M28" s="39"/>
       <c r="N28" s="40"/>
-      <c r="O28" s="99"/>
+      <c r="O28" s="100"/>
       <c r="P28" s="39"/>
       <c r="Q28" s="40"/>
       <c r="R28" s="33"/>
@@ -9693,21 +9775,21 @@
       <c r="Z28" s="35"/>
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A29" s="95"/>
+      <c r="A29" s="104"/>
       <c r="B29" s="40"/>
-      <c r="C29" s="96"/>
+      <c r="C29" s="105"/>
       <c r="D29" s="40"/>
-      <c r="E29" s="96"/>
+      <c r="E29" s="105"/>
       <c r="F29" s="40"/>
-      <c r="G29" s="101"/>
+      <c r="G29" s="95"/>
       <c r="H29" s="39"/>
       <c r="I29" s="40"/>
-      <c r="J29" s="101"/>
+      <c r="J29" s="95"/>
       <c r="K29" s="40"/>
-      <c r="L29" s="99"/>
+      <c r="L29" s="100"/>
       <c r="M29" s="39"/>
       <c r="N29" s="40"/>
-      <c r="O29" s="99"/>
+      <c r="O29" s="100"/>
       <c r="P29" s="39"/>
       <c r="Q29" s="40"/>
       <c r="R29" s="33"/>
@@ -9721,21 +9803,21 @@
       <c r="Z29" s="35"/>
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A30" s="95"/>
+      <c r="A30" s="104"/>
       <c r="B30" s="40"/>
-      <c r="C30" s="96"/>
+      <c r="C30" s="105"/>
       <c r="D30" s="40"/>
-      <c r="E30" s="96"/>
+      <c r="E30" s="105"/>
       <c r="F30" s="40"/>
-      <c r="G30" s="101"/>
+      <c r="G30" s="95"/>
       <c r="H30" s="39"/>
       <c r="I30" s="40"/>
-      <c r="J30" s="101"/>
+      <c r="J30" s="95"/>
       <c r="K30" s="40"/>
-      <c r="L30" s="99"/>
+      <c r="L30" s="100"/>
       <c r="M30" s="39"/>
       <c r="N30" s="40"/>
-      <c r="O30" s="99"/>
+      <c r="O30" s="100"/>
       <c r="P30" s="39"/>
       <c r="Q30" s="40"/>
       <c r="R30" s="33"/>
@@ -9749,23 +9831,23 @@
       <c r="Z30" s="35"/>
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A31" s="97"/>
-      <c r="B31" s="56"/>
-      <c r="C31" s="98"/>
-      <c r="D31" s="56"/>
-      <c r="E31" s="98"/>
-      <c r="F31" s="56"/>
-      <c r="G31" s="104"/>
-      <c r="H31" s="47"/>
-      <c r="I31" s="56"/>
-      <c r="J31" s="104"/>
-      <c r="K31" s="56"/>
-      <c r="L31" s="100"/>
-      <c r="M31" s="47"/>
-      <c r="N31" s="56"/>
-      <c r="O31" s="100"/>
-      <c r="P31" s="47"/>
-      <c r="Q31" s="56"/>
+      <c r="A31" s="107"/>
+      <c r="B31" s="67"/>
+      <c r="C31" s="108"/>
+      <c r="D31" s="67"/>
+      <c r="E31" s="108"/>
+      <c r="F31" s="67"/>
+      <c r="G31" s="99"/>
+      <c r="H31" s="66"/>
+      <c r="I31" s="67"/>
+      <c r="J31" s="99"/>
+      <c r="K31" s="67"/>
+      <c r="L31" s="101"/>
+      <c r="M31" s="66"/>
+      <c r="N31" s="67"/>
+      <c r="O31" s="101"/>
+      <c r="P31" s="66"/>
+      <c r="Q31" s="67"/>
       <c r="R31" s="36"/>
       <c r="S31" s="36"/>
       <c r="T31" s="37"/>
@@ -10763,62 +10845,62 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="136">
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:K19"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="K2:N4"/>
-    <mergeCell ref="O2:P4"/>
-    <mergeCell ref="Q2:R4"/>
-    <mergeCell ref="S2:T4"/>
-    <mergeCell ref="A1:F4"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="O27:Q27"/>
+    <mergeCell ref="O28:Q28"/>
+    <mergeCell ref="O29:Q29"/>
+    <mergeCell ref="O30:Q30"/>
+    <mergeCell ref="O31:Q31"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="O26:Q26"/>
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="G5:T5"/>
     <mergeCell ref="A6:F6"/>
@@ -10843,64 +10925,67 @@
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="E15:F15"/>
     <mergeCell ref="A16:B16"/>
-    <mergeCell ref="O27:Q27"/>
-    <mergeCell ref="O28:Q28"/>
-    <mergeCell ref="O29:Q29"/>
-    <mergeCell ref="O30:Q30"/>
-    <mergeCell ref="O31:Q31"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="O26:Q26"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="K2:N4"/>
+    <mergeCell ref="O2:P4"/>
+    <mergeCell ref="Q2:R4"/>
+    <mergeCell ref="S2:T4"/>
+    <mergeCell ref="A1:F4"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:K19"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
+  <hyperlinks>
+    <hyperlink ref="L21" r:id="rId1" xr:uid="{D6AB78BD-D1E9-4052-889B-F174927032CD}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="landscape"/>
 </worksheet>

--- a/Documents/タスク詳細設計書.xlsx
+++ b/Documents/タスク詳細設計書.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\S-47\Documents\project\taskUN\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DE22809-A13D-4A26-B65C-069C1591D3BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19A645F2-ADE5-44E6-A4C7-46746459F6B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8535" yWindow="555" windowWidth="11415" windowHeight="8955" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="100">
   <si>
     <t>プロジェクト型演習　成果ドキュメント</t>
   </si>
@@ -602,6 +602,108 @@
     <t>http://localhost:8080/taskUN/task-detail.jsp</t>
     <phoneticPr fontId="8"/>
   </si>
+  <si>
+    <t>編集ボタンを押下する</t>
+    <rPh sb="0" eb="2">
+      <t>ヘンシュウ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>オウカ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>削除ボタンを押下する</t>
+    <rPh sb="0" eb="2">
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>オウカ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>一覧へ戻るボタンを押下する</t>
+    <rPh sb="0" eb="2">
+      <t>イチラン</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>モド</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>オウカ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>編集画面が表示される</t>
+    <rPh sb="0" eb="4">
+      <t>ヘンシュウガメン</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>削除画面が表示される</t>
+    <rPh sb="0" eb="4">
+      <t>サクジョガメン</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>タスク一覧画面が表示される</t>
+    <rPh sb="3" eb="7">
+      <t>イチランガメン</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>〇</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>自分以外のタスクの詳細表示</t>
+    <rPh sb="0" eb="4">
+      <t>ジブンイガイ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ショウサイ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>編集、削除ボタンは無く一覧へ戻るボタンのみが表示される</t>
+    <rPh sb="0" eb="2">
+      <t>ヘンシュウ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>ナ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>イチラン</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>モド</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
 </sst>
 </file>
 
@@ -1369,7 +1471,7 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="115">
+  <cellXfs count="114">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1508,56 +1610,23 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1565,11 +1634,11 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1586,17 +1655,26 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
@@ -1607,22 +1685,49 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1632,9 +1737,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1655,41 +1757,11 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -1700,15 +1772,42 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="2" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="45" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="46" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="7" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3460,19 +3559,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="68" t="s">
+      <c r="A1" s="57" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="69"/>
-      <c r="C1" s="70"/>
-      <c r="D1" s="46" t="s">
+      <c r="B1" s="58"/>
+      <c r="C1" s="59"/>
+      <c r="D1" s="78" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="47"/>
-      <c r="F1" s="46" t="s">
+      <c r="E1" s="66"/>
+      <c r="F1" s="78" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="47"/>
+      <c r="G1" s="66"/>
       <c r="H1" s="5" t="s">
         <v>8</v>
       </c>
@@ -3484,72 +3583,72 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="71"/>
+      <c r="A2" s="60"/>
       <c r="B2" s="42"/>
-      <c r="C2" s="51"/>
-      <c r="D2" s="48" t="s">
+      <c r="C2" s="61"/>
+      <c r="D2" s="79" t="s">
         <v>56</v>
       </c>
-      <c r="E2" s="49"/>
-      <c r="F2" s="48" t="s">
+      <c r="E2" s="80"/>
+      <c r="F2" s="79" t="s">
         <v>57</v>
       </c>
-      <c r="G2" s="49"/>
-      <c r="H2" s="54">
+      <c r="G2" s="80"/>
+      <c r="H2" s="83">
         <v>45812</v>
       </c>
-      <c r="I2" s="57" t="s">
+      <c r="I2" s="72" t="s">
         <v>58</v>
       </c>
-      <c r="J2" s="58"/>
+      <c r="J2" s="75"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="71"/>
+      <c r="A3" s="60"/>
       <c r="B3" s="42"/>
-      <c r="C3" s="51"/>
-      <c r="D3" s="50"/>
-      <c r="E3" s="51"/>
-      <c r="F3" s="50"/>
-      <c r="G3" s="51"/>
-      <c r="H3" s="55"/>
-      <c r="I3" s="55"/>
-      <c r="J3" s="59"/>
+      <c r="C3" s="61"/>
+      <c r="D3" s="81"/>
+      <c r="E3" s="61"/>
+      <c r="F3" s="81"/>
+      <c r="G3" s="61"/>
+      <c r="H3" s="73"/>
+      <c r="I3" s="73"/>
+      <c r="J3" s="76"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="72"/>
-      <c r="B4" s="73"/>
-      <c r="C4" s="53"/>
-      <c r="D4" s="52"/>
-      <c r="E4" s="53"/>
-      <c r="F4" s="52"/>
-      <c r="G4" s="53"/>
-      <c r="H4" s="56"/>
-      <c r="I4" s="56"/>
-      <c r="J4" s="60"/>
+      <c r="A4" s="62"/>
+      <c r="B4" s="63"/>
+      <c r="C4" s="64"/>
+      <c r="D4" s="82"/>
+      <c r="E4" s="64"/>
+      <c r="F4" s="82"/>
+      <c r="G4" s="64"/>
+      <c r="H4" s="74"/>
+      <c r="I4" s="74"/>
+      <c r="J4" s="77"/>
     </row>
     <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="74" t="s">
+      <c r="A5" s="65" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="75"/>
-      <c r="C5" s="47"/>
-      <c r="D5" s="81" t="s">
+      <c r="B5" s="50"/>
+      <c r="C5" s="66"/>
+      <c r="D5" s="49" t="s">
         <v>59</v>
       </c>
-      <c r="E5" s="75"/>
-      <c r="F5" s="75"/>
-      <c r="G5" s="75"/>
-      <c r="H5" s="75"/>
-      <c r="I5" s="75"/>
-      <c r="J5" s="82"/>
+      <c r="E5" s="50"/>
+      <c r="F5" s="50"/>
+      <c r="G5" s="50"/>
+      <c r="H5" s="50"/>
+      <c r="I5" s="50"/>
+      <c r="J5" s="51"/>
     </row>
     <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="62" t="s">
+      <c r="A6" s="67" t="s">
         <v>12</v>
       </c>
       <c r="B6" s="39"/>
       <c r="C6" s="40"/>
-      <c r="D6" s="63" t="s">
+      <c r="D6" s="52" t="s">
         <v>60</v>
       </c>
       <c r="E6" s="39"/>
@@ -3557,15 +3656,15 @@
       <c r="G6" s="39"/>
       <c r="H6" s="39"/>
       <c r="I6" s="39"/>
-      <c r="J6" s="64"/>
+      <c r="J6" s="53"/>
     </row>
     <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="62" t="s">
+      <c r="A7" s="67" t="s">
         <v>13</v>
       </c>
       <c r="B7" s="39"/>
       <c r="C7" s="40"/>
-      <c r="D7" s="63" t="s">
+      <c r="D7" s="52" t="s">
         <v>61</v>
       </c>
       <c r="E7" s="39"/>
@@ -3573,15 +3672,15 @@
       <c r="G7" s="39"/>
       <c r="H7" s="39"/>
       <c r="I7" s="39"/>
-      <c r="J7" s="64"/>
+      <c r="J7" s="53"/>
     </row>
     <row r="8" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A8" s="62" t="s">
+      <c r="A8" s="67" t="s">
         <v>14</v>
       </c>
       <c r="B8" s="39"/>
       <c r="C8" s="40"/>
-      <c r="D8" s="63" t="s">
+      <c r="D8" s="52" t="s">
         <v>62</v>
       </c>
       <c r="E8" s="39"/>
@@ -3589,17 +3688,17 @@
       <c r="G8" s="39"/>
       <c r="H8" s="39"/>
       <c r="I8" s="39"/>
-      <c r="J8" s="64"/>
+      <c r="J8" s="53"/>
     </row>
     <row r="9" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A9" s="76" t="s">
+      <c r="A9" s="68" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="61" t="s">
+      <c r="B9" s="71" t="s">
         <v>16</v>
       </c>
       <c r="C9" s="40"/>
-      <c r="D9" s="83" t="s">
+      <c r="D9" s="54" t="s">
         <v>76</v>
       </c>
       <c r="E9" s="39"/>
@@ -3607,43 +3706,43 @@
       <c r="G9" s="39"/>
       <c r="H9" s="39"/>
       <c r="I9" s="39"/>
-      <c r="J9" s="64"/>
+      <c r="J9" s="53"/>
     </row>
     <row r="10" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A10" s="77"/>
-      <c r="B10" s="61" t="s">
+      <c r="A10" s="69"/>
+      <c r="B10" s="71" t="s">
         <v>17</v>
       </c>
       <c r="C10" s="40"/>
-      <c r="D10" s="63"/>
+      <c r="D10" s="52"/>
       <c r="E10" s="39"/>
       <c r="F10" s="39"/>
       <c r="G10" s="39"/>
       <c r="H10" s="39"/>
       <c r="I10" s="39"/>
-      <c r="J10" s="64"/>
+      <c r="J10" s="53"/>
     </row>
     <row r="11" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A11" s="78"/>
-      <c r="B11" s="61" t="s">
+      <c r="A11" s="70"/>
+      <c r="B11" s="71" t="s">
         <v>18</v>
       </c>
       <c r="C11" s="40"/>
-      <c r="D11" s="63"/>
+      <c r="D11" s="52"/>
       <c r="E11" s="39"/>
       <c r="F11" s="39"/>
       <c r="G11" s="39"/>
       <c r="H11" s="39"/>
       <c r="I11" s="39"/>
-      <c r="J11" s="64"/>
+      <c r="J11" s="53"/>
     </row>
     <row r="12" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A12" s="62" t="s">
+      <c r="A12" s="67" t="s">
         <v>19</v>
       </c>
       <c r="B12" s="39"/>
       <c r="C12" s="40"/>
-      <c r="D12" s="63" t="s">
+      <c r="D12" s="52" t="s">
         <v>63</v>
       </c>
       <c r="E12" s="39"/>
@@ -3651,21 +3750,21 @@
       <c r="G12" s="39"/>
       <c r="H12" s="39"/>
       <c r="I12" s="39"/>
-      <c r="J12" s="64"/>
+      <c r="J12" s="53"/>
     </row>
     <row r="13" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A13" s="65" t="s">
+      <c r="A13" s="55" t="s">
         <v>20</v>
       </c>
-      <c r="B13" s="66"/>
-      <c r="C13" s="67"/>
-      <c r="D13" s="79"/>
-      <c r="E13" s="66"/>
-      <c r="F13" s="66"/>
-      <c r="G13" s="66"/>
-      <c r="H13" s="66"/>
-      <c r="I13" s="66"/>
-      <c r="J13" s="80"/>
+      <c r="B13" s="47"/>
+      <c r="C13" s="56"/>
+      <c r="D13" s="46"/>
+      <c r="E13" s="47"/>
+      <c r="F13" s="47"/>
+      <c r="G13" s="47"/>
+      <c r="H13" s="47"/>
+      <c r="I13" s="47"/>
+      <c r="J13" s="48"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -4656,6 +4755,25 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="D12:J12"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A9:A11"/>
+    <mergeCell ref="B9:C9"/>
     <mergeCell ref="D13:J13"/>
     <mergeCell ref="D5:J5"/>
     <mergeCell ref="D6:J6"/>
@@ -4664,25 +4782,6 @@
     <mergeCell ref="D9:J9"/>
     <mergeCell ref="D10:J10"/>
     <mergeCell ref="D11:J11"/>
-    <mergeCell ref="A13:C13"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="A9:A11"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="D12:J12"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
@@ -4704,16 +4803,16 @@
       <c r="A1" s="84" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="69"/>
-      <c r="C1" s="70"/>
-      <c r="D1" s="46" t="s">
+      <c r="B1" s="58"/>
+      <c r="C1" s="59"/>
+      <c r="D1" s="78" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="47"/>
-      <c r="F1" s="46" t="s">
+      <c r="E1" s="66"/>
+      <c r="F1" s="78" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="47"/>
+      <c r="G1" s="66"/>
       <c r="H1" s="4" t="s">
         <v>8</v>
       </c>
@@ -4725,48 +4824,48 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="71"/>
+      <c r="A2" s="60"/>
       <c r="B2" s="42"/>
-      <c r="C2" s="51"/>
-      <c r="D2" s="48" t="s">
+      <c r="C2" s="61"/>
+      <c r="D2" s="79" t="s">
         <v>56</v>
       </c>
-      <c r="E2" s="49"/>
-      <c r="F2" s="48" t="s">
+      <c r="E2" s="80"/>
+      <c r="F2" s="79" t="s">
         <v>57</v>
       </c>
-      <c r="G2" s="49"/>
-      <c r="H2" s="54">
+      <c r="G2" s="80"/>
+      <c r="H2" s="83">
         <v>45810</v>
       </c>
-      <c r="I2" s="57" t="s">
+      <c r="I2" s="72" t="s">
         <v>64</v>
       </c>
-      <c r="J2" s="58"/>
+      <c r="J2" s="75"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="71"/>
+      <c r="A3" s="60"/>
       <c r="B3" s="42"/>
-      <c r="C3" s="51"/>
-      <c r="D3" s="50"/>
-      <c r="E3" s="51"/>
-      <c r="F3" s="50"/>
-      <c r="G3" s="51"/>
-      <c r="H3" s="55"/>
-      <c r="I3" s="55"/>
-      <c r="J3" s="59"/>
+      <c r="C3" s="61"/>
+      <c r="D3" s="81"/>
+      <c r="E3" s="61"/>
+      <c r="F3" s="81"/>
+      <c r="G3" s="61"/>
+      <c r="H3" s="73"/>
+      <c r="I3" s="73"/>
+      <c r="J3" s="76"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="72"/>
-      <c r="B4" s="73"/>
-      <c r="C4" s="53"/>
-      <c r="D4" s="52"/>
-      <c r="E4" s="53"/>
-      <c r="F4" s="52"/>
-      <c r="G4" s="53"/>
-      <c r="H4" s="56"/>
-      <c r="I4" s="56"/>
-      <c r="J4" s="60"/>
+      <c r="A4" s="62"/>
+      <c r="B4" s="63"/>
+      <c r="C4" s="64"/>
+      <c r="D4" s="82"/>
+      <c r="E4" s="64"/>
+      <c r="F4" s="82"/>
+      <c r="G4" s="64"/>
+      <c r="H4" s="74"/>
+      <c r="I4" s="74"/>
+      <c r="J4" s="77"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -6126,16 +6225,16 @@
       <c r="A1" s="84" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="69"/>
-      <c r="C1" s="70"/>
-      <c r="D1" s="46" t="s">
+      <c r="B1" s="58"/>
+      <c r="C1" s="59"/>
+      <c r="D1" s="78" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="47"/>
-      <c r="F1" s="46" t="s">
+      <c r="E1" s="66"/>
+      <c r="F1" s="78" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="47"/>
+      <c r="G1" s="66"/>
       <c r="H1" s="4" t="s">
         <v>8</v>
       </c>
@@ -6147,48 +6246,48 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="71"/>
+      <c r="A2" s="60"/>
       <c r="B2" s="42"/>
-      <c r="C2" s="51"/>
-      <c r="D2" s="48" t="s">
+      <c r="C2" s="61"/>
+      <c r="D2" s="79" t="s">
         <v>56</v>
       </c>
-      <c r="E2" s="49"/>
-      <c r="F2" s="48" t="s">
+      <c r="E2" s="80"/>
+      <c r="F2" s="79" t="s">
         <v>57</v>
       </c>
-      <c r="G2" s="49"/>
-      <c r="H2" s="54">
+      <c r="G2" s="80"/>
+      <c r="H2" s="83">
         <v>45810</v>
       </c>
-      <c r="I2" s="57" t="s">
+      <c r="I2" s="72" t="s">
         <v>64</v>
       </c>
-      <c r="J2" s="58"/>
+      <c r="J2" s="75"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="71"/>
+      <c r="A3" s="60"/>
       <c r="B3" s="42"/>
-      <c r="C3" s="51"/>
-      <c r="D3" s="50"/>
-      <c r="E3" s="51"/>
-      <c r="F3" s="50"/>
-      <c r="G3" s="51"/>
-      <c r="H3" s="55"/>
-      <c r="I3" s="55"/>
-      <c r="J3" s="59"/>
+      <c r="C3" s="61"/>
+      <c r="D3" s="81"/>
+      <c r="E3" s="61"/>
+      <c r="F3" s="81"/>
+      <c r="G3" s="61"/>
+      <c r="H3" s="73"/>
+      <c r="I3" s="73"/>
+      <c r="J3" s="76"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="72"/>
-      <c r="B4" s="73"/>
-      <c r="C4" s="53"/>
-      <c r="D4" s="52"/>
-      <c r="E4" s="53"/>
-      <c r="F4" s="52"/>
-      <c r="G4" s="53"/>
-      <c r="H4" s="56"/>
-      <c r="I4" s="56"/>
-      <c r="J4" s="60"/>
+      <c r="A4" s="62"/>
+      <c r="B4" s="63"/>
+      <c r="C4" s="64"/>
+      <c r="D4" s="82"/>
+      <c r="E4" s="64"/>
+      <c r="F4" s="82"/>
+      <c r="G4" s="64"/>
+      <c r="H4" s="74"/>
+      <c r="I4" s="74"/>
+      <c r="J4" s="77"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -7542,16 +7641,16 @@
       <c r="A1" s="84" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="69"/>
-      <c r="C1" s="70"/>
-      <c r="D1" s="46" t="s">
+      <c r="B1" s="58"/>
+      <c r="C1" s="59"/>
+      <c r="D1" s="78" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="47"/>
-      <c r="F1" s="46" t="s">
+      <c r="E1" s="66"/>
+      <c r="F1" s="78" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="47"/>
+      <c r="G1" s="66"/>
       <c r="H1" s="4" t="s">
         <v>8</v>
       </c>
@@ -7563,67 +7662,67 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="71"/>
+      <c r="A2" s="60"/>
       <c r="B2" s="42"/>
-      <c r="C2" s="51"/>
-      <c r="D2" s="48" t="s">
+      <c r="C2" s="61"/>
+      <c r="D2" s="79" t="s">
         <v>56</v>
       </c>
-      <c r="E2" s="49"/>
-      <c r="F2" s="48" t="s">
+      <c r="E2" s="80"/>
+      <c r="F2" s="79" t="s">
         <v>57</v>
       </c>
-      <c r="G2" s="49"/>
-      <c r="H2" s="54">
+      <c r="G2" s="80"/>
+      <c r="H2" s="83">
         <v>45810</v>
       </c>
-      <c r="I2" s="57" t="s">
+      <c r="I2" s="72" t="s">
         <v>64</v>
       </c>
-      <c r="J2" s="58"/>
+      <c r="J2" s="75"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="71"/>
+      <c r="A3" s="60"/>
       <c r="B3" s="42"/>
-      <c r="C3" s="51"/>
-      <c r="D3" s="50"/>
-      <c r="E3" s="51"/>
-      <c r="F3" s="50"/>
-      <c r="G3" s="51"/>
-      <c r="H3" s="55"/>
-      <c r="I3" s="55"/>
-      <c r="J3" s="59"/>
+      <c r="C3" s="61"/>
+      <c r="D3" s="81"/>
+      <c r="E3" s="61"/>
+      <c r="F3" s="81"/>
+      <c r="G3" s="61"/>
+      <c r="H3" s="73"/>
+      <c r="I3" s="73"/>
+      <c r="J3" s="76"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="71"/>
+      <c r="A4" s="60"/>
       <c r="B4" s="42"/>
-      <c r="C4" s="51"/>
-      <c r="D4" s="50"/>
-      <c r="E4" s="51"/>
-      <c r="F4" s="50"/>
-      <c r="G4" s="51"/>
-      <c r="H4" s="55"/>
-      <c r="I4" s="55"/>
-      <c r="J4" s="59"/>
+      <c r="C4" s="61"/>
+      <c r="D4" s="81"/>
+      <c r="E4" s="61"/>
+      <c r="F4" s="81"/>
+      <c r="G4" s="61"/>
+      <c r="H4" s="73"/>
+      <c r="I4" s="73"/>
+      <c r="J4" s="76"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="85" t="s">
+      <c r="A5" s="86" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="75"/>
-      <c r="C5" s="47"/>
+      <c r="B5" s="50"/>
+      <c r="C5" s="66"/>
       <c r="D5" s="89" t="s">
         <v>65</v>
       </c>
-      <c r="E5" s="75"/>
-      <c r="F5" s="75"/>
-      <c r="G5" s="75"/>
-      <c r="H5" s="75"/>
-      <c r="I5" s="75"/>
-      <c r="J5" s="82"/>
+      <c r="E5" s="50"/>
+      <c r="F5" s="50"/>
+      <c r="G5" s="50"/>
+      <c r="H5" s="50"/>
+      <c r="I5" s="50"/>
+      <c r="J5" s="51"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="87" t="s">
+      <c r="A6" s="88" t="s">
         <v>25</v>
       </c>
       <c r="B6" s="39"/>
@@ -7634,7 +7733,7 @@
       <c r="G6" s="39"/>
       <c r="H6" s="39"/>
       <c r="I6" s="39"/>
-      <c r="J6" s="64"/>
+      <c r="J6" s="53"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
       <c r="A7" s="90"/>
@@ -7649,7 +7748,7 @@
       <c r="J7" s="92"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="71"/>
+      <c r="A8" s="60"/>
       <c r="B8" s="42"/>
       <c r="C8" s="42"/>
       <c r="D8" s="42"/>
@@ -7661,7 +7760,7 @@
       <c r="J8" s="93"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="71"/>
+      <c r="A9" s="60"/>
       <c r="B9" s="42"/>
       <c r="C9" s="42"/>
       <c r="D9" s="42"/>
@@ -7673,7 +7772,7 @@
       <c r="J9" s="93"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="71"/>
+      <c r="A10" s="60"/>
       <c r="B10" s="42"/>
       <c r="C10" s="42"/>
       <c r="D10" s="42"/>
@@ -7685,7 +7784,7 @@
       <c r="J10" s="93"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="71"/>
+      <c r="A11" s="60"/>
       <c r="B11" s="42"/>
       <c r="C11" s="42"/>
       <c r="D11" s="42"/>
@@ -7697,7 +7796,7 @@
       <c r="J11" s="93"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="71"/>
+      <c r="A12" s="60"/>
       <c r="B12" s="42"/>
       <c r="C12" s="42"/>
       <c r="D12" s="42"/>
@@ -7709,7 +7808,7 @@
       <c r="J12" s="93"/>
     </row>
     <row r="13" spans="1:10" ht="62.25" customHeight="1">
-      <c r="A13" s="71"/>
+      <c r="A13" s="60"/>
       <c r="B13" s="42"/>
       <c r="C13" s="42"/>
       <c r="D13" s="42"/>
@@ -7721,7 +7820,7 @@
       <c r="J13" s="93"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="87" t="s">
+      <c r="A14" s="88" t="s">
         <v>26</v>
       </c>
       <c r="B14" s="39"/>
@@ -7732,15 +7831,15 @@
       <c r="G14" s="39"/>
       <c r="H14" s="39"/>
       <c r="I14" s="39"/>
-      <c r="J14" s="64"/>
+      <c r="J14" s="53"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="87" t="s">
+      <c r="A15" s="88" t="s">
         <v>27</v>
       </c>
       <c r="B15" s="39"/>
       <c r="C15" s="40"/>
-      <c r="D15" s="63" t="s">
+      <c r="D15" s="52" t="s">
         <v>74</v>
       </c>
       <c r="E15" s="39"/>
@@ -7755,7 +7854,7 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="87" t="s">
+      <c r="A16" s="88" t="s">
         <v>29</v>
       </c>
       <c r="B16" s="39"/>
@@ -7776,10 +7875,10 @@
         <v>20</v>
       </c>
       <c r="I16" s="39"/>
-      <c r="J16" s="64"/>
+      <c r="J16" s="53"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="88">
+      <c r="A17" s="85">
         <v>1</v>
       </c>
       <c r="B17" s="39"/>
@@ -7794,14 +7893,14 @@
       <c r="G17" s="18" t="s">
         <v>71</v>
       </c>
-      <c r="H17" s="63" t="s">
+      <c r="H17" s="52" t="s">
         <v>75</v>
       </c>
       <c r="I17" s="39"/>
-      <c r="J17" s="64"/>
+      <c r="J17" s="53"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="88">
+      <c r="A18" s="85">
         <v>2</v>
       </c>
       <c r="B18" s="39"/>
@@ -7816,14 +7915,14 @@
       <c r="G18" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="H18" s="63" t="s">
+      <c r="H18" s="52" t="s">
         <v>75</v>
       </c>
       <c r="I18" s="39"/>
-      <c r="J18" s="64"/>
+      <c r="J18" s="53"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="88">
+      <c r="A19" s="85">
         <v>3</v>
       </c>
       <c r="B19" s="39"/>
@@ -7838,59 +7937,59 @@
       <c r="G19" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="H19" s="63" t="s">
+      <c r="H19" s="52" t="s">
         <v>75</v>
       </c>
       <c r="I19" s="39"/>
-      <c r="J19" s="64"/>
+      <c r="J19" s="53"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="88"/>
+      <c r="A20" s="85"/>
       <c r="B20" s="39"/>
       <c r="C20" s="40"/>
       <c r="D20" s="17"/>
       <c r="E20" s="17"/>
       <c r="F20" s="18"/>
       <c r="G20" s="18"/>
-      <c r="H20" s="63"/>
+      <c r="H20" s="52"/>
       <c r="I20" s="39"/>
-      <c r="J20" s="64"/>
+      <c r="J20" s="53"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="88"/>
+      <c r="A21" s="85"/>
       <c r="B21" s="39"/>
       <c r="C21" s="40"/>
       <c r="D21" s="17"/>
       <c r="E21" s="17"/>
       <c r="F21" s="18"/>
       <c r="G21" s="18"/>
-      <c r="H21" s="63"/>
+      <c r="H21" s="52"/>
       <c r="I21" s="39"/>
-      <c r="J21" s="64"/>
+      <c r="J21" s="53"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="88"/>
+      <c r="A22" s="85"/>
       <c r="B22" s="39"/>
       <c r="C22" s="40"/>
       <c r="D22" s="17"/>
       <c r="E22" s="17"/>
       <c r="F22" s="18"/>
       <c r="G22" s="18"/>
-      <c r="H22" s="63"/>
+      <c r="H22" s="52"/>
       <c r="I22" s="39"/>
-      <c r="J22" s="64"/>
+      <c r="J22" s="53"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A23" s="86"/>
-      <c r="B23" s="66"/>
-      <c r="C23" s="67"/>
+      <c r="A23" s="87"/>
+      <c r="B23" s="47"/>
+      <c r="C23" s="56"/>
       <c r="D23" s="19"/>
       <c r="E23" s="19"/>
       <c r="F23" s="20"/>
       <c r="G23" s="20"/>
-      <c r="H23" s="79"/>
-      <c r="I23" s="66"/>
-      <c r="J23" s="80"/>
+      <c r="H23" s="46"/>
+      <c r="I23" s="47"/>
+      <c r="J23" s="48"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
@@ -8871,16 +8970,11 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A1:C4"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="F1:G1"/>
@@ -8897,11 +8991,16 @@
     <mergeCell ref="H17:J17"/>
     <mergeCell ref="D2:E4"/>
     <mergeCell ref="H23:J23"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="H22:J22"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -8921,141 +9020,141 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="68" t="s">
+      <c r="A1" s="57" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="69"/>
-      <c r="C1" s="69"/>
-      <c r="D1" s="69"/>
-      <c r="E1" s="69"/>
-      <c r="F1" s="70"/>
-      <c r="G1" s="46" t="s">
+      <c r="B1" s="58"/>
+      <c r="C1" s="58"/>
+      <c r="D1" s="58"/>
+      <c r="E1" s="58"/>
+      <c r="F1" s="59"/>
+      <c r="G1" s="78" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="75"/>
-      <c r="I1" s="75"/>
-      <c r="J1" s="47"/>
-      <c r="K1" s="46" t="s">
+      <c r="H1" s="50"/>
+      <c r="I1" s="50"/>
+      <c r="J1" s="66"/>
+      <c r="K1" s="78" t="s">
         <v>7</v>
       </c>
-      <c r="L1" s="75"/>
-      <c r="M1" s="75"/>
-      <c r="N1" s="47"/>
-      <c r="O1" s="46" t="s">
+      <c r="L1" s="50"/>
+      <c r="M1" s="50"/>
+      <c r="N1" s="66"/>
+      <c r="O1" s="78" t="s">
         <v>8</v>
       </c>
-      <c r="P1" s="47"/>
-      <c r="Q1" s="46" t="s">
+      <c r="P1" s="66"/>
+      <c r="Q1" s="78" t="s">
         <v>9</v>
       </c>
-      <c r="R1" s="47"/>
-      <c r="S1" s="46" t="s">
+      <c r="R1" s="66"/>
+      <c r="S1" s="78" t="s">
         <v>10</v>
       </c>
-      <c r="T1" s="82"/>
+      <c r="T1" s="51"/>
     </row>
     <row r="2" spans="1:26" ht="18" customHeight="1">
-      <c r="A2" s="71"/>
+      <c r="A2" s="60"/>
       <c r="B2" s="42"/>
       <c r="C2" s="42"/>
       <c r="D2" s="42"/>
       <c r="E2" s="42"/>
-      <c r="F2" s="51"/>
-      <c r="G2" s="48" t="s">
+      <c r="F2" s="61"/>
+      <c r="G2" s="79" t="s">
         <v>56</v>
       </c>
       <c r="H2" s="91"/>
       <c r="I2" s="91"/>
-      <c r="J2" s="49"/>
-      <c r="K2" s="48" t="s">
+      <c r="J2" s="80"/>
+      <c r="K2" s="79" t="s">
         <v>57</v>
       </c>
       <c r="L2" s="91"/>
       <c r="M2" s="91"/>
-      <c r="N2" s="49"/>
-      <c r="O2" s="102">
+      <c r="N2" s="80"/>
+      <c r="O2" s="106">
         <v>45818</v>
       </c>
-      <c r="P2" s="49"/>
-      <c r="Q2" s="48" t="s">
+      <c r="P2" s="80"/>
+      <c r="Q2" s="79" t="s">
         <v>64</v>
       </c>
-      <c r="R2" s="49"/>
-      <c r="S2" s="48"/>
+      <c r="R2" s="80"/>
+      <c r="S2" s="79"/>
       <c r="T2" s="92"/>
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
-      <c r="A3" s="71"/>
+      <c r="A3" s="60"/>
       <c r="B3" s="42"/>
       <c r="C3" s="42"/>
       <c r="D3" s="42"/>
       <c r="E3" s="42"/>
-      <c r="F3" s="51"/>
-      <c r="G3" s="50"/>
+      <c r="F3" s="61"/>
+      <c r="G3" s="81"/>
       <c r="H3" s="42"/>
       <c r="I3" s="42"/>
-      <c r="J3" s="51"/>
-      <c r="K3" s="50"/>
+      <c r="J3" s="61"/>
+      <c r="K3" s="81"/>
       <c r="L3" s="42"/>
       <c r="M3" s="42"/>
-      <c r="N3" s="51"/>
-      <c r="O3" s="50"/>
-      <c r="P3" s="51"/>
-      <c r="Q3" s="50"/>
-      <c r="R3" s="51"/>
-      <c r="S3" s="50"/>
+      <c r="N3" s="61"/>
+      <c r="O3" s="81"/>
+      <c r="P3" s="61"/>
+      <c r="Q3" s="81"/>
+      <c r="R3" s="61"/>
+      <c r="S3" s="81"/>
       <c r="T3" s="93"/>
     </row>
     <row r="4" spans="1:26" ht="18" customHeight="1">
-      <c r="A4" s="72"/>
-      <c r="B4" s="73"/>
-      <c r="C4" s="73"/>
-      <c r="D4" s="73"/>
-      <c r="E4" s="73"/>
-      <c r="F4" s="53"/>
-      <c r="G4" s="52"/>
-      <c r="H4" s="73"/>
-      <c r="I4" s="73"/>
-      <c r="J4" s="53"/>
-      <c r="K4" s="52"/>
-      <c r="L4" s="73"/>
-      <c r="M4" s="73"/>
-      <c r="N4" s="53"/>
-      <c r="O4" s="52"/>
-      <c r="P4" s="53"/>
-      <c r="Q4" s="52"/>
-      <c r="R4" s="53"/>
-      <c r="S4" s="52"/>
-      <c r="T4" s="103"/>
+      <c r="A4" s="62"/>
+      <c r="B4" s="63"/>
+      <c r="C4" s="63"/>
+      <c r="D4" s="63"/>
+      <c r="E4" s="63"/>
+      <c r="F4" s="64"/>
+      <c r="G4" s="82"/>
+      <c r="H4" s="63"/>
+      <c r="I4" s="63"/>
+      <c r="J4" s="64"/>
+      <c r="K4" s="82"/>
+      <c r="L4" s="63"/>
+      <c r="M4" s="63"/>
+      <c r="N4" s="64"/>
+      <c r="O4" s="82"/>
+      <c r="P4" s="64"/>
+      <c r="Q4" s="82"/>
+      <c r="R4" s="64"/>
+      <c r="S4" s="82"/>
+      <c r="T4" s="107"/>
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="85" t="s">
+      <c r="A5" s="86" t="s">
         <v>35</v>
       </c>
-      <c r="B5" s="75"/>
-      <c r="C5" s="75"/>
-      <c r="D5" s="75"/>
-      <c r="E5" s="75"/>
-      <c r="F5" s="47"/>
-      <c r="G5" s="81" t="s">
+      <c r="B5" s="50"/>
+      <c r="C5" s="50"/>
+      <c r="D5" s="50"/>
+      <c r="E5" s="50"/>
+      <c r="F5" s="66"/>
+      <c r="G5" s="49" t="s">
         <v>36</v>
       </c>
-      <c r="H5" s="75"/>
-      <c r="I5" s="75"/>
-      <c r="J5" s="75"/>
-      <c r="K5" s="75"/>
-      <c r="L5" s="75"/>
-      <c r="M5" s="75"/>
-      <c r="N5" s="75"/>
-      <c r="O5" s="75"/>
-      <c r="P5" s="75"/>
-      <c r="Q5" s="75"/>
-      <c r="R5" s="75"/>
-      <c r="S5" s="75"/>
-      <c r="T5" s="82"/>
+      <c r="H5" s="50"/>
+      <c r="I5" s="50"/>
+      <c r="J5" s="50"/>
+      <c r="K5" s="50"/>
+      <c r="L5" s="50"/>
+      <c r="M5" s="50"/>
+      <c r="N5" s="50"/>
+      <c r="O5" s="50"/>
+      <c r="P5" s="50"/>
+      <c r="Q5" s="50"/>
+      <c r="R5" s="50"/>
+      <c r="S5" s="50"/>
+      <c r="T5" s="51"/>
     </row>
     <row r="6" spans="1:26" ht="18" customHeight="1">
-      <c r="A6" s="87" t="s">
+      <c r="A6" s="88" t="s">
         <v>37</v>
       </c>
       <c r="B6" s="39"/>
@@ -9063,7 +9162,7 @@
       <c r="D6" s="39"/>
       <c r="E6" s="39"/>
       <c r="F6" s="40"/>
-      <c r="G6" s="63" t="s">
+      <c r="G6" s="52" t="s">
         <v>21</v>
       </c>
       <c r="H6" s="39"/>
@@ -9078,10 +9177,10 @@
       <c r="Q6" s="39"/>
       <c r="R6" s="39"/>
       <c r="S6" s="39"/>
-      <c r="T6" s="64"/>
+      <c r="T6" s="53"/>
     </row>
     <row r="7" spans="1:26" ht="18" customHeight="1">
-      <c r="A7" s="87" t="s">
+      <c r="A7" s="88" t="s">
         <v>38</v>
       </c>
       <c r="B7" s="39"/>
@@ -9089,7 +9188,7 @@
       <c r="D7" s="39"/>
       <c r="E7" s="39"/>
       <c r="F7" s="40"/>
-      <c r="G7" s="63" t="s">
+      <c r="G7" s="52" t="s">
         <v>59</v>
       </c>
       <c r="H7" s="39"/>
@@ -9104,7 +9203,7 @@
       <c r="Q7" s="39"/>
       <c r="R7" s="39"/>
       <c r="S7" s="39"/>
-      <c r="T7" s="64"/>
+      <c r="T7" s="53"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
       <c r="A8" s="8"/>
@@ -9303,11 +9402,11 @@
       <c r="T14" s="10"/>
     </row>
     <row r="15" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A15" s="87" t="s">
+      <c r="A15" s="88" t="s">
         <v>45</v>
       </c>
       <c r="B15" s="40"/>
-      <c r="C15" s="106" t="s">
+      <c r="C15" s="105" t="s">
         <v>39</v>
       </c>
       <c r="D15" s="40"/>
@@ -9345,40 +9444,46 @@
       </c>
     </row>
     <row r="16" spans="1:26" ht="48" customHeight="1">
-      <c r="A16" s="104">
+      <c r="A16" s="95">
         <v>1</v>
       </c>
       <c r="B16" s="40"/>
-      <c r="C16" s="105" t="s">
+      <c r="C16" s="96" t="s">
         <v>54</v>
       </c>
       <c r="D16" s="40"/>
-      <c r="E16" s="105" t="s">
+      <c r="E16" s="96" t="s">
         <v>55</v>
       </c>
       <c r="F16" s="40"/>
-      <c r="G16" s="95" t="s">
+      <c r="G16" s="104" t="s">
         <v>77</v>
       </c>
       <c r="H16" s="39"/>
       <c r="I16" s="40"/>
-      <c r="J16" s="96" t="s">
+      <c r="J16" s="111" t="s">
         <v>78</v>
       </c>
-      <c r="K16" s="97"/>
-      <c r="L16" s="100" t="s">
+      <c r="K16" s="100"/>
+      <c r="L16" s="102" t="s">
         <v>79</v>
       </c>
       <c r="M16" s="39"/>
       <c r="N16" s="40"/>
-      <c r="O16" s="100" t="s">
+      <c r="O16" s="102" t="s">
         <v>80</v>
       </c>
       <c r="P16" s="39"/>
       <c r="Q16" s="40"/>
-      <c r="R16" s="33"/>
-      <c r="S16" s="33"/>
-      <c r="T16" s="34"/>
+      <c r="R16" s="113">
+        <v>45825</v>
+      </c>
+      <c r="S16" s="33" t="s">
+        <v>64</v>
+      </c>
+      <c r="T16" s="34" t="s">
+        <v>97</v>
+      </c>
       <c r="U16" s="35"/>
       <c r="V16" s="35"/>
       <c r="W16" s="35"/>
@@ -9387,40 +9492,46 @@
       <c r="Z16" s="35"/>
     </row>
     <row r="17" spans="1:26" ht="51" customHeight="1">
-      <c r="A17" s="104">
+      <c r="A17" s="95">
         <v>2</v>
       </c>
       <c r="B17" s="40"/>
-      <c r="C17" s="105" t="s">
+      <c r="C17" s="96" t="s">
         <v>54</v>
       </c>
       <c r="D17" s="40"/>
-      <c r="E17" s="105" t="s">
+      <c r="E17" s="96" t="s">
         <v>55</v>
       </c>
       <c r="F17" s="40"/>
-      <c r="G17" s="96" t="s">
+      <c r="G17" s="111" t="s">
         <v>81</v>
       </c>
-      <c r="H17" s="98"/>
-      <c r="I17" s="97"/>
-      <c r="J17" s="96" t="s">
+      <c r="H17" s="112"/>
+      <c r="I17" s="100"/>
+      <c r="J17" s="111" t="s">
         <v>78</v>
       </c>
-      <c r="K17" s="97"/>
-      <c r="L17" s="100" t="s">
+      <c r="K17" s="100"/>
+      <c r="L17" s="102" t="s">
         <v>79</v>
       </c>
       <c r="M17" s="39"/>
       <c r="N17" s="40"/>
-      <c r="O17" s="100" t="s">
+      <c r="O17" s="102" t="s">
         <v>82</v>
       </c>
       <c r="P17" s="39"/>
       <c r="Q17" s="40"/>
-      <c r="R17" s="33"/>
-      <c r="S17" s="33"/>
-      <c r="T17" s="34"/>
+      <c r="R17" s="113">
+        <v>45825</v>
+      </c>
+      <c r="S17" s="33" t="s">
+        <v>64</v>
+      </c>
+      <c r="T17" s="34" t="s">
+        <v>97</v>
+      </c>
       <c r="U17" s="35"/>
       <c r="V17" s="35"/>
       <c r="W17" s="35"/>
@@ -9429,34 +9540,46 @@
       <c r="Z17" s="35"/>
     </row>
     <row r="18" spans="1:26" ht="59.25" customHeight="1">
-      <c r="A18" s="104">
+      <c r="A18" s="95">
         <v>3</v>
       </c>
       <c r="B18" s="40"/>
-      <c r="C18" s="105" t="s">
+      <c r="C18" s="96" t="s">
         <v>54</v>
       </c>
       <c r="D18" s="40"/>
-      <c r="E18" s="105" t="s">
+      <c r="E18" s="96" t="s">
         <v>55</v>
       </c>
       <c r="F18" s="40"/>
-      <c r="G18" s="95" t="s">
+      <c r="G18" s="104" t="s">
         <v>83</v>
       </c>
       <c r="H18" s="39"/>
       <c r="I18" s="40"/>
-      <c r="J18" s="95"/>
-      <c r="K18" s="40"/>
-      <c r="L18" s="100"/>
+      <c r="J18" s="111" t="s">
+        <v>78</v>
+      </c>
+      <c r="K18" s="100"/>
+      <c r="L18" s="102" t="s">
+        <v>91</v>
+      </c>
       <c r="M18" s="39"/>
       <c r="N18" s="40"/>
-      <c r="O18" s="100"/>
+      <c r="O18" s="102" t="s">
+        <v>94</v>
+      </c>
       <c r="P18" s="39"/>
       <c r="Q18" s="40"/>
-      <c r="R18" s="33"/>
-      <c r="S18" s="33"/>
-      <c r="T18" s="34"/>
+      <c r="R18" s="113">
+        <v>45825</v>
+      </c>
+      <c r="S18" s="33" t="s">
+        <v>64</v>
+      </c>
+      <c r="T18" s="34" t="s">
+        <v>97</v>
+      </c>
       <c r="U18" s="35"/>
       <c r="V18" s="35"/>
       <c r="W18" s="35"/>
@@ -9465,34 +9588,46 @@
       <c r="Z18" s="35"/>
     </row>
     <row r="19" spans="1:26" ht="51.75" customHeight="1">
-      <c r="A19" s="104">
+      <c r="A19" s="95">
         <v>4</v>
       </c>
       <c r="B19" s="40"/>
-      <c r="C19" s="105" t="s">
+      <c r="C19" s="96" t="s">
         <v>54</v>
       </c>
       <c r="D19" s="40"/>
-      <c r="E19" s="105" t="s">
+      <c r="E19" s="96" t="s">
         <v>55</v>
       </c>
       <c r="F19" s="40"/>
-      <c r="G19" s="95" t="s">
+      <c r="G19" s="104" t="s">
         <v>84</v>
       </c>
       <c r="H19" s="39"/>
       <c r="I19" s="40"/>
-      <c r="J19" s="95"/>
-      <c r="K19" s="40"/>
-      <c r="L19" s="100"/>
+      <c r="J19" s="111" t="s">
+        <v>78</v>
+      </c>
+      <c r="K19" s="100"/>
+      <c r="L19" s="102" t="s">
+        <v>92</v>
+      </c>
       <c r="M19" s="39"/>
       <c r="N19" s="40"/>
-      <c r="O19" s="100"/>
+      <c r="O19" s="102" t="s">
+        <v>95</v>
+      </c>
       <c r="P19" s="39"/>
       <c r="Q19" s="40"/>
-      <c r="R19" s="33"/>
-      <c r="S19" s="33"/>
-      <c r="T19" s="34"/>
+      <c r="R19" s="113">
+        <v>45825</v>
+      </c>
+      <c r="S19" s="33" t="s">
+        <v>64</v>
+      </c>
+      <c r="T19" s="34" t="s">
+        <v>97</v>
+      </c>
       <c r="U19" s="35"/>
       <c r="V19" s="35"/>
       <c r="W19" s="35"/>
@@ -9501,34 +9636,46 @@
       <c r="Z19" s="35"/>
     </row>
     <row r="20" spans="1:26" ht="54" customHeight="1">
-      <c r="A20" s="104">
+      <c r="A20" s="95">
         <v>5</v>
       </c>
       <c r="B20" s="40"/>
-      <c r="C20" s="105" t="s">
+      <c r="C20" s="96" t="s">
         <v>54</v>
       </c>
       <c r="D20" s="40"/>
-      <c r="E20" s="105" t="s">
+      <c r="E20" s="96" t="s">
         <v>55</v>
       </c>
       <c r="F20" s="40"/>
-      <c r="G20" s="95" t="s">
+      <c r="G20" s="104" t="s">
         <v>85</v>
       </c>
       <c r="H20" s="39"/>
       <c r="I20" s="40"/>
-      <c r="J20" s="95"/>
-      <c r="K20" s="40"/>
-      <c r="L20" s="100"/>
+      <c r="J20" s="111" t="s">
+        <v>78</v>
+      </c>
+      <c r="K20" s="100"/>
+      <c r="L20" s="102" t="s">
+        <v>93</v>
+      </c>
       <c r="M20" s="39"/>
       <c r="N20" s="40"/>
-      <c r="O20" s="100"/>
+      <c r="O20" s="102" t="s">
+        <v>96</v>
+      </c>
       <c r="P20" s="39"/>
       <c r="Q20" s="40"/>
-      <c r="R20" s="33"/>
-      <c r="S20" s="33"/>
-      <c r="T20" s="34"/>
+      <c r="R20" s="113">
+        <v>45825</v>
+      </c>
+      <c r="S20" s="33" t="s">
+        <v>64</v>
+      </c>
+      <c r="T20" s="34" t="s">
+        <v>97</v>
+      </c>
       <c r="U20" s="35"/>
       <c r="V20" s="35"/>
       <c r="W20" s="35"/>
@@ -9537,40 +9684,46 @@
       <c r="Z20" s="35"/>
     </row>
     <row r="21" spans="1:26" ht="53.25" customHeight="1">
-      <c r="A21" s="109">
+      <c r="A21" s="99">
         <v>7</v>
       </c>
-      <c r="B21" s="97"/>
-      <c r="C21" s="110" t="s">
+      <c r="B21" s="100"/>
+      <c r="C21" s="101" t="s">
         <v>54</v>
       </c>
-      <c r="D21" s="97"/>
-      <c r="E21" s="110" t="s">
+      <c r="D21" s="100"/>
+      <c r="E21" s="101" t="s">
         <v>86</v>
       </c>
-      <c r="F21" s="97"/>
-      <c r="G21" s="96" t="s">
+      <c r="F21" s="100"/>
+      <c r="G21" s="111" t="s">
         <v>87</v>
       </c>
-      <c r="H21" s="98"/>
-      <c r="I21" s="97"/>
-      <c r="J21" s="96" t="s">
+      <c r="H21" s="112"/>
+      <c r="I21" s="100"/>
+      <c r="J21" s="111" t="s">
         <v>88</v>
       </c>
-      <c r="K21" s="97"/>
-      <c r="L21" s="111" t="s">
+      <c r="K21" s="100"/>
+      <c r="L21" s="108" t="s">
         <v>90</v>
       </c>
-      <c r="M21" s="112"/>
-      <c r="N21" s="112"/>
-      <c r="O21" s="100" t="s">
+      <c r="M21" s="109"/>
+      <c r="N21" s="109"/>
+      <c r="O21" s="102" t="s">
         <v>89</v>
       </c>
       <c r="P21" s="39"/>
       <c r="Q21" s="40"/>
-      <c r="R21" s="113"/>
-      <c r="S21" s="113"/>
-      <c r="T21" s="114"/>
+      <c r="R21" s="113">
+        <v>45825</v>
+      </c>
+      <c r="S21" s="33" t="s">
+        <v>64</v>
+      </c>
+      <c r="T21" s="34" t="s">
+        <v>97</v>
+      </c>
       <c r="U21" s="35"/>
       <c r="V21" s="35"/>
       <c r="W21" s="35"/>
@@ -9578,27 +9731,47 @@
       <c r="Y21" s="35"/>
       <c r="Z21" s="35"/>
     </row>
-    <row r="22" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A22" s="104"/>
-      <c r="B22" s="40"/>
-      <c r="C22" s="105"/>
-      <c r="D22" s="40"/>
-      <c r="E22" s="105"/>
+    <row r="22" spans="1:26" ht="62.25" customHeight="1">
+      <c r="A22" s="99">
+        <v>8</v>
+      </c>
+      <c r="B22" s="100"/>
+      <c r="C22" s="101" t="s">
+        <v>54</v>
+      </c>
+      <c r="D22" s="100"/>
+      <c r="E22" s="96" t="s">
+        <v>55</v>
+      </c>
       <c r="F22" s="40"/>
-      <c r="G22" s="95"/>
+      <c r="G22" s="104" t="s">
+        <v>98</v>
+      </c>
       <c r="H22" s="39"/>
       <c r="I22" s="40"/>
-      <c r="J22" s="95"/>
-      <c r="K22" s="40"/>
-      <c r="L22" s="100"/>
+      <c r="J22" s="111" t="s">
+        <v>78</v>
+      </c>
+      <c r="K22" s="100"/>
+      <c r="L22" s="102" t="s">
+        <v>79</v>
+      </c>
       <c r="M22" s="39"/>
       <c r="N22" s="40"/>
-      <c r="O22" s="100"/>
+      <c r="O22" s="102" t="s">
+        <v>99</v>
+      </c>
       <c r="P22" s="39"/>
       <c r="Q22" s="40"/>
-      <c r="R22" s="33"/>
-      <c r="S22" s="33"/>
-      <c r="T22" s="34"/>
+      <c r="R22" s="113">
+        <v>45825</v>
+      </c>
+      <c r="S22" s="33" t="s">
+        <v>64</v>
+      </c>
+      <c r="T22" s="34" t="s">
+        <v>97</v>
+      </c>
       <c r="U22" s="35"/>
       <c r="V22" s="35"/>
       <c r="W22" s="35"/>
@@ -9607,21 +9780,21 @@
       <c r="Z22" s="35"/>
     </row>
     <row r="23" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A23" s="104"/>
+      <c r="A23" s="95"/>
       <c r="B23" s="40"/>
-      <c r="C23" s="105"/>
+      <c r="C23" s="96"/>
       <c r="D23" s="40"/>
-      <c r="E23" s="105"/>
+      <c r="E23" s="96"/>
       <c r="F23" s="40"/>
-      <c r="G23" s="95"/>
+      <c r="G23" s="104"/>
       <c r="H23" s="39"/>
       <c r="I23" s="40"/>
-      <c r="J23" s="95"/>
+      <c r="J23" s="104"/>
       <c r="K23" s="40"/>
-      <c r="L23" s="100"/>
+      <c r="L23" s="102"/>
       <c r="M23" s="39"/>
       <c r="N23" s="40"/>
-      <c r="O23" s="100"/>
+      <c r="O23" s="102"/>
       <c r="P23" s="39"/>
       <c r="Q23" s="40"/>
       <c r="R23" s="33"/>
@@ -9635,21 +9808,21 @@
       <c r="Z23" s="35"/>
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A24" s="104"/>
+      <c r="A24" s="95"/>
       <c r="B24" s="40"/>
-      <c r="C24" s="105"/>
+      <c r="C24" s="96"/>
       <c r="D24" s="40"/>
-      <c r="E24" s="105"/>
+      <c r="E24" s="96"/>
       <c r="F24" s="40"/>
-      <c r="G24" s="95"/>
+      <c r="G24" s="104"/>
       <c r="H24" s="39"/>
       <c r="I24" s="40"/>
-      <c r="J24" s="95"/>
+      <c r="J24" s="104"/>
       <c r="K24" s="40"/>
-      <c r="L24" s="100"/>
+      <c r="L24" s="102"/>
       <c r="M24" s="39"/>
       <c r="N24" s="40"/>
-      <c r="O24" s="100"/>
+      <c r="O24" s="102"/>
       <c r="P24" s="39"/>
       <c r="Q24" s="40"/>
       <c r="R24" s="33"/>
@@ -9663,21 +9836,21 @@
       <c r="Z24" s="35"/>
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A25" s="104"/>
+      <c r="A25" s="95"/>
       <c r="B25" s="40"/>
-      <c r="C25" s="105"/>
+      <c r="C25" s="96"/>
       <c r="D25" s="40"/>
-      <c r="E25" s="105"/>
+      <c r="E25" s="96"/>
       <c r="F25" s="40"/>
-      <c r="G25" s="95"/>
+      <c r="G25" s="104"/>
       <c r="H25" s="39"/>
       <c r="I25" s="40"/>
-      <c r="J25" s="95"/>
+      <c r="J25" s="104"/>
       <c r="K25" s="40"/>
-      <c r="L25" s="100"/>
+      <c r="L25" s="102"/>
       <c r="M25" s="39"/>
       <c r="N25" s="40"/>
-      <c r="O25" s="100"/>
+      <c r="O25" s="102"/>
       <c r="P25" s="39"/>
       <c r="Q25" s="40"/>
       <c r="R25" s="33"/>
@@ -9691,21 +9864,21 @@
       <c r="Z25" s="35"/>
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A26" s="104"/>
+      <c r="A26" s="95"/>
       <c r="B26" s="40"/>
-      <c r="C26" s="105"/>
+      <c r="C26" s="96"/>
       <c r="D26" s="40"/>
-      <c r="E26" s="105"/>
+      <c r="E26" s="96"/>
       <c r="F26" s="40"/>
-      <c r="G26" s="95"/>
+      <c r="G26" s="104"/>
       <c r="H26" s="39"/>
       <c r="I26" s="40"/>
-      <c r="J26" s="95"/>
+      <c r="J26" s="104"/>
       <c r="K26" s="40"/>
-      <c r="L26" s="100"/>
+      <c r="L26" s="102"/>
       <c r="M26" s="39"/>
       <c r="N26" s="40"/>
-      <c r="O26" s="100"/>
+      <c r="O26" s="102"/>
       <c r="P26" s="39"/>
       <c r="Q26" s="40"/>
       <c r="R26" s="33"/>
@@ -9719,21 +9892,21 @@
       <c r="Z26" s="35"/>
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A27" s="104"/>
+      <c r="A27" s="95"/>
       <c r="B27" s="40"/>
-      <c r="C27" s="105"/>
+      <c r="C27" s="96"/>
       <c r="D27" s="40"/>
-      <c r="E27" s="105"/>
+      <c r="E27" s="96"/>
       <c r="F27" s="40"/>
-      <c r="G27" s="95"/>
+      <c r="G27" s="104"/>
       <c r="H27" s="39"/>
       <c r="I27" s="40"/>
-      <c r="J27" s="95"/>
+      <c r="J27" s="104"/>
       <c r="K27" s="40"/>
-      <c r="L27" s="100"/>
+      <c r="L27" s="102"/>
       <c r="M27" s="39"/>
       <c r="N27" s="40"/>
-      <c r="O27" s="100"/>
+      <c r="O27" s="102"/>
       <c r="P27" s="39"/>
       <c r="Q27" s="40"/>
       <c r="R27" s="33"/>
@@ -9747,21 +9920,21 @@
       <c r="Z27" s="35"/>
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A28" s="104"/>
+      <c r="A28" s="95"/>
       <c r="B28" s="40"/>
-      <c r="C28" s="105"/>
+      <c r="C28" s="96"/>
       <c r="D28" s="40"/>
-      <c r="E28" s="105"/>
+      <c r="E28" s="96"/>
       <c r="F28" s="40"/>
-      <c r="G28" s="95"/>
+      <c r="G28" s="104"/>
       <c r="H28" s="39"/>
       <c r="I28" s="40"/>
-      <c r="J28" s="95"/>
+      <c r="J28" s="104"/>
       <c r="K28" s="40"/>
-      <c r="L28" s="100"/>
+      <c r="L28" s="102"/>
       <c r="M28" s="39"/>
       <c r="N28" s="40"/>
-      <c r="O28" s="100"/>
+      <c r="O28" s="102"/>
       <c r="P28" s="39"/>
       <c r="Q28" s="40"/>
       <c r="R28" s="33"/>
@@ -9775,21 +9948,21 @@
       <c r="Z28" s="35"/>
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A29" s="104"/>
+      <c r="A29" s="95"/>
       <c r="B29" s="40"/>
-      <c r="C29" s="105"/>
+      <c r="C29" s="96"/>
       <c r="D29" s="40"/>
-      <c r="E29" s="105"/>
+      <c r="E29" s="96"/>
       <c r="F29" s="40"/>
-      <c r="G29" s="95"/>
+      <c r="G29" s="104"/>
       <c r="H29" s="39"/>
       <c r="I29" s="40"/>
-      <c r="J29" s="95"/>
+      <c r="J29" s="104"/>
       <c r="K29" s="40"/>
-      <c r="L29" s="100"/>
+      <c r="L29" s="102"/>
       <c r="M29" s="39"/>
       <c r="N29" s="40"/>
-      <c r="O29" s="100"/>
+      <c r="O29" s="102"/>
       <c r="P29" s="39"/>
       <c r="Q29" s="40"/>
       <c r="R29" s="33"/>
@@ -9803,21 +9976,21 @@
       <c r="Z29" s="35"/>
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A30" s="104"/>
+      <c r="A30" s="95"/>
       <c r="B30" s="40"/>
-      <c r="C30" s="105"/>
+      <c r="C30" s="96"/>
       <c r="D30" s="40"/>
-      <c r="E30" s="105"/>
+      <c r="E30" s="96"/>
       <c r="F30" s="40"/>
-      <c r="G30" s="95"/>
+      <c r="G30" s="104"/>
       <c r="H30" s="39"/>
       <c r="I30" s="40"/>
-      <c r="J30" s="95"/>
+      <c r="J30" s="104"/>
       <c r="K30" s="40"/>
-      <c r="L30" s="100"/>
+      <c r="L30" s="102"/>
       <c r="M30" s="39"/>
       <c r="N30" s="40"/>
-      <c r="O30" s="100"/>
+      <c r="O30" s="102"/>
       <c r="P30" s="39"/>
       <c r="Q30" s="40"/>
       <c r="R30" s="33"/>
@@ -9831,23 +10004,23 @@
       <c r="Z30" s="35"/>
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A31" s="107"/>
-      <c r="B31" s="67"/>
-      <c r="C31" s="108"/>
-      <c r="D31" s="67"/>
-      <c r="E31" s="108"/>
-      <c r="F31" s="67"/>
-      <c r="G31" s="99"/>
-      <c r="H31" s="66"/>
-      <c r="I31" s="67"/>
-      <c r="J31" s="99"/>
-      <c r="K31" s="67"/>
-      <c r="L31" s="101"/>
-      <c r="M31" s="66"/>
-      <c r="N31" s="67"/>
-      <c r="O31" s="101"/>
-      <c r="P31" s="66"/>
-      <c r="Q31" s="67"/>
+      <c r="A31" s="97"/>
+      <c r="B31" s="56"/>
+      <c r="C31" s="98"/>
+      <c r="D31" s="56"/>
+      <c r="E31" s="98"/>
+      <c r="F31" s="56"/>
+      <c r="G31" s="110"/>
+      <c r="H31" s="47"/>
+      <c r="I31" s="56"/>
+      <c r="J31" s="110"/>
+      <c r="K31" s="56"/>
+      <c r="L31" s="103"/>
+      <c r="M31" s="47"/>
+      <c r="N31" s="56"/>
+      <c r="O31" s="103"/>
+      <c r="P31" s="47"/>
+      <c r="Q31" s="56"/>
       <c r="R31" s="36"/>
       <c r="S31" s="36"/>
       <c r="T31" s="37"/>
@@ -10845,6 +11018,118 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="136">
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:K19"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="K2:N4"/>
+    <mergeCell ref="O2:P4"/>
+    <mergeCell ref="Q2:R4"/>
+    <mergeCell ref="S2:T4"/>
+    <mergeCell ref="A1:F4"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="G5:T5"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="G6:T6"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="G7:T7"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="G20:I20"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="L20:N20"/>
+    <mergeCell ref="O20:Q20"/>
+    <mergeCell ref="L15:N15"/>
+    <mergeCell ref="O15:Q15"/>
+    <mergeCell ref="L16:N16"/>
+    <mergeCell ref="O16:Q16"/>
+    <mergeCell ref="L17:N17"/>
+    <mergeCell ref="O17:Q17"/>
+    <mergeCell ref="O18:Q18"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="O27:Q27"/>
+    <mergeCell ref="O28:Q28"/>
+    <mergeCell ref="O29:Q29"/>
+    <mergeCell ref="O30:Q30"/>
+    <mergeCell ref="O31:Q31"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="O26:Q26"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="A23:B23"/>
     <mergeCell ref="A30:B30"/>
     <mergeCell ref="C30:D30"/>
     <mergeCell ref="E30:F30"/>
@@ -10869,118 +11154,6 @@
     <mergeCell ref="C28:D28"/>
     <mergeCell ref="E28:F28"/>
     <mergeCell ref="A29:B29"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="O27:Q27"/>
-    <mergeCell ref="O28:Q28"/>
-    <mergeCell ref="O29:Q29"/>
-    <mergeCell ref="O30:Q30"/>
-    <mergeCell ref="O31:Q31"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="O26:Q26"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="G5:T5"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="G6:T6"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="G7:T7"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="L20:N20"/>
-    <mergeCell ref="O20:Q20"/>
-    <mergeCell ref="L15:N15"/>
-    <mergeCell ref="O15:Q15"/>
-    <mergeCell ref="L16:N16"/>
-    <mergeCell ref="O16:Q16"/>
-    <mergeCell ref="L17:N17"/>
-    <mergeCell ref="O17:Q17"/>
-    <mergeCell ref="O18:Q18"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="K2:N4"/>
-    <mergeCell ref="O2:P4"/>
-    <mergeCell ref="Q2:R4"/>
-    <mergeCell ref="S2:T4"/>
-    <mergeCell ref="A1:F4"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="G2:J4"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:K19"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <hyperlinks>

--- a/Documents/タスク詳細設計書.xlsx
+++ b/Documents/タスク詳細設計書.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\S-47\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\S-47\Documents\project\taskUN\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A3606C8-031A-4C21-B140-18ACA1DF21D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19A645F2-ADE5-44E6-A4C7-46746459F6B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="100">
   <si>
     <t>プロジェクト型演習　成果ドキュメント</t>
   </si>
@@ -558,6 +558,152 @@
     </rPh>
     <phoneticPr fontId="8"/>
   </si>
+  <si>
+    <t>異常系</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>ログアウト状態でのページ表示</t>
+    <rPh sb="5" eb="7">
+      <t>ジョウタイ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>ログアウト状態であること</t>
+    <rPh sb="5" eb="7">
+      <t>ジョウタイ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>ログインされていませんというメッセージが表示され、その下にログイン画面へ誘導するリンクが表示される</t>
+    <rPh sb="20" eb="22">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>シタ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>ユウドウ</t>
+    </rPh>
+    <rPh sb="44" eb="46">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>http://localhost:8080/taskUN/task-detail.jsp</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>編集ボタンを押下する</t>
+    <rPh sb="0" eb="2">
+      <t>ヘンシュウ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>オウカ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>削除ボタンを押下する</t>
+    <rPh sb="0" eb="2">
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>オウカ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>一覧へ戻るボタンを押下する</t>
+    <rPh sb="0" eb="2">
+      <t>イチラン</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>モド</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>オウカ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>編集画面が表示される</t>
+    <rPh sb="0" eb="4">
+      <t>ヘンシュウガメン</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>削除画面が表示される</t>
+    <rPh sb="0" eb="4">
+      <t>サクジョガメン</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>タスク一覧画面が表示される</t>
+    <rPh sb="3" eb="7">
+      <t>イチランガメン</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>〇</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>自分以外のタスクの詳細表示</t>
+    <rPh sb="0" eb="4">
+      <t>ジブンイガイ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ショウサイ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>編集、削除ボタンは無く一覧へ戻るボタンのみが表示される</t>
+    <rPh sb="0" eb="2">
+      <t>ヘンシュウ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>ナ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>イチラン</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>モド</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
 </sst>
 </file>
 
@@ -566,7 +712,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="[$-411]h:mm"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -636,6 +782,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -1312,11 +1466,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="109">
+  <cellXfs count="114">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1614,6 +1769,15 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -1626,26 +1790,29 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="2" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="56" fontId="7" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
+    <cellStyle name="ハイパーリンク" xfId="2" builtinId="8"/>
     <cellStyle name="標準" xfId="0" builtinId="0"/>
     <cellStyle name="標準 2" xfId="1" xr:uid="{22DBA653-F2E1-482B-8564-0AB808DB1A6C}"/>
   </cellStyles>
@@ -8905,7 +9072,7 @@
       <c r="L2" s="91"/>
       <c r="M2" s="91"/>
       <c r="N2" s="80"/>
-      <c r="O2" s="105">
+      <c r="O2" s="106">
         <v>45818</v>
       </c>
       <c r="P2" s="80"/>
@@ -8958,7 +9125,7 @@
       <c r="Q4" s="82"/>
       <c r="R4" s="64"/>
       <c r="S4" s="82"/>
-      <c r="T4" s="103"/>
+      <c r="T4" s="107"/>
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1">
       <c r="A5" s="86" t="s">
@@ -9239,7 +9406,7 @@
         <v>45</v>
       </c>
       <c r="B15" s="40"/>
-      <c r="C15" s="102" t="s">
+      <c r="C15" s="105" t="s">
         <v>39</v>
       </c>
       <c r="D15" s="40"/>
@@ -9289,28 +9456,34 @@
         <v>55</v>
       </c>
       <c r="F16" s="40"/>
-      <c r="G16" s="101" t="s">
+      <c r="G16" s="104" t="s">
         <v>77</v>
       </c>
       <c r="H16" s="39"/>
       <c r="I16" s="40"/>
-      <c r="J16" s="106" t="s">
+      <c r="J16" s="111" t="s">
         <v>78</v>
       </c>
-      <c r="K16" s="107"/>
-      <c r="L16" s="99" t="s">
+      <c r="K16" s="100"/>
+      <c r="L16" s="102" t="s">
         <v>79</v>
       </c>
       <c r="M16" s="39"/>
       <c r="N16" s="40"/>
-      <c r="O16" s="99" t="s">
+      <c r="O16" s="102" t="s">
         <v>80</v>
       </c>
       <c r="P16" s="39"/>
       <c r="Q16" s="40"/>
-      <c r="R16" s="33"/>
-      <c r="S16" s="33"/>
-      <c r="T16" s="34"/>
+      <c r="R16" s="113">
+        <v>45825</v>
+      </c>
+      <c r="S16" s="33" t="s">
+        <v>64</v>
+      </c>
+      <c r="T16" s="34" t="s">
+        <v>97</v>
+      </c>
       <c r="U16" s="35"/>
       <c r="V16" s="35"/>
       <c r="W16" s="35"/>
@@ -9331,28 +9504,34 @@
         <v>55</v>
       </c>
       <c r="F17" s="40"/>
-      <c r="G17" s="106" t="s">
+      <c r="G17" s="111" t="s">
         <v>81</v>
       </c>
-      <c r="H17" s="108"/>
-      <c r="I17" s="107"/>
-      <c r="J17" s="106" t="s">
+      <c r="H17" s="112"/>
+      <c r="I17" s="100"/>
+      <c r="J17" s="111" t="s">
         <v>78</v>
       </c>
-      <c r="K17" s="107"/>
-      <c r="L17" s="99" t="s">
+      <c r="K17" s="100"/>
+      <c r="L17" s="102" t="s">
         <v>79</v>
       </c>
       <c r="M17" s="39"/>
       <c r="N17" s="40"/>
-      <c r="O17" s="99" t="s">
+      <c r="O17" s="102" t="s">
         <v>82</v>
       </c>
       <c r="P17" s="39"/>
       <c r="Q17" s="40"/>
-      <c r="R17" s="33"/>
-      <c r="S17" s="33"/>
-      <c r="T17" s="34"/>
+      <c r="R17" s="113">
+        <v>45825</v>
+      </c>
+      <c r="S17" s="33" t="s">
+        <v>64</v>
+      </c>
+      <c r="T17" s="34" t="s">
+        <v>97</v>
+      </c>
       <c r="U17" s="35"/>
       <c r="V17" s="35"/>
       <c r="W17" s="35"/>
@@ -9373,22 +9552,34 @@
         <v>55</v>
       </c>
       <c r="F18" s="40"/>
-      <c r="G18" s="101" t="s">
+      <c r="G18" s="104" t="s">
         <v>83</v>
       </c>
       <c r="H18" s="39"/>
       <c r="I18" s="40"/>
-      <c r="J18" s="101"/>
-      <c r="K18" s="40"/>
-      <c r="L18" s="99"/>
+      <c r="J18" s="111" t="s">
+        <v>78</v>
+      </c>
+      <c r="K18" s="100"/>
+      <c r="L18" s="102" t="s">
+        <v>91</v>
+      </c>
       <c r="M18" s="39"/>
       <c r="N18" s="40"/>
-      <c r="O18" s="99"/>
+      <c r="O18" s="102" t="s">
+        <v>94</v>
+      </c>
       <c r="P18" s="39"/>
       <c r="Q18" s="40"/>
-      <c r="R18" s="33"/>
-      <c r="S18" s="33"/>
-      <c r="T18" s="34"/>
+      <c r="R18" s="113">
+        <v>45825</v>
+      </c>
+      <c r="S18" s="33" t="s">
+        <v>64</v>
+      </c>
+      <c r="T18" s="34" t="s">
+        <v>97</v>
+      </c>
       <c r="U18" s="35"/>
       <c r="V18" s="35"/>
       <c r="W18" s="35"/>
@@ -9409,22 +9600,34 @@
         <v>55</v>
       </c>
       <c r="F19" s="40"/>
-      <c r="G19" s="101" t="s">
+      <c r="G19" s="104" t="s">
         <v>84</v>
       </c>
       <c r="H19" s="39"/>
       <c r="I19" s="40"/>
-      <c r="J19" s="101"/>
-      <c r="K19" s="40"/>
-      <c r="L19" s="99"/>
+      <c r="J19" s="111" t="s">
+        <v>78</v>
+      </c>
+      <c r="K19" s="100"/>
+      <c r="L19" s="102" t="s">
+        <v>92</v>
+      </c>
       <c r="M19" s="39"/>
       <c r="N19" s="40"/>
-      <c r="O19" s="99"/>
+      <c r="O19" s="102" t="s">
+        <v>95</v>
+      </c>
       <c r="P19" s="39"/>
       <c r="Q19" s="40"/>
-      <c r="R19" s="33"/>
-      <c r="S19" s="33"/>
-      <c r="T19" s="34"/>
+      <c r="R19" s="113">
+        <v>45825</v>
+      </c>
+      <c r="S19" s="33" t="s">
+        <v>64</v>
+      </c>
+      <c r="T19" s="34" t="s">
+        <v>97</v>
+      </c>
       <c r="U19" s="35"/>
       <c r="V19" s="35"/>
       <c r="W19" s="35"/>
@@ -9445,22 +9648,34 @@
         <v>55</v>
       </c>
       <c r="F20" s="40"/>
-      <c r="G20" s="101" t="s">
+      <c r="G20" s="104" t="s">
         <v>85</v>
       </c>
       <c r="H20" s="39"/>
       <c r="I20" s="40"/>
-      <c r="J20" s="101"/>
-      <c r="K20" s="40"/>
-      <c r="L20" s="99"/>
+      <c r="J20" s="111" t="s">
+        <v>78</v>
+      </c>
+      <c r="K20" s="100"/>
+      <c r="L20" s="102" t="s">
+        <v>93</v>
+      </c>
       <c r="M20" s="39"/>
       <c r="N20" s="40"/>
-      <c r="O20" s="99"/>
+      <c r="O20" s="102" t="s">
+        <v>96</v>
+      </c>
       <c r="P20" s="39"/>
       <c r="Q20" s="40"/>
-      <c r="R20" s="33"/>
-      <c r="S20" s="33"/>
-      <c r="T20" s="34"/>
+      <c r="R20" s="113">
+        <v>45825</v>
+      </c>
+      <c r="S20" s="33" t="s">
+        <v>64</v>
+      </c>
+      <c r="T20" s="34" t="s">
+        <v>97</v>
+      </c>
       <c r="U20" s="35"/>
       <c r="V20" s="35"/>
       <c r="W20" s="35"/>
@@ -9468,27 +9683,47 @@
       <c r="Y20" s="35"/>
       <c r="Z20" s="35"/>
     </row>
-    <row r="21" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A21" s="95"/>
-      <c r="B21" s="40"/>
-      <c r="C21" s="96"/>
-      <c r="D21" s="40"/>
-      <c r="E21" s="96"/>
-      <c r="F21" s="40"/>
-      <c r="G21" s="101"/>
-      <c r="H21" s="39"/>
-      <c r="I21" s="40"/>
-      <c r="J21" s="101"/>
-      <c r="K21" s="40"/>
-      <c r="L21" s="99"/>
-      <c r="M21" s="39"/>
-      <c r="N21" s="40"/>
-      <c r="O21" s="99"/>
+    <row r="21" spans="1:26" ht="53.25" customHeight="1">
+      <c r="A21" s="99">
+        <v>7</v>
+      </c>
+      <c r="B21" s="100"/>
+      <c r="C21" s="101" t="s">
+        <v>54</v>
+      </c>
+      <c r="D21" s="100"/>
+      <c r="E21" s="101" t="s">
+        <v>86</v>
+      </c>
+      <c r="F21" s="100"/>
+      <c r="G21" s="111" t="s">
+        <v>87</v>
+      </c>
+      <c r="H21" s="112"/>
+      <c r="I21" s="100"/>
+      <c r="J21" s="111" t="s">
+        <v>88</v>
+      </c>
+      <c r="K21" s="100"/>
+      <c r="L21" s="108" t="s">
+        <v>90</v>
+      </c>
+      <c r="M21" s="109"/>
+      <c r="N21" s="109"/>
+      <c r="O21" s="102" t="s">
+        <v>89</v>
+      </c>
       <c r="P21" s="39"/>
       <c r="Q21" s="40"/>
-      <c r="R21" s="33"/>
-      <c r="S21" s="33"/>
-      <c r="T21" s="34"/>
+      <c r="R21" s="113">
+        <v>45825</v>
+      </c>
+      <c r="S21" s="33" t="s">
+        <v>64</v>
+      </c>
+      <c r="T21" s="34" t="s">
+        <v>97</v>
+      </c>
       <c r="U21" s="35"/>
       <c r="V21" s="35"/>
       <c r="W21" s="35"/>
@@ -9496,27 +9731,47 @@
       <c r="Y21" s="35"/>
       <c r="Z21" s="35"/>
     </row>
-    <row r="22" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A22" s="95"/>
-      <c r="B22" s="40"/>
-      <c r="C22" s="96"/>
-      <c r="D22" s="40"/>
-      <c r="E22" s="96"/>
+    <row r="22" spans="1:26" ht="62.25" customHeight="1">
+      <c r="A22" s="99">
+        <v>8</v>
+      </c>
+      <c r="B22" s="100"/>
+      <c r="C22" s="101" t="s">
+        <v>54</v>
+      </c>
+      <c r="D22" s="100"/>
+      <c r="E22" s="96" t="s">
+        <v>55</v>
+      </c>
       <c r="F22" s="40"/>
-      <c r="G22" s="101"/>
+      <c r="G22" s="104" t="s">
+        <v>98</v>
+      </c>
       <c r="H22" s="39"/>
       <c r="I22" s="40"/>
-      <c r="J22" s="101"/>
-      <c r="K22" s="40"/>
-      <c r="L22" s="99"/>
+      <c r="J22" s="111" t="s">
+        <v>78</v>
+      </c>
+      <c r="K22" s="100"/>
+      <c r="L22" s="102" t="s">
+        <v>79</v>
+      </c>
       <c r="M22" s="39"/>
       <c r="N22" s="40"/>
-      <c r="O22" s="99"/>
+      <c r="O22" s="102" t="s">
+        <v>99</v>
+      </c>
       <c r="P22" s="39"/>
       <c r="Q22" s="40"/>
-      <c r="R22" s="33"/>
-      <c r="S22" s="33"/>
-      <c r="T22" s="34"/>
+      <c r="R22" s="113">
+        <v>45825</v>
+      </c>
+      <c r="S22" s="33" t="s">
+        <v>64</v>
+      </c>
+      <c r="T22" s="34" t="s">
+        <v>97</v>
+      </c>
       <c r="U22" s="35"/>
       <c r="V22" s="35"/>
       <c r="W22" s="35"/>
@@ -9531,15 +9786,15 @@
       <c r="D23" s="40"/>
       <c r="E23" s="96"/>
       <c r="F23" s="40"/>
-      <c r="G23" s="101"/>
+      <c r="G23" s="104"/>
       <c r="H23" s="39"/>
       <c r="I23" s="40"/>
-      <c r="J23" s="101"/>
+      <c r="J23" s="104"/>
       <c r="K23" s="40"/>
-      <c r="L23" s="99"/>
+      <c r="L23" s="102"/>
       <c r="M23" s="39"/>
       <c r="N23" s="40"/>
-      <c r="O23" s="99"/>
+      <c r="O23" s="102"/>
       <c r="P23" s="39"/>
       <c r="Q23" s="40"/>
       <c r="R23" s="33"/>
@@ -9559,15 +9814,15 @@
       <c r="D24" s="40"/>
       <c r="E24" s="96"/>
       <c r="F24" s="40"/>
-      <c r="G24" s="101"/>
+      <c r="G24" s="104"/>
       <c r="H24" s="39"/>
       <c r="I24" s="40"/>
-      <c r="J24" s="101"/>
+      <c r="J24" s="104"/>
       <c r="K24" s="40"/>
-      <c r="L24" s="99"/>
+      <c r="L24" s="102"/>
       <c r="M24" s="39"/>
       <c r="N24" s="40"/>
-      <c r="O24" s="99"/>
+      <c r="O24" s="102"/>
       <c r="P24" s="39"/>
       <c r="Q24" s="40"/>
       <c r="R24" s="33"/>
@@ -9587,15 +9842,15 @@
       <c r="D25" s="40"/>
       <c r="E25" s="96"/>
       <c r="F25" s="40"/>
-      <c r="G25" s="101"/>
+      <c r="G25" s="104"/>
       <c r="H25" s="39"/>
       <c r="I25" s="40"/>
-      <c r="J25" s="101"/>
+      <c r="J25" s="104"/>
       <c r="K25" s="40"/>
-      <c r="L25" s="99"/>
+      <c r="L25" s="102"/>
       <c r="M25" s="39"/>
       <c r="N25" s="40"/>
-      <c r="O25" s="99"/>
+      <c r="O25" s="102"/>
       <c r="P25" s="39"/>
       <c r="Q25" s="40"/>
       <c r="R25" s="33"/>
@@ -9615,15 +9870,15 @@
       <c r="D26" s="40"/>
       <c r="E26" s="96"/>
       <c r="F26" s="40"/>
-      <c r="G26" s="101"/>
+      <c r="G26" s="104"/>
       <c r="H26" s="39"/>
       <c r="I26" s="40"/>
-      <c r="J26" s="101"/>
+      <c r="J26" s="104"/>
       <c r="K26" s="40"/>
-      <c r="L26" s="99"/>
+      <c r="L26" s="102"/>
       <c r="M26" s="39"/>
       <c r="N26" s="40"/>
-      <c r="O26" s="99"/>
+      <c r="O26" s="102"/>
       <c r="P26" s="39"/>
       <c r="Q26" s="40"/>
       <c r="R26" s="33"/>
@@ -9643,15 +9898,15 @@
       <c r="D27" s="40"/>
       <c r="E27" s="96"/>
       <c r="F27" s="40"/>
-      <c r="G27" s="101"/>
+      <c r="G27" s="104"/>
       <c r="H27" s="39"/>
       <c r="I27" s="40"/>
-      <c r="J27" s="101"/>
+      <c r="J27" s="104"/>
       <c r="K27" s="40"/>
-      <c r="L27" s="99"/>
+      <c r="L27" s="102"/>
       <c r="M27" s="39"/>
       <c r="N27" s="40"/>
-      <c r="O27" s="99"/>
+      <c r="O27" s="102"/>
       <c r="P27" s="39"/>
       <c r="Q27" s="40"/>
       <c r="R27" s="33"/>
@@ -9671,15 +9926,15 @@
       <c r="D28" s="40"/>
       <c r="E28" s="96"/>
       <c r="F28" s="40"/>
-      <c r="G28" s="101"/>
+      <c r="G28" s="104"/>
       <c r="H28" s="39"/>
       <c r="I28" s="40"/>
-      <c r="J28" s="101"/>
+      <c r="J28" s="104"/>
       <c r="K28" s="40"/>
-      <c r="L28" s="99"/>
+      <c r="L28" s="102"/>
       <c r="M28" s="39"/>
       <c r="N28" s="40"/>
-      <c r="O28" s="99"/>
+      <c r="O28" s="102"/>
       <c r="P28" s="39"/>
       <c r="Q28" s="40"/>
       <c r="R28" s="33"/>
@@ -9699,15 +9954,15 @@
       <c r="D29" s="40"/>
       <c r="E29" s="96"/>
       <c r="F29" s="40"/>
-      <c r="G29" s="101"/>
+      <c r="G29" s="104"/>
       <c r="H29" s="39"/>
       <c r="I29" s="40"/>
-      <c r="J29" s="101"/>
+      <c r="J29" s="104"/>
       <c r="K29" s="40"/>
-      <c r="L29" s="99"/>
+      <c r="L29" s="102"/>
       <c r="M29" s="39"/>
       <c r="N29" s="40"/>
-      <c r="O29" s="99"/>
+      <c r="O29" s="102"/>
       <c r="P29" s="39"/>
       <c r="Q29" s="40"/>
       <c r="R29" s="33"/>
@@ -9727,15 +9982,15 @@
       <c r="D30" s="40"/>
       <c r="E30" s="96"/>
       <c r="F30" s="40"/>
-      <c r="G30" s="101"/>
+      <c r="G30" s="104"/>
       <c r="H30" s="39"/>
       <c r="I30" s="40"/>
-      <c r="J30" s="101"/>
+      <c r="J30" s="104"/>
       <c r="K30" s="40"/>
-      <c r="L30" s="99"/>
+      <c r="L30" s="102"/>
       <c r="M30" s="39"/>
       <c r="N30" s="40"/>
-      <c r="O30" s="99"/>
+      <c r="O30" s="102"/>
       <c r="P30" s="39"/>
       <c r="Q30" s="40"/>
       <c r="R30" s="33"/>
@@ -9755,15 +10010,15 @@
       <c r="D31" s="56"/>
       <c r="E31" s="98"/>
       <c r="F31" s="56"/>
-      <c r="G31" s="104"/>
+      <c r="G31" s="110"/>
       <c r="H31" s="47"/>
       <c r="I31" s="56"/>
-      <c r="J31" s="104"/>
+      <c r="J31" s="110"/>
       <c r="K31" s="56"/>
-      <c r="L31" s="100"/>
+      <c r="L31" s="103"/>
       <c r="M31" s="47"/>
       <c r="N31" s="56"/>
-      <c r="O31" s="100"/>
+      <c r="O31" s="103"/>
       <c r="P31" s="47"/>
       <c r="Q31" s="56"/>
       <c r="R31" s="36"/>
@@ -10901,6 +11156,9 @@
     <mergeCell ref="A29:B29"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
+  <hyperlinks>
+    <hyperlink ref="L21" r:id="rId1" xr:uid="{D6AB78BD-D1E9-4052-889B-F174927032CD}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="landscape"/>
 </worksheet>

--- a/Documents/タスク詳細設計書.xlsx
+++ b/Documents/タスク詳細設計書.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\S-47\Documents\project\taskUN\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19A645F2-ADE5-44E6-A4C7-46746459F6B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E85920B7-EA00-452D-A5D1-09CEB6174658}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -683,24 +683,30 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>編集、削除ボタンは無く一覧へ戻るボタンのみが表示される</t>
+    <t>編集、削除ボタンは非活性化し、一覧へ戻るボタンのみ押せる状態となっている</t>
     <rPh sb="0" eb="2">
       <t>ヘンシュウ</t>
     </rPh>
     <rPh sb="3" eb="5">
       <t>サクジョ</t>
     </rPh>
-    <rPh sb="9" eb="10">
-      <t>ナ</t>
+    <rPh sb="9" eb="12">
+      <t>ヒカッセイ</t>
     </rPh>
-    <rPh sb="11" eb="13">
+    <rPh sb="12" eb="13">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
       <t>イチラン</t>
     </rPh>
-    <rPh sb="14" eb="15">
+    <rPh sb="18" eb="19">
       <t>モド</t>
     </rPh>
-    <rPh sb="22" eb="24">
-      <t>ヒョウジ</t>
+    <rPh sb="25" eb="26">
+      <t>オ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>ジョウタイ</t>
     </rPh>
     <phoneticPr fontId="8"/>
   </si>
@@ -1586,6 +1592,9 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="56" fontId="7" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1610,23 +1619,56 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1634,11 +1676,11 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1655,26 +1697,17 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
@@ -1685,49 +1718,22 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1737,6 +1743,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1757,10 +1766,48 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="2" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1768,47 +1815,6 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="2" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="7" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -2393,85 +2399,85 @@
   <sheetData>
     <row r="1" spans="3:16" ht="30" customHeight="1"/>
     <row r="2" spans="3:16" ht="30" customHeight="1">
-      <c r="C2" s="43" t="s">
+      <c r="C2" s="44" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="44"/>
-      <c r="E2" s="44"/>
-      <c r="F2" s="44"/>
-      <c r="G2" s="44"/>
-      <c r="H2" s="44"/>
-      <c r="I2" s="44"/>
-      <c r="J2" s="44"/>
-      <c r="K2" s="44"/>
-      <c r="L2" s="44"/>
-      <c r="M2" s="44"/>
-      <c r="N2" s="44"/>
-      <c r="O2" s="44"/>
+      <c r="D2" s="45"/>
+      <c r="E2" s="45"/>
+      <c r="F2" s="45"/>
+      <c r="G2" s="45"/>
+      <c r="H2" s="45"/>
+      <c r="I2" s="45"/>
+      <c r="J2" s="45"/>
+      <c r="K2" s="45"/>
+      <c r="L2" s="45"/>
+      <c r="M2" s="45"/>
+      <c r="N2" s="45"/>
+      <c r="O2" s="45"/>
       <c r="P2" s="1"/>
     </row>
     <row r="3" spans="3:16" ht="30" customHeight="1">
-      <c r="C3" s="42"/>
-      <c r="D3" s="42"/>
-      <c r="E3" s="42"/>
-      <c r="F3" s="42"/>
-      <c r="G3" s="42"/>
-      <c r="H3" s="42"/>
-      <c r="I3" s="42"/>
-      <c r="J3" s="42"/>
-      <c r="K3" s="42"/>
-      <c r="L3" s="42"/>
-      <c r="M3" s="42"/>
-      <c r="N3" s="42"/>
-      <c r="O3" s="42"/>
+      <c r="C3" s="43"/>
+      <c r="D3" s="43"/>
+      <c r="E3" s="43"/>
+      <c r="F3" s="43"/>
+      <c r="G3" s="43"/>
+      <c r="H3" s="43"/>
+      <c r="I3" s="43"/>
+      <c r="J3" s="43"/>
+      <c r="K3" s="43"/>
+      <c r="L3" s="43"/>
+      <c r="M3" s="43"/>
+      <c r="N3" s="43"/>
+      <c r="O3" s="43"/>
       <c r="P3" s="1"/>
     </row>
     <row r="4" spans="3:16" ht="30" customHeight="1">
-      <c r="C4" s="42"/>
-      <c r="D4" s="42"/>
-      <c r="E4" s="42"/>
-      <c r="F4" s="42"/>
-      <c r="G4" s="42"/>
-      <c r="H4" s="42"/>
-      <c r="I4" s="42"/>
-      <c r="J4" s="42"/>
-      <c r="K4" s="42"/>
-      <c r="L4" s="42"/>
-      <c r="M4" s="42"/>
-      <c r="N4" s="42"/>
-      <c r="O4" s="42"/>
+      <c r="C4" s="43"/>
+      <c r="D4" s="43"/>
+      <c r="E4" s="43"/>
+      <c r="F4" s="43"/>
+      <c r="G4" s="43"/>
+      <c r="H4" s="43"/>
+      <c r="I4" s="43"/>
+      <c r="J4" s="43"/>
+      <c r="K4" s="43"/>
+      <c r="L4" s="43"/>
+      <c r="M4" s="43"/>
+      <c r="N4" s="43"/>
+      <c r="O4" s="43"/>
       <c r="P4" s="1"/>
     </row>
     <row r="5" spans="3:16" ht="30" customHeight="1">
-      <c r="C5" s="42"/>
-      <c r="D5" s="42"/>
-      <c r="E5" s="42"/>
-      <c r="F5" s="42"/>
-      <c r="G5" s="42"/>
-      <c r="H5" s="42"/>
-      <c r="I5" s="42"/>
-      <c r="J5" s="42"/>
-      <c r="K5" s="42"/>
-      <c r="L5" s="42"/>
-      <c r="M5" s="42"/>
-      <c r="N5" s="42"/>
-      <c r="O5" s="42"/>
+      <c r="C5" s="43"/>
+      <c r="D5" s="43"/>
+      <c r="E5" s="43"/>
+      <c r="F5" s="43"/>
+      <c r="G5" s="43"/>
+      <c r="H5" s="43"/>
+      <c r="I5" s="43"/>
+      <c r="J5" s="43"/>
+      <c r="K5" s="43"/>
+      <c r="L5" s="43"/>
+      <c r="M5" s="43"/>
+      <c r="N5" s="43"/>
+      <c r="O5" s="43"/>
       <c r="P5" s="1"/>
     </row>
     <row r="6" spans="3:16" ht="30" customHeight="1">
-      <c r="C6" s="42"/>
-      <c r="D6" s="42"/>
-      <c r="E6" s="42"/>
-      <c r="F6" s="42"/>
-      <c r="G6" s="42"/>
-      <c r="H6" s="42"/>
-      <c r="I6" s="42"/>
-      <c r="J6" s="42"/>
-      <c r="K6" s="42"/>
-      <c r="L6" s="42"/>
-      <c r="M6" s="42"/>
-      <c r="N6" s="42"/>
-      <c r="O6" s="42"/>
+      <c r="C6" s="43"/>
+      <c r="D6" s="43"/>
+      <c r="E6" s="43"/>
+      <c r="F6" s="43"/>
+      <c r="G6" s="43"/>
+      <c r="H6" s="43"/>
+      <c r="I6" s="43"/>
+      <c r="J6" s="43"/>
+      <c r="K6" s="43"/>
+      <c r="L6" s="43"/>
+      <c r="M6" s="43"/>
+      <c r="N6" s="43"/>
+      <c r="O6" s="43"/>
       <c r="P6" s="1"/>
     </row>
     <row r="7" spans="3:16" ht="30" customHeight="1">
@@ -2491,46 +2497,46 @@
       <c r="P7" s="1"/>
     </row>
     <row r="8" spans="3:16" ht="30" customHeight="1">
-      <c r="E8" s="45" t="s">
+      <c r="E8" s="46" t="s">
         <v>1</v>
       </c>
-      <c r="F8" s="42"/>
-      <c r="G8" s="42"/>
-      <c r="H8" s="42"/>
-      <c r="I8" s="42"/>
-      <c r="J8" s="42"/>
-      <c r="K8" s="42"/>
-      <c r="L8" s="42"/>
-      <c r="M8" s="42"/>
+      <c r="F8" s="43"/>
+      <c r="G8" s="43"/>
+      <c r="H8" s="43"/>
+      <c r="I8" s="43"/>
+      <c r="J8" s="43"/>
+      <c r="K8" s="43"/>
+      <c r="L8" s="43"/>
+      <c r="M8" s="43"/>
     </row>
     <row r="9" spans="3:16" ht="30" customHeight="1"/>
     <row r="10" spans="3:16" ht="30" customHeight="1"/>
     <row r="11" spans="3:16" ht="30" customHeight="1"/>
     <row r="12" spans="3:16" ht="30" customHeight="1"/>
     <row r="13" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G13" s="38" t="s">
+      <c r="G13" s="39" t="s">
         <v>2</v>
       </c>
-      <c r="H13" s="40"/>
-      <c r="I13" s="38" t="s">
+      <c r="H13" s="41"/>
+      <c r="I13" s="39" t="s">
         <v>3</v>
       </c>
-      <c r="J13" s="39"/>
-      <c r="K13" s="40"/>
+      <c r="J13" s="40"/>
+      <c r="K13" s="41"/>
     </row>
     <row r="14" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G14" s="38"/>
-      <c r="H14" s="40"/>
-      <c r="I14" s="38"/>
-      <c r="J14" s="39"/>
-      <c r="K14" s="40"/>
+      <c r="G14" s="39"/>
+      <c r="H14" s="41"/>
+      <c r="I14" s="39"/>
+      <c r="J14" s="40"/>
+      <c r="K14" s="41"/>
     </row>
     <row r="15" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G15" s="38"/>
-      <c r="H15" s="40"/>
-      <c r="I15" s="38"/>
-      <c r="J15" s="39"/>
-      <c r="K15" s="40"/>
+      <c r="G15" s="39"/>
+      <c r="H15" s="41"/>
+      <c r="I15" s="39"/>
+      <c r="J15" s="40"/>
+      <c r="K15" s="41"/>
     </row>
     <row r="16" spans="3:16" ht="15.75" customHeight="1">
       <c r="G16" s="3"/>
@@ -2539,13 +2545,13 @@
       <c r="J16" s="3"/>
     </row>
     <row r="17" spans="7:11" ht="30" customHeight="1">
-      <c r="G17" s="41" t="s">
+      <c r="G17" s="42" t="s">
         <v>4</v>
       </c>
-      <c r="H17" s="42"/>
-      <c r="I17" s="42"/>
-      <c r="J17" s="42"/>
-      <c r="K17" s="42"/>
+      <c r="H17" s="43"/>
+      <c r="I17" s="43"/>
+      <c r="J17" s="43"/>
+      <c r="K17" s="43"/>
     </row>
     <row r="18" spans="7:11" ht="14.25" customHeight="1"/>
     <row r="19" spans="7:11" ht="24.75" customHeight="1"/>
@@ -3559,19 +3565,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="57" t="s">
+      <c r="A1" s="69" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="58"/>
-      <c r="C1" s="59"/>
-      <c r="D1" s="78" t="s">
+      <c r="B1" s="70"/>
+      <c r="C1" s="71"/>
+      <c r="D1" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="66"/>
-      <c r="F1" s="78" t="s">
+      <c r="E1" s="48"/>
+      <c r="F1" s="47" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="66"/>
+      <c r="G1" s="48"/>
       <c r="H1" s="5" t="s">
         <v>8</v>
       </c>
@@ -3583,188 +3589,188 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="60"/>
-      <c r="B2" s="42"/>
-      <c r="C2" s="61"/>
-      <c r="D2" s="79" t="s">
+      <c r="A2" s="72"/>
+      <c r="B2" s="43"/>
+      <c r="C2" s="52"/>
+      <c r="D2" s="49" t="s">
         <v>56</v>
       </c>
-      <c r="E2" s="80"/>
-      <c r="F2" s="79" t="s">
+      <c r="E2" s="50"/>
+      <c r="F2" s="49" t="s">
         <v>57</v>
       </c>
-      <c r="G2" s="80"/>
-      <c r="H2" s="83">
+      <c r="G2" s="50"/>
+      <c r="H2" s="55">
         <v>45812</v>
       </c>
-      <c r="I2" s="72" t="s">
+      <c r="I2" s="58" t="s">
         <v>58</v>
       </c>
-      <c r="J2" s="75"/>
+      <c r="J2" s="59"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="60"/>
-      <c r="B3" s="42"/>
-      <c r="C3" s="61"/>
-      <c r="D3" s="81"/>
-      <c r="E3" s="61"/>
-      <c r="F3" s="81"/>
-      <c r="G3" s="61"/>
-      <c r="H3" s="73"/>
-      <c r="I3" s="73"/>
-      <c r="J3" s="76"/>
+      <c r="A3" s="72"/>
+      <c r="B3" s="43"/>
+      <c r="C3" s="52"/>
+      <c r="D3" s="51"/>
+      <c r="E3" s="52"/>
+      <c r="F3" s="51"/>
+      <c r="G3" s="52"/>
+      <c r="H3" s="56"/>
+      <c r="I3" s="56"/>
+      <c r="J3" s="60"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="62"/>
-      <c r="B4" s="63"/>
-      <c r="C4" s="64"/>
-      <c r="D4" s="82"/>
-      <c r="E4" s="64"/>
-      <c r="F4" s="82"/>
-      <c r="G4" s="64"/>
-      <c r="H4" s="74"/>
-      <c r="I4" s="74"/>
-      <c r="J4" s="77"/>
+      <c r="A4" s="73"/>
+      <c r="B4" s="74"/>
+      <c r="C4" s="54"/>
+      <c r="D4" s="53"/>
+      <c r="E4" s="54"/>
+      <c r="F4" s="53"/>
+      <c r="G4" s="54"/>
+      <c r="H4" s="57"/>
+      <c r="I4" s="57"/>
+      <c r="J4" s="61"/>
     </row>
     <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="65" t="s">
+      <c r="A5" s="75" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="50"/>
-      <c r="C5" s="66"/>
-      <c r="D5" s="49" t="s">
+      <c r="B5" s="76"/>
+      <c r="C5" s="48"/>
+      <c r="D5" s="82" t="s">
         <v>59</v>
       </c>
-      <c r="E5" s="50"/>
-      <c r="F5" s="50"/>
-      <c r="G5" s="50"/>
-      <c r="H5" s="50"/>
-      <c r="I5" s="50"/>
-      <c r="J5" s="51"/>
+      <c r="E5" s="76"/>
+      <c r="F5" s="76"/>
+      <c r="G5" s="76"/>
+      <c r="H5" s="76"/>
+      <c r="I5" s="76"/>
+      <c r="J5" s="83"/>
     </row>
     <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="67" t="s">
+      <c r="A6" s="63" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="39"/>
-      <c r="C6" s="40"/>
-      <c r="D6" s="52" t="s">
+      <c r="B6" s="40"/>
+      <c r="C6" s="41"/>
+      <c r="D6" s="64" t="s">
         <v>60</v>
       </c>
-      <c r="E6" s="39"/>
-      <c r="F6" s="39"/>
-      <c r="G6" s="39"/>
-      <c r="H6" s="39"/>
-      <c r="I6" s="39"/>
-      <c r="J6" s="53"/>
+      <c r="E6" s="40"/>
+      <c r="F6" s="40"/>
+      <c r="G6" s="40"/>
+      <c r="H6" s="40"/>
+      <c r="I6" s="40"/>
+      <c r="J6" s="65"/>
     </row>
     <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="67" t="s">
+      <c r="A7" s="63" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="39"/>
-      <c r="C7" s="40"/>
-      <c r="D7" s="52" t="s">
+      <c r="B7" s="40"/>
+      <c r="C7" s="41"/>
+      <c r="D7" s="64" t="s">
         <v>61</v>
       </c>
-      <c r="E7" s="39"/>
-      <c r="F7" s="39"/>
-      <c r="G7" s="39"/>
-      <c r="H7" s="39"/>
-      <c r="I7" s="39"/>
-      <c r="J7" s="53"/>
+      <c r="E7" s="40"/>
+      <c r="F7" s="40"/>
+      <c r="G7" s="40"/>
+      <c r="H7" s="40"/>
+      <c r="I7" s="40"/>
+      <c r="J7" s="65"/>
     </row>
     <row r="8" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A8" s="67" t="s">
+      <c r="A8" s="63" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="39"/>
-      <c r="C8" s="40"/>
-      <c r="D8" s="52" t="s">
+      <c r="B8" s="40"/>
+      <c r="C8" s="41"/>
+      <c r="D8" s="64" t="s">
         <v>62</v>
       </c>
-      <c r="E8" s="39"/>
-      <c r="F8" s="39"/>
-      <c r="G8" s="39"/>
-      <c r="H8" s="39"/>
-      <c r="I8" s="39"/>
-      <c r="J8" s="53"/>
+      <c r="E8" s="40"/>
+      <c r="F8" s="40"/>
+      <c r="G8" s="40"/>
+      <c r="H8" s="40"/>
+      <c r="I8" s="40"/>
+      <c r="J8" s="65"/>
     </row>
     <row r="9" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A9" s="68" t="s">
+      <c r="A9" s="77" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="71" t="s">
+      <c r="B9" s="62" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="40"/>
-      <c r="D9" s="54" t="s">
+      <c r="C9" s="41"/>
+      <c r="D9" s="84" t="s">
         <v>76</v>
       </c>
-      <c r="E9" s="39"/>
-      <c r="F9" s="39"/>
-      <c r="G9" s="39"/>
-      <c r="H9" s="39"/>
-      <c r="I9" s="39"/>
-      <c r="J9" s="53"/>
+      <c r="E9" s="40"/>
+      <c r="F9" s="40"/>
+      <c r="G9" s="40"/>
+      <c r="H9" s="40"/>
+      <c r="I9" s="40"/>
+      <c r="J9" s="65"/>
     </row>
     <row r="10" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A10" s="69"/>
-      <c r="B10" s="71" t="s">
+      <c r="A10" s="78"/>
+      <c r="B10" s="62" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="40"/>
-      <c r="D10" s="52"/>
-      <c r="E10" s="39"/>
-      <c r="F10" s="39"/>
-      <c r="G10" s="39"/>
-      <c r="H10" s="39"/>
-      <c r="I10" s="39"/>
-      <c r="J10" s="53"/>
+      <c r="C10" s="41"/>
+      <c r="D10" s="64"/>
+      <c r="E10" s="40"/>
+      <c r="F10" s="40"/>
+      <c r="G10" s="40"/>
+      <c r="H10" s="40"/>
+      <c r="I10" s="40"/>
+      <c r="J10" s="65"/>
     </row>
     <row r="11" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A11" s="70"/>
-      <c r="B11" s="71" t="s">
+      <c r="A11" s="79"/>
+      <c r="B11" s="62" t="s">
         <v>18</v>
       </c>
-      <c r="C11" s="40"/>
-      <c r="D11" s="52"/>
-      <c r="E11" s="39"/>
-      <c r="F11" s="39"/>
-      <c r="G11" s="39"/>
-      <c r="H11" s="39"/>
-      <c r="I11" s="39"/>
-      <c r="J11" s="53"/>
+      <c r="C11" s="41"/>
+      <c r="D11" s="64"/>
+      <c r="E11" s="40"/>
+      <c r="F11" s="40"/>
+      <c r="G11" s="40"/>
+      <c r="H11" s="40"/>
+      <c r="I11" s="40"/>
+      <c r="J11" s="65"/>
     </row>
     <row r="12" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A12" s="67" t="s">
+      <c r="A12" s="63" t="s">
         <v>19</v>
       </c>
-      <c r="B12" s="39"/>
-      <c r="C12" s="40"/>
-      <c r="D12" s="52" t="s">
+      <c r="B12" s="40"/>
+      <c r="C12" s="41"/>
+      <c r="D12" s="64" t="s">
         <v>63</v>
       </c>
-      <c r="E12" s="39"/>
-      <c r="F12" s="39"/>
-      <c r="G12" s="39"/>
-      <c r="H12" s="39"/>
-      <c r="I12" s="39"/>
-      <c r="J12" s="53"/>
+      <c r="E12" s="40"/>
+      <c r="F12" s="40"/>
+      <c r="G12" s="40"/>
+      <c r="H12" s="40"/>
+      <c r="I12" s="40"/>
+      <c r="J12" s="65"/>
     </row>
     <row r="13" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A13" s="55" t="s">
+      <c r="A13" s="66" t="s">
         <v>20</v>
       </c>
-      <c r="B13" s="47"/>
-      <c r="C13" s="56"/>
-      <c r="D13" s="46"/>
-      <c r="E13" s="47"/>
-      <c r="F13" s="47"/>
-      <c r="G13" s="47"/>
-      <c r="H13" s="47"/>
-      <c r="I13" s="47"/>
-      <c r="J13" s="48"/>
+      <c r="B13" s="67"/>
+      <c r="C13" s="68"/>
+      <c r="D13" s="80"/>
+      <c r="E13" s="67"/>
+      <c r="F13" s="67"/>
+      <c r="G13" s="67"/>
+      <c r="H13" s="67"/>
+      <c r="I13" s="67"/>
+      <c r="J13" s="81"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -4755,17 +4761,14 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="D12:J12"/>
+    <mergeCell ref="D13:J13"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="D6:J6"/>
+    <mergeCell ref="D7:J7"/>
+    <mergeCell ref="D8:J8"/>
+    <mergeCell ref="D9:J9"/>
+    <mergeCell ref="D10:J10"/>
+    <mergeCell ref="D11:J11"/>
     <mergeCell ref="A13:C13"/>
     <mergeCell ref="A1:C4"/>
     <mergeCell ref="A5:C5"/>
@@ -4774,14 +4777,17 @@
     <mergeCell ref="A8:C8"/>
     <mergeCell ref="A9:A11"/>
     <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D13:J13"/>
-    <mergeCell ref="D5:J5"/>
-    <mergeCell ref="D6:J6"/>
-    <mergeCell ref="D7:J7"/>
-    <mergeCell ref="D8:J8"/>
-    <mergeCell ref="D9:J9"/>
-    <mergeCell ref="D10:J10"/>
-    <mergeCell ref="D11:J11"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="D12:J12"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
@@ -4800,19 +4806,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="84" t="s">
+      <c r="A1" s="85" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="58"/>
-      <c r="C1" s="59"/>
-      <c r="D1" s="78" t="s">
+      <c r="B1" s="70"/>
+      <c r="C1" s="71"/>
+      <c r="D1" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="66"/>
-      <c r="F1" s="78" t="s">
+      <c r="E1" s="48"/>
+      <c r="F1" s="47" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="66"/>
+      <c r="G1" s="48"/>
       <c r="H1" s="4" t="s">
         <v>8</v>
       </c>
@@ -4824,48 +4830,48 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="60"/>
-      <c r="B2" s="42"/>
-      <c r="C2" s="61"/>
-      <c r="D2" s="79" t="s">
+      <c r="A2" s="72"/>
+      <c r="B2" s="43"/>
+      <c r="C2" s="52"/>
+      <c r="D2" s="49" t="s">
         <v>56</v>
       </c>
-      <c r="E2" s="80"/>
-      <c r="F2" s="79" t="s">
+      <c r="E2" s="50"/>
+      <c r="F2" s="49" t="s">
         <v>57</v>
       </c>
-      <c r="G2" s="80"/>
-      <c r="H2" s="83">
+      <c r="G2" s="50"/>
+      <c r="H2" s="55">
         <v>45810</v>
       </c>
-      <c r="I2" s="72" t="s">
+      <c r="I2" s="58" t="s">
         <v>64</v>
       </c>
-      <c r="J2" s="75"/>
+      <c r="J2" s="59"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="60"/>
-      <c r="B3" s="42"/>
-      <c r="C3" s="61"/>
-      <c r="D3" s="81"/>
-      <c r="E3" s="61"/>
-      <c r="F3" s="81"/>
-      <c r="G3" s="61"/>
-      <c r="H3" s="73"/>
-      <c r="I3" s="73"/>
-      <c r="J3" s="76"/>
+      <c r="A3" s="72"/>
+      <c r="B3" s="43"/>
+      <c r="C3" s="52"/>
+      <c r="D3" s="51"/>
+      <c r="E3" s="52"/>
+      <c r="F3" s="51"/>
+      <c r="G3" s="52"/>
+      <c r="H3" s="56"/>
+      <c r="I3" s="56"/>
+      <c r="J3" s="60"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="62"/>
-      <c r="B4" s="63"/>
-      <c r="C4" s="64"/>
-      <c r="D4" s="82"/>
-      <c r="E4" s="64"/>
-      <c r="F4" s="82"/>
-      <c r="G4" s="64"/>
-      <c r="H4" s="74"/>
-      <c r="I4" s="74"/>
-      <c r="J4" s="77"/>
+      <c r="A4" s="73"/>
+      <c r="B4" s="74"/>
+      <c r="C4" s="54"/>
+      <c r="D4" s="53"/>
+      <c r="E4" s="54"/>
+      <c r="F4" s="53"/>
+      <c r="G4" s="54"/>
+      <c r="H4" s="57"/>
+      <c r="I4" s="57"/>
+      <c r="J4" s="61"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -6222,19 +6228,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="84" t="s">
+      <c r="A1" s="85" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="58"/>
-      <c r="C1" s="59"/>
-      <c r="D1" s="78" t="s">
+      <c r="B1" s="70"/>
+      <c r="C1" s="71"/>
+      <c r="D1" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="66"/>
-      <c r="F1" s="78" t="s">
+      <c r="E1" s="48"/>
+      <c r="F1" s="47" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="66"/>
+      <c r="G1" s="48"/>
       <c r="H1" s="4" t="s">
         <v>8</v>
       </c>
@@ -6246,48 +6252,48 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="60"/>
-      <c r="B2" s="42"/>
-      <c r="C2" s="61"/>
-      <c r="D2" s="79" t="s">
+      <c r="A2" s="72"/>
+      <c r="B2" s="43"/>
+      <c r="C2" s="52"/>
+      <c r="D2" s="49" t="s">
         <v>56</v>
       </c>
-      <c r="E2" s="80"/>
-      <c r="F2" s="79" t="s">
+      <c r="E2" s="50"/>
+      <c r="F2" s="49" t="s">
         <v>57</v>
       </c>
-      <c r="G2" s="80"/>
-      <c r="H2" s="83">
+      <c r="G2" s="50"/>
+      <c r="H2" s="55">
         <v>45810</v>
       </c>
-      <c r="I2" s="72" t="s">
+      <c r="I2" s="58" t="s">
         <v>64</v>
       </c>
-      <c r="J2" s="75"/>
+      <c r="J2" s="59"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="60"/>
-      <c r="B3" s="42"/>
-      <c r="C3" s="61"/>
-      <c r="D3" s="81"/>
-      <c r="E3" s="61"/>
-      <c r="F3" s="81"/>
-      <c r="G3" s="61"/>
-      <c r="H3" s="73"/>
-      <c r="I3" s="73"/>
-      <c r="J3" s="76"/>
+      <c r="A3" s="72"/>
+      <c r="B3" s="43"/>
+      <c r="C3" s="52"/>
+      <c r="D3" s="51"/>
+      <c r="E3" s="52"/>
+      <c r="F3" s="51"/>
+      <c r="G3" s="52"/>
+      <c r="H3" s="56"/>
+      <c r="I3" s="56"/>
+      <c r="J3" s="60"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="62"/>
-      <c r="B4" s="63"/>
-      <c r="C4" s="64"/>
-      <c r="D4" s="82"/>
-      <c r="E4" s="64"/>
-      <c r="F4" s="82"/>
-      <c r="G4" s="64"/>
-      <c r="H4" s="74"/>
-      <c r="I4" s="74"/>
-      <c r="J4" s="77"/>
+      <c r="A4" s="73"/>
+      <c r="B4" s="74"/>
+      <c r="C4" s="54"/>
+      <c r="D4" s="53"/>
+      <c r="E4" s="54"/>
+      <c r="F4" s="53"/>
+      <c r="G4" s="54"/>
+      <c r="H4" s="57"/>
+      <c r="I4" s="57"/>
+      <c r="J4" s="61"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -7638,19 +7644,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="84" t="s">
+      <c r="A1" s="85" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="58"/>
-      <c r="C1" s="59"/>
-      <c r="D1" s="78" t="s">
+      <c r="B1" s="70"/>
+      <c r="C1" s="71"/>
+      <c r="D1" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="66"/>
-      <c r="F1" s="78" t="s">
+      <c r="E1" s="48"/>
+      <c r="F1" s="47" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="66"/>
+      <c r="G1" s="48"/>
       <c r="H1" s="4" t="s">
         <v>8</v>
       </c>
@@ -7662,190 +7668,190 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="60"/>
-      <c r="B2" s="42"/>
-      <c r="C2" s="61"/>
-      <c r="D2" s="79" t="s">
+      <c r="A2" s="72"/>
+      <c r="B2" s="43"/>
+      <c r="C2" s="52"/>
+      <c r="D2" s="49" t="s">
         <v>56</v>
       </c>
-      <c r="E2" s="80"/>
-      <c r="F2" s="79" t="s">
+      <c r="E2" s="50"/>
+      <c r="F2" s="49" t="s">
         <v>57</v>
       </c>
-      <c r="G2" s="80"/>
-      <c r="H2" s="83">
+      <c r="G2" s="50"/>
+      <c r="H2" s="55">
         <v>45810</v>
       </c>
-      <c r="I2" s="72" t="s">
+      <c r="I2" s="58" t="s">
         <v>64</v>
       </c>
-      <c r="J2" s="75"/>
+      <c r="J2" s="59"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="60"/>
-      <c r="B3" s="42"/>
-      <c r="C3" s="61"/>
-      <c r="D3" s="81"/>
-      <c r="E3" s="61"/>
-      <c r="F3" s="81"/>
-      <c r="G3" s="61"/>
-      <c r="H3" s="73"/>
-      <c r="I3" s="73"/>
-      <c r="J3" s="76"/>
+      <c r="A3" s="72"/>
+      <c r="B3" s="43"/>
+      <c r="C3" s="52"/>
+      <c r="D3" s="51"/>
+      <c r="E3" s="52"/>
+      <c r="F3" s="51"/>
+      <c r="G3" s="52"/>
+      <c r="H3" s="56"/>
+      <c r="I3" s="56"/>
+      <c r="J3" s="60"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="60"/>
-      <c r="B4" s="42"/>
-      <c r="C4" s="61"/>
-      <c r="D4" s="81"/>
-      <c r="E4" s="61"/>
-      <c r="F4" s="81"/>
-      <c r="G4" s="61"/>
-      <c r="H4" s="73"/>
-      <c r="I4" s="73"/>
-      <c r="J4" s="76"/>
+      <c r="A4" s="72"/>
+      <c r="B4" s="43"/>
+      <c r="C4" s="52"/>
+      <c r="D4" s="51"/>
+      <c r="E4" s="52"/>
+      <c r="F4" s="51"/>
+      <c r="G4" s="52"/>
+      <c r="H4" s="56"/>
+      <c r="I4" s="56"/>
+      <c r="J4" s="60"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
       <c r="A5" s="86" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="50"/>
-      <c r="C5" s="66"/>
-      <c r="D5" s="89" t="s">
+      <c r="B5" s="76"/>
+      <c r="C5" s="48"/>
+      <c r="D5" s="90" t="s">
         <v>65</v>
       </c>
-      <c r="E5" s="50"/>
-      <c r="F5" s="50"/>
-      <c r="G5" s="50"/>
-      <c r="H5" s="50"/>
-      <c r="I5" s="50"/>
-      <c r="J5" s="51"/>
+      <c r="E5" s="76"/>
+      <c r="F5" s="76"/>
+      <c r="G5" s="76"/>
+      <c r="H5" s="76"/>
+      <c r="I5" s="76"/>
+      <c r="J5" s="83"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
       <c r="A6" s="88" t="s">
         <v>25</v>
       </c>
-      <c r="B6" s="39"/>
-      <c r="C6" s="39"/>
-      <c r="D6" s="39"/>
-      <c r="E6" s="39"/>
-      <c r="F6" s="39"/>
-      <c r="G6" s="39"/>
-      <c r="H6" s="39"/>
-      <c r="I6" s="39"/>
-      <c r="J6" s="53"/>
+      <c r="B6" s="40"/>
+      <c r="C6" s="40"/>
+      <c r="D6" s="40"/>
+      <c r="E6" s="40"/>
+      <c r="F6" s="40"/>
+      <c r="G6" s="40"/>
+      <c r="H6" s="40"/>
+      <c r="I6" s="40"/>
+      <c r="J6" s="65"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="90"/>
-      <c r="B7" s="91"/>
-      <c r="C7" s="91"/>
-      <c r="D7" s="91"/>
-      <c r="E7" s="91"/>
-      <c r="F7" s="91"/>
-      <c r="G7" s="91"/>
-      <c r="H7" s="91"/>
-      <c r="I7" s="91"/>
-      <c r="J7" s="92"/>
+      <c r="A7" s="91"/>
+      <c r="B7" s="92"/>
+      <c r="C7" s="92"/>
+      <c r="D7" s="92"/>
+      <c r="E7" s="92"/>
+      <c r="F7" s="92"/>
+      <c r="G7" s="92"/>
+      <c r="H7" s="92"/>
+      <c r="I7" s="92"/>
+      <c r="J7" s="93"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="60"/>
-      <c r="B8" s="42"/>
-      <c r="C8" s="42"/>
-      <c r="D8" s="42"/>
-      <c r="E8" s="42"/>
-      <c r="F8" s="42"/>
-      <c r="G8" s="42"/>
-      <c r="H8" s="42"/>
-      <c r="I8" s="42"/>
-      <c r="J8" s="93"/>
+      <c r="A8" s="72"/>
+      <c r="B8" s="43"/>
+      <c r="C8" s="43"/>
+      <c r="D8" s="43"/>
+      <c r="E8" s="43"/>
+      <c r="F8" s="43"/>
+      <c r="G8" s="43"/>
+      <c r="H8" s="43"/>
+      <c r="I8" s="43"/>
+      <c r="J8" s="94"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="60"/>
-      <c r="B9" s="42"/>
-      <c r="C9" s="42"/>
-      <c r="D9" s="42"/>
-      <c r="E9" s="42"/>
-      <c r="F9" s="42"/>
-      <c r="G9" s="42"/>
-      <c r="H9" s="42"/>
-      <c r="I9" s="42"/>
-      <c r="J9" s="93"/>
+      <c r="A9" s="72"/>
+      <c r="B9" s="43"/>
+      <c r="C9" s="43"/>
+      <c r="D9" s="43"/>
+      <c r="E9" s="43"/>
+      <c r="F9" s="43"/>
+      <c r="G9" s="43"/>
+      <c r="H9" s="43"/>
+      <c r="I9" s="43"/>
+      <c r="J9" s="94"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="60"/>
-      <c r="B10" s="42"/>
-      <c r="C10" s="42"/>
-      <c r="D10" s="42"/>
-      <c r="E10" s="42"/>
-      <c r="F10" s="42"/>
-      <c r="G10" s="42"/>
-      <c r="H10" s="42"/>
-      <c r="I10" s="42"/>
-      <c r="J10" s="93"/>
+      <c r="A10" s="72"/>
+      <c r="B10" s="43"/>
+      <c r="C10" s="43"/>
+      <c r="D10" s="43"/>
+      <c r="E10" s="43"/>
+      <c r="F10" s="43"/>
+      <c r="G10" s="43"/>
+      <c r="H10" s="43"/>
+      <c r="I10" s="43"/>
+      <c r="J10" s="94"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="60"/>
-      <c r="B11" s="42"/>
-      <c r="C11" s="42"/>
-      <c r="D11" s="42"/>
-      <c r="E11" s="42"/>
-      <c r="F11" s="42"/>
-      <c r="G11" s="42"/>
-      <c r="H11" s="42"/>
-      <c r="I11" s="42"/>
-      <c r="J11" s="93"/>
+      <c r="A11" s="72"/>
+      <c r="B11" s="43"/>
+      <c r="C11" s="43"/>
+      <c r="D11" s="43"/>
+      <c r="E11" s="43"/>
+      <c r="F11" s="43"/>
+      <c r="G11" s="43"/>
+      <c r="H11" s="43"/>
+      <c r="I11" s="43"/>
+      <c r="J11" s="94"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="60"/>
-      <c r="B12" s="42"/>
-      <c r="C12" s="42"/>
-      <c r="D12" s="42"/>
-      <c r="E12" s="42"/>
-      <c r="F12" s="42"/>
-      <c r="G12" s="42"/>
-      <c r="H12" s="42"/>
-      <c r="I12" s="42"/>
-      <c r="J12" s="93"/>
+      <c r="A12" s="72"/>
+      <c r="B12" s="43"/>
+      <c r="C12" s="43"/>
+      <c r="D12" s="43"/>
+      <c r="E12" s="43"/>
+      <c r="F12" s="43"/>
+      <c r="G12" s="43"/>
+      <c r="H12" s="43"/>
+      <c r="I12" s="43"/>
+      <c r="J12" s="94"/>
     </row>
     <row r="13" spans="1:10" ht="62.25" customHeight="1">
-      <c r="A13" s="60"/>
-      <c r="B13" s="42"/>
-      <c r="C13" s="42"/>
-      <c r="D13" s="42"/>
-      <c r="E13" s="42"/>
-      <c r="F13" s="42"/>
-      <c r="G13" s="42"/>
-      <c r="H13" s="42"/>
-      <c r="I13" s="42"/>
-      <c r="J13" s="93"/>
+      <c r="A13" s="72"/>
+      <c r="B13" s="43"/>
+      <c r="C13" s="43"/>
+      <c r="D13" s="43"/>
+      <c r="E13" s="43"/>
+      <c r="F13" s="43"/>
+      <c r="G13" s="43"/>
+      <c r="H13" s="43"/>
+      <c r="I13" s="43"/>
+      <c r="J13" s="94"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
       <c r="A14" s="88" t="s">
         <v>26</v>
       </c>
-      <c r="B14" s="39"/>
-      <c r="C14" s="39"/>
-      <c r="D14" s="39"/>
-      <c r="E14" s="39"/>
-      <c r="F14" s="39"/>
-      <c r="G14" s="39"/>
-      <c r="H14" s="39"/>
-      <c r="I14" s="39"/>
-      <c r="J14" s="53"/>
+      <c r="B14" s="40"/>
+      <c r="C14" s="40"/>
+      <c r="D14" s="40"/>
+      <c r="E14" s="40"/>
+      <c r="F14" s="40"/>
+      <c r="G14" s="40"/>
+      <c r="H14" s="40"/>
+      <c r="I14" s="40"/>
+      <c r="J14" s="65"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
       <c r="A15" s="88" t="s">
         <v>27</v>
       </c>
-      <c r="B15" s="39"/>
-      <c r="C15" s="40"/>
-      <c r="D15" s="52" t="s">
+      <c r="B15" s="40"/>
+      <c r="C15" s="41"/>
+      <c r="D15" s="64" t="s">
         <v>74</v>
       </c>
-      <c r="E15" s="39"/>
-      <c r="F15" s="39"/>
-      <c r="G15" s="39"/>
-      <c r="H15" s="40"/>
+      <c r="E15" s="40"/>
+      <c r="F15" s="40"/>
+      <c r="G15" s="40"/>
+      <c r="H15" s="41"/>
       <c r="I15" s="15" t="s">
         <v>28</v>
       </c>
@@ -7857,8 +7863,8 @@
       <c r="A16" s="88" t="s">
         <v>29</v>
       </c>
-      <c r="B16" s="39"/>
-      <c r="C16" s="40"/>
+      <c r="B16" s="40"/>
+      <c r="C16" s="41"/>
       <c r="D16" s="15" t="s">
         <v>30</v>
       </c>
@@ -7871,18 +7877,18 @@
       <c r="G16" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="H16" s="94" t="s">
+      <c r="H16" s="95" t="s">
         <v>20</v>
       </c>
-      <c r="I16" s="39"/>
-      <c r="J16" s="53"/>
+      <c r="I16" s="40"/>
+      <c r="J16" s="65"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="85">
+      <c r="A17" s="89">
         <v>1</v>
       </c>
-      <c r="B17" s="39"/>
-      <c r="C17" s="40"/>
+      <c r="B17" s="40"/>
+      <c r="C17" s="41"/>
       <c r="D17" s="17" t="s">
         <v>67</v>
       </c>
@@ -7893,18 +7899,18 @@
       <c r="G17" s="18" t="s">
         <v>71</v>
       </c>
-      <c r="H17" s="52" t="s">
+      <c r="H17" s="64" t="s">
         <v>75</v>
       </c>
-      <c r="I17" s="39"/>
-      <c r="J17" s="53"/>
+      <c r="I17" s="40"/>
+      <c r="J17" s="65"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="85">
+      <c r="A18" s="89">
         <v>2</v>
       </c>
-      <c r="B18" s="39"/>
-      <c r="C18" s="40"/>
+      <c r="B18" s="40"/>
+      <c r="C18" s="41"/>
       <c r="D18" s="17" t="s">
         <v>68</v>
       </c>
@@ -7915,18 +7921,18 @@
       <c r="G18" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="H18" s="52" t="s">
+      <c r="H18" s="64" t="s">
         <v>75</v>
       </c>
-      <c r="I18" s="39"/>
-      <c r="J18" s="53"/>
+      <c r="I18" s="40"/>
+      <c r="J18" s="65"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="85">
+      <c r="A19" s="89">
         <v>3</v>
       </c>
-      <c r="B19" s="39"/>
-      <c r="C19" s="40"/>
+      <c r="B19" s="40"/>
+      <c r="C19" s="41"/>
       <c r="D19" s="17" t="s">
         <v>69</v>
       </c>
@@ -7937,59 +7943,59 @@
       <c r="G19" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="H19" s="52" t="s">
+      <c r="H19" s="64" t="s">
         <v>75</v>
       </c>
-      <c r="I19" s="39"/>
-      <c r="J19" s="53"/>
+      <c r="I19" s="40"/>
+      <c r="J19" s="65"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="85"/>
-      <c r="B20" s="39"/>
-      <c r="C20" s="40"/>
+      <c r="A20" s="89"/>
+      <c r="B20" s="40"/>
+      <c r="C20" s="41"/>
       <c r="D20" s="17"/>
       <c r="E20" s="17"/>
       <c r="F20" s="18"/>
       <c r="G20" s="18"/>
-      <c r="H20" s="52"/>
-      <c r="I20" s="39"/>
-      <c r="J20" s="53"/>
+      <c r="H20" s="64"/>
+      <c r="I20" s="40"/>
+      <c r="J20" s="65"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="85"/>
-      <c r="B21" s="39"/>
-      <c r="C21" s="40"/>
+      <c r="A21" s="89"/>
+      <c r="B21" s="40"/>
+      <c r="C21" s="41"/>
       <c r="D21" s="17"/>
       <c r="E21" s="17"/>
       <c r="F21" s="18"/>
       <c r="G21" s="18"/>
-      <c r="H21" s="52"/>
-      <c r="I21" s="39"/>
-      <c r="J21" s="53"/>
+      <c r="H21" s="64"/>
+      <c r="I21" s="40"/>
+      <c r="J21" s="65"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="85"/>
-      <c r="B22" s="39"/>
-      <c r="C22" s="40"/>
+      <c r="A22" s="89"/>
+      <c r="B22" s="40"/>
+      <c r="C22" s="41"/>
       <c r="D22" s="17"/>
       <c r="E22" s="17"/>
       <c r="F22" s="18"/>
       <c r="G22" s="18"/>
-      <c r="H22" s="52"/>
-      <c r="I22" s="39"/>
-      <c r="J22" s="53"/>
+      <c r="H22" s="64"/>
+      <c r="I22" s="40"/>
+      <c r="J22" s="65"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1">
       <c r="A23" s="87"/>
-      <c r="B23" s="47"/>
-      <c r="C23" s="56"/>
+      <c r="B23" s="67"/>
+      <c r="C23" s="68"/>
       <c r="D23" s="19"/>
       <c r="E23" s="19"/>
       <c r="F23" s="20"/>
       <c r="G23" s="20"/>
-      <c r="H23" s="46"/>
-      <c r="I23" s="47"/>
-      <c r="J23" s="48"/>
+      <c r="H23" s="80"/>
+      <c r="I23" s="67"/>
+      <c r="J23" s="81"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
@@ -8970,11 +8976,16 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A22:C22"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="F1:G1"/>
@@ -8991,16 +9002,11 @@
     <mergeCell ref="H17:J17"/>
     <mergeCell ref="D2:E4"/>
     <mergeCell ref="H23:J23"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A1:C4"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -9020,190 +9026,190 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="57" t="s">
+      <c r="A1" s="69" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="58"/>
-      <c r="C1" s="58"/>
-      <c r="D1" s="58"/>
-      <c r="E1" s="58"/>
-      <c r="F1" s="59"/>
-      <c r="G1" s="78" t="s">
+      <c r="B1" s="70"/>
+      <c r="C1" s="70"/>
+      <c r="D1" s="70"/>
+      <c r="E1" s="70"/>
+      <c r="F1" s="71"/>
+      <c r="G1" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="50"/>
-      <c r="I1" s="50"/>
-      <c r="J1" s="66"/>
-      <c r="K1" s="78" t="s">
+      <c r="H1" s="76"/>
+      <c r="I1" s="76"/>
+      <c r="J1" s="48"/>
+      <c r="K1" s="47" t="s">
         <v>7</v>
       </c>
-      <c r="L1" s="50"/>
-      <c r="M1" s="50"/>
-      <c r="N1" s="66"/>
-      <c r="O1" s="78" t="s">
+      <c r="L1" s="76"/>
+      <c r="M1" s="76"/>
+      <c r="N1" s="48"/>
+      <c r="O1" s="47" t="s">
         <v>8</v>
       </c>
-      <c r="P1" s="66"/>
-      <c r="Q1" s="78" t="s">
+      <c r="P1" s="48"/>
+      <c r="Q1" s="47" t="s">
         <v>9</v>
       </c>
-      <c r="R1" s="66"/>
-      <c r="S1" s="78" t="s">
+      <c r="R1" s="48"/>
+      <c r="S1" s="47" t="s">
         <v>10</v>
       </c>
-      <c r="T1" s="51"/>
+      <c r="T1" s="83"/>
     </row>
     <row r="2" spans="1:26" ht="18" customHeight="1">
-      <c r="A2" s="60"/>
-      <c r="B2" s="42"/>
-      <c r="C2" s="42"/>
-      <c r="D2" s="42"/>
-      <c r="E2" s="42"/>
-      <c r="F2" s="61"/>
-      <c r="G2" s="79" t="s">
+      <c r="A2" s="72"/>
+      <c r="B2" s="43"/>
+      <c r="C2" s="43"/>
+      <c r="D2" s="43"/>
+      <c r="E2" s="43"/>
+      <c r="F2" s="52"/>
+      <c r="G2" s="49" t="s">
         <v>56</v>
       </c>
-      <c r="H2" s="91"/>
-      <c r="I2" s="91"/>
-      <c r="J2" s="80"/>
-      <c r="K2" s="79" t="s">
+      <c r="H2" s="92"/>
+      <c r="I2" s="92"/>
+      <c r="J2" s="50"/>
+      <c r="K2" s="49" t="s">
         <v>57</v>
       </c>
-      <c r="L2" s="91"/>
-      <c r="M2" s="91"/>
-      <c r="N2" s="80"/>
-      <c r="O2" s="106">
+      <c r="L2" s="92"/>
+      <c r="M2" s="92"/>
+      <c r="N2" s="50"/>
+      <c r="O2" s="105">
         <v>45818</v>
       </c>
-      <c r="P2" s="80"/>
-      <c r="Q2" s="79" t="s">
+      <c r="P2" s="50"/>
+      <c r="Q2" s="49" t="s">
         <v>64</v>
       </c>
-      <c r="R2" s="80"/>
-      <c r="S2" s="79"/>
-      <c r="T2" s="92"/>
+      <c r="R2" s="50"/>
+      <c r="S2" s="49"/>
+      <c r="T2" s="93"/>
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
-      <c r="A3" s="60"/>
-      <c r="B3" s="42"/>
-      <c r="C3" s="42"/>
-      <c r="D3" s="42"/>
-      <c r="E3" s="42"/>
-      <c r="F3" s="61"/>
-      <c r="G3" s="81"/>
-      <c r="H3" s="42"/>
-      <c r="I3" s="42"/>
-      <c r="J3" s="61"/>
-      <c r="K3" s="81"/>
-      <c r="L3" s="42"/>
-      <c r="M3" s="42"/>
-      <c r="N3" s="61"/>
-      <c r="O3" s="81"/>
-      <c r="P3" s="61"/>
-      <c r="Q3" s="81"/>
-      <c r="R3" s="61"/>
-      <c r="S3" s="81"/>
-      <c r="T3" s="93"/>
+      <c r="A3" s="72"/>
+      <c r="B3" s="43"/>
+      <c r="C3" s="43"/>
+      <c r="D3" s="43"/>
+      <c r="E3" s="43"/>
+      <c r="F3" s="52"/>
+      <c r="G3" s="51"/>
+      <c r="H3" s="43"/>
+      <c r="I3" s="43"/>
+      <c r="J3" s="52"/>
+      <c r="K3" s="51"/>
+      <c r="L3" s="43"/>
+      <c r="M3" s="43"/>
+      <c r="N3" s="52"/>
+      <c r="O3" s="51"/>
+      <c r="P3" s="52"/>
+      <c r="Q3" s="51"/>
+      <c r="R3" s="52"/>
+      <c r="S3" s="51"/>
+      <c r="T3" s="94"/>
     </row>
     <row r="4" spans="1:26" ht="18" customHeight="1">
-      <c r="A4" s="62"/>
-      <c r="B4" s="63"/>
-      <c r="C4" s="63"/>
-      <c r="D4" s="63"/>
-      <c r="E4" s="63"/>
-      <c r="F4" s="64"/>
-      <c r="G4" s="82"/>
-      <c r="H4" s="63"/>
-      <c r="I4" s="63"/>
-      <c r="J4" s="64"/>
-      <c r="K4" s="82"/>
-      <c r="L4" s="63"/>
-      <c r="M4" s="63"/>
-      <c r="N4" s="64"/>
-      <c r="O4" s="82"/>
-      <c r="P4" s="64"/>
-      <c r="Q4" s="82"/>
-      <c r="R4" s="64"/>
-      <c r="S4" s="82"/>
-      <c r="T4" s="107"/>
+      <c r="A4" s="73"/>
+      <c r="B4" s="74"/>
+      <c r="C4" s="74"/>
+      <c r="D4" s="74"/>
+      <c r="E4" s="74"/>
+      <c r="F4" s="54"/>
+      <c r="G4" s="53"/>
+      <c r="H4" s="74"/>
+      <c r="I4" s="74"/>
+      <c r="J4" s="54"/>
+      <c r="K4" s="53"/>
+      <c r="L4" s="74"/>
+      <c r="M4" s="74"/>
+      <c r="N4" s="54"/>
+      <c r="O4" s="53"/>
+      <c r="P4" s="54"/>
+      <c r="Q4" s="53"/>
+      <c r="R4" s="54"/>
+      <c r="S4" s="53"/>
+      <c r="T4" s="106"/>
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1">
       <c r="A5" s="86" t="s">
         <v>35</v>
       </c>
-      <c r="B5" s="50"/>
-      <c r="C5" s="50"/>
-      <c r="D5" s="50"/>
-      <c r="E5" s="50"/>
-      <c r="F5" s="66"/>
-      <c r="G5" s="49" t="s">
+      <c r="B5" s="76"/>
+      <c r="C5" s="76"/>
+      <c r="D5" s="76"/>
+      <c r="E5" s="76"/>
+      <c r="F5" s="48"/>
+      <c r="G5" s="82" t="s">
         <v>36</v>
       </c>
-      <c r="H5" s="50"/>
-      <c r="I5" s="50"/>
-      <c r="J5" s="50"/>
-      <c r="K5" s="50"/>
-      <c r="L5" s="50"/>
-      <c r="M5" s="50"/>
-      <c r="N5" s="50"/>
-      <c r="O5" s="50"/>
-      <c r="P5" s="50"/>
-      <c r="Q5" s="50"/>
-      <c r="R5" s="50"/>
-      <c r="S5" s="50"/>
-      <c r="T5" s="51"/>
+      <c r="H5" s="76"/>
+      <c r="I5" s="76"/>
+      <c r="J5" s="76"/>
+      <c r="K5" s="76"/>
+      <c r="L5" s="76"/>
+      <c r="M5" s="76"/>
+      <c r="N5" s="76"/>
+      <c r="O5" s="76"/>
+      <c r="P5" s="76"/>
+      <c r="Q5" s="76"/>
+      <c r="R5" s="76"/>
+      <c r="S5" s="76"/>
+      <c r="T5" s="83"/>
     </row>
     <row r="6" spans="1:26" ht="18" customHeight="1">
       <c r="A6" s="88" t="s">
         <v>37</v>
       </c>
-      <c r="B6" s="39"/>
-      <c r="C6" s="39"/>
-      <c r="D6" s="39"/>
-      <c r="E6" s="39"/>
-      <c r="F6" s="40"/>
-      <c r="G6" s="52" t="s">
+      <c r="B6" s="40"/>
+      <c r="C6" s="40"/>
+      <c r="D6" s="40"/>
+      <c r="E6" s="40"/>
+      <c r="F6" s="41"/>
+      <c r="G6" s="64" t="s">
         <v>21</v>
       </c>
-      <c r="H6" s="39"/>
-      <c r="I6" s="39"/>
-      <c r="J6" s="39"/>
-      <c r="K6" s="39"/>
-      <c r="L6" s="39"/>
-      <c r="M6" s="39"/>
-      <c r="N6" s="39"/>
-      <c r="O6" s="39"/>
-      <c r="P6" s="39"/>
-      <c r="Q6" s="39"/>
-      <c r="R6" s="39"/>
-      <c r="S6" s="39"/>
-      <c r="T6" s="53"/>
+      <c r="H6" s="40"/>
+      <c r="I6" s="40"/>
+      <c r="J6" s="40"/>
+      <c r="K6" s="40"/>
+      <c r="L6" s="40"/>
+      <c r="M6" s="40"/>
+      <c r="N6" s="40"/>
+      <c r="O6" s="40"/>
+      <c r="P6" s="40"/>
+      <c r="Q6" s="40"/>
+      <c r="R6" s="40"/>
+      <c r="S6" s="40"/>
+      <c r="T6" s="65"/>
     </row>
     <row r="7" spans="1:26" ht="18" customHeight="1">
       <c r="A7" s="88" t="s">
         <v>38</v>
       </c>
-      <c r="B7" s="39"/>
-      <c r="C7" s="39"/>
-      <c r="D7" s="39"/>
-      <c r="E7" s="39"/>
-      <c r="F7" s="40"/>
-      <c r="G7" s="52" t="s">
+      <c r="B7" s="40"/>
+      <c r="C7" s="40"/>
+      <c r="D7" s="40"/>
+      <c r="E7" s="40"/>
+      <c r="F7" s="41"/>
+      <c r="G7" s="64" t="s">
         <v>59</v>
       </c>
-      <c r="H7" s="39"/>
-      <c r="I7" s="39"/>
-      <c r="J7" s="39"/>
-      <c r="K7" s="39"/>
-      <c r="L7" s="39"/>
-      <c r="M7" s="39"/>
-      <c r="N7" s="39"/>
-      <c r="O7" s="39"/>
-      <c r="P7" s="39"/>
-      <c r="Q7" s="39"/>
-      <c r="R7" s="39"/>
-      <c r="S7" s="39"/>
-      <c r="T7" s="53"/>
+      <c r="H7" s="40"/>
+      <c r="I7" s="40"/>
+      <c r="J7" s="40"/>
+      <c r="K7" s="40"/>
+      <c r="L7" s="40"/>
+      <c r="M7" s="40"/>
+      <c r="N7" s="40"/>
+      <c r="O7" s="40"/>
+      <c r="P7" s="40"/>
+      <c r="Q7" s="40"/>
+      <c r="R7" s="40"/>
+      <c r="S7" s="40"/>
+      <c r="T7" s="65"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
       <c r="A8" s="8"/>
@@ -9405,34 +9411,34 @@
       <c r="A15" s="88" t="s">
         <v>45</v>
       </c>
-      <c r="B15" s="40"/>
-      <c r="C15" s="105" t="s">
+      <c r="B15" s="41"/>
+      <c r="C15" s="109" t="s">
         <v>39</v>
       </c>
-      <c r="D15" s="40"/>
-      <c r="E15" s="94" t="s">
+      <c r="D15" s="41"/>
+      <c r="E15" s="95" t="s">
         <v>46</v>
       </c>
-      <c r="F15" s="40"/>
-      <c r="G15" s="94" t="s">
+      <c r="F15" s="41"/>
+      <c r="G15" s="95" t="s">
         <v>47</v>
       </c>
-      <c r="H15" s="39"/>
-      <c r="I15" s="40"/>
-      <c r="J15" s="94" t="s">
+      <c r="H15" s="40"/>
+      <c r="I15" s="41"/>
+      <c r="J15" s="95" t="s">
         <v>48</v>
       </c>
-      <c r="K15" s="40"/>
-      <c r="L15" s="94" t="s">
+      <c r="K15" s="41"/>
+      <c r="L15" s="95" t="s">
         <v>49</v>
       </c>
-      <c r="M15" s="39"/>
-      <c r="N15" s="40"/>
-      <c r="O15" s="94" t="s">
+      <c r="M15" s="40"/>
+      <c r="N15" s="41"/>
+      <c r="O15" s="95" t="s">
         <v>50</v>
       </c>
-      <c r="P15" s="39"/>
-      <c r="Q15" s="40"/>
+      <c r="P15" s="40"/>
+      <c r="Q15" s="41"/>
       <c r="R15" s="15" t="s">
         <v>51</v>
       </c>
@@ -9444,38 +9450,38 @@
       </c>
     </row>
     <row r="16" spans="1:26" ht="48" customHeight="1">
-      <c r="A16" s="95">
+      <c r="A16" s="107">
         <v>1</v>
       </c>
-      <c r="B16" s="40"/>
-      <c r="C16" s="96" t="s">
+      <c r="B16" s="41"/>
+      <c r="C16" s="108" t="s">
         <v>54</v>
       </c>
-      <c r="D16" s="40"/>
-      <c r="E16" s="96" t="s">
+      <c r="D16" s="41"/>
+      <c r="E16" s="108" t="s">
         <v>55</v>
       </c>
-      <c r="F16" s="40"/>
-      <c r="G16" s="104" t="s">
+      <c r="F16" s="41"/>
+      <c r="G16" s="96" t="s">
         <v>77</v>
       </c>
-      <c r="H16" s="39"/>
-      <c r="I16" s="40"/>
-      <c r="J16" s="111" t="s">
+      <c r="H16" s="40"/>
+      <c r="I16" s="41"/>
+      <c r="J16" s="97" t="s">
         <v>78</v>
       </c>
-      <c r="K16" s="100"/>
-      <c r="L16" s="102" t="s">
+      <c r="K16" s="98"/>
+      <c r="L16" s="101" t="s">
         <v>79</v>
       </c>
-      <c r="M16" s="39"/>
-      <c r="N16" s="40"/>
-      <c r="O16" s="102" t="s">
+      <c r="M16" s="40"/>
+      <c r="N16" s="41"/>
+      <c r="O16" s="101" t="s">
         <v>80</v>
       </c>
-      <c r="P16" s="39"/>
-      <c r="Q16" s="40"/>
-      <c r="R16" s="113">
+      <c r="P16" s="40"/>
+      <c r="Q16" s="41"/>
+      <c r="R16" s="38">
         <v>45825</v>
       </c>
       <c r="S16" s="33" t="s">
@@ -9492,38 +9498,38 @@
       <c r="Z16" s="35"/>
     </row>
     <row r="17" spans="1:26" ht="51" customHeight="1">
-      <c r="A17" s="95">
+      <c r="A17" s="107">
         <v>2</v>
       </c>
-      <c r="B17" s="40"/>
-      <c r="C17" s="96" t="s">
+      <c r="B17" s="41"/>
+      <c r="C17" s="108" t="s">
         <v>54</v>
       </c>
-      <c r="D17" s="40"/>
-      <c r="E17" s="96" t="s">
+      <c r="D17" s="41"/>
+      <c r="E17" s="108" t="s">
         <v>55</v>
       </c>
-      <c r="F17" s="40"/>
-      <c r="G17" s="111" t="s">
+      <c r="F17" s="41"/>
+      <c r="G17" s="97" t="s">
         <v>81</v>
       </c>
-      <c r="H17" s="112"/>
-      <c r="I17" s="100"/>
-      <c r="J17" s="111" t="s">
+      <c r="H17" s="99"/>
+      <c r="I17" s="98"/>
+      <c r="J17" s="97" t="s">
         <v>78</v>
       </c>
-      <c r="K17" s="100"/>
-      <c r="L17" s="102" t="s">
+      <c r="K17" s="98"/>
+      <c r="L17" s="101" t="s">
         <v>79</v>
       </c>
-      <c r="M17" s="39"/>
-      <c r="N17" s="40"/>
-      <c r="O17" s="102" t="s">
+      <c r="M17" s="40"/>
+      <c r="N17" s="41"/>
+      <c r="O17" s="101" t="s">
         <v>82</v>
       </c>
-      <c r="P17" s="39"/>
-      <c r="Q17" s="40"/>
-      <c r="R17" s="113">
+      <c r="P17" s="40"/>
+      <c r="Q17" s="41"/>
+      <c r="R17" s="38">
         <v>45825</v>
       </c>
       <c r="S17" s="33" t="s">
@@ -9540,38 +9546,38 @@
       <c r="Z17" s="35"/>
     </row>
     <row r="18" spans="1:26" ht="59.25" customHeight="1">
-      <c r="A18" s="95">
+      <c r="A18" s="107">
         <v>3</v>
       </c>
-      <c r="B18" s="40"/>
-      <c r="C18" s="96" t="s">
+      <c r="B18" s="41"/>
+      <c r="C18" s="108" t="s">
         <v>54</v>
       </c>
-      <c r="D18" s="40"/>
-      <c r="E18" s="96" t="s">
+      <c r="D18" s="41"/>
+      <c r="E18" s="108" t="s">
         <v>55</v>
       </c>
-      <c r="F18" s="40"/>
-      <c r="G18" s="104" t="s">
+      <c r="F18" s="41"/>
+      <c r="G18" s="96" t="s">
         <v>83</v>
       </c>
-      <c r="H18" s="39"/>
-      <c r="I18" s="40"/>
-      <c r="J18" s="111" t="s">
+      <c r="H18" s="40"/>
+      <c r="I18" s="41"/>
+      <c r="J18" s="97" t="s">
         <v>78</v>
       </c>
-      <c r="K18" s="100"/>
-      <c r="L18" s="102" t="s">
+      <c r="K18" s="98"/>
+      <c r="L18" s="101" t="s">
         <v>91</v>
       </c>
-      <c r="M18" s="39"/>
-      <c r="N18" s="40"/>
-      <c r="O18" s="102" t="s">
+      <c r="M18" s="40"/>
+      <c r="N18" s="41"/>
+      <c r="O18" s="101" t="s">
         <v>94</v>
       </c>
-      <c r="P18" s="39"/>
-      <c r="Q18" s="40"/>
-      <c r="R18" s="113">
+      <c r="P18" s="40"/>
+      <c r="Q18" s="41"/>
+      <c r="R18" s="38">
         <v>45825</v>
       </c>
       <c r="S18" s="33" t="s">
@@ -9588,38 +9594,38 @@
       <c r="Z18" s="35"/>
     </row>
     <row r="19" spans="1:26" ht="51.75" customHeight="1">
-      <c r="A19" s="95">
+      <c r="A19" s="107">
         <v>4</v>
       </c>
-      <c r="B19" s="40"/>
-      <c r="C19" s="96" t="s">
+      <c r="B19" s="41"/>
+      <c r="C19" s="108" t="s">
         <v>54</v>
       </c>
-      <c r="D19" s="40"/>
-      <c r="E19" s="96" t="s">
+      <c r="D19" s="41"/>
+      <c r="E19" s="108" t="s">
         <v>55</v>
       </c>
-      <c r="F19" s="40"/>
-      <c r="G19" s="104" t="s">
+      <c r="F19" s="41"/>
+      <c r="G19" s="96" t="s">
         <v>84</v>
       </c>
-      <c r="H19" s="39"/>
-      <c r="I19" s="40"/>
-      <c r="J19" s="111" t="s">
+      <c r="H19" s="40"/>
+      <c r="I19" s="41"/>
+      <c r="J19" s="97" t="s">
         <v>78</v>
       </c>
-      <c r="K19" s="100"/>
-      <c r="L19" s="102" t="s">
+      <c r="K19" s="98"/>
+      <c r="L19" s="101" t="s">
         <v>92</v>
       </c>
-      <c r="M19" s="39"/>
-      <c r="N19" s="40"/>
-      <c r="O19" s="102" t="s">
+      <c r="M19" s="40"/>
+      <c r="N19" s="41"/>
+      <c r="O19" s="101" t="s">
         <v>95</v>
       </c>
-      <c r="P19" s="39"/>
-      <c r="Q19" s="40"/>
-      <c r="R19" s="113">
+      <c r="P19" s="40"/>
+      <c r="Q19" s="41"/>
+      <c r="R19" s="38">
         <v>45825</v>
       </c>
       <c r="S19" s="33" t="s">
@@ -9636,38 +9642,38 @@
       <c r="Z19" s="35"/>
     </row>
     <row r="20" spans="1:26" ht="54" customHeight="1">
-      <c r="A20" s="95">
+      <c r="A20" s="107">
         <v>5</v>
       </c>
-      <c r="B20" s="40"/>
-      <c r="C20" s="96" t="s">
+      <c r="B20" s="41"/>
+      <c r="C20" s="108" t="s">
         <v>54</v>
       </c>
-      <c r="D20" s="40"/>
-      <c r="E20" s="96" t="s">
+      <c r="D20" s="41"/>
+      <c r="E20" s="108" t="s">
         <v>55</v>
       </c>
-      <c r="F20" s="40"/>
-      <c r="G20" s="104" t="s">
+      <c r="F20" s="41"/>
+      <c r="G20" s="96" t="s">
         <v>85</v>
       </c>
-      <c r="H20" s="39"/>
-      <c r="I20" s="40"/>
-      <c r="J20" s="111" t="s">
+      <c r="H20" s="40"/>
+      <c r="I20" s="41"/>
+      <c r="J20" s="97" t="s">
         <v>78</v>
       </c>
-      <c r="K20" s="100"/>
-      <c r="L20" s="102" t="s">
+      <c r="K20" s="98"/>
+      <c r="L20" s="101" t="s">
         <v>93</v>
       </c>
-      <c r="M20" s="39"/>
-      <c r="N20" s="40"/>
-      <c r="O20" s="102" t="s">
+      <c r="M20" s="40"/>
+      <c r="N20" s="41"/>
+      <c r="O20" s="101" t="s">
         <v>96</v>
       </c>
-      <c r="P20" s="39"/>
-      <c r="Q20" s="40"/>
-      <c r="R20" s="113">
+      <c r="P20" s="40"/>
+      <c r="Q20" s="41"/>
+      <c r="R20" s="38">
         <v>45825</v>
       </c>
       <c r="S20" s="33" t="s">
@@ -9684,38 +9690,38 @@
       <c r="Z20" s="35"/>
     </row>
     <row r="21" spans="1:26" ht="53.25" customHeight="1">
-      <c r="A21" s="99">
+      <c r="A21" s="110">
         <v>7</v>
       </c>
-      <c r="B21" s="100"/>
-      <c r="C21" s="101" t="s">
+      <c r="B21" s="98"/>
+      <c r="C21" s="111" t="s">
         <v>54</v>
       </c>
-      <c r="D21" s="100"/>
-      <c r="E21" s="101" t="s">
+      <c r="D21" s="98"/>
+      <c r="E21" s="111" t="s">
         <v>86</v>
       </c>
-      <c r="F21" s="100"/>
-      <c r="G21" s="111" t="s">
+      <c r="F21" s="98"/>
+      <c r="G21" s="97" t="s">
         <v>87</v>
       </c>
-      <c r="H21" s="112"/>
-      <c r="I21" s="100"/>
-      <c r="J21" s="111" t="s">
+      <c r="H21" s="99"/>
+      <c r="I21" s="98"/>
+      <c r="J21" s="97" t="s">
         <v>88</v>
       </c>
-      <c r="K21" s="100"/>
-      <c r="L21" s="108" t="s">
+      <c r="K21" s="98"/>
+      <c r="L21" s="103" t="s">
         <v>90</v>
       </c>
-      <c r="M21" s="109"/>
-      <c r="N21" s="109"/>
-      <c r="O21" s="102" t="s">
+      <c r="M21" s="104"/>
+      <c r="N21" s="104"/>
+      <c r="O21" s="101" t="s">
         <v>89</v>
       </c>
-      <c r="P21" s="39"/>
-      <c r="Q21" s="40"/>
-      <c r="R21" s="113">
+      <c r="P21" s="40"/>
+      <c r="Q21" s="41"/>
+      <c r="R21" s="38">
         <v>45825</v>
       </c>
       <c r="S21" s="33" t="s">
@@ -9732,38 +9738,38 @@
       <c r="Z21" s="35"/>
     </row>
     <row r="22" spans="1:26" ht="62.25" customHeight="1">
-      <c r="A22" s="99">
+      <c r="A22" s="110">
         <v>8</v>
       </c>
-      <c r="B22" s="100"/>
-      <c r="C22" s="101" t="s">
+      <c r="B22" s="98"/>
+      <c r="C22" s="111" t="s">
         <v>54</v>
       </c>
-      <c r="D22" s="100"/>
-      <c r="E22" s="96" t="s">
+      <c r="D22" s="98"/>
+      <c r="E22" s="108" t="s">
         <v>55</v>
       </c>
-      <c r="F22" s="40"/>
-      <c r="G22" s="104" t="s">
+      <c r="F22" s="41"/>
+      <c r="G22" s="96" t="s">
         <v>98</v>
       </c>
-      <c r="H22" s="39"/>
-      <c r="I22" s="40"/>
-      <c r="J22" s="111" t="s">
+      <c r="H22" s="40"/>
+      <c r="I22" s="41"/>
+      <c r="J22" s="97" t="s">
         <v>78</v>
       </c>
-      <c r="K22" s="100"/>
-      <c r="L22" s="102" t="s">
+      <c r="K22" s="98"/>
+      <c r="L22" s="101" t="s">
         <v>79</v>
       </c>
-      <c r="M22" s="39"/>
-      <c r="N22" s="40"/>
-      <c r="O22" s="102" t="s">
+      <c r="M22" s="40"/>
+      <c r="N22" s="41"/>
+      <c r="O22" s="101" t="s">
         <v>99</v>
       </c>
-      <c r="P22" s="39"/>
-      <c r="Q22" s="40"/>
-      <c r="R22" s="113">
+      <c r="P22" s="40"/>
+      <c r="Q22" s="41"/>
+      <c r="R22" s="38">
         <v>45825</v>
       </c>
       <c r="S22" s="33" t="s">
@@ -9779,24 +9785,24 @@
       <c r="Y22" s="35"/>
       <c r="Z22" s="35"/>
     </row>
-    <row r="23" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A23" s="95"/>
-      <c r="B23" s="40"/>
-      <c r="C23" s="96"/>
-      <c r="D23" s="40"/>
-      <c r="E23" s="96"/>
-      <c r="F23" s="40"/>
-      <c r="G23" s="104"/>
-      <c r="H23" s="39"/>
-      <c r="I23" s="40"/>
-      <c r="J23" s="104"/>
-      <c r="K23" s="40"/>
-      <c r="L23" s="102"/>
-      <c r="M23" s="39"/>
-      <c r="N23" s="40"/>
-      <c r="O23" s="102"/>
-      <c r="P23" s="39"/>
-      <c r="Q23" s="40"/>
+    <row r="23" spans="1:26" ht="53.25" customHeight="1">
+      <c r="A23" s="107"/>
+      <c r="B23" s="41"/>
+      <c r="C23" s="108"/>
+      <c r="D23" s="41"/>
+      <c r="E23" s="108"/>
+      <c r="F23" s="41"/>
+      <c r="G23" s="96"/>
+      <c r="H23" s="40"/>
+      <c r="I23" s="41"/>
+      <c r="J23" s="96"/>
+      <c r="K23" s="41"/>
+      <c r="L23" s="101"/>
+      <c r="M23" s="40"/>
+      <c r="N23" s="41"/>
+      <c r="O23" s="101"/>
+      <c r="P23" s="40"/>
+      <c r="Q23" s="41"/>
       <c r="R23" s="33"/>
       <c r="S23" s="33"/>
       <c r="T23" s="34"/>
@@ -9808,23 +9814,23 @@
       <c r="Z23" s="35"/>
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A24" s="95"/>
-      <c r="B24" s="40"/>
-      <c r="C24" s="96"/>
-      <c r="D24" s="40"/>
-      <c r="E24" s="96"/>
-      <c r="F24" s="40"/>
-      <c r="G24" s="104"/>
-      <c r="H24" s="39"/>
-      <c r="I24" s="40"/>
-      <c r="J24" s="104"/>
-      <c r="K24" s="40"/>
-      <c r="L24" s="102"/>
-      <c r="M24" s="39"/>
-      <c r="N24" s="40"/>
-      <c r="O24" s="102"/>
-      <c r="P24" s="39"/>
-      <c r="Q24" s="40"/>
+      <c r="A24" s="107"/>
+      <c r="B24" s="41"/>
+      <c r="C24" s="108"/>
+      <c r="D24" s="41"/>
+      <c r="E24" s="108"/>
+      <c r="F24" s="41"/>
+      <c r="G24" s="96"/>
+      <c r="H24" s="40"/>
+      <c r="I24" s="41"/>
+      <c r="J24" s="96"/>
+      <c r="K24" s="41"/>
+      <c r="L24" s="101"/>
+      <c r="M24" s="40"/>
+      <c r="N24" s="41"/>
+      <c r="O24" s="101"/>
+      <c r="P24" s="40"/>
+      <c r="Q24" s="41"/>
       <c r="R24" s="33"/>
       <c r="S24" s="33"/>
       <c r="T24" s="34"/>
@@ -9836,23 +9842,23 @@
       <c r="Z24" s="35"/>
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A25" s="95"/>
-      <c r="B25" s="40"/>
-      <c r="C25" s="96"/>
-      <c r="D25" s="40"/>
-      <c r="E25" s="96"/>
-      <c r="F25" s="40"/>
-      <c r="G25" s="104"/>
-      <c r="H25" s="39"/>
-      <c r="I25" s="40"/>
-      <c r="J25" s="104"/>
-      <c r="K25" s="40"/>
-      <c r="L25" s="102"/>
-      <c r="M25" s="39"/>
-      <c r="N25" s="40"/>
-      <c r="O25" s="102"/>
-      <c r="P25" s="39"/>
-      <c r="Q25" s="40"/>
+      <c r="A25" s="107"/>
+      <c r="B25" s="41"/>
+      <c r="C25" s="108"/>
+      <c r="D25" s="41"/>
+      <c r="E25" s="108"/>
+      <c r="F25" s="41"/>
+      <c r="G25" s="96"/>
+      <c r="H25" s="40"/>
+      <c r="I25" s="41"/>
+      <c r="J25" s="96"/>
+      <c r="K25" s="41"/>
+      <c r="L25" s="101"/>
+      <c r="M25" s="40"/>
+      <c r="N25" s="41"/>
+      <c r="O25" s="101"/>
+      <c r="P25" s="40"/>
+      <c r="Q25" s="41"/>
       <c r="R25" s="33"/>
       <c r="S25" s="33"/>
       <c r="T25" s="34"/>
@@ -9864,23 +9870,23 @@
       <c r="Z25" s="35"/>
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A26" s="95"/>
-      <c r="B26" s="40"/>
-      <c r="C26" s="96"/>
-      <c r="D26" s="40"/>
-      <c r="E26" s="96"/>
-      <c r="F26" s="40"/>
-      <c r="G26" s="104"/>
-      <c r="H26" s="39"/>
-      <c r="I26" s="40"/>
-      <c r="J26" s="104"/>
-      <c r="K26" s="40"/>
-      <c r="L26" s="102"/>
-      <c r="M26" s="39"/>
-      <c r="N26" s="40"/>
-      <c r="O26" s="102"/>
-      <c r="P26" s="39"/>
-      <c r="Q26" s="40"/>
+      <c r="A26" s="107"/>
+      <c r="B26" s="41"/>
+      <c r="C26" s="108"/>
+      <c r="D26" s="41"/>
+      <c r="E26" s="108"/>
+      <c r="F26" s="41"/>
+      <c r="G26" s="96"/>
+      <c r="H26" s="40"/>
+      <c r="I26" s="41"/>
+      <c r="J26" s="96"/>
+      <c r="K26" s="41"/>
+      <c r="L26" s="101"/>
+      <c r="M26" s="40"/>
+      <c r="N26" s="41"/>
+      <c r="O26" s="101"/>
+      <c r="P26" s="40"/>
+      <c r="Q26" s="41"/>
       <c r="R26" s="33"/>
       <c r="S26" s="33"/>
       <c r="T26" s="34"/>
@@ -9892,23 +9898,23 @@
       <c r="Z26" s="35"/>
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A27" s="95"/>
-      <c r="B27" s="40"/>
-      <c r="C27" s="96"/>
-      <c r="D27" s="40"/>
-      <c r="E27" s="96"/>
-      <c r="F27" s="40"/>
-      <c r="G27" s="104"/>
-      <c r="H27" s="39"/>
-      <c r="I27" s="40"/>
-      <c r="J27" s="104"/>
-      <c r="K27" s="40"/>
-      <c r="L27" s="102"/>
-      <c r="M27" s="39"/>
-      <c r="N27" s="40"/>
-      <c r="O27" s="102"/>
-      <c r="P27" s="39"/>
-      <c r="Q27" s="40"/>
+      <c r="A27" s="107"/>
+      <c r="B27" s="41"/>
+      <c r="C27" s="108"/>
+      <c r="D27" s="41"/>
+      <c r="E27" s="108"/>
+      <c r="F27" s="41"/>
+      <c r="G27" s="96"/>
+      <c r="H27" s="40"/>
+      <c r="I27" s="41"/>
+      <c r="J27" s="96"/>
+      <c r="K27" s="41"/>
+      <c r="L27" s="101"/>
+      <c r="M27" s="40"/>
+      <c r="N27" s="41"/>
+      <c r="O27" s="101"/>
+      <c r="P27" s="40"/>
+      <c r="Q27" s="41"/>
       <c r="R27" s="33"/>
       <c r="S27" s="33"/>
       <c r="T27" s="34"/>
@@ -9920,23 +9926,23 @@
       <c r="Z27" s="35"/>
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A28" s="95"/>
-      <c r="B28" s="40"/>
-      <c r="C28" s="96"/>
-      <c r="D28" s="40"/>
-      <c r="E28" s="96"/>
-      <c r="F28" s="40"/>
-      <c r="G28" s="104"/>
-      <c r="H28" s="39"/>
-      <c r="I28" s="40"/>
-      <c r="J28" s="104"/>
-      <c r="K28" s="40"/>
-      <c r="L28" s="102"/>
-      <c r="M28" s="39"/>
-      <c r="N28" s="40"/>
-      <c r="O28" s="102"/>
-      <c r="P28" s="39"/>
-      <c r="Q28" s="40"/>
+      <c r="A28" s="107"/>
+      <c r="B28" s="41"/>
+      <c r="C28" s="108"/>
+      <c r="D28" s="41"/>
+      <c r="E28" s="108"/>
+      <c r="F28" s="41"/>
+      <c r="G28" s="96"/>
+      <c r="H28" s="40"/>
+      <c r="I28" s="41"/>
+      <c r="J28" s="96"/>
+      <c r="K28" s="41"/>
+      <c r="L28" s="101"/>
+      <c r="M28" s="40"/>
+      <c r="N28" s="41"/>
+      <c r="O28" s="101"/>
+      <c r="P28" s="40"/>
+      <c r="Q28" s="41"/>
       <c r="R28" s="33"/>
       <c r="S28" s="33"/>
       <c r="T28" s="34"/>
@@ -9948,23 +9954,23 @@
       <c r="Z28" s="35"/>
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A29" s="95"/>
-      <c r="B29" s="40"/>
-      <c r="C29" s="96"/>
-      <c r="D29" s="40"/>
-      <c r="E29" s="96"/>
-      <c r="F29" s="40"/>
-      <c r="G29" s="104"/>
-      <c r="H29" s="39"/>
-      <c r="I29" s="40"/>
-      <c r="J29" s="104"/>
-      <c r="K29" s="40"/>
-      <c r="L29" s="102"/>
-      <c r="M29" s="39"/>
-      <c r="N29" s="40"/>
-      <c r="O29" s="102"/>
-      <c r="P29" s="39"/>
-      <c r="Q29" s="40"/>
+      <c r="A29" s="107"/>
+      <c r="B29" s="41"/>
+      <c r="C29" s="108"/>
+      <c r="D29" s="41"/>
+      <c r="E29" s="108"/>
+      <c r="F29" s="41"/>
+      <c r="G29" s="96"/>
+      <c r="H29" s="40"/>
+      <c r="I29" s="41"/>
+      <c r="J29" s="96"/>
+      <c r="K29" s="41"/>
+      <c r="L29" s="101"/>
+      <c r="M29" s="40"/>
+      <c r="N29" s="41"/>
+      <c r="O29" s="101"/>
+      <c r="P29" s="40"/>
+      <c r="Q29" s="41"/>
       <c r="R29" s="33"/>
       <c r="S29" s="33"/>
       <c r="T29" s="34"/>
@@ -9976,23 +9982,23 @@
       <c r="Z29" s="35"/>
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A30" s="95"/>
-      <c r="B30" s="40"/>
-      <c r="C30" s="96"/>
-      <c r="D30" s="40"/>
-      <c r="E30" s="96"/>
-      <c r="F30" s="40"/>
-      <c r="G30" s="104"/>
-      <c r="H30" s="39"/>
-      <c r="I30" s="40"/>
-      <c r="J30" s="104"/>
-      <c r="K30" s="40"/>
-      <c r="L30" s="102"/>
-      <c r="M30" s="39"/>
-      <c r="N30" s="40"/>
-      <c r="O30" s="102"/>
-      <c r="P30" s="39"/>
-      <c r="Q30" s="40"/>
+      <c r="A30" s="107"/>
+      <c r="B30" s="41"/>
+      <c r="C30" s="108"/>
+      <c r="D30" s="41"/>
+      <c r="E30" s="108"/>
+      <c r="F30" s="41"/>
+      <c r="G30" s="96"/>
+      <c r="H30" s="40"/>
+      <c r="I30" s="41"/>
+      <c r="J30" s="96"/>
+      <c r="K30" s="41"/>
+      <c r="L30" s="101"/>
+      <c r="M30" s="40"/>
+      <c r="N30" s="41"/>
+      <c r="O30" s="101"/>
+      <c r="P30" s="40"/>
+      <c r="Q30" s="41"/>
       <c r="R30" s="33"/>
       <c r="S30" s="33"/>
       <c r="T30" s="34"/>
@@ -10004,23 +10010,23 @@
       <c r="Z30" s="35"/>
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A31" s="97"/>
-      <c r="B31" s="56"/>
-      <c r="C31" s="98"/>
-      <c r="D31" s="56"/>
-      <c r="E31" s="98"/>
-      <c r="F31" s="56"/>
-      <c r="G31" s="110"/>
-      <c r="H31" s="47"/>
-      <c r="I31" s="56"/>
-      <c r="J31" s="110"/>
-      <c r="K31" s="56"/>
-      <c r="L31" s="103"/>
-      <c r="M31" s="47"/>
-      <c r="N31" s="56"/>
-      <c r="O31" s="103"/>
-      <c r="P31" s="47"/>
-      <c r="Q31" s="56"/>
+      <c r="A31" s="112"/>
+      <c r="B31" s="68"/>
+      <c r="C31" s="113"/>
+      <c r="D31" s="68"/>
+      <c r="E31" s="113"/>
+      <c r="F31" s="68"/>
+      <c r="G31" s="100"/>
+      <c r="H31" s="67"/>
+      <c r="I31" s="68"/>
+      <c r="J31" s="100"/>
+      <c r="K31" s="68"/>
+      <c r="L31" s="102"/>
+      <c r="M31" s="67"/>
+      <c r="N31" s="68"/>
+      <c r="O31" s="102"/>
+      <c r="P31" s="67"/>
+      <c r="Q31" s="68"/>
       <c r="R31" s="36"/>
       <c r="S31" s="36"/>
       <c r="T31" s="37"/>
@@ -11018,62 +11024,62 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="136">
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:K19"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="K2:N4"/>
-    <mergeCell ref="O2:P4"/>
-    <mergeCell ref="Q2:R4"/>
-    <mergeCell ref="S2:T4"/>
-    <mergeCell ref="A1:F4"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="O27:Q27"/>
+    <mergeCell ref="O28:Q28"/>
+    <mergeCell ref="O29:Q29"/>
+    <mergeCell ref="O30:Q30"/>
+    <mergeCell ref="O31:Q31"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="O26:Q26"/>
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="G5:T5"/>
     <mergeCell ref="A6:F6"/>
@@ -11098,62 +11104,62 @@
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="E15:F15"/>
     <mergeCell ref="A16:B16"/>
-    <mergeCell ref="O27:Q27"/>
-    <mergeCell ref="O28:Q28"/>
-    <mergeCell ref="O29:Q29"/>
-    <mergeCell ref="O30:Q30"/>
-    <mergeCell ref="O31:Q31"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="O26:Q26"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="K2:N4"/>
+    <mergeCell ref="O2:P4"/>
+    <mergeCell ref="Q2:R4"/>
+    <mergeCell ref="S2:T4"/>
+    <mergeCell ref="A1:F4"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:K19"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <hyperlinks>

--- a/Documents/タスク詳細設計書.xlsx
+++ b/Documents/タスク詳細設計書.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\S-47\Documents\project\taskUN\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E85920B7-EA00-452D-A5D1-09CEB6174658}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19A645F2-ADE5-44E6-A4C7-46746459F6B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -683,30 +683,24 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>編集、削除ボタンは非活性化し、一覧へ戻るボタンのみ押せる状態となっている</t>
+    <t>編集、削除ボタンは無く一覧へ戻るボタンのみが表示される</t>
     <rPh sb="0" eb="2">
       <t>ヘンシュウ</t>
     </rPh>
     <rPh sb="3" eb="5">
       <t>サクジョ</t>
     </rPh>
-    <rPh sb="9" eb="12">
-      <t>ヒカッセイ</t>
+    <rPh sb="9" eb="10">
+      <t>ナ</t>
     </rPh>
-    <rPh sb="12" eb="13">
-      <t>カ</t>
-    </rPh>
-    <rPh sb="15" eb="17">
+    <rPh sb="11" eb="13">
       <t>イチラン</t>
     </rPh>
-    <rPh sb="18" eb="19">
+    <rPh sb="14" eb="15">
       <t>モド</t>
     </rPh>
-    <rPh sb="25" eb="26">
-      <t>オ</t>
-    </rPh>
-    <rPh sb="28" eb="30">
-      <t>ジョウタイ</t>
+    <rPh sb="22" eb="24">
+      <t>ヒョウジ</t>
     </rPh>
     <phoneticPr fontId="8"/>
   </si>
@@ -1592,9 +1586,6 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="56" fontId="7" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1619,56 +1610,23 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1676,11 +1634,11 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1697,17 +1655,26 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
@@ -1718,22 +1685,49 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1743,9 +1737,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1766,20 +1757,26 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1787,34 +1784,31 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="2" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="56" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="2" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="56" fontId="7" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -2399,85 +2393,85 @@
   <sheetData>
     <row r="1" spans="3:16" ht="30" customHeight="1"/>
     <row r="2" spans="3:16" ht="30" customHeight="1">
-      <c r="C2" s="44" t="s">
+      <c r="C2" s="43" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="45"/>
-      <c r="E2" s="45"/>
-      <c r="F2" s="45"/>
-      <c r="G2" s="45"/>
-      <c r="H2" s="45"/>
-      <c r="I2" s="45"/>
-      <c r="J2" s="45"/>
-      <c r="K2" s="45"/>
-      <c r="L2" s="45"/>
-      <c r="M2" s="45"/>
-      <c r="N2" s="45"/>
-      <c r="O2" s="45"/>
+      <c r="D2" s="44"/>
+      <c r="E2" s="44"/>
+      <c r="F2" s="44"/>
+      <c r="G2" s="44"/>
+      <c r="H2" s="44"/>
+      <c r="I2" s="44"/>
+      <c r="J2" s="44"/>
+      <c r="K2" s="44"/>
+      <c r="L2" s="44"/>
+      <c r="M2" s="44"/>
+      <c r="N2" s="44"/>
+      <c r="O2" s="44"/>
       <c r="P2" s="1"/>
     </row>
     <row r="3" spans="3:16" ht="30" customHeight="1">
-      <c r="C3" s="43"/>
-      <c r="D3" s="43"/>
-      <c r="E3" s="43"/>
-      <c r="F3" s="43"/>
-      <c r="G3" s="43"/>
-      <c r="H3" s="43"/>
-      <c r="I3" s="43"/>
-      <c r="J3" s="43"/>
-      <c r="K3" s="43"/>
-      <c r="L3" s="43"/>
-      <c r="M3" s="43"/>
-      <c r="N3" s="43"/>
-      <c r="O3" s="43"/>
+      <c r="C3" s="42"/>
+      <c r="D3" s="42"/>
+      <c r="E3" s="42"/>
+      <c r="F3" s="42"/>
+      <c r="G3" s="42"/>
+      <c r="H3" s="42"/>
+      <c r="I3" s="42"/>
+      <c r="J3" s="42"/>
+      <c r="K3" s="42"/>
+      <c r="L3" s="42"/>
+      <c r="M3" s="42"/>
+      <c r="N3" s="42"/>
+      <c r="O3" s="42"/>
       <c r="P3" s="1"/>
     </row>
     <row r="4" spans="3:16" ht="30" customHeight="1">
-      <c r="C4" s="43"/>
-      <c r="D4" s="43"/>
-      <c r="E4" s="43"/>
-      <c r="F4" s="43"/>
-      <c r="G4" s="43"/>
-      <c r="H4" s="43"/>
-      <c r="I4" s="43"/>
-      <c r="J4" s="43"/>
-      <c r="K4" s="43"/>
-      <c r="L4" s="43"/>
-      <c r="M4" s="43"/>
-      <c r="N4" s="43"/>
-      <c r="O4" s="43"/>
+      <c r="C4" s="42"/>
+      <c r="D4" s="42"/>
+      <c r="E4" s="42"/>
+      <c r="F4" s="42"/>
+      <c r="G4" s="42"/>
+      <c r="H4" s="42"/>
+      <c r="I4" s="42"/>
+      <c r="J4" s="42"/>
+      <c r="K4" s="42"/>
+      <c r="L4" s="42"/>
+      <c r="M4" s="42"/>
+      <c r="N4" s="42"/>
+      <c r="O4" s="42"/>
       <c r="P4" s="1"/>
     </row>
     <row r="5" spans="3:16" ht="30" customHeight="1">
-      <c r="C5" s="43"/>
-      <c r="D5" s="43"/>
-      <c r="E5" s="43"/>
-      <c r="F5" s="43"/>
-      <c r="G5" s="43"/>
-      <c r="H5" s="43"/>
-      <c r="I5" s="43"/>
-      <c r="J5" s="43"/>
-      <c r="K5" s="43"/>
-      <c r="L5" s="43"/>
-      <c r="M5" s="43"/>
-      <c r="N5" s="43"/>
-      <c r="O5" s="43"/>
+      <c r="C5" s="42"/>
+      <c r="D5" s="42"/>
+      <c r="E5" s="42"/>
+      <c r="F5" s="42"/>
+      <c r="G5" s="42"/>
+      <c r="H5" s="42"/>
+      <c r="I5" s="42"/>
+      <c r="J5" s="42"/>
+      <c r="K5" s="42"/>
+      <c r="L5" s="42"/>
+      <c r="M5" s="42"/>
+      <c r="N5" s="42"/>
+      <c r="O5" s="42"/>
       <c r="P5" s="1"/>
     </row>
     <row r="6" spans="3:16" ht="30" customHeight="1">
-      <c r="C6" s="43"/>
-      <c r="D6" s="43"/>
-      <c r="E6" s="43"/>
-      <c r="F6" s="43"/>
-      <c r="G6" s="43"/>
-      <c r="H6" s="43"/>
-      <c r="I6" s="43"/>
-      <c r="J6" s="43"/>
-      <c r="K6" s="43"/>
-      <c r="L6" s="43"/>
-      <c r="M6" s="43"/>
-      <c r="N6" s="43"/>
-      <c r="O6" s="43"/>
+      <c r="C6" s="42"/>
+      <c r="D6" s="42"/>
+      <c r="E6" s="42"/>
+      <c r="F6" s="42"/>
+      <c r="G6" s="42"/>
+      <c r="H6" s="42"/>
+      <c r="I6" s="42"/>
+      <c r="J6" s="42"/>
+      <c r="K6" s="42"/>
+      <c r="L6" s="42"/>
+      <c r="M6" s="42"/>
+      <c r="N6" s="42"/>
+      <c r="O6" s="42"/>
       <c r="P6" s="1"/>
     </row>
     <row r="7" spans="3:16" ht="30" customHeight="1">
@@ -2497,46 +2491,46 @@
       <c r="P7" s="1"/>
     </row>
     <row r="8" spans="3:16" ht="30" customHeight="1">
-      <c r="E8" s="46" t="s">
+      <c r="E8" s="45" t="s">
         <v>1</v>
       </c>
-      <c r="F8" s="43"/>
-      <c r="G8" s="43"/>
-      <c r="H8" s="43"/>
-      <c r="I8" s="43"/>
-      <c r="J8" s="43"/>
-      <c r="K8" s="43"/>
-      <c r="L8" s="43"/>
-      <c r="M8" s="43"/>
+      <c r="F8" s="42"/>
+      <c r="G8" s="42"/>
+      <c r="H8" s="42"/>
+      <c r="I8" s="42"/>
+      <c r="J8" s="42"/>
+      <c r="K8" s="42"/>
+      <c r="L8" s="42"/>
+      <c r="M8" s="42"/>
     </row>
     <row r="9" spans="3:16" ht="30" customHeight="1"/>
     <row r="10" spans="3:16" ht="30" customHeight="1"/>
     <row r="11" spans="3:16" ht="30" customHeight="1"/>
     <row r="12" spans="3:16" ht="30" customHeight="1"/>
     <row r="13" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G13" s="39" t="s">
+      <c r="G13" s="38" t="s">
         <v>2</v>
       </c>
-      <c r="H13" s="41"/>
-      <c r="I13" s="39" t="s">
+      <c r="H13" s="40"/>
+      <c r="I13" s="38" t="s">
         <v>3</v>
       </c>
-      <c r="J13" s="40"/>
-      <c r="K13" s="41"/>
+      <c r="J13" s="39"/>
+      <c r="K13" s="40"/>
     </row>
     <row r="14" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G14" s="39"/>
-      <c r="H14" s="41"/>
-      <c r="I14" s="39"/>
-      <c r="J14" s="40"/>
-      <c r="K14" s="41"/>
+      <c r="G14" s="38"/>
+      <c r="H14" s="40"/>
+      <c r="I14" s="38"/>
+      <c r="J14" s="39"/>
+      <c r="K14" s="40"/>
     </row>
     <row r="15" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G15" s="39"/>
-      <c r="H15" s="41"/>
-      <c r="I15" s="39"/>
-      <c r="J15" s="40"/>
-      <c r="K15" s="41"/>
+      <c r="G15" s="38"/>
+      <c r="H15" s="40"/>
+      <c r="I15" s="38"/>
+      <c r="J15" s="39"/>
+      <c r="K15" s="40"/>
     </row>
     <row r="16" spans="3:16" ht="15.75" customHeight="1">
       <c r="G16" s="3"/>
@@ -2545,13 +2539,13 @@
       <c r="J16" s="3"/>
     </row>
     <row r="17" spans="7:11" ht="30" customHeight="1">
-      <c r="G17" s="42" t="s">
+      <c r="G17" s="41" t="s">
         <v>4</v>
       </c>
-      <c r="H17" s="43"/>
-      <c r="I17" s="43"/>
-      <c r="J17" s="43"/>
-      <c r="K17" s="43"/>
+      <c r="H17" s="42"/>
+      <c r="I17" s="42"/>
+      <c r="J17" s="42"/>
+      <c r="K17" s="42"/>
     </row>
     <row r="18" spans="7:11" ht="14.25" customHeight="1"/>
     <row r="19" spans="7:11" ht="24.75" customHeight="1"/>
@@ -3565,19 +3559,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="69" t="s">
+      <c r="A1" s="57" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="70"/>
-      <c r="C1" s="71"/>
-      <c r="D1" s="47" t="s">
+      <c r="B1" s="58"/>
+      <c r="C1" s="59"/>
+      <c r="D1" s="78" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="48"/>
-      <c r="F1" s="47" t="s">
+      <c r="E1" s="66"/>
+      <c r="F1" s="78" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="48"/>
+      <c r="G1" s="66"/>
       <c r="H1" s="5" t="s">
         <v>8</v>
       </c>
@@ -3589,188 +3583,188 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="72"/>
-      <c r="B2" s="43"/>
-      <c r="C2" s="52"/>
-      <c r="D2" s="49" t="s">
+      <c r="A2" s="60"/>
+      <c r="B2" s="42"/>
+      <c r="C2" s="61"/>
+      <c r="D2" s="79" t="s">
         <v>56</v>
       </c>
-      <c r="E2" s="50"/>
-      <c r="F2" s="49" t="s">
+      <c r="E2" s="80"/>
+      <c r="F2" s="79" t="s">
         <v>57</v>
       </c>
-      <c r="G2" s="50"/>
-      <c r="H2" s="55">
+      <c r="G2" s="80"/>
+      <c r="H2" s="83">
         <v>45812</v>
       </c>
-      <c r="I2" s="58" t="s">
+      <c r="I2" s="72" t="s">
         <v>58</v>
       </c>
-      <c r="J2" s="59"/>
+      <c r="J2" s="75"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="72"/>
-      <c r="B3" s="43"/>
-      <c r="C3" s="52"/>
-      <c r="D3" s="51"/>
-      <c r="E3" s="52"/>
-      <c r="F3" s="51"/>
-      <c r="G3" s="52"/>
-      <c r="H3" s="56"/>
-      <c r="I3" s="56"/>
-      <c r="J3" s="60"/>
+      <c r="A3" s="60"/>
+      <c r="B3" s="42"/>
+      <c r="C3" s="61"/>
+      <c r="D3" s="81"/>
+      <c r="E3" s="61"/>
+      <c r="F3" s="81"/>
+      <c r="G3" s="61"/>
+      <c r="H3" s="73"/>
+      <c r="I3" s="73"/>
+      <c r="J3" s="76"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="73"/>
-      <c r="B4" s="74"/>
-      <c r="C4" s="54"/>
-      <c r="D4" s="53"/>
-      <c r="E4" s="54"/>
-      <c r="F4" s="53"/>
-      <c r="G4" s="54"/>
-      <c r="H4" s="57"/>
-      <c r="I4" s="57"/>
-      <c r="J4" s="61"/>
+      <c r="A4" s="62"/>
+      <c r="B4" s="63"/>
+      <c r="C4" s="64"/>
+      <c r="D4" s="82"/>
+      <c r="E4" s="64"/>
+      <c r="F4" s="82"/>
+      <c r="G4" s="64"/>
+      <c r="H4" s="74"/>
+      <c r="I4" s="74"/>
+      <c r="J4" s="77"/>
     </row>
     <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="75" t="s">
+      <c r="A5" s="65" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="76"/>
-      <c r="C5" s="48"/>
-      <c r="D5" s="82" t="s">
+      <c r="B5" s="50"/>
+      <c r="C5" s="66"/>
+      <c r="D5" s="49" t="s">
         <v>59</v>
       </c>
-      <c r="E5" s="76"/>
-      <c r="F5" s="76"/>
-      <c r="G5" s="76"/>
-      <c r="H5" s="76"/>
-      <c r="I5" s="76"/>
-      <c r="J5" s="83"/>
+      <c r="E5" s="50"/>
+      <c r="F5" s="50"/>
+      <c r="G5" s="50"/>
+      <c r="H5" s="50"/>
+      <c r="I5" s="50"/>
+      <c r="J5" s="51"/>
     </row>
     <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="63" t="s">
+      <c r="A6" s="67" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="40"/>
-      <c r="C6" s="41"/>
-      <c r="D6" s="64" t="s">
+      <c r="B6" s="39"/>
+      <c r="C6" s="40"/>
+      <c r="D6" s="52" t="s">
         <v>60</v>
       </c>
-      <c r="E6" s="40"/>
-      <c r="F6" s="40"/>
-      <c r="G6" s="40"/>
-      <c r="H6" s="40"/>
-      <c r="I6" s="40"/>
-      <c r="J6" s="65"/>
+      <c r="E6" s="39"/>
+      <c r="F6" s="39"/>
+      <c r="G6" s="39"/>
+      <c r="H6" s="39"/>
+      <c r="I6" s="39"/>
+      <c r="J6" s="53"/>
     </row>
     <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="63" t="s">
+      <c r="A7" s="67" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="40"/>
-      <c r="C7" s="41"/>
-      <c r="D7" s="64" t="s">
+      <c r="B7" s="39"/>
+      <c r="C7" s="40"/>
+      <c r="D7" s="52" t="s">
         <v>61</v>
       </c>
-      <c r="E7" s="40"/>
-      <c r="F7" s="40"/>
-      <c r="G7" s="40"/>
-      <c r="H7" s="40"/>
-      <c r="I7" s="40"/>
-      <c r="J7" s="65"/>
+      <c r="E7" s="39"/>
+      <c r="F7" s="39"/>
+      <c r="G7" s="39"/>
+      <c r="H7" s="39"/>
+      <c r="I7" s="39"/>
+      <c r="J7" s="53"/>
     </row>
     <row r="8" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A8" s="63" t="s">
+      <c r="A8" s="67" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="40"/>
-      <c r="C8" s="41"/>
-      <c r="D8" s="64" t="s">
+      <c r="B8" s="39"/>
+      <c r="C8" s="40"/>
+      <c r="D8" s="52" t="s">
         <v>62</v>
       </c>
-      <c r="E8" s="40"/>
-      <c r="F8" s="40"/>
-      <c r="G8" s="40"/>
-      <c r="H8" s="40"/>
-      <c r="I8" s="40"/>
-      <c r="J8" s="65"/>
+      <c r="E8" s="39"/>
+      <c r="F8" s="39"/>
+      <c r="G8" s="39"/>
+      <c r="H8" s="39"/>
+      <c r="I8" s="39"/>
+      <c r="J8" s="53"/>
     </row>
     <row r="9" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A9" s="77" t="s">
+      <c r="A9" s="68" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="62" t="s">
+      <c r="B9" s="71" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="41"/>
-      <c r="D9" s="84" t="s">
+      <c r="C9" s="40"/>
+      <c r="D9" s="54" t="s">
         <v>76</v>
       </c>
-      <c r="E9" s="40"/>
-      <c r="F9" s="40"/>
-      <c r="G9" s="40"/>
-      <c r="H9" s="40"/>
-      <c r="I9" s="40"/>
-      <c r="J9" s="65"/>
+      <c r="E9" s="39"/>
+      <c r="F9" s="39"/>
+      <c r="G9" s="39"/>
+      <c r="H9" s="39"/>
+      <c r="I9" s="39"/>
+      <c r="J9" s="53"/>
     </row>
     <row r="10" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A10" s="78"/>
-      <c r="B10" s="62" t="s">
+      <c r="A10" s="69"/>
+      <c r="B10" s="71" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="41"/>
-      <c r="D10" s="64"/>
-      <c r="E10" s="40"/>
-      <c r="F10" s="40"/>
-      <c r="G10" s="40"/>
-      <c r="H10" s="40"/>
-      <c r="I10" s="40"/>
-      <c r="J10" s="65"/>
+      <c r="C10" s="40"/>
+      <c r="D10" s="52"/>
+      <c r="E10" s="39"/>
+      <c r="F10" s="39"/>
+      <c r="G10" s="39"/>
+      <c r="H10" s="39"/>
+      <c r="I10" s="39"/>
+      <c r="J10" s="53"/>
     </row>
     <row r="11" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A11" s="79"/>
-      <c r="B11" s="62" t="s">
+      <c r="A11" s="70"/>
+      <c r="B11" s="71" t="s">
         <v>18</v>
       </c>
-      <c r="C11" s="41"/>
-      <c r="D11" s="64"/>
-      <c r="E11" s="40"/>
-      <c r="F11" s="40"/>
-      <c r="G11" s="40"/>
-      <c r="H11" s="40"/>
-      <c r="I11" s="40"/>
-      <c r="J11" s="65"/>
+      <c r="C11" s="40"/>
+      <c r="D11" s="52"/>
+      <c r="E11" s="39"/>
+      <c r="F11" s="39"/>
+      <c r="G11" s="39"/>
+      <c r="H11" s="39"/>
+      <c r="I11" s="39"/>
+      <c r="J11" s="53"/>
     </row>
     <row r="12" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A12" s="63" t="s">
+      <c r="A12" s="67" t="s">
         <v>19</v>
       </c>
-      <c r="B12" s="40"/>
-      <c r="C12" s="41"/>
-      <c r="D12" s="64" t="s">
+      <c r="B12" s="39"/>
+      <c r="C12" s="40"/>
+      <c r="D12" s="52" t="s">
         <v>63</v>
       </c>
-      <c r="E12" s="40"/>
-      <c r="F12" s="40"/>
-      <c r="G12" s="40"/>
-      <c r="H12" s="40"/>
-      <c r="I12" s="40"/>
-      <c r="J12" s="65"/>
+      <c r="E12" s="39"/>
+      <c r="F12" s="39"/>
+      <c r="G12" s="39"/>
+      <c r="H12" s="39"/>
+      <c r="I12" s="39"/>
+      <c r="J12" s="53"/>
     </row>
     <row r="13" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A13" s="66" t="s">
+      <c r="A13" s="55" t="s">
         <v>20</v>
       </c>
-      <c r="B13" s="67"/>
-      <c r="C13" s="68"/>
-      <c r="D13" s="80"/>
-      <c r="E13" s="67"/>
-      <c r="F13" s="67"/>
-      <c r="G13" s="67"/>
-      <c r="H13" s="67"/>
-      <c r="I13" s="67"/>
-      <c r="J13" s="81"/>
+      <c r="B13" s="47"/>
+      <c r="C13" s="56"/>
+      <c r="D13" s="46"/>
+      <c r="E13" s="47"/>
+      <c r="F13" s="47"/>
+      <c r="G13" s="47"/>
+      <c r="H13" s="47"/>
+      <c r="I13" s="47"/>
+      <c r="J13" s="48"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -4761,6 +4755,25 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="D12:J12"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A9:A11"/>
+    <mergeCell ref="B9:C9"/>
     <mergeCell ref="D13:J13"/>
     <mergeCell ref="D5:J5"/>
     <mergeCell ref="D6:J6"/>
@@ -4769,25 +4782,6 @@
     <mergeCell ref="D9:J9"/>
     <mergeCell ref="D10:J10"/>
     <mergeCell ref="D11:J11"/>
-    <mergeCell ref="A13:C13"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="A9:A11"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="D12:J12"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
@@ -4806,19 +4800,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="85" t="s">
+      <c r="A1" s="84" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="70"/>
-      <c r="C1" s="71"/>
-      <c r="D1" s="47" t="s">
+      <c r="B1" s="58"/>
+      <c r="C1" s="59"/>
+      <c r="D1" s="78" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="48"/>
-      <c r="F1" s="47" t="s">
+      <c r="E1" s="66"/>
+      <c r="F1" s="78" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="48"/>
+      <c r="G1" s="66"/>
       <c r="H1" s="4" t="s">
         <v>8</v>
       </c>
@@ -4830,48 +4824,48 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="72"/>
-      <c r="B2" s="43"/>
-      <c r="C2" s="52"/>
-      <c r="D2" s="49" t="s">
+      <c r="A2" s="60"/>
+      <c r="B2" s="42"/>
+      <c r="C2" s="61"/>
+      <c r="D2" s="79" t="s">
         <v>56</v>
       </c>
-      <c r="E2" s="50"/>
-      <c r="F2" s="49" t="s">
+      <c r="E2" s="80"/>
+      <c r="F2" s="79" t="s">
         <v>57</v>
       </c>
-      <c r="G2" s="50"/>
-      <c r="H2" s="55">
+      <c r="G2" s="80"/>
+      <c r="H2" s="83">
         <v>45810</v>
       </c>
-      <c r="I2" s="58" t="s">
+      <c r="I2" s="72" t="s">
         <v>64</v>
       </c>
-      <c r="J2" s="59"/>
+      <c r="J2" s="75"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="72"/>
-      <c r="B3" s="43"/>
-      <c r="C3" s="52"/>
-      <c r="D3" s="51"/>
-      <c r="E3" s="52"/>
-      <c r="F3" s="51"/>
-      <c r="G3" s="52"/>
-      <c r="H3" s="56"/>
-      <c r="I3" s="56"/>
-      <c r="J3" s="60"/>
+      <c r="A3" s="60"/>
+      <c r="B3" s="42"/>
+      <c r="C3" s="61"/>
+      <c r="D3" s="81"/>
+      <c r="E3" s="61"/>
+      <c r="F3" s="81"/>
+      <c r="G3" s="61"/>
+      <c r="H3" s="73"/>
+      <c r="I3" s="73"/>
+      <c r="J3" s="76"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="73"/>
-      <c r="B4" s="74"/>
-      <c r="C4" s="54"/>
-      <c r="D4" s="53"/>
-      <c r="E4" s="54"/>
-      <c r="F4" s="53"/>
-      <c r="G4" s="54"/>
-      <c r="H4" s="57"/>
-      <c r="I4" s="57"/>
-      <c r="J4" s="61"/>
+      <c r="A4" s="62"/>
+      <c r="B4" s="63"/>
+      <c r="C4" s="64"/>
+      <c r="D4" s="82"/>
+      <c r="E4" s="64"/>
+      <c r="F4" s="82"/>
+      <c r="G4" s="64"/>
+      <c r="H4" s="74"/>
+      <c r="I4" s="74"/>
+      <c r="J4" s="77"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -6228,19 +6222,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="85" t="s">
+      <c r="A1" s="84" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="70"/>
-      <c r="C1" s="71"/>
-      <c r="D1" s="47" t="s">
+      <c r="B1" s="58"/>
+      <c r="C1" s="59"/>
+      <c r="D1" s="78" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="48"/>
-      <c r="F1" s="47" t="s">
+      <c r="E1" s="66"/>
+      <c r="F1" s="78" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="48"/>
+      <c r="G1" s="66"/>
       <c r="H1" s="4" t="s">
         <v>8</v>
       </c>
@@ -6252,48 +6246,48 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="72"/>
-      <c r="B2" s="43"/>
-      <c r="C2" s="52"/>
-      <c r="D2" s="49" t="s">
+      <c r="A2" s="60"/>
+      <c r="B2" s="42"/>
+      <c r="C2" s="61"/>
+      <c r="D2" s="79" t="s">
         <v>56</v>
       </c>
-      <c r="E2" s="50"/>
-      <c r="F2" s="49" t="s">
+      <c r="E2" s="80"/>
+      <c r="F2" s="79" t="s">
         <v>57</v>
       </c>
-      <c r="G2" s="50"/>
-      <c r="H2" s="55">
+      <c r="G2" s="80"/>
+      <c r="H2" s="83">
         <v>45810</v>
       </c>
-      <c r="I2" s="58" t="s">
+      <c r="I2" s="72" t="s">
         <v>64</v>
       </c>
-      <c r="J2" s="59"/>
+      <c r="J2" s="75"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="72"/>
-      <c r="B3" s="43"/>
-      <c r="C3" s="52"/>
-      <c r="D3" s="51"/>
-      <c r="E3" s="52"/>
-      <c r="F3" s="51"/>
-      <c r="G3" s="52"/>
-      <c r="H3" s="56"/>
-      <c r="I3" s="56"/>
-      <c r="J3" s="60"/>
+      <c r="A3" s="60"/>
+      <c r="B3" s="42"/>
+      <c r="C3" s="61"/>
+      <c r="D3" s="81"/>
+      <c r="E3" s="61"/>
+      <c r="F3" s="81"/>
+      <c r="G3" s="61"/>
+      <c r="H3" s="73"/>
+      <c r="I3" s="73"/>
+      <c r="J3" s="76"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="73"/>
-      <c r="B4" s="74"/>
-      <c r="C4" s="54"/>
-      <c r="D4" s="53"/>
-      <c r="E4" s="54"/>
-      <c r="F4" s="53"/>
-      <c r="G4" s="54"/>
-      <c r="H4" s="57"/>
-      <c r="I4" s="57"/>
-      <c r="J4" s="61"/>
+      <c r="A4" s="62"/>
+      <c r="B4" s="63"/>
+      <c r="C4" s="64"/>
+      <c r="D4" s="82"/>
+      <c r="E4" s="64"/>
+      <c r="F4" s="82"/>
+      <c r="G4" s="64"/>
+      <c r="H4" s="74"/>
+      <c r="I4" s="74"/>
+      <c r="J4" s="77"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -7644,19 +7638,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="85" t="s">
+      <c r="A1" s="84" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="70"/>
-      <c r="C1" s="71"/>
-      <c r="D1" s="47" t="s">
+      <c r="B1" s="58"/>
+      <c r="C1" s="59"/>
+      <c r="D1" s="78" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="48"/>
-      <c r="F1" s="47" t="s">
+      <c r="E1" s="66"/>
+      <c r="F1" s="78" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="48"/>
+      <c r="G1" s="66"/>
       <c r="H1" s="4" t="s">
         <v>8</v>
       </c>
@@ -7668,190 +7662,190 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="72"/>
-      <c r="B2" s="43"/>
-      <c r="C2" s="52"/>
-      <c r="D2" s="49" t="s">
+      <c r="A2" s="60"/>
+      <c r="B2" s="42"/>
+      <c r="C2" s="61"/>
+      <c r="D2" s="79" t="s">
         <v>56</v>
       </c>
-      <c r="E2" s="50"/>
-      <c r="F2" s="49" t="s">
+      <c r="E2" s="80"/>
+      <c r="F2" s="79" t="s">
         <v>57</v>
       </c>
-      <c r="G2" s="50"/>
-      <c r="H2" s="55">
+      <c r="G2" s="80"/>
+      <c r="H2" s="83">
         <v>45810</v>
       </c>
-      <c r="I2" s="58" t="s">
+      <c r="I2" s="72" t="s">
         <v>64</v>
       </c>
-      <c r="J2" s="59"/>
+      <c r="J2" s="75"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="72"/>
-      <c r="B3" s="43"/>
-      <c r="C3" s="52"/>
-      <c r="D3" s="51"/>
-      <c r="E3" s="52"/>
-      <c r="F3" s="51"/>
-      <c r="G3" s="52"/>
-      <c r="H3" s="56"/>
-      <c r="I3" s="56"/>
-      <c r="J3" s="60"/>
+      <c r="A3" s="60"/>
+      <c r="B3" s="42"/>
+      <c r="C3" s="61"/>
+      <c r="D3" s="81"/>
+      <c r="E3" s="61"/>
+      <c r="F3" s="81"/>
+      <c r="G3" s="61"/>
+      <c r="H3" s="73"/>
+      <c r="I3" s="73"/>
+      <c r="J3" s="76"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="72"/>
-      <c r="B4" s="43"/>
-      <c r="C4" s="52"/>
-      <c r="D4" s="51"/>
-      <c r="E4" s="52"/>
-      <c r="F4" s="51"/>
-      <c r="G4" s="52"/>
-      <c r="H4" s="56"/>
-      <c r="I4" s="56"/>
-      <c r="J4" s="60"/>
+      <c r="A4" s="60"/>
+      <c r="B4" s="42"/>
+      <c r="C4" s="61"/>
+      <c r="D4" s="81"/>
+      <c r="E4" s="61"/>
+      <c r="F4" s="81"/>
+      <c r="G4" s="61"/>
+      <c r="H4" s="73"/>
+      <c r="I4" s="73"/>
+      <c r="J4" s="76"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
       <c r="A5" s="86" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="76"/>
-      <c r="C5" s="48"/>
-      <c r="D5" s="90" t="s">
+      <c r="B5" s="50"/>
+      <c r="C5" s="66"/>
+      <c r="D5" s="89" t="s">
         <v>65</v>
       </c>
-      <c r="E5" s="76"/>
-      <c r="F5" s="76"/>
-      <c r="G5" s="76"/>
-      <c r="H5" s="76"/>
-      <c r="I5" s="76"/>
-      <c r="J5" s="83"/>
+      <c r="E5" s="50"/>
+      <c r="F5" s="50"/>
+      <c r="G5" s="50"/>
+      <c r="H5" s="50"/>
+      <c r="I5" s="50"/>
+      <c r="J5" s="51"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
       <c r="A6" s="88" t="s">
         <v>25</v>
       </c>
-      <c r="B6" s="40"/>
-      <c r="C6" s="40"/>
-      <c r="D6" s="40"/>
-      <c r="E6" s="40"/>
-      <c r="F6" s="40"/>
-      <c r="G6" s="40"/>
-      <c r="H6" s="40"/>
-      <c r="I6" s="40"/>
-      <c r="J6" s="65"/>
+      <c r="B6" s="39"/>
+      <c r="C6" s="39"/>
+      <c r="D6" s="39"/>
+      <c r="E6" s="39"/>
+      <c r="F6" s="39"/>
+      <c r="G6" s="39"/>
+      <c r="H6" s="39"/>
+      <c r="I6" s="39"/>
+      <c r="J6" s="53"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="91"/>
-      <c r="B7" s="92"/>
-      <c r="C7" s="92"/>
-      <c r="D7" s="92"/>
-      <c r="E7" s="92"/>
-      <c r="F7" s="92"/>
-      <c r="G7" s="92"/>
-      <c r="H7" s="92"/>
-      <c r="I7" s="92"/>
-      <c r="J7" s="93"/>
+      <c r="A7" s="90"/>
+      <c r="B7" s="91"/>
+      <c r="C7" s="91"/>
+      <c r="D7" s="91"/>
+      <c r="E7" s="91"/>
+      <c r="F7" s="91"/>
+      <c r="G7" s="91"/>
+      <c r="H7" s="91"/>
+      <c r="I7" s="91"/>
+      <c r="J7" s="92"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="72"/>
-      <c r="B8" s="43"/>
-      <c r="C8" s="43"/>
-      <c r="D8" s="43"/>
-      <c r="E8" s="43"/>
-      <c r="F8" s="43"/>
-      <c r="G8" s="43"/>
-      <c r="H8" s="43"/>
-      <c r="I8" s="43"/>
-      <c r="J8" s="94"/>
+      <c r="A8" s="60"/>
+      <c r="B8" s="42"/>
+      <c r="C8" s="42"/>
+      <c r="D8" s="42"/>
+      <c r="E8" s="42"/>
+      <c r="F8" s="42"/>
+      <c r="G8" s="42"/>
+      <c r="H8" s="42"/>
+      <c r="I8" s="42"/>
+      <c r="J8" s="93"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="72"/>
-      <c r="B9" s="43"/>
-      <c r="C9" s="43"/>
-      <c r="D9" s="43"/>
-      <c r="E9" s="43"/>
-      <c r="F9" s="43"/>
-      <c r="G9" s="43"/>
-      <c r="H9" s="43"/>
-      <c r="I9" s="43"/>
-      <c r="J9" s="94"/>
+      <c r="A9" s="60"/>
+      <c r="B9" s="42"/>
+      <c r="C9" s="42"/>
+      <c r="D9" s="42"/>
+      <c r="E9" s="42"/>
+      <c r="F9" s="42"/>
+      <c r="G9" s="42"/>
+      <c r="H9" s="42"/>
+      <c r="I9" s="42"/>
+      <c r="J9" s="93"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="72"/>
-      <c r="B10" s="43"/>
-      <c r="C10" s="43"/>
-      <c r="D10" s="43"/>
-      <c r="E10" s="43"/>
-      <c r="F10" s="43"/>
-      <c r="G10" s="43"/>
-      <c r="H10" s="43"/>
-      <c r="I10" s="43"/>
-      <c r="J10" s="94"/>
+      <c r="A10" s="60"/>
+      <c r="B10" s="42"/>
+      <c r="C10" s="42"/>
+      <c r="D10" s="42"/>
+      <c r="E10" s="42"/>
+      <c r="F10" s="42"/>
+      <c r="G10" s="42"/>
+      <c r="H10" s="42"/>
+      <c r="I10" s="42"/>
+      <c r="J10" s="93"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="72"/>
-      <c r="B11" s="43"/>
-      <c r="C11" s="43"/>
-      <c r="D11" s="43"/>
-      <c r="E11" s="43"/>
-      <c r="F11" s="43"/>
-      <c r="G11" s="43"/>
-      <c r="H11" s="43"/>
-      <c r="I11" s="43"/>
-      <c r="J11" s="94"/>
+      <c r="A11" s="60"/>
+      <c r="B11" s="42"/>
+      <c r="C11" s="42"/>
+      <c r="D11" s="42"/>
+      <c r="E11" s="42"/>
+      <c r="F11" s="42"/>
+      <c r="G11" s="42"/>
+      <c r="H11" s="42"/>
+      <c r="I11" s="42"/>
+      <c r="J11" s="93"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="72"/>
-      <c r="B12" s="43"/>
-      <c r="C12" s="43"/>
-      <c r="D12" s="43"/>
-      <c r="E12" s="43"/>
-      <c r="F12" s="43"/>
-      <c r="G12" s="43"/>
-      <c r="H12" s="43"/>
-      <c r="I12" s="43"/>
-      <c r="J12" s="94"/>
+      <c r="A12" s="60"/>
+      <c r="B12" s="42"/>
+      <c r="C12" s="42"/>
+      <c r="D12" s="42"/>
+      <c r="E12" s="42"/>
+      <c r="F12" s="42"/>
+      <c r="G12" s="42"/>
+      <c r="H12" s="42"/>
+      <c r="I12" s="42"/>
+      <c r="J12" s="93"/>
     </row>
     <row r="13" spans="1:10" ht="62.25" customHeight="1">
-      <c r="A13" s="72"/>
-      <c r="B13" s="43"/>
-      <c r="C13" s="43"/>
-      <c r="D13" s="43"/>
-      <c r="E13" s="43"/>
-      <c r="F13" s="43"/>
-      <c r="G13" s="43"/>
-      <c r="H13" s="43"/>
-      <c r="I13" s="43"/>
-      <c r="J13" s="94"/>
+      <c r="A13" s="60"/>
+      <c r="B13" s="42"/>
+      <c r="C13" s="42"/>
+      <c r="D13" s="42"/>
+      <c r="E13" s="42"/>
+      <c r="F13" s="42"/>
+      <c r="G13" s="42"/>
+      <c r="H13" s="42"/>
+      <c r="I13" s="42"/>
+      <c r="J13" s="93"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
       <c r="A14" s="88" t="s">
         <v>26</v>
       </c>
-      <c r="B14" s="40"/>
-      <c r="C14" s="40"/>
-      <c r="D14" s="40"/>
-      <c r="E14" s="40"/>
-      <c r="F14" s="40"/>
-      <c r="G14" s="40"/>
-      <c r="H14" s="40"/>
-      <c r="I14" s="40"/>
-      <c r="J14" s="65"/>
+      <c r="B14" s="39"/>
+      <c r="C14" s="39"/>
+      <c r="D14" s="39"/>
+      <c r="E14" s="39"/>
+      <c r="F14" s="39"/>
+      <c r="G14" s="39"/>
+      <c r="H14" s="39"/>
+      <c r="I14" s="39"/>
+      <c r="J14" s="53"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
       <c r="A15" s="88" t="s">
         <v>27</v>
       </c>
-      <c r="B15" s="40"/>
-      <c r="C15" s="41"/>
-      <c r="D15" s="64" t="s">
+      <c r="B15" s="39"/>
+      <c r="C15" s="40"/>
+      <c r="D15" s="52" t="s">
         <v>74</v>
       </c>
-      <c r="E15" s="40"/>
-      <c r="F15" s="40"/>
-      <c r="G15" s="40"/>
-      <c r="H15" s="41"/>
+      <c r="E15" s="39"/>
+      <c r="F15" s="39"/>
+      <c r="G15" s="39"/>
+      <c r="H15" s="40"/>
       <c r="I15" s="15" t="s">
         <v>28</v>
       </c>
@@ -7863,8 +7857,8 @@
       <c r="A16" s="88" t="s">
         <v>29</v>
       </c>
-      <c r="B16" s="40"/>
-      <c r="C16" s="41"/>
+      <c r="B16" s="39"/>
+      <c r="C16" s="40"/>
       <c r="D16" s="15" t="s">
         <v>30</v>
       </c>
@@ -7877,18 +7871,18 @@
       <c r="G16" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="H16" s="95" t="s">
+      <c r="H16" s="94" t="s">
         <v>20</v>
       </c>
-      <c r="I16" s="40"/>
-      <c r="J16" s="65"/>
+      <c r="I16" s="39"/>
+      <c r="J16" s="53"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="89">
+      <c r="A17" s="85">
         <v>1</v>
       </c>
-      <c r="B17" s="40"/>
-      <c r="C17" s="41"/>
+      <c r="B17" s="39"/>
+      <c r="C17" s="40"/>
       <c r="D17" s="17" t="s">
         <v>67</v>
       </c>
@@ -7899,18 +7893,18 @@
       <c r="G17" s="18" t="s">
         <v>71</v>
       </c>
-      <c r="H17" s="64" t="s">
+      <c r="H17" s="52" t="s">
         <v>75</v>
       </c>
-      <c r="I17" s="40"/>
-      <c r="J17" s="65"/>
+      <c r="I17" s="39"/>
+      <c r="J17" s="53"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="89">
+      <c r="A18" s="85">
         <v>2</v>
       </c>
-      <c r="B18" s="40"/>
-      <c r="C18" s="41"/>
+      <c r="B18" s="39"/>
+      <c r="C18" s="40"/>
       <c r="D18" s="17" t="s">
         <v>68</v>
       </c>
@@ -7921,18 +7915,18 @@
       <c r="G18" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="H18" s="64" t="s">
+      <c r="H18" s="52" t="s">
         <v>75</v>
       </c>
-      <c r="I18" s="40"/>
-      <c r="J18" s="65"/>
+      <c r="I18" s="39"/>
+      <c r="J18" s="53"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="89">
+      <c r="A19" s="85">
         <v>3</v>
       </c>
-      <c r="B19" s="40"/>
-      <c r="C19" s="41"/>
+      <c r="B19" s="39"/>
+      <c r="C19" s="40"/>
       <c r="D19" s="17" t="s">
         <v>69</v>
       </c>
@@ -7943,59 +7937,59 @@
       <c r="G19" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="H19" s="64" t="s">
+      <c r="H19" s="52" t="s">
         <v>75</v>
       </c>
-      <c r="I19" s="40"/>
-      <c r="J19" s="65"/>
+      <c r="I19" s="39"/>
+      <c r="J19" s="53"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="89"/>
-      <c r="B20" s="40"/>
-      <c r="C20" s="41"/>
+      <c r="A20" s="85"/>
+      <c r="B20" s="39"/>
+      <c r="C20" s="40"/>
       <c r="D20" s="17"/>
       <c r="E20" s="17"/>
       <c r="F20" s="18"/>
       <c r="G20" s="18"/>
-      <c r="H20" s="64"/>
-      <c r="I20" s="40"/>
-      <c r="J20" s="65"/>
+      <c r="H20" s="52"/>
+      <c r="I20" s="39"/>
+      <c r="J20" s="53"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="89"/>
-      <c r="B21" s="40"/>
-      <c r="C21" s="41"/>
+      <c r="A21" s="85"/>
+      <c r="B21" s="39"/>
+      <c r="C21" s="40"/>
       <c r="D21" s="17"/>
       <c r="E21" s="17"/>
       <c r="F21" s="18"/>
       <c r="G21" s="18"/>
-      <c r="H21" s="64"/>
-      <c r="I21" s="40"/>
-      <c r="J21" s="65"/>
+      <c r="H21" s="52"/>
+      <c r="I21" s="39"/>
+      <c r="J21" s="53"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="89"/>
-      <c r="B22" s="40"/>
-      <c r="C22" s="41"/>
+      <c r="A22" s="85"/>
+      <c r="B22" s="39"/>
+      <c r="C22" s="40"/>
       <c r="D22" s="17"/>
       <c r="E22" s="17"/>
       <c r="F22" s="18"/>
       <c r="G22" s="18"/>
-      <c r="H22" s="64"/>
-      <c r="I22" s="40"/>
-      <c r="J22" s="65"/>
+      <c r="H22" s="52"/>
+      <c r="I22" s="39"/>
+      <c r="J22" s="53"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1">
       <c r="A23" s="87"/>
-      <c r="B23" s="67"/>
-      <c r="C23" s="68"/>
+      <c r="B23" s="47"/>
+      <c r="C23" s="56"/>
       <c r="D23" s="19"/>
       <c r="E23" s="19"/>
       <c r="F23" s="20"/>
       <c r="G23" s="20"/>
-      <c r="H23" s="80"/>
-      <c r="I23" s="67"/>
-      <c r="J23" s="81"/>
+      <c r="H23" s="46"/>
+      <c r="I23" s="47"/>
+      <c r="J23" s="48"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
@@ -8976,16 +8970,11 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A1:C4"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="F1:G1"/>
@@ -9002,11 +8991,16 @@
     <mergeCell ref="H17:J17"/>
     <mergeCell ref="D2:E4"/>
     <mergeCell ref="H23:J23"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="H22:J22"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -9026,190 +9020,190 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="69" t="s">
+      <c r="A1" s="57" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="70"/>
-      <c r="C1" s="70"/>
-      <c r="D1" s="70"/>
-      <c r="E1" s="70"/>
-      <c r="F1" s="71"/>
-      <c r="G1" s="47" t="s">
+      <c r="B1" s="58"/>
+      <c r="C1" s="58"/>
+      <c r="D1" s="58"/>
+      <c r="E1" s="58"/>
+      <c r="F1" s="59"/>
+      <c r="G1" s="78" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="76"/>
-      <c r="I1" s="76"/>
-      <c r="J1" s="48"/>
-      <c r="K1" s="47" t="s">
+      <c r="H1" s="50"/>
+      <c r="I1" s="50"/>
+      <c r="J1" s="66"/>
+      <c r="K1" s="78" t="s">
         <v>7</v>
       </c>
-      <c r="L1" s="76"/>
-      <c r="M1" s="76"/>
-      <c r="N1" s="48"/>
-      <c r="O1" s="47" t="s">
+      <c r="L1" s="50"/>
+      <c r="M1" s="50"/>
+      <c r="N1" s="66"/>
+      <c r="O1" s="78" t="s">
         <v>8</v>
       </c>
-      <c r="P1" s="48"/>
-      <c r="Q1" s="47" t="s">
+      <c r="P1" s="66"/>
+      <c r="Q1" s="78" t="s">
         <v>9</v>
       </c>
-      <c r="R1" s="48"/>
-      <c r="S1" s="47" t="s">
+      <c r="R1" s="66"/>
+      <c r="S1" s="78" t="s">
         <v>10</v>
       </c>
-      <c r="T1" s="83"/>
+      <c r="T1" s="51"/>
     </row>
     <row r="2" spans="1:26" ht="18" customHeight="1">
-      <c r="A2" s="72"/>
-      <c r="B2" s="43"/>
-      <c r="C2" s="43"/>
-      <c r="D2" s="43"/>
-      <c r="E2" s="43"/>
-      <c r="F2" s="52"/>
-      <c r="G2" s="49" t="s">
+      <c r="A2" s="60"/>
+      <c r="B2" s="42"/>
+      <c r="C2" s="42"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="42"/>
+      <c r="F2" s="61"/>
+      <c r="G2" s="79" t="s">
         <v>56</v>
       </c>
-      <c r="H2" s="92"/>
-      <c r="I2" s="92"/>
-      <c r="J2" s="50"/>
-      <c r="K2" s="49" t="s">
+      <c r="H2" s="91"/>
+      <c r="I2" s="91"/>
+      <c r="J2" s="80"/>
+      <c r="K2" s="79" t="s">
         <v>57</v>
       </c>
-      <c r="L2" s="92"/>
-      <c r="M2" s="92"/>
-      <c r="N2" s="50"/>
-      <c r="O2" s="105">
+      <c r="L2" s="91"/>
+      <c r="M2" s="91"/>
+      <c r="N2" s="80"/>
+      <c r="O2" s="106">
         <v>45818</v>
       </c>
-      <c r="P2" s="50"/>
-      <c r="Q2" s="49" t="s">
+      <c r="P2" s="80"/>
+      <c r="Q2" s="79" t="s">
         <v>64</v>
       </c>
-      <c r="R2" s="50"/>
-      <c r="S2" s="49"/>
-      <c r="T2" s="93"/>
+      <c r="R2" s="80"/>
+      <c r="S2" s="79"/>
+      <c r="T2" s="92"/>
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
-      <c r="A3" s="72"/>
-      <c r="B3" s="43"/>
-      <c r="C3" s="43"/>
-      <c r="D3" s="43"/>
-      <c r="E3" s="43"/>
-      <c r="F3" s="52"/>
-      <c r="G3" s="51"/>
-      <c r="H3" s="43"/>
-      <c r="I3" s="43"/>
-      <c r="J3" s="52"/>
-      <c r="K3" s="51"/>
-      <c r="L3" s="43"/>
-      <c r="M3" s="43"/>
-      <c r="N3" s="52"/>
-      <c r="O3" s="51"/>
-      <c r="P3" s="52"/>
-      <c r="Q3" s="51"/>
-      <c r="R3" s="52"/>
-      <c r="S3" s="51"/>
-      <c r="T3" s="94"/>
+      <c r="A3" s="60"/>
+      <c r="B3" s="42"/>
+      <c r="C3" s="42"/>
+      <c r="D3" s="42"/>
+      <c r="E3" s="42"/>
+      <c r="F3" s="61"/>
+      <c r="G3" s="81"/>
+      <c r="H3" s="42"/>
+      <c r="I3" s="42"/>
+      <c r="J3" s="61"/>
+      <c r="K3" s="81"/>
+      <c r="L3" s="42"/>
+      <c r="M3" s="42"/>
+      <c r="N3" s="61"/>
+      <c r="O3" s="81"/>
+      <c r="P3" s="61"/>
+      <c r="Q3" s="81"/>
+      <c r="R3" s="61"/>
+      <c r="S3" s="81"/>
+      <c r="T3" s="93"/>
     </row>
     <row r="4" spans="1:26" ht="18" customHeight="1">
-      <c r="A4" s="73"/>
-      <c r="B4" s="74"/>
-      <c r="C4" s="74"/>
-      <c r="D4" s="74"/>
-      <c r="E4" s="74"/>
-      <c r="F4" s="54"/>
-      <c r="G4" s="53"/>
-      <c r="H4" s="74"/>
-      <c r="I4" s="74"/>
-      <c r="J4" s="54"/>
-      <c r="K4" s="53"/>
-      <c r="L4" s="74"/>
-      <c r="M4" s="74"/>
-      <c r="N4" s="54"/>
-      <c r="O4" s="53"/>
-      <c r="P4" s="54"/>
-      <c r="Q4" s="53"/>
-      <c r="R4" s="54"/>
-      <c r="S4" s="53"/>
-      <c r="T4" s="106"/>
+      <c r="A4" s="62"/>
+      <c r="B4" s="63"/>
+      <c r="C4" s="63"/>
+      <c r="D4" s="63"/>
+      <c r="E4" s="63"/>
+      <c r="F4" s="64"/>
+      <c r="G4" s="82"/>
+      <c r="H4" s="63"/>
+      <c r="I4" s="63"/>
+      <c r="J4" s="64"/>
+      <c r="K4" s="82"/>
+      <c r="L4" s="63"/>
+      <c r="M4" s="63"/>
+      <c r="N4" s="64"/>
+      <c r="O4" s="82"/>
+      <c r="P4" s="64"/>
+      <c r="Q4" s="82"/>
+      <c r="R4" s="64"/>
+      <c r="S4" s="82"/>
+      <c r="T4" s="107"/>
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1">
       <c r="A5" s="86" t="s">
         <v>35</v>
       </c>
-      <c r="B5" s="76"/>
-      <c r="C5" s="76"/>
-      <c r="D5" s="76"/>
-      <c r="E5" s="76"/>
-      <c r="F5" s="48"/>
-      <c r="G5" s="82" t="s">
+      <c r="B5" s="50"/>
+      <c r="C5" s="50"/>
+      <c r="D5" s="50"/>
+      <c r="E5" s="50"/>
+      <c r="F5" s="66"/>
+      <c r="G5" s="49" t="s">
         <v>36</v>
       </c>
-      <c r="H5" s="76"/>
-      <c r="I5" s="76"/>
-      <c r="J5" s="76"/>
-      <c r="K5" s="76"/>
-      <c r="L5" s="76"/>
-      <c r="M5" s="76"/>
-      <c r="N5" s="76"/>
-      <c r="O5" s="76"/>
-      <c r="P5" s="76"/>
-      <c r="Q5" s="76"/>
-      <c r="R5" s="76"/>
-      <c r="S5" s="76"/>
-      <c r="T5" s="83"/>
+      <c r="H5" s="50"/>
+      <c r="I5" s="50"/>
+      <c r="J5" s="50"/>
+      <c r="K5" s="50"/>
+      <c r="L5" s="50"/>
+      <c r="M5" s="50"/>
+      <c r="N5" s="50"/>
+      <c r="O5" s="50"/>
+      <c r="P5" s="50"/>
+      <c r="Q5" s="50"/>
+      <c r="R5" s="50"/>
+      <c r="S5" s="50"/>
+      <c r="T5" s="51"/>
     </row>
     <row r="6" spans="1:26" ht="18" customHeight="1">
       <c r="A6" s="88" t="s">
         <v>37</v>
       </c>
-      <c r="B6" s="40"/>
-      <c r="C6" s="40"/>
-      <c r="D6" s="40"/>
-      <c r="E6" s="40"/>
-      <c r="F6" s="41"/>
-      <c r="G6" s="64" t="s">
+      <c r="B6" s="39"/>
+      <c r="C6" s="39"/>
+      <c r="D6" s="39"/>
+      <c r="E6" s="39"/>
+      <c r="F6" s="40"/>
+      <c r="G6" s="52" t="s">
         <v>21</v>
       </c>
-      <c r="H6" s="40"/>
-      <c r="I6" s="40"/>
-      <c r="J6" s="40"/>
-      <c r="K6" s="40"/>
-      <c r="L6" s="40"/>
-      <c r="M6" s="40"/>
-      <c r="N6" s="40"/>
-      <c r="O6" s="40"/>
-      <c r="P6" s="40"/>
-      <c r="Q6" s="40"/>
-      <c r="R6" s="40"/>
-      <c r="S6" s="40"/>
-      <c r="T6" s="65"/>
+      <c r="H6" s="39"/>
+      <c r="I6" s="39"/>
+      <c r="J6" s="39"/>
+      <c r="K6" s="39"/>
+      <c r="L6" s="39"/>
+      <c r="M6" s="39"/>
+      <c r="N6" s="39"/>
+      <c r="O6" s="39"/>
+      <c r="P6" s="39"/>
+      <c r="Q6" s="39"/>
+      <c r="R6" s="39"/>
+      <c r="S6" s="39"/>
+      <c r="T6" s="53"/>
     </row>
     <row r="7" spans="1:26" ht="18" customHeight="1">
       <c r="A7" s="88" t="s">
         <v>38</v>
       </c>
-      <c r="B7" s="40"/>
-      <c r="C7" s="40"/>
-      <c r="D7" s="40"/>
-      <c r="E7" s="40"/>
-      <c r="F7" s="41"/>
-      <c r="G7" s="64" t="s">
+      <c r="B7" s="39"/>
+      <c r="C7" s="39"/>
+      <c r="D7" s="39"/>
+      <c r="E7" s="39"/>
+      <c r="F7" s="40"/>
+      <c r="G7" s="52" t="s">
         <v>59</v>
       </c>
-      <c r="H7" s="40"/>
-      <c r="I7" s="40"/>
-      <c r="J7" s="40"/>
-      <c r="K7" s="40"/>
-      <c r="L7" s="40"/>
-      <c r="M7" s="40"/>
-      <c r="N7" s="40"/>
-      <c r="O7" s="40"/>
-      <c r="P7" s="40"/>
-      <c r="Q7" s="40"/>
-      <c r="R7" s="40"/>
-      <c r="S7" s="40"/>
-      <c r="T7" s="65"/>
+      <c r="H7" s="39"/>
+      <c r="I7" s="39"/>
+      <c r="J7" s="39"/>
+      <c r="K7" s="39"/>
+      <c r="L7" s="39"/>
+      <c r="M7" s="39"/>
+      <c r="N7" s="39"/>
+      <c r="O7" s="39"/>
+      <c r="P7" s="39"/>
+      <c r="Q7" s="39"/>
+      <c r="R7" s="39"/>
+      <c r="S7" s="39"/>
+      <c r="T7" s="53"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
       <c r="A8" s="8"/>
@@ -9411,34 +9405,34 @@
       <c r="A15" s="88" t="s">
         <v>45</v>
       </c>
-      <c r="B15" s="41"/>
-      <c r="C15" s="109" t="s">
+      <c r="B15" s="40"/>
+      <c r="C15" s="105" t="s">
         <v>39</v>
       </c>
-      <c r="D15" s="41"/>
-      <c r="E15" s="95" t="s">
+      <c r="D15" s="40"/>
+      <c r="E15" s="94" t="s">
         <v>46</v>
       </c>
-      <c r="F15" s="41"/>
-      <c r="G15" s="95" t="s">
+      <c r="F15" s="40"/>
+      <c r="G15" s="94" t="s">
         <v>47</v>
       </c>
-      <c r="H15" s="40"/>
-      <c r="I15" s="41"/>
-      <c r="J15" s="95" t="s">
+      <c r="H15" s="39"/>
+      <c r="I15" s="40"/>
+      <c r="J15" s="94" t="s">
         <v>48</v>
       </c>
-      <c r="K15" s="41"/>
-      <c r="L15" s="95" t="s">
+      <c r="K15" s="40"/>
+      <c r="L15" s="94" t="s">
         <v>49</v>
       </c>
-      <c r="M15" s="40"/>
-      <c r="N15" s="41"/>
-      <c r="O15" s="95" t="s">
+      <c r="M15" s="39"/>
+      <c r="N15" s="40"/>
+      <c r="O15" s="94" t="s">
         <v>50</v>
       </c>
-      <c r="P15" s="40"/>
-      <c r="Q15" s="41"/>
+      <c r="P15" s="39"/>
+      <c r="Q15" s="40"/>
       <c r="R15" s="15" t="s">
         <v>51</v>
       </c>
@@ -9450,38 +9444,38 @@
       </c>
     </row>
     <row r="16" spans="1:26" ht="48" customHeight="1">
-      <c r="A16" s="107">
+      <c r="A16" s="95">
         <v>1</v>
       </c>
-      <c r="B16" s="41"/>
-      <c r="C16" s="108" t="s">
+      <c r="B16" s="40"/>
+      <c r="C16" s="96" t="s">
         <v>54</v>
       </c>
-      <c r="D16" s="41"/>
-      <c r="E16" s="108" t="s">
+      <c r="D16" s="40"/>
+      <c r="E16" s="96" t="s">
         <v>55</v>
       </c>
-      <c r="F16" s="41"/>
-      <c r="G16" s="96" t="s">
+      <c r="F16" s="40"/>
+      <c r="G16" s="104" t="s">
         <v>77</v>
       </c>
-      <c r="H16" s="40"/>
-      <c r="I16" s="41"/>
-      <c r="J16" s="97" t="s">
+      <c r="H16" s="39"/>
+      <c r="I16" s="40"/>
+      <c r="J16" s="111" t="s">
         <v>78</v>
       </c>
-      <c r="K16" s="98"/>
-      <c r="L16" s="101" t="s">
+      <c r="K16" s="100"/>
+      <c r="L16" s="102" t="s">
         <v>79</v>
       </c>
-      <c r="M16" s="40"/>
-      <c r="N16" s="41"/>
-      <c r="O16" s="101" t="s">
+      <c r="M16" s="39"/>
+      <c r="N16" s="40"/>
+      <c r="O16" s="102" t="s">
         <v>80</v>
       </c>
-      <c r="P16" s="40"/>
-      <c r="Q16" s="41"/>
-      <c r="R16" s="38">
+      <c r="P16" s="39"/>
+      <c r="Q16" s="40"/>
+      <c r="R16" s="113">
         <v>45825</v>
       </c>
       <c r="S16" s="33" t="s">
@@ -9498,38 +9492,38 @@
       <c r="Z16" s="35"/>
     </row>
     <row r="17" spans="1:26" ht="51" customHeight="1">
-      <c r="A17" s="107">
+      <c r="A17" s="95">
         <v>2</v>
       </c>
-      <c r="B17" s="41"/>
-      <c r="C17" s="108" t="s">
+      <c r="B17" s="40"/>
+      <c r="C17" s="96" t="s">
         <v>54</v>
       </c>
-      <c r="D17" s="41"/>
-      <c r="E17" s="108" t="s">
+      <c r="D17" s="40"/>
+      <c r="E17" s="96" t="s">
         <v>55</v>
       </c>
-      <c r="F17" s="41"/>
-      <c r="G17" s="97" t="s">
+      <c r="F17" s="40"/>
+      <c r="G17" s="111" t="s">
         <v>81</v>
       </c>
-      <c r="H17" s="99"/>
-      <c r="I17" s="98"/>
-      <c r="J17" s="97" t="s">
+      <c r="H17" s="112"/>
+      <c r="I17" s="100"/>
+      <c r="J17" s="111" t="s">
         <v>78</v>
       </c>
-      <c r="K17" s="98"/>
-      <c r="L17" s="101" t="s">
+      <c r="K17" s="100"/>
+      <c r="L17" s="102" t="s">
         <v>79</v>
       </c>
-      <c r="M17" s="40"/>
-      <c r="N17" s="41"/>
-      <c r="O17" s="101" t="s">
+      <c r="M17" s="39"/>
+      <c r="N17" s="40"/>
+      <c r="O17" s="102" t="s">
         <v>82</v>
       </c>
-      <c r="P17" s="40"/>
-      <c r="Q17" s="41"/>
-      <c r="R17" s="38">
+      <c r="P17" s="39"/>
+      <c r="Q17" s="40"/>
+      <c r="R17" s="113">
         <v>45825</v>
       </c>
       <c r="S17" s="33" t="s">
@@ -9546,38 +9540,38 @@
       <c r="Z17" s="35"/>
     </row>
     <row r="18" spans="1:26" ht="59.25" customHeight="1">
-      <c r="A18" s="107">
+      <c r="A18" s="95">
         <v>3</v>
       </c>
-      <c r="B18" s="41"/>
-      <c r="C18" s="108" t="s">
+      <c r="B18" s="40"/>
+      <c r="C18" s="96" t="s">
         <v>54</v>
       </c>
-      <c r="D18" s="41"/>
-      <c r="E18" s="108" t="s">
+      <c r="D18" s="40"/>
+      <c r="E18" s="96" t="s">
         <v>55</v>
       </c>
-      <c r="F18" s="41"/>
-      <c r="G18" s="96" t="s">
+      <c r="F18" s="40"/>
+      <c r="G18" s="104" t="s">
         <v>83</v>
       </c>
-      <c r="H18" s="40"/>
-      <c r="I18" s="41"/>
-      <c r="J18" s="97" t="s">
+      <c r="H18" s="39"/>
+      <c r="I18" s="40"/>
+      <c r="J18" s="111" t="s">
         <v>78</v>
       </c>
-      <c r="K18" s="98"/>
-      <c r="L18" s="101" t="s">
+      <c r="K18" s="100"/>
+      <c r="L18" s="102" t="s">
         <v>91</v>
       </c>
-      <c r="M18" s="40"/>
-      <c r="N18" s="41"/>
-      <c r="O18" s="101" t="s">
+      <c r="M18" s="39"/>
+      <c r="N18" s="40"/>
+      <c r="O18" s="102" t="s">
         <v>94</v>
       </c>
-      <c r="P18" s="40"/>
-      <c r="Q18" s="41"/>
-      <c r="R18" s="38">
+      <c r="P18" s="39"/>
+      <c r="Q18" s="40"/>
+      <c r="R18" s="113">
         <v>45825</v>
       </c>
       <c r="S18" s="33" t="s">
@@ -9594,38 +9588,38 @@
       <c r="Z18" s="35"/>
     </row>
     <row r="19" spans="1:26" ht="51.75" customHeight="1">
-      <c r="A19" s="107">
+      <c r="A19" s="95">
         <v>4</v>
       </c>
-      <c r="B19" s="41"/>
-      <c r="C19" s="108" t="s">
+      <c r="B19" s="40"/>
+      <c r="C19" s="96" t="s">
         <v>54</v>
       </c>
-      <c r="D19" s="41"/>
-      <c r="E19" s="108" t="s">
+      <c r="D19" s="40"/>
+      <c r="E19" s="96" t="s">
         <v>55</v>
       </c>
-      <c r="F19" s="41"/>
-      <c r="G19" s="96" t="s">
+      <c r="F19" s="40"/>
+      <c r="G19" s="104" t="s">
         <v>84</v>
       </c>
-      <c r="H19" s="40"/>
-      <c r="I19" s="41"/>
-      <c r="J19" s="97" t="s">
+      <c r="H19" s="39"/>
+      <c r="I19" s="40"/>
+      <c r="J19" s="111" t="s">
         <v>78</v>
       </c>
-      <c r="K19" s="98"/>
-      <c r="L19" s="101" t="s">
+      <c r="K19" s="100"/>
+      <c r="L19" s="102" t="s">
         <v>92</v>
       </c>
-      <c r="M19" s="40"/>
-      <c r="N19" s="41"/>
-      <c r="O19" s="101" t="s">
+      <c r="M19" s="39"/>
+      <c r="N19" s="40"/>
+      <c r="O19" s="102" t="s">
         <v>95</v>
       </c>
-      <c r="P19" s="40"/>
-      <c r="Q19" s="41"/>
-      <c r="R19" s="38">
+      <c r="P19" s="39"/>
+      <c r="Q19" s="40"/>
+      <c r="R19" s="113">
         <v>45825</v>
       </c>
       <c r="S19" s="33" t="s">
@@ -9642,38 +9636,38 @@
       <c r="Z19" s="35"/>
     </row>
     <row r="20" spans="1:26" ht="54" customHeight="1">
-      <c r="A20" s="107">
+      <c r="A20" s="95">
         <v>5</v>
       </c>
-      <c r="B20" s="41"/>
-      <c r="C20" s="108" t="s">
+      <c r="B20" s="40"/>
+      <c r="C20" s="96" t="s">
         <v>54</v>
       </c>
-      <c r="D20" s="41"/>
-      <c r="E20" s="108" t="s">
+      <c r="D20" s="40"/>
+      <c r="E20" s="96" t="s">
         <v>55</v>
       </c>
-      <c r="F20" s="41"/>
-      <c r="G20" s="96" t="s">
+      <c r="F20" s="40"/>
+      <c r="G20" s="104" t="s">
         <v>85</v>
       </c>
-      <c r="H20" s="40"/>
-      <c r="I20" s="41"/>
-      <c r="J20" s="97" t="s">
+      <c r="H20" s="39"/>
+      <c r="I20" s="40"/>
+      <c r="J20" s="111" t="s">
         <v>78</v>
       </c>
-      <c r="K20" s="98"/>
-      <c r="L20" s="101" t="s">
+      <c r="K20" s="100"/>
+      <c r="L20" s="102" t="s">
         <v>93</v>
       </c>
-      <c r="M20" s="40"/>
-      <c r="N20" s="41"/>
-      <c r="O20" s="101" t="s">
+      <c r="M20" s="39"/>
+      <c r="N20" s="40"/>
+      <c r="O20" s="102" t="s">
         <v>96</v>
       </c>
-      <c r="P20" s="40"/>
-      <c r="Q20" s="41"/>
-      <c r="R20" s="38">
+      <c r="P20" s="39"/>
+      <c r="Q20" s="40"/>
+      <c r="R20" s="113">
         <v>45825</v>
       </c>
       <c r="S20" s="33" t="s">
@@ -9690,38 +9684,38 @@
       <c r="Z20" s="35"/>
     </row>
     <row r="21" spans="1:26" ht="53.25" customHeight="1">
-      <c r="A21" s="110">
+      <c r="A21" s="99">
         <v>7</v>
       </c>
-      <c r="B21" s="98"/>
-      <c r="C21" s="111" t="s">
+      <c r="B21" s="100"/>
+      <c r="C21" s="101" t="s">
         <v>54</v>
       </c>
-      <c r="D21" s="98"/>
-      <c r="E21" s="111" t="s">
+      <c r="D21" s="100"/>
+      <c r="E21" s="101" t="s">
         <v>86</v>
       </c>
-      <c r="F21" s="98"/>
-      <c r="G21" s="97" t="s">
+      <c r="F21" s="100"/>
+      <c r="G21" s="111" t="s">
         <v>87</v>
       </c>
-      <c r="H21" s="99"/>
-      <c r="I21" s="98"/>
-      <c r="J21" s="97" t="s">
+      <c r="H21" s="112"/>
+      <c r="I21" s="100"/>
+      <c r="J21" s="111" t="s">
         <v>88</v>
       </c>
-      <c r="K21" s="98"/>
-      <c r="L21" s="103" t="s">
+      <c r="K21" s="100"/>
+      <c r="L21" s="108" t="s">
         <v>90</v>
       </c>
-      <c r="M21" s="104"/>
-      <c r="N21" s="104"/>
-      <c r="O21" s="101" t="s">
+      <c r="M21" s="109"/>
+      <c r="N21" s="109"/>
+      <c r="O21" s="102" t="s">
         <v>89</v>
       </c>
-      <c r="P21" s="40"/>
-      <c r="Q21" s="41"/>
-      <c r="R21" s="38">
+      <c r="P21" s="39"/>
+      <c r="Q21" s="40"/>
+      <c r="R21" s="113">
         <v>45825</v>
       </c>
       <c r="S21" s="33" t="s">
@@ -9738,38 +9732,38 @@
       <c r="Z21" s="35"/>
     </row>
     <row r="22" spans="1:26" ht="62.25" customHeight="1">
-      <c r="A22" s="110">
+      <c r="A22" s="99">
         <v>8</v>
       </c>
-      <c r="B22" s="98"/>
-      <c r="C22" s="111" t="s">
+      <c r="B22" s="100"/>
+      <c r="C22" s="101" t="s">
         <v>54</v>
       </c>
-      <c r="D22" s="98"/>
-      <c r="E22" s="108" t="s">
+      <c r="D22" s="100"/>
+      <c r="E22" s="96" t="s">
         <v>55</v>
       </c>
-      <c r="F22" s="41"/>
-      <c r="G22" s="96" t="s">
+      <c r="F22" s="40"/>
+      <c r="G22" s="104" t="s">
         <v>98</v>
       </c>
-      <c r="H22" s="40"/>
-      <c r="I22" s="41"/>
-      <c r="J22" s="97" t="s">
+      <c r="H22" s="39"/>
+      <c r="I22" s="40"/>
+      <c r="J22" s="111" t="s">
         <v>78</v>
       </c>
-      <c r="K22" s="98"/>
-      <c r="L22" s="101" t="s">
+      <c r="K22" s="100"/>
+      <c r="L22" s="102" t="s">
         <v>79</v>
       </c>
-      <c r="M22" s="40"/>
-      <c r="N22" s="41"/>
-      <c r="O22" s="101" t="s">
+      <c r="M22" s="39"/>
+      <c r="N22" s="40"/>
+      <c r="O22" s="102" t="s">
         <v>99</v>
       </c>
-      <c r="P22" s="40"/>
-      <c r="Q22" s="41"/>
-      <c r="R22" s="38">
+      <c r="P22" s="39"/>
+      <c r="Q22" s="40"/>
+      <c r="R22" s="113">
         <v>45825</v>
       </c>
       <c r="S22" s="33" t="s">
@@ -9785,24 +9779,24 @@
       <c r="Y22" s="35"/>
       <c r="Z22" s="35"/>
     </row>
-    <row r="23" spans="1:26" ht="53.25" customHeight="1">
-      <c r="A23" s="107"/>
-      <c r="B23" s="41"/>
-      <c r="C23" s="108"/>
-      <c r="D23" s="41"/>
-      <c r="E23" s="108"/>
-      <c r="F23" s="41"/>
-      <c r="G23" s="96"/>
-      <c r="H23" s="40"/>
-      <c r="I23" s="41"/>
-      <c r="J23" s="96"/>
-      <c r="K23" s="41"/>
-      <c r="L23" s="101"/>
-      <c r="M23" s="40"/>
-      <c r="N23" s="41"/>
-      <c r="O23" s="101"/>
-      <c r="P23" s="40"/>
-      <c r="Q23" s="41"/>
+    <row r="23" spans="1:26" ht="12.75" customHeight="1">
+      <c r="A23" s="95"/>
+      <c r="B23" s="40"/>
+      <c r="C23" s="96"/>
+      <c r="D23" s="40"/>
+      <c r="E23" s="96"/>
+      <c r="F23" s="40"/>
+      <c r="G23" s="104"/>
+      <c r="H23" s="39"/>
+      <c r="I23" s="40"/>
+      <c r="J23" s="104"/>
+      <c r="K23" s="40"/>
+      <c r="L23" s="102"/>
+      <c r="M23" s="39"/>
+      <c r="N23" s="40"/>
+      <c r="O23" s="102"/>
+      <c r="P23" s="39"/>
+      <c r="Q23" s="40"/>
       <c r="R23" s="33"/>
       <c r="S23" s="33"/>
       <c r="T23" s="34"/>
@@ -9814,23 +9808,23 @@
       <c r="Z23" s="35"/>
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A24" s="107"/>
-      <c r="B24" s="41"/>
-      <c r="C24" s="108"/>
-      <c r="D24" s="41"/>
-      <c r="E24" s="108"/>
-      <c r="F24" s="41"/>
-      <c r="G24" s="96"/>
-      <c r="H24" s="40"/>
-      <c r="I24" s="41"/>
-      <c r="J24" s="96"/>
-      <c r="K24" s="41"/>
-      <c r="L24" s="101"/>
-      <c r="M24" s="40"/>
-      <c r="N24" s="41"/>
-      <c r="O24" s="101"/>
-      <c r="P24" s="40"/>
-      <c r="Q24" s="41"/>
+      <c r="A24" s="95"/>
+      <c r="B24" s="40"/>
+      <c r="C24" s="96"/>
+      <c r="D24" s="40"/>
+      <c r="E24" s="96"/>
+      <c r="F24" s="40"/>
+      <c r="G24" s="104"/>
+      <c r="H24" s="39"/>
+      <c r="I24" s="40"/>
+      <c r="J24" s="104"/>
+      <c r="K24" s="40"/>
+      <c r="L24" s="102"/>
+      <c r="M24" s="39"/>
+      <c r="N24" s="40"/>
+      <c r="O24" s="102"/>
+      <c r="P24" s="39"/>
+      <c r="Q24" s="40"/>
       <c r="R24" s="33"/>
       <c r="S24" s="33"/>
       <c r="T24" s="34"/>
@@ -9842,23 +9836,23 @@
       <c r="Z24" s="35"/>
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A25" s="107"/>
-      <c r="B25" s="41"/>
-      <c r="C25" s="108"/>
-      <c r="D25" s="41"/>
-      <c r="E25" s="108"/>
-      <c r="F25" s="41"/>
-      <c r="G25" s="96"/>
-      <c r="H25" s="40"/>
-      <c r="I25" s="41"/>
-      <c r="J25" s="96"/>
-      <c r="K25" s="41"/>
-      <c r="L25" s="101"/>
-      <c r="M25" s="40"/>
-      <c r="N25" s="41"/>
-      <c r="O25" s="101"/>
-      <c r="P25" s="40"/>
-      <c r="Q25" s="41"/>
+      <c r="A25" s="95"/>
+      <c r="B25" s="40"/>
+      <c r="C25" s="96"/>
+      <c r="D25" s="40"/>
+      <c r="E25" s="96"/>
+      <c r="F25" s="40"/>
+      <c r="G25" s="104"/>
+      <c r="H25" s="39"/>
+      <c r="I25" s="40"/>
+      <c r="J25" s="104"/>
+      <c r="K25" s="40"/>
+      <c r="L25" s="102"/>
+      <c r="M25" s="39"/>
+      <c r="N25" s="40"/>
+      <c r="O25" s="102"/>
+      <c r="P25" s="39"/>
+      <c r="Q25" s="40"/>
       <c r="R25" s="33"/>
       <c r="S25" s="33"/>
       <c r="T25" s="34"/>
@@ -9870,23 +9864,23 @@
       <c r="Z25" s="35"/>
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A26" s="107"/>
-      <c r="B26" s="41"/>
-      <c r="C26" s="108"/>
-      <c r="D26" s="41"/>
-      <c r="E26" s="108"/>
-      <c r="F26" s="41"/>
-      <c r="G26" s="96"/>
-      <c r="H26" s="40"/>
-      <c r="I26" s="41"/>
-      <c r="J26" s="96"/>
-      <c r="K26" s="41"/>
-      <c r="L26" s="101"/>
-      <c r="M26" s="40"/>
-      <c r="N26" s="41"/>
-      <c r="O26" s="101"/>
-      <c r="P26" s="40"/>
-      <c r="Q26" s="41"/>
+      <c r="A26" s="95"/>
+      <c r="B26" s="40"/>
+      <c r="C26" s="96"/>
+      <c r="D26" s="40"/>
+      <c r="E26" s="96"/>
+      <c r="F26" s="40"/>
+      <c r="G26" s="104"/>
+      <c r="H26" s="39"/>
+      <c r="I26" s="40"/>
+      <c r="J26" s="104"/>
+      <c r="K26" s="40"/>
+      <c r="L26" s="102"/>
+      <c r="M26" s="39"/>
+      <c r="N26" s="40"/>
+      <c r="O26" s="102"/>
+      <c r="P26" s="39"/>
+      <c r="Q26" s="40"/>
       <c r="R26" s="33"/>
       <c r="S26" s="33"/>
       <c r="T26" s="34"/>
@@ -9898,23 +9892,23 @@
       <c r="Z26" s="35"/>
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A27" s="107"/>
-      <c r="B27" s="41"/>
-      <c r="C27" s="108"/>
-      <c r="D27" s="41"/>
-      <c r="E27" s="108"/>
-      <c r="F27" s="41"/>
-      <c r="G27" s="96"/>
-      <c r="H27" s="40"/>
-      <c r="I27" s="41"/>
-      <c r="J27" s="96"/>
-      <c r="K27" s="41"/>
-      <c r="L27" s="101"/>
-      <c r="M27" s="40"/>
-      <c r="N27" s="41"/>
-      <c r="O27" s="101"/>
-      <c r="P27" s="40"/>
-      <c r="Q27" s="41"/>
+      <c r="A27" s="95"/>
+      <c r="B27" s="40"/>
+      <c r="C27" s="96"/>
+      <c r="D27" s="40"/>
+      <c r="E27" s="96"/>
+      <c r="F27" s="40"/>
+      <c r="G27" s="104"/>
+      <c r="H27" s="39"/>
+      <c r="I27" s="40"/>
+      <c r="J27" s="104"/>
+      <c r="K27" s="40"/>
+      <c r="L27" s="102"/>
+      <c r="M27" s="39"/>
+      <c r="N27" s="40"/>
+      <c r="O27" s="102"/>
+      <c r="P27" s="39"/>
+      <c r="Q27" s="40"/>
       <c r="R27" s="33"/>
       <c r="S27" s="33"/>
       <c r="T27" s="34"/>
@@ -9926,23 +9920,23 @@
       <c r="Z27" s="35"/>
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A28" s="107"/>
-      <c r="B28" s="41"/>
-      <c r="C28" s="108"/>
-      <c r="D28" s="41"/>
-      <c r="E28" s="108"/>
-      <c r="F28" s="41"/>
-      <c r="G28" s="96"/>
-      <c r="H28" s="40"/>
-      <c r="I28" s="41"/>
-      <c r="J28" s="96"/>
-      <c r="K28" s="41"/>
-      <c r="L28" s="101"/>
-      <c r="M28" s="40"/>
-      <c r="N28" s="41"/>
-      <c r="O28" s="101"/>
-      <c r="P28" s="40"/>
-      <c r="Q28" s="41"/>
+      <c r="A28" s="95"/>
+      <c r="B28" s="40"/>
+      <c r="C28" s="96"/>
+      <c r="D28" s="40"/>
+      <c r="E28" s="96"/>
+      <c r="F28" s="40"/>
+      <c r="G28" s="104"/>
+      <c r="H28" s="39"/>
+      <c r="I28" s="40"/>
+      <c r="J28" s="104"/>
+      <c r="K28" s="40"/>
+      <c r="L28" s="102"/>
+      <c r="M28" s="39"/>
+      <c r="N28" s="40"/>
+      <c r="O28" s="102"/>
+      <c r="P28" s="39"/>
+      <c r="Q28" s="40"/>
       <c r="R28" s="33"/>
       <c r="S28" s="33"/>
       <c r="T28" s="34"/>
@@ -9954,23 +9948,23 @@
       <c r="Z28" s="35"/>
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A29" s="107"/>
-      <c r="B29" s="41"/>
-      <c r="C29" s="108"/>
-      <c r="D29" s="41"/>
-      <c r="E29" s="108"/>
-      <c r="F29" s="41"/>
-      <c r="G29" s="96"/>
-      <c r="H29" s="40"/>
-      <c r="I29" s="41"/>
-      <c r="J29" s="96"/>
-      <c r="K29" s="41"/>
-      <c r="L29" s="101"/>
-      <c r="M29" s="40"/>
-      <c r="N29" s="41"/>
-      <c r="O29" s="101"/>
-      <c r="P29" s="40"/>
-      <c r="Q29" s="41"/>
+      <c r="A29" s="95"/>
+      <c r="B29" s="40"/>
+      <c r="C29" s="96"/>
+      <c r="D29" s="40"/>
+      <c r="E29" s="96"/>
+      <c r="F29" s="40"/>
+      <c r="G29" s="104"/>
+      <c r="H29" s="39"/>
+      <c r="I29" s="40"/>
+      <c r="J29" s="104"/>
+      <c r="K29" s="40"/>
+      <c r="L29" s="102"/>
+      <c r="M29" s="39"/>
+      <c r="N29" s="40"/>
+      <c r="O29" s="102"/>
+      <c r="P29" s="39"/>
+      <c r="Q29" s="40"/>
       <c r="R29" s="33"/>
       <c r="S29" s="33"/>
       <c r="T29" s="34"/>
@@ -9982,23 +9976,23 @@
       <c r="Z29" s="35"/>
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A30" s="107"/>
-      <c r="B30" s="41"/>
-      <c r="C30" s="108"/>
-      <c r="D30" s="41"/>
-      <c r="E30" s="108"/>
-      <c r="F30" s="41"/>
-      <c r="G30" s="96"/>
-      <c r="H30" s="40"/>
-      <c r="I30" s="41"/>
-      <c r="J30" s="96"/>
-      <c r="K30" s="41"/>
-      <c r="L30" s="101"/>
-      <c r="M30" s="40"/>
-      <c r="N30" s="41"/>
-      <c r="O30" s="101"/>
-      <c r="P30" s="40"/>
-      <c r="Q30" s="41"/>
+      <c r="A30" s="95"/>
+      <c r="B30" s="40"/>
+      <c r="C30" s="96"/>
+      <c r="D30" s="40"/>
+      <c r="E30" s="96"/>
+      <c r="F30" s="40"/>
+      <c r="G30" s="104"/>
+      <c r="H30" s="39"/>
+      <c r="I30" s="40"/>
+      <c r="J30" s="104"/>
+      <c r="K30" s="40"/>
+      <c r="L30" s="102"/>
+      <c r="M30" s="39"/>
+      <c r="N30" s="40"/>
+      <c r="O30" s="102"/>
+      <c r="P30" s="39"/>
+      <c r="Q30" s="40"/>
       <c r="R30" s="33"/>
       <c r="S30" s="33"/>
       <c r="T30" s="34"/>
@@ -10010,23 +10004,23 @@
       <c r="Z30" s="35"/>
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A31" s="112"/>
-      <c r="B31" s="68"/>
-      <c r="C31" s="113"/>
-      <c r="D31" s="68"/>
-      <c r="E31" s="113"/>
-      <c r="F31" s="68"/>
-      <c r="G31" s="100"/>
-      <c r="H31" s="67"/>
-      <c r="I31" s="68"/>
-      <c r="J31" s="100"/>
-      <c r="K31" s="68"/>
-      <c r="L31" s="102"/>
-      <c r="M31" s="67"/>
-      <c r="N31" s="68"/>
-      <c r="O31" s="102"/>
-      <c r="P31" s="67"/>
-      <c r="Q31" s="68"/>
+      <c r="A31" s="97"/>
+      <c r="B31" s="56"/>
+      <c r="C31" s="98"/>
+      <c r="D31" s="56"/>
+      <c r="E31" s="98"/>
+      <c r="F31" s="56"/>
+      <c r="G31" s="110"/>
+      <c r="H31" s="47"/>
+      <c r="I31" s="56"/>
+      <c r="J31" s="110"/>
+      <c r="K31" s="56"/>
+      <c r="L31" s="103"/>
+      <c r="M31" s="47"/>
+      <c r="N31" s="56"/>
+      <c r="O31" s="103"/>
+      <c r="P31" s="47"/>
+      <c r="Q31" s="56"/>
       <c r="R31" s="36"/>
       <c r="S31" s="36"/>
       <c r="T31" s="37"/>
@@ -11024,6 +11018,118 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="136">
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:K19"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="K2:N4"/>
+    <mergeCell ref="O2:P4"/>
+    <mergeCell ref="Q2:R4"/>
+    <mergeCell ref="S2:T4"/>
+    <mergeCell ref="A1:F4"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="G5:T5"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="G6:T6"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="G7:T7"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="G20:I20"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="L20:N20"/>
+    <mergeCell ref="O20:Q20"/>
+    <mergeCell ref="L15:N15"/>
+    <mergeCell ref="O15:Q15"/>
+    <mergeCell ref="L16:N16"/>
+    <mergeCell ref="O16:Q16"/>
+    <mergeCell ref="L17:N17"/>
+    <mergeCell ref="O17:Q17"/>
+    <mergeCell ref="O18:Q18"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="O27:Q27"/>
+    <mergeCell ref="O28:Q28"/>
+    <mergeCell ref="O29:Q29"/>
+    <mergeCell ref="O30:Q30"/>
+    <mergeCell ref="O31:Q31"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="O26:Q26"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="A23:B23"/>
     <mergeCell ref="A30:B30"/>
     <mergeCell ref="C30:D30"/>
     <mergeCell ref="E30:F30"/>
@@ -11048,118 +11154,6 @@
     <mergeCell ref="C28:D28"/>
     <mergeCell ref="E28:F28"/>
     <mergeCell ref="A29:B29"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="O27:Q27"/>
-    <mergeCell ref="O28:Q28"/>
-    <mergeCell ref="O29:Q29"/>
-    <mergeCell ref="O30:Q30"/>
-    <mergeCell ref="O31:Q31"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="O26:Q26"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="G5:T5"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="G6:T6"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="G7:T7"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="L20:N20"/>
-    <mergeCell ref="O20:Q20"/>
-    <mergeCell ref="L15:N15"/>
-    <mergeCell ref="O15:Q15"/>
-    <mergeCell ref="L16:N16"/>
-    <mergeCell ref="O16:Q16"/>
-    <mergeCell ref="L17:N17"/>
-    <mergeCell ref="O17:Q17"/>
-    <mergeCell ref="O18:Q18"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="K2:N4"/>
-    <mergeCell ref="O2:P4"/>
-    <mergeCell ref="Q2:R4"/>
-    <mergeCell ref="S2:T4"/>
-    <mergeCell ref="A1:F4"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="G2:J4"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:K19"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <hyperlinks>
